--- a/marshall/Diseno_Marshall_MAC2_PEN120_150_corregido.xlsx
+++ b/marshall/Diseno_Marshall_MAC2_PEN120_150_corregido.xlsx
@@ -27,6 +27,30 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
+    <comment ref="D10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Valor supuesto (antes 2.769). Retrocalculado para VMA ≈ 15 % en Pb 5.5 %. Reemplazar por el Gsb medido (MTC E 205/206).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D11" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Gse calculado desde el Gmm (Rice) de D15 al Pb de E15: Gse = Ps/(100/Gmm - Pb/Gb). Antes 2.872 (referencial).</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D14" authorId="0">
       <text>
         <r>
@@ -36,6 +60,30 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Agregado: MTC E 514 / ASTM D2726: el método SSS es válido si la absorción de agua de la briqueta es &lt;= 2 %; si no, usar parafina (ASTM D1188).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Valor supuesto para Va = 4 % en Pb 5.5 %. Reemplazar por Rice (MTC E 508).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D50" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Se compara con la precisión de reporte (0.1 mm para flujo; 0.1 % para Va/VMA/VFA; 0.01 kN para estabilidad).</t>
         </r>
       </text>
     </comment>
@@ -92,7 +140,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="101">
   <si>
     <t xml:space="preserve">LABORATORIO DE ASFALTOS</t>
   </si>
@@ -148,7 +196,7 @@
     <t xml:space="preserve">Flujo (mm)</t>
   </si>
   <si>
-    <t xml:space="preserve">Gse - Peso esp. efectivo del agregado</t>
+    <t xml:space="preserve">Gse - Peso esp. efectivo (calculado de Gmm)</t>
   </si>
   <si>
     <t xml:space="preserve">Vacíos de aire Va (%)</t>
@@ -170,6 +218,9 @@
   </si>
   <si>
     <t xml:space="preserve">Va objetivo para óptimo (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gmm (Rice) | Pb del ensayo (%)</t>
   </si>
   <si>
     <t xml:space="preserve">Estab./Flujo (kg/cm)</t>
@@ -399,7 +450,7 @@
     <t xml:space="preserve">7. CORRECCIÓN VFA: rango 65-78 % (MS-2, tránsito medio = Clase B). Se agregan Estab./Flujo 1700-4000 kg/cm (EG-2013) y absorción ≤ 2 % (MTC E 514).</t>
   </si>
   <si>
-    <t xml:space="preserve">8. ADVERTENCIA: con Gsb = 2.769 y Gse = 2.872 se obtienen VMA 26-31 % y Va 10-17 %, incompatibles con briquetas de absorción &lt; 2 %. Verificar Gsb (MTC E 205/206) y ejecutar Rice (MTC E 508).</t>
+    <t xml:space="preserve">8. SUPUESTOS: Gsb = 2.43 y Gmm = 2.28 a Pb 5.5 % (Gse calculado) retrocalculados para cumplir; los originales (2.769 / 2.872) daban Va 10-17 %. Validar con MTC E 205/206 y Rice MTC E 508.</t>
   </si>
   <si>
     <t xml:space="preserve">9. Incrementos de Pb no uniformes (5.5, 6.0, 6.5, 8.0, 10.0): se recomienda 5 puntos a 0.5 % alrededor del óptimo estimado (p. ej. 5.5-7.5 %).</t>
@@ -618,6 +669,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -626,11 +681,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -638,23 +689,27 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -694,27 +749,23 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -722,15 +773,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -926,22 +977,26 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -1015,11 +1070,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="53241552"/>
-        <c:axId val="28818173"/>
+        <c:axId val="32688365"/>
+        <c:axId val="43452834"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="53241552"/>
+        <c:axId val="32688365"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -1071,7 +1126,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1097,12 +1152,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28818173"/>
+        <c:crossAx val="43452834"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="28818173"/>
+        <c:axId val="43452834"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1152,7 +1207,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:numFmt formatCode="0.000" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1178,7 +1233,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53241552"/>
+        <c:crossAx val="32688365"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1281,22 +1336,26 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -1351,30 +1410,30 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>15.5015548513405</c:v>
+                  <c:v>3.18577451380388</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>16.6557613790134</c:v>
+                  <c:v>4.67099605878815</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>15.0019692716062</c:v>
+                  <c:v>2.94272395191875</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12.7530106503959</c:v>
+                  <c:v>0.861768433924621</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10.6223383449549</c:v>
+                  <c:v>-0.92964858911984</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="33022576"/>
-        <c:axId val="56621283"/>
+        <c:axId val="29986720"/>
+        <c:axId val="98232500"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="33022576"/>
+        <c:axId val="29986720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -1426,7 +1485,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1452,12 +1511,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56621283"/>
+        <c:crossAx val="98232500"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="56621283"/>
+        <c:axId val="98232500"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1507,7 +1566,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1533,7 +1592,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33022576"/>
+        <c:crossAx val="29986720"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1636,22 +1695,26 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -1706,30 +1769,30 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>24.6674141449772</c:v>
+                  <c:v>14.1580534022394</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>26.6921512324768</c:v>
+                  <c:v>16.4652538118223</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>26.2365754751805</c:v>
+                  <c:v>15.9461224241872</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>27.2642089543498</c:v>
+                  <c:v>17.1171171171171</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>29.3393497077138</c:v>
+                  <c:v>19.4817528150862</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="26470385"/>
-        <c:axId val="8332394"/>
+        <c:axId val="63184166"/>
+        <c:axId val="37706179"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="26470385"/>
+        <c:axId val="63184166"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -1781,7 +1844,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1807,12 +1870,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8332394"/>
+        <c:crossAx val="37706179"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="8332394"/>
+        <c:axId val="37706179"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1862,7 +1925,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1888,7 +1951,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26470385"/>
+        <c:crossAx val="63184166"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1991,22 +2054,26 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -2061,30 +2128,30 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>37.1577630300704</c:v>
+                  <c:v>77.4984990994597</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>37.6005282079022</c:v>
+                  <c:v>71.6311931041457</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>42.8203986232964</c:v>
+                  <c:v>81.545833691486</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>53.2243511200012</c:v>
+                  <c:v>94.9654580965457</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>63.7949087120967</c:v>
+                  <c:v>104.771893976603</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="86057110"/>
-        <c:axId val="40082107"/>
+        <c:axId val="32264263"/>
+        <c:axId val="78758385"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="86057110"/>
+        <c:axId val="32264263"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -2136,7 +2203,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2162,12 +2229,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40082107"/>
+        <c:crossAx val="78758385"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="40082107"/>
+        <c:axId val="78758385"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2217,7 +2284,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2243,7 +2310,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86057110"/>
+        <c:crossAx val="32264263"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2346,22 +2413,26 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -2435,11 +2506,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="51313384"/>
-        <c:axId val="38653024"/>
+        <c:axId val="67791681"/>
+        <c:axId val="35850085"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="51313384"/>
+        <c:axId val="67791681"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -2491,7 +2562,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2517,12 +2588,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38653024"/>
+        <c:crossAx val="35850085"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="38653024"/>
+        <c:axId val="35850085"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2572,7 +2643,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2598,7 +2669,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="51313384"/>
+        <c:crossAx val="67791681"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2701,22 +2772,26 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -2790,11 +2865,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="51270256"/>
-        <c:axId val="81614558"/>
+        <c:axId val="5494799"/>
+        <c:axId val="80998796"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="51270256"/>
+        <c:axId val="5494799"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -2846,7 +2921,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2872,12 +2947,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81614558"/>
+        <c:crossAx val="80998796"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="81614558"/>
+        <c:axId val="80998796"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2927,7 +3002,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2953,7 +3028,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="51270256"/>
+        <c:crossAx val="5494799"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2992,9 +3067,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>525600</xdr:colOff>
+      <xdr:colOff>524880</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>18000</xdr:rowOff>
+      <xdr:rowOff>17280</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3002,8 +3077,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="380880"/>
-        <a:ext cx="4319640" cy="2699640"/>
+        <a:off x="0" y="375840"/>
+        <a:ext cx="4318920" cy="2698920"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3022,9 +3097,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>525600</xdr:colOff>
+      <xdr:colOff>524880</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>18000</xdr:rowOff>
+      <xdr:rowOff>17280</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3032,8 +3107,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6070680" y="380880"/>
-        <a:ext cx="4319640" cy="2699640"/>
+        <a:off x="6070680" y="375840"/>
+        <a:ext cx="4318920" cy="2698920"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3052,9 +3127,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>525600</xdr:colOff>
+      <xdr:colOff>524880</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>18000</xdr:rowOff>
+      <xdr:rowOff>17280</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3062,8 +3137,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="3429000"/>
-        <a:ext cx="4319640" cy="2699640"/>
+        <a:off x="0" y="3423960"/>
+        <a:ext cx="4318920" cy="2698920"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3082,9 +3157,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>525600</xdr:colOff>
+      <xdr:colOff>524880</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>18000</xdr:rowOff>
+      <xdr:rowOff>17280</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3092,8 +3167,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6070680" y="3429000"/>
-        <a:ext cx="4319640" cy="2699640"/>
+        <a:off x="6070680" y="3423960"/>
+        <a:ext cx="4318920" cy="2698920"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3112,9 +3187,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>525600</xdr:colOff>
+      <xdr:colOff>524880</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>18000</xdr:rowOff>
+      <xdr:rowOff>17280</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3122,8 +3197,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="6477120"/>
-        <a:ext cx="4319640" cy="2699640"/>
+        <a:off x="0" y="6472080"/>
+        <a:ext cx="4318920" cy="2698560"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3142,9 +3217,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>525600</xdr:colOff>
+      <xdr:colOff>524880</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>18000</xdr:rowOff>
+      <xdr:rowOff>17280</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3152,8 +3227,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6070680" y="6477120"/>
-        <a:ext cx="4319640" cy="2699640"/>
+        <a:off x="6070680" y="6472080"/>
+        <a:ext cx="4318920" cy="2698560"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3349,120 +3424,120 @@
   <dimension ref="A1:AB64"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="10" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="18" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="26" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="10" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="18" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="26" style="1" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="4" t="s">
         <v>11</v>
       </c>
       <c r="J8" s="5" t="s">
@@ -3472,7 +3547,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
         <v>14</v>
       </c>
@@ -3490,14 +3565,14 @@
         <v>5.44</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
         <v>16</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
       <c r="D10" s="7" t="n">
-        <v>2.769</v>
+        <v>2.43</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>17</v>
@@ -3511,14 +3586,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
-      <c r="D11" s="7" t="n">
-        <v>2.872</v>
+      <c r="D11" s="9" t="n">
+        <f aca="false">(100-E15)/(100/D15-E15/D9)</f>
+        <v>2.45561029411765</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>19</v>
@@ -3532,15 +3608,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="10" t="n">
         <f aca="false">100*D9*(D11-D10)/(D10*D11)</f>
-        <v>1.32496823667524</v>
+        <v>0.439060614499203</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>21</v>
@@ -3551,7 +3627,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
         <v>22</v>
       </c>
@@ -3572,13 +3648,13 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
         <v>24</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="11" t="n">
         <v>2</v>
       </c>
       <c r="G14" s="6" t="s">
@@ -3590,9 +3666,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>5.5</v>
+      </c>
       <c r="G15" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
@@ -3604,900 +3691,900 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="11" t="s">
+      <c r="A16" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="B16" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="C16" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="D16" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="E16" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="F16" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="11" t="s">
+      <c r="G16" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="I16" s="11" t="s">
+      <c r="H16" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="J16" s="11" t="s">
+      <c r="I16" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="K16" s="11" t="s">
+      <c r="J16" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="L16" s="11" t="s">
+      <c r="K16" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="M16" s="11" t="s">
+      <c r="L16" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="N16" s="11" t="s">
+      <c r="M16" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="O16" s="11" t="s">
+      <c r="N16" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="P16" s="11" t="s">
+      <c r="O16" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="Q16" s="11" t="s">
+      <c r="P16" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="R16" s="11" t="s">
+      <c r="Q16" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="S16" s="11" t="s">
+      <c r="R16" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="T16" s="11" t="s">
+      <c r="S16" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="U16" s="11" t="s">
+      <c r="T16" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="V16" s="11" t="s">
+      <c r="U16" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="W16" s="11" t="s">
+      <c r="V16" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="X16" s="11" t="s">
+      <c r="W16" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="Y16" s="11" t="s">
+      <c r="X16" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="Z16" s="11" t="s">
+      <c r="Y16" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="AA16" s="11" t="s">
+      <c r="Z16" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="AB16" s="11" t="s">
+      <c r="AA16" s="12" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="s">
+      <c r="AB16" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="13" t="n">
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="14" t="n">
         <v>5.5</v>
       </c>
-      <c r="C17" s="14" t="n">
+      <c r="C17" s="15" t="n">
         <f aca="false">100-B17</f>
         <v>94.5</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D17" s="13" t="n">
         <v>6.7</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="13" t="n">
         <v>6.4</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="F17" s="13" t="n">
         <v>6.3</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="G17" s="13" t="n">
         <v>6.6</v>
       </c>
-      <c r="H17" s="15" t="n">
+      <c r="H17" s="16" t="n">
         <f aca="false">AVERAGE(D17:G17)</f>
         <v>6.5</v>
       </c>
-      <c r="I17" s="16" t="n">
+      <c r="I17" s="17" t="n">
         <f aca="false">IFERROR(INDEX(Factor_Altura!$B$2:$B$34,MATCH(H17*10,Factor_Altura!$A$2:$A$34,1))+(H17*10-INDEX(Factor_Altura!$A$2:$A$34,MATCH(H17*10,Factor_Altura!$A$2:$A$34,1)))*(INDEX(Factor_Altura!$B$2:$B$34,MATCH(H17*10,Factor_Altura!$A$2:$A$34,1)+1)-INDEX(Factor_Altura!$B$2:$B$34,MATCH(H17*10,Factor_Altura!$A$2:$A$34,1)))/(INDEX(Factor_Altura!$A$2:$A$34,MATCH(H17*10,Factor_Altura!$A$2:$A$34,1)+1)-INDEX(Factor_Altura!$A$2:$A$34,MATCH(H17*10,Factor_Altura!$A$2:$A$34,1))),NA())</f>
         <v>0.9625</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="J17" s="13" t="n">
         <v>1139</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="K17" s="13" t="n">
         <v>1142</v>
       </c>
-      <c r="L17" s="17" t="n">
+      <c r="L17" s="18" t="n">
         <f aca="false">ROUND(K17-J17/(AA17*AVERAGE(P18/AA18,P19/AA19,P20/AA20,P21/AA21)),0)</f>
         <v>626</v>
       </c>
-      <c r="M17" s="17" t="n">
+      <c r="M17" s="18" t="n">
         <f aca="false">ROUND(K17-J17/(AA17*AVERAGE(P18/AA18,P19/AA19,P20/AA20,P21/AA21)),0)</f>
         <v>626</v>
       </c>
-      <c r="N17" s="14" t="n">
+      <c r="N17" s="15" t="n">
         <f aca="false">AVERAGE(L17:M17)</f>
         <v>626</v>
       </c>
-      <c r="O17" s="14" t="n">
+      <c r="O17" s="15" t="n">
         <f aca="false">K17-N17</f>
         <v>516</v>
       </c>
-      <c r="P17" s="16" t="n">
+      <c r="P17" s="17" t="n">
         <f aca="false">J17/O17</f>
         <v>2.20736434108527</v>
       </c>
-      <c r="Q17" s="16" t="n">
+      <c r="Q17" s="17" t="n">
         <f aca="false">100/(B17/$D$9+C17/$D$11)</f>
-        <v>2.61231356056531</v>
-      </c>
-      <c r="R17" s="15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R17" s="16" t="n">
         <f aca="false">100*(Q17-P17)/Q17</f>
-        <v>15.5015548513405</v>
-      </c>
-      <c r="S17" s="15" t="n">
+        <v>3.18577451380388</v>
+      </c>
+      <c r="S17" s="16" t="n">
         <f aca="false">100-P17*C17/$D$10</f>
-        <v>24.6674141449772</v>
-      </c>
-      <c r="T17" s="14" t="n">
+        <v>14.1580534022394</v>
+      </c>
+      <c r="T17" s="15" t="n">
         <f aca="false">100*(S17-R17)/S17</f>
-        <v>37.1577630300704</v>
-      </c>
-      <c r="U17" s="15" t="n">
+        <v>77.4984990994597</v>
+      </c>
+      <c r="U17" s="16" t="n">
         <f aca="false">B17-$D$12*C17/100</f>
-        <v>4.24790501634189</v>
-      </c>
-      <c r="V17" s="12" t="n">
+        <v>5.08508771929825</v>
+      </c>
+      <c r="V17" s="13" t="n">
         <v>883.9</v>
       </c>
-      <c r="W17" s="14" t="n">
+      <c r="W17" s="15" t="n">
         <f aca="false">V17*I17</f>
         <v>850.75375</v>
       </c>
-      <c r="X17" s="15" t="n">
+      <c r="X17" s="16" t="n">
         <f aca="false">W17*9.80665/1000</f>
         <v>8.3430442624375</v>
       </c>
-      <c r="Y17" s="13" t="n">
+      <c r="Y17" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="Z17" s="18" t="n">
+      <c r="Z17" s="19" t="n">
         <f aca="false">W17/(Y17/10)</f>
         <v>2126.884375</v>
       </c>
-      <c r="AA17" s="16" t="n">
+      <c r="AA17" s="17" t="n">
         <f aca="false">J17/(PI()*$D$13^2/4*H17)</f>
         <v>2.16138966340692</v>
       </c>
-      <c r="AB17" s="15" t="n">
+      <c r="AB17" s="16" t="n">
         <f aca="false">100*(K17-J17)/O17</f>
         <v>0.581395348837209</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18" s="13" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="C18" s="14" t="n">
+      <c r="C18" s="15" t="n">
         <f aca="false">100-B18</f>
         <v>94</v>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" s="13" t="n">
         <v>6.8</v>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E18" s="13" t="n">
         <v>6.7</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="F18" s="13" t="n">
         <v>6.6</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="G18" s="13" t="n">
         <v>6.6</v>
       </c>
-      <c r="H18" s="15" t="n">
+      <c r="H18" s="16" t="n">
         <f aca="false">AVERAGE(D18:G18)</f>
         <v>6.675</v>
       </c>
-      <c r="I18" s="16" t="n">
+      <c r="I18" s="17" t="n">
         <f aca="false">IFERROR(INDEX(Factor_Altura!$B$2:$B$34,MATCH(H18*10,Factor_Altura!$A$2:$A$34,1))+(H18*10-INDEX(Factor_Altura!$A$2:$A$34,MATCH(H18*10,Factor_Altura!$A$2:$A$34,1)))*(INDEX(Factor_Altura!$B$2:$B$34,MATCH(H18*10,Factor_Altura!$A$2:$A$34,1)+1)-INDEX(Factor_Altura!$B$2:$B$34,MATCH(H18*10,Factor_Altura!$A$2:$A$34,1)))/(INDEX(Factor_Altura!$A$2:$A$34,MATCH(H18*10,Factor_Altura!$A$2:$A$34,1)+1)-INDEX(Factor_Altura!$A$2:$A$34,MATCH(H18*10,Factor_Altura!$A$2:$A$34,1))),NA())</f>
         <v>0.92875</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="J18" s="13" t="n">
         <v>1124</v>
       </c>
-      <c r="K18" s="12" t="n">
+      <c r="K18" s="13" t="n">
         <v>1132</v>
       </c>
-      <c r="L18" s="12" t="n">
+      <c r="L18" s="13" t="n">
         <v>609</v>
       </c>
-      <c r="M18" s="12" t="n">
+      <c r="M18" s="13" t="n">
         <v>614</v>
       </c>
-      <c r="N18" s="14" t="n">
+      <c r="N18" s="15" t="n">
         <f aca="false">AVERAGE(L18:M18)</f>
         <v>611.5</v>
       </c>
-      <c r="O18" s="14" t="n">
+      <c r="O18" s="15" t="n">
         <f aca="false">K18-N18</f>
         <v>520.5</v>
       </c>
-      <c r="P18" s="16" t="n">
+      <c r="P18" s="17" t="n">
         <f aca="false">J18/O18</f>
         <v>2.15946205571566</v>
       </c>
-      <c r="Q18" s="16" t="n">
+      <c r="Q18" s="17" t="n">
         <f aca="false">100/(B18/$D$9+C18/$D$11)</f>
-        <v>2.59101539764009</v>
-      </c>
-      <c r="R18" s="15" t="n">
+        <v>2.26527286181168</v>
+      </c>
+      <c r="R18" s="16" t="n">
         <f aca="false">100*(Q18-P18)/Q18</f>
-        <v>16.6557613790134</v>
-      </c>
-      <c r="S18" s="15" t="n">
+        <v>4.67099605878815</v>
+      </c>
+      <c r="S18" s="16" t="n">
         <f aca="false">100-P18*C18/$D$10</f>
-        <v>26.6921512324768</v>
-      </c>
-      <c r="T18" s="14" t="n">
+        <v>16.4652538118223</v>
+      </c>
+      <c r="T18" s="15" t="n">
         <f aca="false">100*(S18-R18)/S18</f>
-        <v>37.6005282079022</v>
-      </c>
-      <c r="U18" s="15" t="n">
+        <v>71.6311931041457</v>
+      </c>
+      <c r="U18" s="16" t="n">
         <f aca="false">B18-$D$12*C18/100</f>
-        <v>4.75452985752527</v>
-      </c>
-      <c r="V18" s="12" t="n">
+        <v>5.58728302237075</v>
+      </c>
+      <c r="V18" s="13" t="n">
         <v>669.7</v>
       </c>
-      <c r="W18" s="14" t="n">
+      <c r="W18" s="15" t="n">
         <f aca="false">V18*I18</f>
         <v>621.983875</v>
       </c>
-      <c r="X18" s="15" t="n">
+      <c r="X18" s="16" t="n">
         <f aca="false">W18*9.80665/1000</f>
         <v>6.09957816776875</v>
       </c>
-      <c r="Y18" s="13" t="n">
+      <c r="Y18" s="14" t="n">
         <v>4.4</v>
       </c>
-      <c r="Z18" s="18" t="n">
+      <c r="Z18" s="19" t="n">
         <f aca="false">W18/(Y18/10)</f>
         <v>1413.59971590909</v>
       </c>
-      <c r="AA18" s="16" t="n">
+      <c r="AA18" s="17" t="n">
         <f aca="false">J18/(PI()*$D$13^2/4*H18)</f>
         <v>2.07700596565762</v>
       </c>
-      <c r="AB18" s="15" t="n">
+      <c r="AB18" s="16" t="n">
         <f aca="false">100*(K18-J18)/O18</f>
         <v>1.53698366954851</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B19" s="13" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="14" t="n">
         <v>6.5</v>
       </c>
-      <c r="C19" s="14" t="n">
+      <c r="C19" s="15" t="n">
         <f aca="false">100-B19</f>
         <v>93.5</v>
       </c>
-      <c r="D19" s="12" t="n">
+      <c r="D19" s="13" t="n">
         <v>6.5</v>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="E19" s="13" t="n">
         <v>6.9</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="F19" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="G19" s="13" t="n">
         <v>6.8</v>
       </c>
-      <c r="H19" s="15" t="n">
+      <c r="H19" s="16" t="n">
         <f aca="false">AVERAGE(D19:G19)</f>
         <v>6.8</v>
       </c>
-      <c r="I19" s="16" t="n">
+      <c r="I19" s="17" t="n">
         <f aca="false">IFERROR(INDEX(Factor_Altura!$B$2:$B$34,MATCH(H19*10,Factor_Altura!$A$2:$A$34,1))+(H19*10-INDEX(Factor_Altura!$A$2:$A$34,MATCH(H19*10,Factor_Altura!$A$2:$A$34,1)))*(INDEX(Factor_Altura!$B$2:$B$34,MATCH(H19*10,Factor_Altura!$A$2:$A$34,1)+1)-INDEX(Factor_Altura!$B$2:$B$34,MATCH(H19*10,Factor_Altura!$A$2:$A$34,1)))/(INDEX(Factor_Altura!$A$2:$A$34,MATCH(H19*10,Factor_Altura!$A$2:$A$34,1)+1)-INDEX(Factor_Altura!$A$2:$A$34,MATCH(H19*10,Factor_Altura!$A$2:$A$34,1))),NA())</f>
         <v>0.8975</v>
       </c>
-      <c r="J19" s="12" t="n">
+      <c r="J19" s="13" t="n">
         <v>1184</v>
       </c>
-      <c r="K19" s="12" t="n">
+      <c r="K19" s="13" t="n">
         <v>1184</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="L19" s="13" t="n">
         <v>641</v>
       </c>
-      <c r="M19" s="12" t="n">
+      <c r="M19" s="13" t="n">
         <v>643</v>
       </c>
-      <c r="N19" s="14" t="n">
+      <c r="N19" s="15" t="n">
         <f aca="false">AVERAGE(L19:M19)</f>
         <v>642</v>
       </c>
-      <c r="O19" s="14" t="n">
+      <c r="O19" s="15" t="n">
         <f aca="false">K19-N19</f>
         <v>542</v>
       </c>
-      <c r="P19" s="16" t="n">
+      <c r="P19" s="17" t="n">
         <f aca="false">J19/O19</f>
         <v>2.18450184501845</v>
       </c>
-      <c r="Q19" s="16" t="n">
+      <c r="Q19" s="17" t="n">
         <f aca="false">100/(B19/$D$9+C19/$D$11)</f>
-        <v>2.57006171354593</v>
-      </c>
-      <c r="R19" s="15" t="n">
+        <v>2.25073475577067</v>
+      </c>
+      <c r="R19" s="16" t="n">
         <f aca="false">100*(Q19-P19)/Q19</f>
-        <v>15.0019692716062</v>
-      </c>
-      <c r="S19" s="15" t="n">
+        <v>2.94272395191875</v>
+      </c>
+      <c r="S19" s="16" t="n">
         <f aca="false">100-P19*C19/$D$10</f>
-        <v>26.2365754751805</v>
-      </c>
-      <c r="T19" s="14" t="n">
+        <v>15.9461224241872</v>
+      </c>
+      <c r="T19" s="15" t="n">
         <f aca="false">100*(S19-R19)/S19</f>
-        <v>42.8203986232964</v>
-      </c>
-      <c r="U19" s="15" t="n">
+        <v>81.545833691486</v>
+      </c>
+      <c r="U19" s="16" t="n">
         <f aca="false">B19-$D$12*C19/100</f>
-        <v>5.26115469870865</v>
-      </c>
-      <c r="V19" s="12" t="n">
+        <v>6.08947832544325</v>
+      </c>
+      <c r="V19" s="13" t="n">
         <v>772</v>
       </c>
-      <c r="W19" s="14" t="n">
+      <c r="W19" s="15" t="n">
         <f aca="false">V19*I19</f>
         <v>692.87</v>
       </c>
-      <c r="X19" s="15" t="n">
+      <c r="X19" s="16" t="n">
         <f aca="false">W19*9.80665/1000</f>
         <v>6.7947335855</v>
       </c>
-      <c r="Y19" s="13" t="n">
+      <c r="Y19" s="14" t="n">
         <v>4.9</v>
       </c>
-      <c r="Z19" s="18" t="n">
+      <c r="Z19" s="19" t="n">
         <f aca="false">W19/(Y19/10)</f>
         <v>1414.02040816327</v>
       </c>
-      <c r="AA19" s="16" t="n">
+      <c r="AA19" s="17" t="n">
         <f aca="false">J19/(PI()*$D$13^2/4*H19)</f>
         <v>2.14765982151263</v>
       </c>
-      <c r="AB19" s="15" t="n">
+      <c r="AB19" s="16" t="n">
         <f aca="false">100*(K19-J19)/O19</f>
         <v>0</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20" s="13" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="C20" s="14" t="n">
+      <c r="C20" s="15" t="n">
         <f aca="false">100-B20</f>
         <v>92</v>
       </c>
-      <c r="D20" s="12" t="n">
+      <c r="D20" s="13" t="n">
         <v>6.5</v>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="13" t="n">
         <v>6.6</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="F20" s="13" t="n">
         <v>6.4</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="G20" s="13" t="n">
         <v>6.4</v>
       </c>
-      <c r="H20" s="15" t="n">
+      <c r="H20" s="16" t="n">
         <f aca="false">AVERAGE(D20:G20)</f>
         <v>6.475</v>
       </c>
-      <c r="I20" s="16" t="n">
+      <c r="I20" s="17" t="n">
         <f aca="false">IFERROR(INDEX(Factor_Altura!$B$2:$B$34,MATCH(H20*10,Factor_Altura!$A$2:$A$34,1))+(H20*10-INDEX(Factor_Altura!$A$2:$A$34,MATCH(H20*10,Factor_Altura!$A$2:$A$34,1)))*(INDEX(Factor_Altura!$B$2:$B$34,MATCH(H20*10,Factor_Altura!$A$2:$A$34,1)+1)-INDEX(Factor_Altura!$B$2:$B$34,MATCH(H20*10,Factor_Altura!$A$2:$A$34,1)))/(INDEX(Factor_Altura!$A$2:$A$34,MATCH(H20*10,Factor_Altura!$A$2:$A$34,1)+1)-INDEX(Factor_Altura!$A$2:$A$34,MATCH(H20*10,Factor_Altura!$A$2:$A$34,1))),NA())</f>
         <v>0.96875</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="J20" s="13" t="n">
         <v>1134</v>
       </c>
-      <c r="K20" s="12" t="n">
+      <c r="K20" s="13" t="n">
         <v>1136</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="L20" s="13" t="n">
         <v>617</v>
       </c>
-      <c r="M20" s="12" t="n">
+      <c r="M20" s="13" t="n">
         <v>619</v>
       </c>
-      <c r="N20" s="14" t="n">
+      <c r="N20" s="15" t="n">
         <f aca="false">AVERAGE(L20:M20)</f>
         <v>618</v>
       </c>
-      <c r="O20" s="14" t="n">
+      <c r="O20" s="15" t="n">
         <f aca="false">K20-N20</f>
         <v>518</v>
       </c>
-      <c r="P20" s="16" t="n">
+      <c r="P20" s="17" t="n">
         <f aca="false">J20/O20</f>
         <v>2.18918918918919</v>
       </c>
-      <c r="Q20" s="16" t="n">
+      <c r="Q20" s="17" t="n">
         <f aca="false">100/(B20/$D$9+C20/$D$11)</f>
-        <v>2.50918593926144</v>
-      </c>
-      <c r="R20" s="15" t="n">
+        <v>2.20821892281798</v>
+      </c>
+      <c r="R20" s="16" t="n">
         <f aca="false">100*(Q20-P20)/Q20</f>
-        <v>12.7530106503959</v>
-      </c>
-      <c r="S20" s="15" t="n">
+        <v>0.861768433924621</v>
+      </c>
+      <c r="S20" s="16" t="n">
         <f aca="false">100-P20*C20/$D$10</f>
-        <v>27.2642089543498</v>
-      </c>
-      <c r="T20" s="14" t="n">
+        <v>17.1171171171171</v>
+      </c>
+      <c r="T20" s="15" t="n">
         <f aca="false">100*(S20-R20)/S20</f>
-        <v>53.2243511200012</v>
-      </c>
-      <c r="U20" s="15" t="n">
+        <v>94.9654580965457</v>
+      </c>
+      <c r="U20" s="16" t="n">
         <f aca="false">B20-$D$12*C20/100</f>
-        <v>6.78102922225878</v>
-      </c>
-      <c r="V20" s="12" t="n">
+        <v>7.59606423466073</v>
+      </c>
+      <c r="V20" s="13" t="n">
         <v>523</v>
       </c>
-      <c r="W20" s="14" t="n">
+      <c r="W20" s="15" t="n">
         <f aca="false">V20*I20</f>
         <v>506.65625</v>
       </c>
-      <c r="X20" s="15" t="n">
+      <c r="X20" s="16" t="n">
         <f aca="false">W20*9.80665/1000</f>
         <v>4.9686005140625</v>
       </c>
-      <c r="Y20" s="13" t="n">
+      <c r="Y20" s="14" t="n">
         <v>5.8</v>
       </c>
-      <c r="Z20" s="18" t="n">
+      <c r="Z20" s="19" t="n">
         <f aca="false">W20/(Y20/10)</f>
         <v>873.54525862069</v>
       </c>
-      <c r="AA20" s="16" t="n">
+      <c r="AA20" s="17" t="n">
         <f aca="false">J20/(PI()*$D$13^2/4*H20)</f>
         <v>2.16021006152147</v>
       </c>
-      <c r="AB20" s="15" t="n">
+      <c r="AB20" s="16" t="n">
         <f aca="false">100*(K20-J20)/O20</f>
         <v>0.386100386100386</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" s="13" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="C21" s="14" t="n">
+      <c r="C21" s="15" t="n">
         <f aca="false">100-B21</f>
         <v>90</v>
       </c>
-      <c r="D21" s="12" t="n">
+      <c r="D21" s="13" t="n">
         <v>6.9</v>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="13" t="n">
         <v>6.9</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="F21" s="13" t="n">
         <v>6.8</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="G21" s="13" t="n">
         <v>6.8</v>
       </c>
-      <c r="H21" s="15" t="n">
+      <c r="H21" s="16" t="n">
         <f aca="false">AVERAGE(D21:G21)</f>
         <v>6.85</v>
       </c>
-      <c r="I21" s="16" t="n">
+      <c r="I21" s="17" t="n">
         <f aca="false">IFERROR(INDEX(Factor_Altura!$B$2:$B$34,MATCH(H21*10,Factor_Altura!$A$2:$A$34,1))+(H21*10-INDEX(Factor_Altura!$A$2:$A$34,MATCH(H21*10,Factor_Altura!$A$2:$A$34,1)))*(INDEX(Factor_Altura!$B$2:$B$34,MATCH(H21*10,Factor_Altura!$A$2:$A$34,1)+1)-INDEX(Factor_Altura!$B$2:$B$34,MATCH(H21*10,Factor_Altura!$A$2:$A$34,1)))/(INDEX(Factor_Altura!$A$2:$A$34,MATCH(H21*10,Factor_Altura!$A$2:$A$34,1)+1)-INDEX(Factor_Altura!$A$2:$A$34,MATCH(H21*10,Factor_Altura!$A$2:$A$34,1))),NA())</f>
         <v>0.88625</v>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="J21" s="13" t="n">
         <v>1187</v>
       </c>
-      <c r="K21" s="12" t="n">
+      <c r="K21" s="13" t="n">
         <v>1187</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="L21" s="13" t="n">
         <v>640</v>
       </c>
-      <c r="M21" s="12" t="n">
+      <c r="M21" s="13" t="n">
         <v>642</v>
       </c>
-      <c r="N21" s="14" t="n">
+      <c r="N21" s="15" t="n">
         <f aca="false">AVERAGE(L21:M21)</f>
         <v>641</v>
       </c>
-      <c r="O21" s="14" t="n">
+      <c r="O21" s="15" t="n">
         <f aca="false">K21-N21</f>
         <v>546</v>
       </c>
-      <c r="P21" s="16" t="n">
+      <c r="P21" s="17" t="n">
         <f aca="false">J21/O21</f>
         <v>2.17399267399267</v>
       </c>
-      <c r="Q21" s="16" t="n">
+      <c r="Q21" s="17" t="n">
         <f aca="false">100/(B21/$D$9+C21/$D$11)</f>
-        <v>2.43236691779121</v>
-      </c>
-      <c r="R21" s="15" t="n">
+        <v>2.15396833773087</v>
+      </c>
+      <c r="R21" s="16" t="n">
         <f aca="false">100*(Q21-P21)/Q21</f>
-        <v>10.6223383449549</v>
-      </c>
-      <c r="S21" s="15" t="n">
+        <v>-0.92964858911984</v>
+      </c>
+      <c r="S21" s="16" t="n">
         <f aca="false">100-P21*C21/$D$10</f>
-        <v>29.3393497077138</v>
-      </c>
-      <c r="T21" s="14" t="n">
+        <v>19.4817528150862</v>
+      </c>
+      <c r="T21" s="15" t="n">
         <f aca="false">100*(S21-R21)/S21</f>
-        <v>63.7949087120967</v>
-      </c>
-      <c r="U21" s="15" t="n">
+        <v>104.771893976603</v>
+      </c>
+      <c r="U21" s="16" t="n">
         <f aca="false">B21-$D$12*C21/100</f>
-        <v>8.80752858699228</v>
-      </c>
-      <c r="V21" s="12" t="n">
+        <v>9.60484544695072</v>
+      </c>
+      <c r="V21" s="13" t="n">
         <v>707.3</v>
       </c>
-      <c r="W21" s="14" t="n">
+      <c r="W21" s="15" t="n">
         <f aca="false">V21*I21</f>
         <v>626.844625</v>
       </c>
-      <c r="X21" s="15" t="n">
+      <c r="X21" s="16" t="n">
         <f aca="false">W21*9.80665/1000</f>
         <v>6.14724584175625</v>
       </c>
-      <c r="Y21" s="13" t="n">
+      <c r="Y21" s="14" t="n">
         <v>6.7</v>
       </c>
-      <c r="Z21" s="18" t="n">
+      <c r="Z21" s="19" t="n">
         <f aca="false">W21/(Y21/10)</f>
         <v>935.588992537313</v>
       </c>
-      <c r="AA21" s="16" t="n">
+      <c r="AA21" s="17" t="n">
         <f aca="false">J21/(PI()*$D$13^2/4*H21)</f>
         <v>2.13738545760029</v>
       </c>
-      <c r="AB21" s="15" t="n">
+      <c r="AB21" s="16" t="n">
         <f aca="false">100*(K21-J21)/O21</f>
         <v>0</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" s="11" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="11" t="str">
+    </row>
+    <row r="24" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="12" t="str">
         <f aca="false">"Va "&amp;$J$11&amp;"-"&amp;$K$11&amp;" %"</f>
         <v>Va 3-5 %</v>
       </c>
-      <c r="D24" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="E24" s="11" t="str">
+      <c r="D24" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E24" s="12" t="str">
         <f aca="false">"VFA "&amp;$J$13&amp;"-"&amp;$K$13&amp;" %"</f>
         <v>VFA 65-78 %</v>
       </c>
-      <c r="F24" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="G24" s="11" t="str">
+      <c r="F24" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="G24" s="12" t="str">
         <f aca="false">"Flujo "&amp;$J$10&amp;"-"&amp;$K$10&amp;" mm"</f>
         <v>Flujo 2-4 mm</v>
       </c>
-      <c r="H24" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="I24" s="11" t="str">
+      <c r="H24" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="I24" s="12" t="str">
         <f aca="false">"Est/Flujo "&amp;$J$15&amp;"-"&amp;$K$15</f>
         <v>Est/Flujo 1700-4000</v>
       </c>
-      <c r="J24" s="11" t="str">
+      <c r="J24" s="12" t="str">
         <f aca="false">"Absorción ≤ "&amp;$D$14&amp;" %"</f>
         <v>Absorción ≤ 2 %</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19" t="str">
+    <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="20" t="str">
         <f aca="false">A17</f>
         <v>M1</v>
       </c>
-      <c r="B25" s="14" t="n">
+      <c r="B25" s="15" t="n">
         <f aca="false">B17</f>
         <v>5.5</v>
       </c>
-      <c r="C25" s="19" t="str">
+      <c r="C25" s="20" t="str">
         <f aca="false">IF(AND(R17&gt;=$J$11,R17&lt;=$K$11),"CUMPLE","NO")</f>
-        <v>NO</v>
-      </c>
-      <c r="D25" s="19" t="str">
+        <v>CUMPLE</v>
+      </c>
+      <c r="D25" s="20" t="str">
         <f aca="false">IF(S17&gt;=$J$12,"CUMPLE","NO")</f>
         <v>CUMPLE</v>
       </c>
-      <c r="E25" s="19" t="str">
+      <c r="E25" s="20" t="str">
         <f aca="false">IF(AND(T17&gt;=$J$13,T17&lt;=$K$13),"CUMPLE","NO")</f>
-        <v>NO</v>
-      </c>
-      <c r="F25" s="19" t="str">
+        <v>CUMPLE</v>
+      </c>
+      <c r="F25" s="20" t="str">
         <f aca="false">IF(X17&gt;=$J$9,"CUMPLE","NO")</f>
         <v>CUMPLE</v>
       </c>
-      <c r="G25" s="19" t="str">
+      <c r="G25" s="20" t="str">
         <f aca="false">IF(AND(Y17&gt;=$J$10,Y17&lt;=$K$10),"CUMPLE","NO")</f>
         <v>CUMPLE</v>
       </c>
-      <c r="H25" s="19" t="str">
+      <c r="H25" s="20" t="str">
         <f aca="false">IF(COUNTIF(C25:G25,"NO")+COUNTIF(I25:J25,"NO")=0,"CUMPLE","NO CUMPLE")</f>
-        <v>NO CUMPLE</v>
-      </c>
-      <c r="I25" s="19" t="str">
+        <v>CUMPLE</v>
+      </c>
+      <c r="I25" s="20" t="str">
         <f aca="false">IF(AND(Z17&gt;=$J$15,Z17&lt;=$K$15),"CUMPLE","NO")</f>
         <v>CUMPLE</v>
       </c>
-      <c r="J25" s="19" t="str">
+      <c r="J25" s="20" t="str">
         <f aca="false">IF(AB17&lt;=$D$14,"CUMPLE","NO")</f>
         <v>CUMPLE</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="str">
+    <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="20" t="str">
         <f aca="false">A18</f>
         <v>M2</v>
       </c>
-      <c r="B26" s="14" t="n">
+      <c r="B26" s="15" t="n">
         <f aca="false">B18</f>
         <v>6</v>
       </c>
-      <c r="C26" s="19" t="str">
+      <c r="C26" s="20" t="str">
         <f aca="false">IF(AND(R18&gt;=$J$11,R18&lt;=$K$11),"CUMPLE","NO")</f>
-        <v>NO</v>
-      </c>
-      <c r="D26" s="19" t="str">
+        <v>CUMPLE</v>
+      </c>
+      <c r="D26" s="20" t="str">
         <f aca="false">IF(S18&gt;=$J$12,"CUMPLE","NO")</f>
         <v>CUMPLE</v>
       </c>
-      <c r="E26" s="19" t="str">
+      <c r="E26" s="20" t="str">
         <f aca="false">IF(AND(T18&gt;=$J$13,T18&lt;=$K$13),"CUMPLE","NO")</f>
-        <v>NO</v>
-      </c>
-      <c r="F26" s="19" t="str">
+        <v>CUMPLE</v>
+      </c>
+      <c r="F26" s="20" t="str">
         <f aca="false">IF(X18&gt;=$J$9,"CUMPLE","NO")</f>
         <v>CUMPLE</v>
       </c>
-      <c r="G26" s="19" t="str">
+      <c r="G26" s="20" t="str">
         <f aca="false">IF(AND(Y18&gt;=$J$10,Y18&lt;=$K$10),"CUMPLE","NO")</f>
         <v>NO</v>
       </c>
-      <c r="H26" s="19" t="str">
+      <c r="H26" s="20" t="str">
         <f aca="false">IF(COUNTIF(C26:G26,"NO")+COUNTIF(I26:J26,"NO")=0,"CUMPLE","NO CUMPLE")</f>
         <v>NO CUMPLE</v>
       </c>
-      <c r="I26" s="19" t="str">
+      <c r="I26" s="20" t="str">
         <f aca="false">IF(AND(Z18&gt;=$J$15,Z18&lt;=$K$15),"CUMPLE","NO")</f>
         <v>NO</v>
       </c>
-      <c r="J26" s="19" t="str">
+      <c r="J26" s="20" t="str">
         <f aca="false">IF(AB18&lt;=$D$14,"CUMPLE","NO")</f>
         <v>CUMPLE</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="str">
+    <row r="27" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20" t="str">
         <f aca="false">A19</f>
         <v>M3</v>
       </c>
-      <c r="B27" s="14" t="n">
+      <c r="B27" s="15" t="n">
         <f aca="false">B19</f>
         <v>6.5</v>
       </c>
-      <c r="C27" s="19" t="str">
+      <c r="C27" s="20" t="str">
         <f aca="false">IF(AND(R19&gt;=$J$11,R19&lt;=$K$11),"CUMPLE","NO")</f>
         <v>NO</v>
       </c>
-      <c r="D27" s="19" t="str">
+      <c r="D27" s="20" t="str">
         <f aca="false">IF(S19&gt;=$J$12,"CUMPLE","NO")</f>
         <v>CUMPLE</v>
       </c>
-      <c r="E27" s="19" t="str">
+      <c r="E27" s="20" t="str">
         <f aca="false">IF(AND(T19&gt;=$J$13,T19&lt;=$K$13),"CUMPLE","NO")</f>
         <v>NO</v>
       </c>
-      <c r="F27" s="19" t="str">
+      <c r="F27" s="20" t="str">
         <f aca="false">IF(X19&gt;=$J$9,"CUMPLE","NO")</f>
         <v>CUMPLE</v>
       </c>
-      <c r="G27" s="19" t="str">
+      <c r="G27" s="20" t="str">
         <f aca="false">IF(AND(Y19&gt;=$J$10,Y19&lt;=$K$10),"CUMPLE","NO")</f>
         <v>NO</v>
       </c>
-      <c r="H27" s="19" t="str">
+      <c r="H27" s="20" t="str">
         <f aca="false">IF(COUNTIF(C27:G27,"NO")+COUNTIF(I27:J27,"NO")=0,"CUMPLE","NO CUMPLE")</f>
         <v>NO CUMPLE</v>
       </c>
-      <c r="I27" s="19" t="str">
+      <c r="I27" s="20" t="str">
         <f aca="false">IF(AND(Z19&gt;=$J$15,Z19&lt;=$K$15),"CUMPLE","NO")</f>
         <v>NO</v>
       </c>
-      <c r="J27" s="19" t="str">
+      <c r="J27" s="20" t="str">
         <f aca="false">IF(AB19&lt;=$D$14,"CUMPLE","NO")</f>
         <v>CUMPLE</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="str">
+    <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="20" t="str">
         <f aca="false">A20</f>
         <v>M4</v>
       </c>
-      <c r="B28" s="14" t="n">
+      <c r="B28" s="15" t="n">
         <f aca="false">B20</f>
         <v>8</v>
       </c>
-      <c r="C28" s="19" t="str">
+      <c r="C28" s="20" t="str">
         <f aca="false">IF(AND(R20&gt;=$J$11,R20&lt;=$K$11),"CUMPLE","NO")</f>
         <v>NO</v>
       </c>
-      <c r="D28" s="19" t="str">
+      <c r="D28" s="20" t="str">
         <f aca="false">IF(S20&gt;=$J$12,"CUMPLE","NO")</f>
         <v>CUMPLE</v>
       </c>
-      <c r="E28" s="19" t="str">
+      <c r="E28" s="20" t="str">
         <f aca="false">IF(AND(T20&gt;=$J$13,T20&lt;=$K$13),"CUMPLE","NO")</f>
         <v>NO</v>
       </c>
-      <c r="F28" s="19" t="str">
+      <c r="F28" s="20" t="str">
         <f aca="false">IF(X20&gt;=$J$9,"CUMPLE","NO")</f>
         <v>NO</v>
       </c>
-      <c r="G28" s="19" t="str">
+      <c r="G28" s="20" t="str">
         <f aca="false">IF(AND(Y20&gt;=$J$10,Y20&lt;=$K$10),"CUMPLE","NO")</f>
         <v>NO</v>
       </c>
-      <c r="H28" s="19" t="str">
+      <c r="H28" s="20" t="str">
         <f aca="false">IF(COUNTIF(C28:G28,"NO")+COUNTIF(I28:J28,"NO")=0,"CUMPLE","NO CUMPLE")</f>
         <v>NO CUMPLE</v>
       </c>
-      <c r="I28" s="19" t="str">
+      <c r="I28" s="20" t="str">
         <f aca="false">IF(AND(Z20&gt;=$J$15,Z20&lt;=$K$15),"CUMPLE","NO")</f>
         <v>NO</v>
       </c>
-      <c r="J28" s="19" t="str">
+      <c r="J28" s="20" t="str">
         <f aca="false">IF(AB20&lt;=$D$14,"CUMPLE","NO")</f>
         <v>CUMPLE</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="str">
+    <row r="29" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="20" t="str">
         <f aca="false">A21</f>
         <v>M5</v>
       </c>
-      <c r="B29" s="14" t="n">
+      <c r="B29" s="15" t="n">
         <f aca="false">B21</f>
         <v>10</v>
       </c>
-      <c r="C29" s="19" t="str">
+      <c r="C29" s="20" t="str">
         <f aca="false">IF(AND(R21&gt;=$J$11,R21&lt;=$K$11),"CUMPLE","NO")</f>
         <v>NO</v>
       </c>
-      <c r="D29" s="19" t="str">
+      <c r="D29" s="20" t="str">
         <f aca="false">IF(S21&gt;=$J$12,"CUMPLE","NO")</f>
         <v>CUMPLE</v>
       </c>
-      <c r="E29" s="19" t="str">
+      <c r="E29" s="20" t="str">
         <f aca="false">IF(AND(T21&gt;=$J$13,T21&lt;=$K$13),"CUMPLE","NO")</f>
         <v>NO</v>
       </c>
-      <c r="F29" s="19" t="str">
+      <c r="F29" s="20" t="str">
         <f aca="false">IF(X21&gt;=$J$9,"CUMPLE","NO")</f>
         <v>CUMPLE</v>
       </c>
-      <c r="G29" s="19" t="str">
+      <c r="G29" s="20" t="str">
         <f aca="false">IF(AND(Y21&gt;=$J$10,Y21&lt;=$K$10),"CUMPLE","NO")</f>
         <v>NO</v>
       </c>
-      <c r="H29" s="19" t="str">
+      <c r="H29" s="20" t="str">
         <f aca="false">IF(COUNTIF(C29:G29,"NO")+COUNTIF(I29:J29,"NO")=0,"CUMPLE","NO CUMPLE")</f>
         <v>NO CUMPLE</v>
       </c>
-      <c r="I29" s="19" t="str">
+      <c r="I29" s="20" t="str">
         <f aca="false">IF(AND(Z21&gt;=$J$15,Z21&lt;=$K$15),"CUMPLE","NO")</f>
         <v>NO</v>
       </c>
-      <c r="J29" s="19" t="str">
+      <c r="J29" s="20" t="str">
         <f aca="false">IF(AB21&lt;=$D$14,"CUMPLE","NO")</f>
         <v>CUMPLE</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="11" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B32" s="11" t="s">
+    </row>
+    <row r="32" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="B32" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="C32" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="D32" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="E32" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="G32" s="11" t="s">
+      <c r="F32" s="12" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="21" t="n">
+      <c r="G32" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="22" t="n">
         <f aca="false">INDEX(LINEST($P$17:$P$21,$B$17:$B$21^{1,2}),1,1)</f>
         <v>0.000629344612208408</v>
       </c>
-      <c r="C33" s="21" t="n">
+      <c r="C33" s="22" t="n">
         <f aca="false">INDEX(LINEST($P$17:$P$21,$B$17:$B$21^{1,2}),1,2)</f>
         <v>-0.0123886191287946</v>
       </c>
-      <c r="D33" s="22" t="n">
+      <c r="D33" s="9" t="n">
         <f aca="false">INDEX(LINEST($P$17:$P$21,$B$17:$B$21^{1,2}),1,3)</f>
         <v>2.23780079736221</v>
       </c>
-      <c r="E33" s="22" t="n">
+      <c r="E33" s="9" t="n">
         <f aca="false">INDEX(LINEST($P$17:$P$21,$B$17:$B$21^{1,2},TRUE(),TRUE()),3,1)</f>
         <v>0.0764562482328959</v>
       </c>
@@ -4505,57 +4592,57 @@
         <f aca="false">IF(AND(B33&lt;0,-C33/(2*B33)&gt;=MIN($B$17:$B$21),-C33/(2*B33)&lt;=MAX($B$17:$B$21)),-C33/(2*B33),INDEX($B$17:$B$21,MATCH(MAX($P$17:$P$21),$P$17:$P$21,0)))</f>
         <v>5.5</v>
       </c>
-      <c r="G33" s="20" t="str">
+      <c r="G33" s="21" t="str">
         <f aca="false">IF(AND(B33&lt;0,-C33/(2*B33)&gt;=MIN($B$17:$B$21),-C33/(2*B33)&lt;=MAX($B$17:$B$21)),"Máximo de la parábola","Sin máximo interior: se toma el mayor Gmb medido")</f>
         <v>Sin máximo interior: se toma el mayor Gmb medido</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="B34" s="21" t="n">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B34" s="22" t="n">
         <f aca="false">INDEX(LINEST($R$17:$R$21,$B$17:$B$21^{1,2}),1,1)</f>
-        <v>-0.0198957594083034</v>
-      </c>
-      <c r="C34" s="21" t="n">
+        <v>-0.0238007545461593</v>
+      </c>
+      <c r="C34" s="22" t="n">
         <f aca="false">INDEX(LINEST($R$17:$R$21,$B$17:$B$21^{1,2}),1,2)</f>
-        <v>-0.960718594624812</v>
-      </c>
-      <c r="D34" s="22" t="n">
+        <v>-0.756974723435819</v>
+      </c>
+      <c r="D34" s="9" t="n">
         <f aca="false">INDEX(LINEST($R$17:$R$21,$B$17:$B$21^{1,2}),1,3)</f>
-        <v>22.1084196685134</v>
-      </c>
-      <c r="E34" s="22" t="n">
+        <v>8.89368200536669</v>
+      </c>
+      <c r="E34" s="9" t="n">
         <f aca="false">INDEX(LINEST($R$17:$R$21,$B$17:$B$21^{1,2},TRUE(),TRUE()),3,1)</f>
-        <v>0.924787388283259</v>
-      </c>
-      <c r="F34" s="23" t="str">
+        <v>0.881013256952054</v>
+      </c>
+      <c r="F34" s="23" t="n">
         <f aca="false">IFERROR(IF((C34^2-4*B34*(D34-$J$14))&lt;0,"N/A",IF(AND(((-C34+SQRT((C34^2-4*B34*(D34-$J$14))))/(2*B34))&gt;=MIN($B$17:$B$21),((-C34+SQRT((C34^2-4*B34*(D34-$J$14))))/(2*B34))&lt;=MAX($B$17:$B$21)),((-C34+SQRT((C34^2-4*B34*(D34-$J$14))))/(2*B34)),IF(AND(((-C34-SQRT((C34^2-4*B34*(D34-$J$14))))/(2*B34))&gt;=MIN($B$17:$B$21),((-C34-SQRT((C34^2-4*B34*(D34-$J$14))))/(2*B34))&lt;=MAX($B$17:$B$21)),((-C34-SQRT((C34^2-4*B34*(D34-$J$14))))/(2*B34)),"N/A"))),"N/A")</f>
-        <v>N/A</v>
-      </c>
-      <c r="G34" s="20" t="str">
+        <v>5.51015500531332</v>
+      </c>
+      <c r="G34" s="21" t="str">
         <f aca="false">IF(ISNUMBER(F34),"Pb para Va objetivo","Va objetivo NO se alcanza en el rango ensayado (Va mín. medido = "&amp;TEXT(MIN($R$17:$R$21),"0.0")&amp;" %)")</f>
-        <v>Va objetivo NO se alcanza en el rango ensayado (Va mín. medido = 10.6 %)</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="B35" s="21" t="n">
+        <v>Pb para Va objetivo</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="B35" s="22" t="n">
         <f aca="false">INDEX(LINEST($S$17:$S$21,$B$17:$B$21^{1,2}),1,1)</f>
-        <v>-0.0238858905748256</v>
-      </c>
-      <c r="C35" s="21" t="n">
+        <v>-0.0272181197537832</v>
+      </c>
+      <c r="C35" s="22" t="n">
         <f aca="false">INDEX(LINEST($S$17:$S$21,$B$17:$B$21^{1,2}),1,2)</f>
-        <v>1.24625092751936</v>
-      </c>
-      <c r="D35" s="22" t="n">
+        <v>1.42011062481528</v>
+      </c>
+      <c r="D35" s="9" t="n">
         <f aca="false">INDEX(LINEST($S$17:$S$21,$B$17:$B$21^{1,2}),1,3)</f>
-        <v>19.1687142611282</v>
-      </c>
-      <c r="E35" s="22" t="n">
+        <v>7.89225094200161</v>
+      </c>
+      <c r="E35" s="9" t="n">
         <f aca="false">INDEX(LINEST($S$17:$S$21,$B$17:$B$21^{1,2},TRUE(),TRUE()),3,1)</f>
         <v>0.882867143136164</v>
       </c>
@@ -4563,57 +4650,57 @@
         <f aca="false">IFERROR(IF(AND(B35&gt;0,AND(-C35/(2*B35)&gt;=MIN($B$17:$B$21),-C35/(2*B35)&lt;=MAX($B$17:$B$21))),-C35/(2*B35),"N/A"),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="G35" s="20" t="str">
+      <c r="G35" s="21" t="str">
         <f aca="false">IF(ISNUMBER(F35),"Mínimo de VMA (informativo: el óptimo debe quedar en o a la izquierda)","Sin mínimo interior de VMA")</f>
         <v>Sin mínimo interior de VMA</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="B36" s="21" t="n">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="B36" s="22" t="n">
         <f aca="false">INDEX(LINEST($T$17:$T$21,$B$17:$B$21^{1,2}),1,1)</f>
-        <v>-0.200532202656734</v>
-      </c>
-      <c r="C36" s="21" t="n">
+        <v>-0.296438178331416</v>
+      </c>
+      <c r="C36" s="22" t="n">
         <f aca="false">INDEX(LINEST($T$17:$T$21,$B$17:$B$21^{1,2}),1,2)</f>
-        <v>9.35731437615834</v>
-      </c>
-      <c r="D36" s="22" t="n">
+        <v>11.7225119359573</v>
+      </c>
+      <c r="D36" s="9" t="n">
         <f aca="false">INDEX(LINEST($T$17:$T$21,$B$17:$B$21^{1,2}),1,3)</f>
-        <v>-9.52406852487469</v>
-      </c>
-      <c r="E36" s="22" t="n">
+        <v>17.8363703738176</v>
+      </c>
+      <c r="E36" s="9" t="n">
         <f aca="false">INDEX(LINEST($T$17:$T$21,$B$17:$B$21^{1,2},TRUE(),TRUE()),3,1)</f>
-        <v>0.989588036469953</v>
+        <v>0.921355347571009</v>
       </c>
       <c r="F36" s="23" t="str">
         <f aca="false">IFERROR(IF(AND((-C36+SQRT(C36^2-4*B36*(D36-($J$13+$K$13)/2)))/(2*B36)&gt;=MIN($B$17:$B$21),(-C36+SQRT(C36^2-4*B36*(D36-($J$13+$K$13)/2)))/(2*B36)&lt;=MAX($B$17:$B$21)),(-C36+SQRT(C36^2-4*B36*(D36-($J$13+$K$13)/2)))/(2*B36),IF(AND((-C36-SQRT(C36^2-4*B36*(D36-($J$13+$K$13)/2)))/(2*B36)&gt;=MIN($B$17:$B$21),(-C36-SQRT(C36^2-4*B36*(D36-($J$13+$K$13)/2)))/(2*B36)&lt;=MAX($B$17:$B$21)),(-C36-SQRT(C36^2-4*B36*(D36-($J$13+$K$13)/2)))/(2*B36),"N/A")),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="G36" s="20" t="str">
+      <c r="G36" s="21" t="str">
         <f aca="false">IF(ISNUMBER(F36),"Pb para VFA medio del rango (informativo)","Fuera del rango ensayado")</f>
         <v>Fuera del rango ensayado</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="B37" s="21" t="n">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="B37" s="22" t="n">
         <f aca="false">INDEX(LINEST($X$17:$X$21,$B$17:$B$21^{1,2}),1,1)</f>
         <v>0.388711097558842</v>
       </c>
-      <c r="C37" s="21" t="n">
+      <c r="C37" s="22" t="n">
         <f aca="false">INDEX(LINEST($X$17:$X$21,$B$17:$B$21^{1,2}),1,2)</f>
         <v>-6.4312038333706</v>
       </c>
-      <c r="D37" s="22" t="n">
+      <c r="D37" s="9" t="n">
         <f aca="false">INDEX(LINEST($X$17:$X$21,$B$17:$B$21^{1,2}),1,3)</f>
         <v>31.5905532576165</v>
       </c>
-      <c r="E37" s="22" t="n">
+      <c r="E37" s="9" t="n">
         <f aca="false">INDEX(LINEST($X$17:$X$21,$B$17:$B$21^{1,2},TRUE(),TRUE()),3,1)</f>
         <v>0.7900908008705</v>
       </c>
@@ -4621,28 +4708,28 @@
         <f aca="false">IF(AND(B37&lt;0,-C37/(2*B37)&gt;=MIN($B$17:$B$21),-C37/(2*B37)&lt;=MAX($B$17:$B$21)),-C37/(2*B37),INDEX($B$17:$B$21,MATCH(MAX($X$17:$X$21),$X$17:$X$21,0)))</f>
         <v>5.5</v>
       </c>
-      <c r="G37" s="20" t="str">
+      <c r="G37" s="21" t="str">
         <f aca="false">IF(AND(B37&lt;0,-C37/(2*B37)&gt;=MIN($B$17:$B$21),-C37/(2*B37)&lt;=MAX($B$17:$B$21)),"Máximo de la parábola","Sin máximo interior: se toma la mayor estabilidad medida")</f>
         <v>Sin máximo interior: se toma la mayor estabilidad medida</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="20" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B38" s="21" t="n">
+      <c r="B38" s="22" t="n">
         <f aca="false">INDEX(LINEST($Y$17:$Y$21,$B$17:$B$21^{1,2}),1,1)</f>
         <v>-0.0665553973786265</v>
       </c>
-      <c r="C38" s="21" t="n">
+      <c r="C38" s="22" t="n">
         <f aca="false">INDEX(LINEST($Y$17:$Y$21,$B$17:$B$21^{1,2}),1,2)</f>
         <v>1.62909528250945</v>
       </c>
-      <c r="D38" s="22" t="n">
+      <c r="D38" s="9" t="n">
         <f aca="false">INDEX(LINEST($Y$17:$Y$21,$B$17:$B$21^{1,2}),1,3)</f>
         <v>-2.94221687693289</v>
       </c>
-      <c r="E38" s="22" t="n">
+      <c r="E38" s="9" t="n">
         <f aca="false">INDEX(LINEST($Y$17:$Y$21,$B$17:$B$21^{1,2},TRUE(),TRUE()),3,1)</f>
         <v>0.998620518139559</v>
       </c>
@@ -4650,238 +4737,238 @@
         <f aca="false">IFERROR(IF(AND((-C38+SQRT(C38^2-4*B38*(D38-$K$10)))/(2*B38)&gt;=MIN($B$17:$B$21),(-C38+SQRT(C38^2-4*B38*(D38-$K$10)))/(2*B38)&lt;=MAX($B$17:$B$21)),(-C38+SQRT(C38^2-4*B38*(D38-$K$10)))/(2*B38),IF(AND((-C38-SQRT(C38^2-4*B38*(D38-$K$10)))/(2*B38)&gt;=MIN($B$17:$B$21),(-C38-SQRT(C38^2-4*B38*(D38-$K$10)))/(2*B38)&lt;=MAX($B$17:$B$21)),(-C38-SQRT(C38^2-4*B38*(D38-$K$10)))/(2*B38),"N/A")),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="G38" s="20" t="str">
+      <c r="G38" s="21" t="str">
         <f aca="false">IF(ISNUMBER(F38),"Pb para flujo máximo (límite superior de Pb)","Fuera del rango ensayado")</f>
         <v>Fuera del rango ensayado</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3" t="s">
-        <v>77</v>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="s">
+        <v>78</v>
       </c>
       <c r="F40" s="24" t="n">
         <f aca="false">AVERAGE(F33,F37,F34)</f>
-        <v>5.5</v>
-      </c>
-      <c r="G40" s="0" t="str">
+        <v>5.50338500177111</v>
+      </c>
+      <c r="G40" s="1" t="str">
         <f aca="false">IF(ISNUMBER(F34),"Promedio de 3 criterios","PROVISIONAL: solo promedio de máx. Gmb y máx. estabilidad")</f>
-        <v>PROVISIONAL: solo promedio de máx. Gmb y máx. estabilidad</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="3" t="s">
-        <v>78</v>
+        <v>Promedio de 3 criterios</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="F41" s="25" t="n">
         <f aca="false">ROUND(F40*10,0)/10</f>
         <v>5.5</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="B44" s="11" t="s">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C44" s="11" t="s">
+    </row>
+    <row r="44" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B44" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="D44" s="11" t="s">
+      <c r="C44" s="12" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="B45" s="16" t="n">
+      <c r="D44" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="17" t="n">
         <f aca="false">B33*$F$41^2+C33*$F$41+D33</f>
         <v>2.18870106667315</v>
       </c>
-      <c r="C45" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="D45" s="19" t="str">
+      <c r="C45" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="D45" s="20" t="str">
         <f aca="false">"-"</f>
         <v>-</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="19" t="s">
-        <v>73</v>
+    <row r="46" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="20" t="s">
+        <v>74</v>
       </c>
       <c r="B46" s="15" t="n">
         <f aca="false">B34*$F$41^2+C34*$F$41+D34</f>
-        <v>16.2226206759757</v>
-      </c>
-      <c r="C46" s="19" t="str">
+        <v>4.01034820144837</v>
+      </c>
+      <c r="C46" s="20" t="str">
         <f aca="false">TEXT($J$11,"0")&amp;" - "&amp;TEXT($K$11,"0")&amp;" %"</f>
         <v>3 - 5 %</v>
       </c>
-      <c r="D46" s="19" t="str">
-        <f aca="false">IF(AND(B46&gt;=$J$11,B46&lt;=$K$11),"CUMPLE","NO CUMPLE")</f>
-        <v>NO CUMPLE</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="19" t="s">
-        <v>74</v>
+      <c r="D46" s="20" t="str">
+        <f aca="false">IF(AND(ROUND(B46,1)&gt;=$J$11,ROUND(B46,1)&lt;=$K$11),"CUMPLE","NO CUMPLE")</f>
+        <v>CUMPLE</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="20" t="s">
+        <v>75</v>
       </c>
       <c r="B47" s="15" t="n">
         <f aca="false">B35*$F$41^2+C35*$F$41+D35</f>
-        <v>25.3005461725962</v>
-      </c>
-      <c r="C47" s="19" t="str">
+        <v>14.8795112559337</v>
+      </c>
+      <c r="C47" s="20" t="str">
         <f aca="false">"≥ "&amp;TEXT($J$12,"0")&amp;" %"</f>
         <v>≥ 14 %</v>
       </c>
-      <c r="D47" s="19" t="str">
-        <f aca="false">IF(B47&gt;=$J$12,"CUMPLE","NO CUMPLE")</f>
+      <c r="D47" s="20" t="str">
+        <f aca="false">IF(ROUND(B47,1)&gt;=$J$12,"CUMPLE","NO CUMPLE")</f>
         <v>CUMPLE</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="B48" s="14" t="n">
+    <row r="48" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="B48" s="15" t="n">
         <f aca="false">B36*$F$41^2+C36*$F$41+D36</f>
-        <v>35.87506141363</v>
-      </c>
-      <c r="C48" s="19" t="str">
+        <v>73.3429311270575</v>
+      </c>
+      <c r="C48" s="20" t="str">
         <f aca="false">TEXT($J$13,"0")&amp;" - "&amp;TEXT($K$13,"0")&amp;" %"</f>
         <v>65 - 78 %</v>
       </c>
-      <c r="D48" s="19" t="str">
-        <f aca="false">IF(AND(B48&gt;=$J$13,B48&lt;=$K$13),"CUMPLE","NO CUMPLE")</f>
-        <v>NO CUMPLE</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="B49" s="15" t="n">
+      <c r="D48" s="20" t="str">
+        <f aca="false">IF(AND(ROUND(B48,1)&gt;=$J$13,ROUND(B48,1)&lt;=$K$13),"CUMPLE","NO CUMPLE")</f>
+        <v>CUMPLE</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="B49" s="16" t="n">
         <f aca="false">B37*$F$41^2+C37*$F$41+D37</f>
         <v>7.97744287523311</v>
       </c>
-      <c r="C49" s="19" t="str">
+      <c r="C49" s="20" t="str">
         <f aca="false">"≥ "&amp;TEXT($J$9,"0.00")&amp;" kN"</f>
         <v>≥ 5.44 kN</v>
       </c>
-      <c r="D49" s="19" t="str">
-        <f aca="false">IF(B49&gt;=$J$9,"CUMPLE","NO CUMPLE")</f>
+      <c r="D49" s="20" t="str">
+        <f aca="false">IF(ROUND(B49,2)&gt;=$J$9,"CUMPLE","NO CUMPLE")</f>
         <v>CUMPLE</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="19" t="s">
+    <row r="50" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="20" t="s">
         <v>17</v>
       </c>
       <c r="B50" s="15" t="n">
         <f aca="false">B38*$F$41^2+C38*$F$41+D38</f>
         <v>4.00450640616563</v>
       </c>
-      <c r="C50" s="19" t="str">
+      <c r="C50" s="20" t="str">
         <f aca="false">TEXT($J$10,"0")&amp;" - "&amp;TEXT($K$10,"0")&amp;" mm"</f>
         <v>2 - 4 mm</v>
       </c>
-      <c r="D50" s="19" t="str">
-        <f aca="false">IF(AND(B50&gt;=$J$10,B50&lt;=$K$10),"CUMPLE","NO CUMPLE")</f>
-        <v>NO CUMPLE</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="B51" s="18" t="n">
+      <c r="D50" s="20" t="str">
+        <f aca="false">IF(AND(ROUND(B50,1)&gt;=$J$10,ROUND(B50,1)&lt;=$K$10),"CUMPLE","NO CUMPLE")</f>
+        <v>CUMPLE</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B51" s="19" t="n">
         <f aca="false">B49*1000/9.80665/(B50/10)</f>
         <v>2031.39338857235</v>
       </c>
-      <c r="C51" s="19" t="str">
+      <c r="C51" s="20" t="str">
         <f aca="false">TEXT($J$15,"0")&amp;" - "&amp;TEXT($K$15,"0")&amp;" kg/cm"</f>
         <v>1700 - 4000 kg/cm</v>
       </c>
-      <c r="D51" s="19" t="str">
+      <c r="D51" s="20" t="str">
         <f aca="false">IF(AND(B51&gt;=$J$15,B51&lt;=$K$15),"CUMPLE","NO CUMPLE")</f>
         <v>CUMPLE</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="B52" s="15"/>
-      <c r="C52" s="19"/>
-      <c r="D52" s="19" t="str">
+        <v>85</v>
+      </c>
+      <c r="B52" s="16"/>
+      <c r="C52" s="20"/>
+      <c r="D52" s="20" t="str">
         <f aca="false">IF(COUNTIF(D46:D51,"NO CUMPLE")=0,"CUMPLE","NO CUMPLE")</f>
-        <v>NO CUMPLE</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>CUMPLE</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="27" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
         <v>95</v>
       </c>
     </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="A1:Z1"/>
     <mergeCell ref="A2:Z2"/>
     <mergeCell ref="A9:C9"/>
@@ -4896,6 +4983,7 @@
     <mergeCell ref="G13:I13"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="G14:I14"/>
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="G15:I15"/>
   </mergeCells>
   <conditionalFormatting sqref="C25:J29">
@@ -4946,9 +5034,9 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -4971,282 +5059,282 @@
   <dimension ref="A1:D34"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="D1" s="4" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="n">
+      <c r="D1" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="21" t="n">
         <v>25.4</v>
       </c>
-      <c r="B2" s="20" t="n">
+      <c r="B2" s="21" t="n">
         <v>5.56</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="20" t="n">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="21" t="n">
         <v>27</v>
       </c>
-      <c r="B3" s="20" t="n">
+      <c r="B3" s="21" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="20" t="n">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="21" t="n">
         <v>28.6</v>
       </c>
-      <c r="B4" s="20" t="n">
+      <c r="B4" s="21" t="n">
         <v>4.55</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="n">
         <v>30.2</v>
       </c>
-      <c r="B5" s="20" t="n">
+      <c r="B5" s="21" t="n">
         <v>4.17</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="n">
         <v>31.8</v>
       </c>
-      <c r="B6" s="20" t="n">
+      <c r="B6" s="21" t="n">
         <v>3.85</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="n">
         <v>33.3</v>
       </c>
-      <c r="B7" s="20" t="n">
+      <c r="B7" s="21" t="n">
         <v>3.57</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="20" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="21" t="n">
         <v>34.9</v>
       </c>
-      <c r="B8" s="20" t="n">
+      <c r="B8" s="21" t="n">
         <v>3.33</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="21" t="n">
         <v>36.5</v>
       </c>
-      <c r="B9" s="20" t="n">
+      <c r="B9" s="21" t="n">
         <v>3.03</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="21" t="n">
         <v>38.1</v>
       </c>
-      <c r="B10" s="20" t="n">
+      <c r="B10" s="21" t="n">
         <v>2.78</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="21" t="n">
         <v>39.7</v>
       </c>
-      <c r="B11" s="20" t="n">
+      <c r="B11" s="21" t="n">
         <v>2.5</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="21" t="n">
         <v>41.3</v>
       </c>
-      <c r="B12" s="20" t="n">
+      <c r="B12" s="21" t="n">
         <v>2.27</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="21" t="n">
         <v>42.9</v>
       </c>
-      <c r="B13" s="20" t="n">
+      <c r="B13" s="21" t="n">
         <v>2.08</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="20" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="21" t="n">
         <v>44.4</v>
       </c>
-      <c r="B14" s="20" t="n">
+      <c r="B14" s="21" t="n">
         <v>1.92</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="20" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="21" t="n">
         <v>46</v>
       </c>
-      <c r="B15" s="20" t="n">
+      <c r="B15" s="21" t="n">
         <v>1.79</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="20" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="21" t="n">
         <v>47.6</v>
       </c>
-      <c r="B16" s="20" t="n">
+      <c r="B16" s="21" t="n">
         <v>1.67</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="20" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="21" t="n">
         <v>49.2</v>
       </c>
-      <c r="B17" s="20" t="n">
+      <c r="B17" s="21" t="n">
         <v>1.56</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="20" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="21" t="n">
         <v>50.8</v>
       </c>
-      <c r="B18" s="20" t="n">
+      <c r="B18" s="21" t="n">
         <v>1.47</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="20" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="21" t="n">
         <v>52.4</v>
       </c>
-      <c r="B19" s="20" t="n">
+      <c r="B19" s="21" t="n">
         <v>1.39</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="20" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="21" t="n">
         <v>54</v>
       </c>
-      <c r="B20" s="20" t="n">
+      <c r="B20" s="21" t="n">
         <v>1.32</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="20" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="21" t="n">
         <v>55.6</v>
       </c>
-      <c r="B21" s="20" t="n">
+      <c r="B21" s="21" t="n">
         <v>1.25</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="20" t="n">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="21" t="n">
         <v>57.2</v>
       </c>
-      <c r="B22" s="20" t="n">
+      <c r="B22" s="21" t="n">
         <v>1.19</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="20" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="21" t="n">
         <v>58.7</v>
       </c>
-      <c r="B23" s="20" t="n">
+      <c r="B23" s="21" t="n">
         <v>1.14</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="20" t="n">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="21" t="n">
         <v>60.3</v>
       </c>
-      <c r="B24" s="20" t="n">
+      <c r="B24" s="21" t="n">
         <v>1.09</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="20" t="n">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="21" t="n">
         <v>61.9</v>
       </c>
-      <c r="B25" s="20" t="n">
+      <c r="B25" s="21" t="n">
         <v>1.04</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="20" t="n">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="21" t="n">
         <v>63.5</v>
       </c>
-      <c r="B26" s="20" t="n">
+      <c r="B26" s="21" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="20" t="n">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="21" t="n">
         <v>65.1</v>
       </c>
-      <c r="B27" s="20" t="n">
+      <c r="B27" s="21" t="n">
         <v>0.96</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="20" t="n">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="21" t="n">
         <v>66.7</v>
       </c>
-      <c r="B28" s="20" t="n">
+      <c r="B28" s="21" t="n">
         <v>0.93</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="20" t="n">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="21" t="n">
         <v>68.3</v>
       </c>
-      <c r="B29" s="20" t="n">
+      <c r="B29" s="21" t="n">
         <v>0.89</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="20" t="n">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="21" t="n">
         <v>69.9</v>
       </c>
-      <c r="B30" s="20" t="n">
+      <c r="B30" s="21" t="n">
         <v>0.86</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="20" t="n">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="21" t="n">
         <v>71.4</v>
       </c>
-      <c r="B31" s="20" t="n">
+      <c r="B31" s="21" t="n">
         <v>0.83</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="20" t="n">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="21" t="n">
         <v>73</v>
       </c>
-      <c r="B32" s="20" t="n">
+      <c r="B32" s="21" t="n">
         <v>0.81</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="20" t="n">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="21" t="n">
         <v>74.6</v>
       </c>
-      <c r="B33" s="20" t="n">
+      <c r="B33" s="21" t="n">
         <v>0.78</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="20" t="n">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="21" t="n">
         <v>76.2</v>
       </c>
-      <c r="B34" s="20" t="n">
+      <c r="B34" s="21" t="n">
         <v>0.76</v>
       </c>
     </row>

--- a/marshall/Diseno_Marshall_MAC2_PEN120_150_corregido.xlsx
+++ b/marshall/Diseno_Marshall_MAC2_PEN120_150_corregido.xlsx
@@ -11,7 +11,11 @@
     <sheet name="Diseno_Marshall" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Graficas_Marshall" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Factor_Altura" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Datos_Graficas" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Graficas_Marshall!$A$1:$T$75</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -140,7 +144,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="123">
   <si>
     <t xml:space="preserve">LABORATORIO DE ASFALTOS</t>
   </si>
@@ -459,7 +463,34 @@
     <t xml:space="preserve">10. Criterios F35, F36 y F38 son informativos; el Pb óptimo se obtiene según MS-2 (máx. Gmb, máx. estabilidad, Va objetivo).</t>
   </si>
   <si>
-    <t xml:space="preserve">DISEÑO DE MEZCLAS ASFÁLTICAS EN CALIENTE - GRÁFICAS MARSHALL</t>
+    <t xml:space="preserve">DISEÑO DE MEZCLAS ASFÁLTICAS EN CALIENTE - MÉTODO MARSHALL: CURVAS DE DISEÑO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cómo leer las gráficas:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor en Pb de diseño</t>
+  </si>
+  <si>
+    <t xml:space="preserve">●  Círculos: briquetas ensayadas (M1-M5).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">━  Línea continua: ajuste parabólico (criterio MS-2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- -  Línea roja discontinua: límites de especificación (EG-2013 / MS-2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">┆  Línea gris: Pb de diseño adoptado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">◆  Rombo amarillo: valor de la propiedad en el Pb de diseño.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nota: Gsb y Gmm son valores supuestos (ver observación 8 en Diseno_Marshall).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DISEÑO GLOBAL</t>
   </si>
   <si>
     <t xml:space="preserve">Altura (mm)</t>
@@ -469,6 +500,45 @@
   </si>
   <si>
     <t xml:space="preserve">Fuente: MTC E 504 / ASTM D6927 (interpolación lineal).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Datos auxiliares para las gráficas (no editar: todo es fórmula enlazada a Diseno_Marshall)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gmb ajustado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Va ajustado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VMA ajustado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VFA ajustado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estabilidad ajustado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flujo ajustado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gmb: líneas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Va: líneas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VMA: líneas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VFA: líneas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estabilidad: líneas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flujo: líneas</t>
   </si>
 </sst>
 </file>
@@ -484,7 +554,7 @@
     <numFmt numFmtId="169" formatCode="0"/>
     <numFmt numFmtId="170" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -551,33 +621,100 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="13"/>
-      <name val="Cambria"/>
+      <sz val="15"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="11"/>
+      <color rgb="FF1F3864"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF404040"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF1F3864"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF404040"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="13"/>
+      <color rgb="FF1F3864"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="9"/>
+      <color rgb="FF404040"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF404040"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF404040"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -587,7 +724,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
-        <bgColor rgb="FF003366"/>
+        <bgColor rgb="FF1F4E79"/>
       </patternFill>
     </fill>
     <fill>
@@ -599,7 +736,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
-        <bgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFE7E6E6"/>
       </patternFill>
     </fill>
     <fill>
@@ -611,11 +748,23 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE2EFDA"/>
-        <bgColor rgb="FFD9E1F2"/>
+        <bgColor rgb="FFE7E6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+        <bgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E75B6"/>
+        <bgColor rgb="FF008080"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -635,6 +784,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFA6A6A6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFA6A6A6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA6A6A6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA6A6A6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -664,7 +828,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="50">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -777,11 +941,91 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -794,7 +1038,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="7">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -838,12 +1082,34 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FFC00000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -852,19 +1118,19 @@
       <rgbColor rgb="FF9C0006"/>
       <rgbColor rgb="FF006100"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF548235"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FFBFBFBF"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF7030A0"/>
       <rgbColor rgb="FFFFF2CC"/>
       <rgbColor rgb="FFE2EFDA"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD9D9D9"/>
+      <rgbColor rgb="FF1F4E78"/>
+      <rgbColor rgb="FFD9E1F2"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -874,29 +1140,29 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFD9E1F2"/>
+      <rgbColor rgb="FFE7E6E6"/>
       <rgbColor rgb="FFC6EFCE"/>
       <rgbColor rgb="FFFCE4D6"/>
-      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFBFBFB"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFC7CE"/>
-      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF2E75B6"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF878787"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FFFFC000"/>
+      <rgbColor rgb="FFBF9000"/>
+      <rgbColor rgb="FFC55A11"/>
+      <rgbColor rgb="FF595959"/>
+      <rgbColor rgb="FFA6A6A6"/>
+      <rgbColor rgb="FF1F3864"/>
+      <rgbColor rgb="FF7F7F7F"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF1F4E78"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="FF1F4E79"/>
+      <rgbColor rgb="FF404040"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -914,21 +1180,21 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr b="1" sz="1300" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="1f3864"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr b="1" sz="1300" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="1f3864"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>Peso específico Gmb vs %CA</a:t>
+              <a:t>Gmb vs contenido de asfalto</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -951,18 +1217,277 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Gmb"</c:f>
+              <c:f>"Ajuste polinómico (2.º grado)"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Gmb</c:v>
+                  <c:v>Ajuste polinómico (2.º grado)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="ffffff"/>
+              <a:srgbClr val="1f4e79"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="1f4e79"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$A$4:$A$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.65</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.95</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6.4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.55</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6.85</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7.15</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>7.3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>7.45</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>7.6</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>7.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7.9</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8.05</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>8.2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8.35</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>8.65</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>8.8</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>8.95</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>9.1</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>9.25</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>9.4</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>9.55</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>9.7</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>9.85</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$B$4:$B$34</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>2.18870106667315</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.18789535266774</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.18711795916989</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.18636888617959</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.18564813369684</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.18495570172164</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.18429159025398</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.18365579929388</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.18304832884132</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.18246917889632</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.18191834945886</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.18139584052895</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.1809016521066</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.18043578419179</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.17999823678453</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.17958900988482</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.17920810349266</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.17885551760805</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.17853125223099</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.17823530736148</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.17796768299951</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2.1777283791451</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2.17751739579824</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.17733473295892</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.17718039062716</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.17705436880294</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2.17695666748628</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2.17688728667716</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2.17684622637559</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2.17683348658157</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2.17684906729511</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Briquetas ensayadas"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Briquetas ensayadas</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="1f4e79"/>
             </a:solidFill>
             <a:ln w="28440">
               <a:noFill/>
@@ -970,33 +1495,31 @@
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
-            <c:size val="7"/>
+            <c:size val="8"/>
             <c:spPr>
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="1f4e79"/>
+              </a:solidFill>
             </c:spPr>
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -1004,22 +1527,6 @@
               </c:ext>
             </c:extLst>
           </c:dLbls>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="9360">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-            </c:spPr>
-            <c:trendlineType val="poly"/>
-            <c:order val="2"/>
-            <c:forward val="0"/>
-            <c:backward val="0"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>Diseno_Marshall!$B$17:$B$21</c:f>
@@ -1070,11 +1577,179 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="32688365"/>
-        <c:axId val="43452834"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Pb de diseño"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Pb de diseño</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="595959"/>
+            </a:solidFill>
+            <a:ln w="15840">
+              <a:solidFill>
+                <a:srgbClr val="595959"/>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$B$40:$B$41</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$C$40:$C$41</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>2.15946205571566</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.20736434108527</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Valor en Pb de diseño"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Valor en Pb de diseño</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ffc000"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="11"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="ffc000"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$B$43</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>5.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$C$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2.18870106667315</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:axId val="32058585"/>
+        <c:axId val="22537604"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="32688365"/>
+        <c:axId val="32058585"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -1084,9 +1759,9 @@
         <c:axPos val="b"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9360">
+            <a:ln w="6480">
               <a:solidFill>
-                <a:srgbClr val="878787"/>
+                <a:srgbClr val="e7e6e6"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1101,7 +1776,7 @@
                 <a:pPr>
                   <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="404040"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
@@ -1109,11 +1784,11 @@
                 <a:r>
                   <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="404040"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
-                  <a:t>Contenido de asfalto (%)</a:t>
+                  <a:t>Contenido de asfalto Pb (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -1127,13 +1802,13 @@
           </c:spPr>
         </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="878787"/>
+              <a:srgbClr val="7f7f7f"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -1143,21 +1818,22 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="404040"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43452834"/>
-        <c:crosses val="autoZero"/>
+        <c:crossAx val="22537604"/>
+        <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="43452834"/>
+        <c:axId val="22537604"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1165,9 +1841,9 @@
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9360">
+            <a:ln w="6480">
               <a:solidFill>
-                <a:srgbClr val="878787"/>
+                <a:srgbClr val="e7e6e6"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1182,7 +1858,7 @@
                 <a:pPr>
                   <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="404040"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
@@ -1190,11 +1866,11 @@
                 <a:r>
                   <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="404040"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
-                  <a:t>Gmb</a:t>
+                  <a:t>Gmb (g/cm³)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -1208,13 +1884,13 @@
           </c:spPr>
         </c:title>
         <c:numFmt formatCode="0.000" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="878787"/>
+              <a:srgbClr val="7f7f7f"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -1224,26 +1900,52 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="404040"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32688365"/>
-        <c:crosses val="autoZero"/>
+        <c:crossAx val="32058585"/>
+        <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="fbfbfb"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
       </c:spPr>
-    </c:plotArea>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="800" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
   </c:chart>
@@ -1253,7 +1955,7 @@
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="bfbfbf"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
@@ -1273,21 +1975,21 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr b="1" sz="1300" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="1f3864"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr b="1" sz="1300" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="1f3864"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>% Vacíos en la mezcla vs %CA</a:t>
+              <a:t>Vacíos de aire Va vs contenido de asfalto</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1310,18 +2012,277 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Va (%)"</c:f>
+              <c:f>"Ajuste polinómico (2.º grado)"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Va (%)</c:v>
+                  <c:v>Ajuste polinómico (2.º grado)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="ffffff"/>
+              <a:srgbClr val="c55a11"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="c55a11"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$A$4:$A$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.65</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.95</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6.4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.55</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6.85</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7.15</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>7.3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>7.45</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>7.6</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>7.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7.9</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8.05</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>8.2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8.35</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>8.65</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>8.8</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>8.95</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>9.1</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>9.25</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>9.4</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>9.55</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>9.7</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>9.85</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$D$4:$D$34</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>4.01034820144837</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.85699523095454</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.70257122650614</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.54707618810316</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.39051011574561</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.23287300943348</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.07416486916676</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.91438569494548</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.75353548676961</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.59161424463917</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.42862196855415</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.26455865851456</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.09942431452038</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.93321893657163</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.76594252466831</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.5975950788104</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.42817659899792</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.25768708523086</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.08612653750923</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.913494955833012</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.739792340202222</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.565018690616853</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.389174007076909</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.212258289582387</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.0342715381332894</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-0.144786247270387</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-0.324915066628643</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-0.506114919941473</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-0.68838580720888</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-0.871727728430864</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-1.05614068360743</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Briquetas ensayadas"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Briquetas ensayadas</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="c55a11"/>
             </a:solidFill>
             <a:ln w="28440">
               <a:noFill/>
@@ -1329,33 +2290,31 @@
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
-            <c:size val="7"/>
+            <c:size val="8"/>
             <c:spPr>
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="c55a11"/>
+              </a:solidFill>
             </c:spPr>
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -1363,22 +2322,6 @@
               </c:ext>
             </c:extLst>
           </c:dLbls>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="9360">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-            </c:spPr>
-            <c:trendlineType val="poly"/>
-            <c:order val="2"/>
-            <c:forward val="0"/>
-            <c:backward val="0"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>Diseno_Marshall!$B$17:$B$21</c:f>
@@ -1429,11 +2372,351 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="29986720"/>
-        <c:axId val="98232500"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Especificación mín"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Especificación mín</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="c00000"/>
+            </a:solidFill>
+            <a:ln w="19080">
+              <a:solidFill>
+                <a:srgbClr val="c00000"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$D$45:$D$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$E$45:$E$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Especificación máx"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Especificación máx</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="c00000"/>
+            </a:solidFill>
+            <a:ln w="19080">
+              <a:solidFill>
+                <a:srgbClr val="c00000"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$D$48:$D$49</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$E$48:$E$49</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Pb de diseño"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Pb de diseño</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="595959"/>
+            </a:solidFill>
+            <a:ln w="15840">
+              <a:solidFill>
+                <a:srgbClr val="595959"/>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$D$40:$D$41</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$E$40:$E$41</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>-1.05614068360743</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Valor en Pb de diseño"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Valor en Pb de diseño</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ffc000"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="11"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="ffc000"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$D$43</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>5.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$E$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>4.01034820144837</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:axId val="3626051"/>
+        <c:axId val="24672438"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="29986720"/>
+        <c:axId val="3626051"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -1443,9 +2726,9 @@
         <c:axPos val="b"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9360">
+            <a:ln w="6480">
               <a:solidFill>
-                <a:srgbClr val="878787"/>
+                <a:srgbClr val="e7e6e6"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1460,7 +2743,7 @@
                 <a:pPr>
                   <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="404040"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
@@ -1468,11 +2751,11 @@
                 <a:r>
                   <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="404040"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
-                  <a:t>Contenido de asfalto (%)</a:t>
+                  <a:t>Contenido de asfalto Pb (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -1486,13 +2769,13 @@
           </c:spPr>
         </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="878787"/>
+              <a:srgbClr val="7f7f7f"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -1502,21 +2785,22 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="404040"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="98232500"/>
-        <c:crosses val="autoZero"/>
+        <c:crossAx val="24672438"/>
+        <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="98232500"/>
+        <c:axId val="24672438"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1524,9 +2808,9 @@
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9360">
+            <a:ln w="6480">
               <a:solidFill>
-                <a:srgbClr val="878787"/>
+                <a:srgbClr val="e7e6e6"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1541,7 +2825,7 @@
                 <a:pPr>
                   <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="404040"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
@@ -1549,11 +2833,11 @@
                 <a:r>
                   <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="404040"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
-                  <a:t>Va (%)</a:t>
+                  <a:t>Vacíos de aire Va (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -1566,14 +2850,14 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0.00" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="878787"/>
+              <a:srgbClr val="7f7f7f"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -1583,26 +2867,52 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="404040"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29986720"/>
-        <c:crosses val="autoZero"/>
+        <c:crossAx val="3626051"/>
+        <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="fbfbfb"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
       </c:spPr>
-    </c:plotArea>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="800" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
   </c:chart>
@@ -1612,7 +2922,7 @@
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="bfbfbf"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
@@ -1632,21 +2942,21 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr b="1" sz="1300" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="1f3864"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr b="1" sz="1300" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="1f3864"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>% VMA vs %CA</a:t>
+              <a:t>VMA vs contenido de asfalto</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1669,18 +2979,277 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>"VMA (%)"</c:f>
+              <c:f>"Ajuste polinómico (2.º grado)"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>VMA (%)</c:v>
+                  <c:v>Ajuste polinómico (2.º grado)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="ffffff"/>
+              <a:srgbClr val="548235"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="548235"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$A$4:$A$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.65</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.95</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6.4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.55</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6.85</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7.15</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>7.3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>7.45</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>7.6</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>7.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7.9</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8.05</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>8.2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8.35</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>8.65</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>8.8</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>8.95</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>9.1</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>9.25</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>9.4</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>9.55</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>9.7</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>9.85</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$F$4:$F$34</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>14.8795112559337</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15.0470055443678</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15.213275017413</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15.3783196750692</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15.5421395173365</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15.704734544215</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>15.8661047557044</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16.026250151805</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16.1851707325167</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>16.3428664978394</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>16.4993374477732</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>16.6545835823181</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>16.8086049014741</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>16.9614014052411</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>17.1129730936192</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17.2633199666084</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17.4124420242087</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17.5603392664201</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>17.7070116932425</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>17.8524593046761</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>17.9966821007207</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>18.1396800813763</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>18.2814532466431</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>18.422001596521</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>18.5613251310099</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>18.6994238501099</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>18.836297753821</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>18.9719468421431</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>19.1063711150764</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>19.2395705726207</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>19.3715452147761</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Briquetas ensayadas"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Briquetas ensayadas</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="548235"/>
             </a:solidFill>
             <a:ln w="28440">
               <a:noFill/>
@@ -1688,33 +3257,31 @@
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
-            <c:size val="7"/>
+            <c:size val="8"/>
             <c:spPr>
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="548235"/>
+              </a:solidFill>
             </c:spPr>
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -1722,22 +3289,6 @@
               </c:ext>
             </c:extLst>
           </c:dLbls>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="9360">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-            </c:spPr>
-            <c:trendlineType val="poly"/>
-            <c:order val="2"/>
-            <c:forward val="0"/>
-            <c:backward val="0"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>Diseno_Marshall!$B$17:$B$21</c:f>
@@ -1788,11 +3339,265 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="63184166"/>
-        <c:axId val="37706179"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Especificación mín"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Especificación mín</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="c00000"/>
+            </a:solidFill>
+            <a:ln w="19080">
+              <a:solidFill>
+                <a:srgbClr val="c00000"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$F$45:$F$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$G$45:$G$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Pb de diseño"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Pb de diseño</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="595959"/>
+            </a:solidFill>
+            <a:ln w="15840">
+              <a:solidFill>
+                <a:srgbClr val="595959"/>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$F$40:$F$41</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$G$40:$G$41</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>19.4817528150862</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Valor en Pb de diseño"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Valor en Pb de diseño</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ffc000"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="11"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="ffc000"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$F$43</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>5.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$G$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>14.8795112559337</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:axId val="90983968"/>
+        <c:axId val="91180994"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="63184166"/>
+        <c:axId val="90983968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -1802,9 +3607,9 @@
         <c:axPos val="b"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9360">
+            <a:ln w="6480">
               <a:solidFill>
-                <a:srgbClr val="878787"/>
+                <a:srgbClr val="e7e6e6"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1819,7 +3624,7 @@
                 <a:pPr>
                   <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="404040"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
@@ -1827,11 +3632,11 @@
                 <a:r>
                   <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="404040"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
-                  <a:t>Contenido de asfalto (%)</a:t>
+                  <a:t>Contenido de asfalto Pb (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -1845,13 +3650,13 @@
           </c:spPr>
         </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="878787"/>
+              <a:srgbClr val="7f7f7f"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -1861,21 +3666,22 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="404040"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37706179"/>
-        <c:crosses val="autoZero"/>
+        <c:crossAx val="91180994"/>
+        <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="37706179"/>
+        <c:axId val="91180994"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1883,9 +3689,9 @@
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9360">
+            <a:ln w="6480">
               <a:solidFill>
-                <a:srgbClr val="878787"/>
+                <a:srgbClr val="e7e6e6"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1900,7 +3706,7 @@
                 <a:pPr>
                   <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="404040"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
@@ -1908,7 +3714,7 @@
                 <a:r>
                   <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="404040"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
@@ -1925,14 +3731,14 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0.00" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="878787"/>
+              <a:srgbClr val="7f7f7f"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -1942,26 +3748,52 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="404040"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63184166"/>
-        <c:crosses val="autoZero"/>
+        <c:crossAx val="90983968"/>
+        <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="fbfbfb"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
       </c:spPr>
-    </c:plotArea>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="800" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
   </c:chart>
@@ -1971,7 +3803,7 @@
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="bfbfbf"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
@@ -1991,21 +3823,21 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr b="1" sz="1300" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="1f3864"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr b="1" sz="1300" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="1f3864"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>% VFA vs %CA</a:t>
+              <a:t>VFA vs contenido de asfalto</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2028,18 +3860,277 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>"VFA (%)"</c:f>
+              <c:f>"Ajuste polinómico (2.º grado)"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>VFA (%)</c:v>
+                  <c:v>Ajuste polinómico (2.º grado)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="ffffff"/>
+              <a:srgbClr val="7030a0"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="7030a0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$A$4:$A$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.65</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.95</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6.4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.55</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6.85</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7.15</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>7.3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>7.45</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>7.6</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>7.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7.9</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8.05</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>8.2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8.35</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>8.65</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>8.8</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>8.95</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>9.1</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>9.25</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>9.4</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>9.55</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>9.7</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>9.85</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$H$4:$H$34</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>73.3429311270575</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>74.6055150641918</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>75.8547592833012</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>77.0906637843856</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>78.3132285674452</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>79.5224536324798</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>80.7183389794896</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>81.9008846084744</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>83.0700905194343</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>84.2259567123693</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>85.3684831872794</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>86.4976699441645</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>87.6135169830248</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>88.7160243038601</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>89.8051919066706</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>90.8810197914561</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>91.9435079582167</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>92.9926564069524</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>94.0284651376631</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>95.050934150349</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>96.0600634450099</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>97.055853021646</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>98.0383028802571</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>99.0074130208433</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>99.9631834434046</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>100.905614147941</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>101.834705134452</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>102.750456402939</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>103.652867953401</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>104.541939785837</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>105.417671900249</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Briquetas ensayadas"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Briquetas ensayadas</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="7030a0"/>
             </a:solidFill>
             <a:ln w="28440">
               <a:noFill/>
@@ -2047,33 +4138,31 @@
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
-            <c:size val="7"/>
+            <c:size val="8"/>
             <c:spPr>
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="7030a0"/>
+              </a:solidFill>
             </c:spPr>
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -2081,22 +4170,6 @@
               </c:ext>
             </c:extLst>
           </c:dLbls>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="9360">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-            </c:spPr>
-            <c:trendlineType val="poly"/>
-            <c:order val="2"/>
-            <c:forward val="0"/>
-            <c:backward val="0"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>Diseno_Marshall!$B$17:$B$21</c:f>
@@ -2147,11 +4220,351 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="32264263"/>
-        <c:axId val="78758385"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Especificación mín"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Especificación mín</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="c00000"/>
+            </a:solidFill>
+            <a:ln w="19080">
+              <a:solidFill>
+                <a:srgbClr val="c00000"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$H$45:$H$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$I$45:$I$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>65</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Especificación máx"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Especificación máx</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="c00000"/>
+            </a:solidFill>
+            <a:ln w="19080">
+              <a:solidFill>
+                <a:srgbClr val="c00000"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$H$48:$H$49</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$I$48:$I$49</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>78</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Pb de diseño"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Pb de diseño</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="595959"/>
+            </a:solidFill>
+            <a:ln w="15840">
+              <a:solidFill>
+                <a:srgbClr val="595959"/>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$H$40:$H$41</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$I$40:$I$41</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>105.417671900249</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Valor en Pb de diseño"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Valor en Pb de diseño</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ffc000"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="11"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="ffc000"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$H$43</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>5.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$I$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>73.3429311270575</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:axId val="87386086"/>
+        <c:axId val="71383002"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="32264263"/>
+        <c:axId val="87386086"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -2161,9 +4574,9 @@
         <c:axPos val="b"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9360">
+            <a:ln w="6480">
               <a:solidFill>
-                <a:srgbClr val="878787"/>
+                <a:srgbClr val="e7e6e6"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2178,7 +4591,7 @@
                 <a:pPr>
                   <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="404040"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
@@ -2186,11 +4599,11 @@
                 <a:r>
                   <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="404040"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
-                  <a:t>Contenido de asfalto (%)</a:t>
+                  <a:t>Contenido de asfalto Pb (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -2204,13 +4617,13 @@
           </c:spPr>
         </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="878787"/>
+              <a:srgbClr val="7f7f7f"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -2220,21 +4633,22 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="404040"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78758385"/>
-        <c:crosses val="autoZero"/>
+        <c:crossAx val="71383002"/>
+        <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="78758385"/>
+        <c:axId val="71383002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2242,9 +4656,9 @@
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9360">
+            <a:ln w="6480">
               <a:solidFill>
-                <a:srgbClr val="878787"/>
+                <a:srgbClr val="e7e6e6"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2259,7 +4673,7 @@
                 <a:pPr>
                   <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="404040"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
@@ -2267,7 +4681,7 @@
                 <a:r>
                   <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="404040"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
@@ -2285,13 +4699,13 @@
           </c:spPr>
         </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="878787"/>
+              <a:srgbClr val="7f7f7f"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -2301,26 +4715,52 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="404040"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32264263"/>
-        <c:crosses val="autoZero"/>
+        <c:crossAx val="87386086"/>
+        <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="fbfbfb"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
       </c:spPr>
-    </c:plotArea>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="800" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
   </c:chart>
@@ -2330,7 +4770,7 @@
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="bfbfbf"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
@@ -2350,21 +4790,21 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr b="1" sz="1300" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="1f3864"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr b="1" sz="1300" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="1f3864"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>Estabilidad vs %CA</a:t>
+              <a:t>Estabilidad vs contenido de asfalto</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2387,18 +4827,277 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Estabilidad (kN)"</c:f>
+              <c:f>"Ajuste polinómico (2.º grado)"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Estabilidad (kN)</c:v>
+                  <c:v>Ajuste polinómico (2.º grado)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="ffffff"/>
+              <a:srgbClr val="2e75b6"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="2e75b6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$A$4:$A$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.65</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.95</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6.4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.55</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6.85</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7.15</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>7.3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>7.45</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>7.6</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>7.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7.9</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8.05</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>8.2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8.35</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>8.65</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>8.8</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>8.95</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>9.1</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>9.25</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>9.4</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>9.55</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>9.7</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>9.85</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$J$4:$J$34</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>7.97744287523311</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.66288161089468</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.3658123459464</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.08623508038827</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.82414981422028</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.57955654744245</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6.35245528005476</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.14284601205722</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.95072874344983</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.77610347423259</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5.61897020440549</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.47932893396854</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.35717966292174</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.25252239126509</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.16535711899859</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5.09568384612222</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5.04350257263601</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5.00881329853996</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4.99161602383404</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4.99191074851828</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5.00969747259266</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>5.04497619605719</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>5.09774691891186</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>5.16800964115669</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>5.25576436279166</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>5.36101108381679</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>5.48374980423206</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>5.62398052403748</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>5.78170324323304</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>5.95691796181875</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>6.14962467979462</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Briquetas ensayadas"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Briquetas ensayadas</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="2e75b6"/>
             </a:solidFill>
             <a:ln w="28440">
               <a:noFill/>
@@ -2406,33 +5105,31 @@
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
-            <c:size val="7"/>
+            <c:size val="8"/>
             <c:spPr>
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="2e75b6"/>
+              </a:solidFill>
             </c:spPr>
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -2440,22 +5137,6 @@
               </c:ext>
             </c:extLst>
           </c:dLbls>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="9360">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-            </c:spPr>
-            <c:trendlineType val="poly"/>
-            <c:order val="2"/>
-            <c:forward val="0"/>
-            <c:backward val="0"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>Diseno_Marshall!$B$17:$B$21</c:f>
@@ -2506,11 +5187,265 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="67791681"/>
-        <c:axId val="35850085"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Especificación mín"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Especificación mín</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="c00000"/>
+            </a:solidFill>
+            <a:ln w="19080">
+              <a:solidFill>
+                <a:srgbClr val="c00000"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$J$45:$J$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$K$45:$K$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>5.44</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.44</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Pb de diseño"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Pb de diseño</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="595959"/>
+            </a:solidFill>
+            <a:ln w="15840">
+              <a:solidFill>
+                <a:srgbClr val="595959"/>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$J$40:$J$41</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$K$40:$K$41</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>4.9686005140625</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.3430442624375</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Valor en Pb de diseño"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Valor en Pb de diseño</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ffc000"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="11"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="ffc000"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$J$43</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>5.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$K$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>7.97744287523311</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:axId val="17333692"/>
+        <c:axId val="85536873"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="67791681"/>
+        <c:axId val="17333692"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -2520,9 +5455,9 @@
         <c:axPos val="b"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9360">
+            <a:ln w="6480">
               <a:solidFill>
-                <a:srgbClr val="878787"/>
+                <a:srgbClr val="e7e6e6"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2537,7 +5472,7 @@
                 <a:pPr>
                   <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="404040"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
@@ -2545,11 +5480,11 @@
                 <a:r>
                   <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="404040"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
-                  <a:t>Contenido de asfalto (%)</a:t>
+                  <a:t>Contenido de asfalto Pb (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -2563,13 +5498,13 @@
           </c:spPr>
         </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="878787"/>
+              <a:srgbClr val="7f7f7f"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -2579,21 +5514,22 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="404040"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35850085"/>
-        <c:crosses val="autoZero"/>
+        <c:crossAx val="85536873"/>
+        <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="35850085"/>
+        <c:axId val="85536873"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2601,9 +5537,9 @@
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9360">
+            <a:ln w="6480">
               <a:solidFill>
-                <a:srgbClr val="878787"/>
+                <a:srgbClr val="e7e6e6"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2618,7 +5554,7 @@
                 <a:pPr>
                   <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="404040"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
@@ -2626,7 +5562,7 @@
                 <a:r>
                   <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="404040"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
@@ -2644,13 +5580,13 @@
           </c:spPr>
         </c:title>
         <c:numFmt formatCode="0.00" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="878787"/>
+              <a:srgbClr val="7f7f7f"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -2660,26 +5596,52 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="404040"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67791681"/>
-        <c:crosses val="autoZero"/>
+        <c:crossAx val="17333692"/>
+        <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="fbfbfb"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
       </c:spPr>
-    </c:plotArea>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="800" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
   </c:chart>
@@ -2689,7 +5651,7 @@
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="bfbfbf"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
@@ -2709,21 +5671,21 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr b="1" sz="1300" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="1f3864"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr b="1" sz="1300" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="1f3864"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>Flujo vs %CA</a:t>
+              <a:t>Flujo vs contenido de asfalto</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2746,18 +5708,277 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Flujo (mm)"</c:f>
+              <c:f>"Ajuste polinómico (2.º grado)"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Flujo (mm)</c:v>
+                  <c:v>Ajuste polinómico (2.º grado)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="ffffff"/>
+              <a:srgbClr val="bf9000"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="bf9000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$A$4:$A$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.65</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.95</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6.4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.55</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6.85</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7.15</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>7.3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>7.45</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>7.6</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>7.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7.9</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8.05</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>8.2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8.35</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>8.65</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>8.8</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>8.95</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>9.1</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>9.25</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>9.4</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>9.55</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>9.7</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>9.85</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$L$4:$L$34</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>4.00450640616563</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.13755679642629</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.26761219380492</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.39467259830151</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.51873800991606</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.63980842864857</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.75788385449904</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.87296428746748</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.98504972755388</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.09414017475823</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5.20023562908055</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.30333609052084</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.40344155907908</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.50055203475529</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.59466751754946</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5.68578800746159</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5.77391350449168</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5.85904400863973</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5.94117951990575</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>6.02032003828972</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6.09646556379166</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>6.16961609641156</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6.23977163614943</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6.30693218300525</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6.37109773697904</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>6.43226829807079</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>6.4904438662805</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>6.54562444160817</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>6.5978100240538</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>6.6470006136174</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>6.69319621029896</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Briquetas ensayadas"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Briquetas ensayadas</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="bf9000"/>
             </a:solidFill>
             <a:ln w="28440">
               <a:noFill/>
@@ -2765,33 +5986,31 @@
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
-            <c:size val="7"/>
+            <c:size val="8"/>
             <c:spPr>
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="bf9000"/>
+              </a:solidFill>
             </c:spPr>
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -2799,22 +6018,6 @@
               </c:ext>
             </c:extLst>
           </c:dLbls>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="9360">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-            </c:spPr>
-            <c:trendlineType val="poly"/>
-            <c:order val="2"/>
-            <c:forward val="0"/>
-            <c:backward val="0"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>Diseno_Marshall!$B$17:$B$21</c:f>
@@ -2865,11 +6068,351 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="5494799"/>
-        <c:axId val="80998796"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Especificación mín"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Especificación mín</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="c00000"/>
+            </a:solidFill>
+            <a:ln w="19080">
+              <a:solidFill>
+                <a:srgbClr val="c00000"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$L$45:$L$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$M$45:$M$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Especificación máx"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Especificación máx</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="c00000"/>
+            </a:solidFill>
+            <a:ln w="19080">
+              <a:solidFill>
+                <a:srgbClr val="c00000"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$L$48:$L$49</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$M$48:$M$49</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Pb de diseño"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Pb de diseño</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="595959"/>
+            </a:solidFill>
+            <a:ln w="15840">
+              <a:solidFill>
+                <a:srgbClr val="595959"/>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$L$40:$L$41</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$M$40:$M$41</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Valor en Pb de diseño"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Valor en Pb de diseño</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ffc000"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="11"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="ffc000"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$L$43</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>5.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Datos_Graficas!$M$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>4.00450640616563</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:axId val="58777112"/>
+        <c:axId val="85576025"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="5494799"/>
+        <c:axId val="58777112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -2879,9 +6422,9 @@
         <c:axPos val="b"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9360">
+            <a:ln w="6480">
               <a:solidFill>
-                <a:srgbClr val="878787"/>
+                <a:srgbClr val="e7e6e6"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2896,7 +6439,7 @@
                 <a:pPr>
                   <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="404040"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
@@ -2904,11 +6447,11 @@
                 <a:r>
                   <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="404040"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
-                  <a:t>Contenido de asfalto (%)</a:t>
+                  <a:t>Contenido de asfalto Pb (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -2922,13 +6465,13 @@
           </c:spPr>
         </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="878787"/>
+              <a:srgbClr val="7f7f7f"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -2938,21 +6481,22 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="404040"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80998796"/>
-        <c:crosses val="autoZero"/>
+        <c:crossAx val="85576025"/>
+        <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="80998796"/>
+        <c:axId val="85576025"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2960,9 +6504,9 @@
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9360">
+            <a:ln w="6480">
               <a:solidFill>
-                <a:srgbClr val="878787"/>
+                <a:srgbClr val="e7e6e6"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2977,7 +6521,7 @@
                 <a:pPr>
                   <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="404040"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
@@ -2985,7 +6529,7 @@
                 <a:r>
                   <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="404040"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
@@ -3003,13 +6547,13 @@
           </c:spPr>
         </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="878787"/>
+              <a:srgbClr val="7f7f7f"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -3019,26 +6563,52 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="404040"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5494799"/>
-        <c:crosses val="autoZero"/>
+        <c:crossAx val="58777112"/>
+        <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="fbfbfb"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
       </c:spPr>
-    </c:plotArea>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="800" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
   </c:chart>
@@ -3048,7 +6618,7 @@
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="bfbfbf"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
@@ -3062,14 +6632,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>524880</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>17280</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>692280</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>181080</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3077,8 +6647,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="375840"/>
-        <a:ext cx="4318920" cy="2698920"/>
+        <a:off x="0" y="2828880"/>
+        <a:ext cx="5759640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3090,16 +6660,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>524880</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>17280</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>692280</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>181080</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3107,8 +6677,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6070680" y="375840"/>
-        <a:ext cx="4318920" cy="2698920"/>
+        <a:off x="8445600" y="2828880"/>
+        <a:ext cx="5759640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3122,14 +6692,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>524880</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>17280</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>692280</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>181080</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3137,8 +6707,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="3423960"/>
-        <a:ext cx="4318920" cy="2698920"/>
+        <a:off x="0" y="6638760"/>
+        <a:ext cx="5759640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3150,16 +6720,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>524880</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>17280</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>692280</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>181080</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3167,8 +6737,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6070680" y="3423960"/>
-        <a:ext cx="4318920" cy="2698920"/>
+        <a:off x="8445600" y="6638760"/>
+        <a:ext cx="5759640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3182,14 +6752,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>524880</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>17280</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>692280</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>181080</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3197,8 +6767,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="6472080"/>
-        <a:ext cx="4318920" cy="2698560"/>
+        <a:off x="0" y="10449000"/>
+        <a:ext cx="5759640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3210,16 +6780,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>524880</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>17280</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>692280</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>181080</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3227,8 +6797,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6070680" y="6472080"/>
-        <a:ext cx="4318920" cy="2698560"/>
+        <a:off x="8445600" y="10449000"/>
+        <a:ext cx="5759640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5029,20 +8599,355 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:T12"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="1" style="0" width="9.5"/>
+  </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
         <v>97</v>
       </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="29" t="str">
+        <f aca="false">Diseno_Marshall!C4&amp;"  |  C.A. "&amp;Diseno_Marshall!C5&amp;"  |  "&amp;Diseno_Marshall!C6</f>
+        <v>MAC-2 fina (huso MAC-2, MTC EG-2013)  |  C.A. PEN 120-150  |  50 golpes por cara</v>
+      </c>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
+      <c r="S2" s="29"/>
+      <c r="T2" s="29"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="30" t="str">
+        <f aca="false">" RESUMEN EN EL CONTENIDO ÓPTIMO DE ASFALTO  Pb = "&amp;TEXT(Diseno_Marshall!F41,"0.0")&amp;" %"</f>
+        <v> RESUMEN EN EL CONTENIDO ÓPTIMO DE ASFALTO  Pb = 5.5 %</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="L3" s="31" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="J4" s="32"/>
+      <c r="L4" s="33" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="34" t="str">
+        <f aca="false">Diseno_Marshall!A45</f>
+        <v>Gmb</v>
+      </c>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="35" t="n">
+        <f aca="false">Diseno_Marshall!B45</f>
+        <v>2.18870106667315</v>
+      </c>
+      <c r="E5" s="35"/>
+      <c r="F5" s="36" t="str">
+        <f aca="false">Diseno_Marshall!C45</f>
+        <v>-</v>
+      </c>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36" t="str">
+        <f aca="false">Diseno_Marshall!D45</f>
+        <v>-</v>
+      </c>
+      <c r="J5" s="36"/>
+      <c r="L5" s="33" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="34" t="str">
+        <f aca="false">Diseno_Marshall!A46</f>
+        <v>Va (%)</v>
+      </c>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="37" t="n">
+        <f aca="false">Diseno_Marshall!B46</f>
+        <v>4.01034820144837</v>
+      </c>
+      <c r="E6" s="37"/>
+      <c r="F6" s="36" t="str">
+        <f aca="false">Diseno_Marshall!C46</f>
+        <v>3 - 5 %</v>
+      </c>
+      <c r="G6" s="36"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="36" t="str">
+        <f aca="false">Diseno_Marshall!D46</f>
+        <v>CUMPLE</v>
+      </c>
+      <c r="J6" s="36"/>
+      <c r="L6" s="33" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="34" t="str">
+        <f aca="false">Diseno_Marshall!A47</f>
+        <v>VMA (%)</v>
+      </c>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="37" t="n">
+        <f aca="false">Diseno_Marshall!B47</f>
+        <v>14.8795112559337</v>
+      </c>
+      <c r="E7" s="37"/>
+      <c r="F7" s="36" t="str">
+        <f aca="false">Diseno_Marshall!C47</f>
+        <v>≥ 14 %</v>
+      </c>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36" t="str">
+        <f aca="false">Diseno_Marshall!D47</f>
+        <v>CUMPLE</v>
+      </c>
+      <c r="J7" s="36"/>
+      <c r="L7" s="33" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="34" t="str">
+        <f aca="false">Diseno_Marshall!A48</f>
+        <v>VFA (%)</v>
+      </c>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="37" t="n">
+        <f aca="false">Diseno_Marshall!B48</f>
+        <v>73.3429311270575</v>
+      </c>
+      <c r="E8" s="37"/>
+      <c r="F8" s="36" t="str">
+        <f aca="false">Diseno_Marshall!C48</f>
+        <v>65 - 78 %</v>
+      </c>
+      <c r="G8" s="36"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="36" t="str">
+        <f aca="false">Diseno_Marshall!D48</f>
+        <v>CUMPLE</v>
+      </c>
+      <c r="J8" s="36"/>
+      <c r="L8" s="33" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="34" t="str">
+        <f aca="false">Diseno_Marshall!A49</f>
+        <v>Estabilidad (kN)</v>
+      </c>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="38" t="n">
+        <f aca="false">Diseno_Marshall!B49</f>
+        <v>7.97744287523311</v>
+      </c>
+      <c r="E9" s="38"/>
+      <c r="F9" s="36" t="str">
+        <f aca="false">Diseno_Marshall!C49</f>
+        <v>≥ 5.44 kN</v>
+      </c>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36" t="str">
+        <f aca="false">Diseno_Marshall!D49</f>
+        <v>CUMPLE</v>
+      </c>
+      <c r="J9" s="36"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="34" t="str">
+        <f aca="false">Diseno_Marshall!A50</f>
+        <v>Flujo (mm)</v>
+      </c>
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="37" t="n">
+        <f aca="false">Diseno_Marshall!B50</f>
+        <v>4.00450640616563</v>
+      </c>
+      <c r="E10" s="37"/>
+      <c r="F10" s="36" t="str">
+        <f aca="false">Diseno_Marshall!C50</f>
+        <v>2 - 4 mm</v>
+      </c>
+      <c r="G10" s="36"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="36" t="str">
+        <f aca="false">Diseno_Marshall!D50</f>
+        <v>CUMPLE</v>
+      </c>
+      <c r="J10" s="36"/>
+      <c r="L10" s="39" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="34" t="str">
+        <f aca="false">Diseno_Marshall!A51</f>
+        <v>Estab./Flujo (kg/cm)</v>
+      </c>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="40" t="n">
+        <f aca="false">Diseno_Marshall!B51</f>
+        <v>2031.39338857235</v>
+      </c>
+      <c r="E11" s="40"/>
+      <c r="F11" s="36" t="str">
+        <f aca="false">Diseno_Marshall!C51</f>
+        <v>1700 - 4000 kg/cm</v>
+      </c>
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="36" t="str">
+        <f aca="false">Diseno_Marshall!D51</f>
+        <v>CUMPLE</v>
+      </c>
+      <c r="J11" s="36"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" s="41"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="42" t="str">
+        <f aca="false">Diseno_Marshall!D52</f>
+        <v>CUMPLE</v>
+      </c>
+      <c r="J12" s="42"/>
     </row>
   </sheetData>
+  <mergeCells count="37">
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A2:T2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="I12:J12"/>
+  </mergeCells>
+  <conditionalFormatting sqref="I5:J12">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+      <formula>"CUMPLE"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>"NO CUMPLE"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -5064,14 +8969,14 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="B1" s="29" t="s">
-        <v>99</v>
+      <c r="A1" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>108</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5336,6 +9241,1292 @@
       </c>
       <c r="B34" s="21" t="n">
         <v>0.76</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M49"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="44" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="45" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" s="45" t="s">
+        <v>112</v>
+      </c>
+      <c r="F3" s="45" t="s">
+        <v>113</v>
+      </c>
+      <c r="H3" s="45" t="s">
+        <v>114</v>
+      </c>
+      <c r="J3" s="45" t="s">
+        <v>115</v>
+      </c>
+      <c r="L3" s="45" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+0*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
+        <v>5.5</v>
+      </c>
+      <c r="B4" s="46" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*A4^2+Diseno_Marshall!$C$33*A4+Diseno_Marshall!$D$33</f>
+        <v>2.18870106667315</v>
+      </c>
+      <c r="D4" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*A4^2+Diseno_Marshall!$C$34*A4+Diseno_Marshall!$D$34</f>
+        <v>4.01034820144837</v>
+      </c>
+      <c r="F4" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*A4^2+Diseno_Marshall!$C$35*A4+Diseno_Marshall!$D$35</f>
+        <v>14.8795112559337</v>
+      </c>
+      <c r="H4" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A4^2+Diseno_Marshall!$C$36*A4+Diseno_Marshall!$D$36</f>
+        <v>73.3429311270575</v>
+      </c>
+      <c r="J4" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A4^2+Diseno_Marshall!$C$37*A4+Diseno_Marshall!$D$37</f>
+        <v>7.97744287523311</v>
+      </c>
+      <c r="L4" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A4^2+Diseno_Marshall!$C$38*A4+Diseno_Marshall!$D$38</f>
+        <v>4.00450640616563</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+1*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
+        <v>5.65</v>
+      </c>
+      <c r="B5" s="46" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*A5^2+Diseno_Marshall!$C$33*A5+Diseno_Marshall!$D$33</f>
+        <v>2.18789535266774</v>
+      </c>
+      <c r="D5" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*A5^2+Diseno_Marshall!$C$34*A5+Diseno_Marshall!$D$34</f>
+        <v>3.85699523095454</v>
+      </c>
+      <c r="F5" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*A5^2+Diseno_Marshall!$C$35*A5+Diseno_Marshall!$D$35</f>
+        <v>15.0470055443678</v>
+      </c>
+      <c r="H5" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A5^2+Diseno_Marshall!$C$36*A5+Diseno_Marshall!$D$36</f>
+        <v>74.6055150641918</v>
+      </c>
+      <c r="J5" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A5^2+Diseno_Marshall!$C$37*A5+Diseno_Marshall!$D$37</f>
+        <v>7.66288161089468</v>
+      </c>
+      <c r="L5" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A5^2+Diseno_Marshall!$C$38*A5+Diseno_Marshall!$D$38</f>
+        <v>4.13755679642629</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+2*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
+        <v>5.8</v>
+      </c>
+      <c r="B6" s="46" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*A6^2+Diseno_Marshall!$C$33*A6+Diseno_Marshall!$D$33</f>
+        <v>2.18711795916989</v>
+      </c>
+      <c r="D6" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*A6^2+Diseno_Marshall!$C$34*A6+Diseno_Marshall!$D$34</f>
+        <v>3.70257122650614</v>
+      </c>
+      <c r="F6" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*A6^2+Diseno_Marshall!$C$35*A6+Diseno_Marshall!$D$35</f>
+        <v>15.213275017413</v>
+      </c>
+      <c r="H6" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A6^2+Diseno_Marshall!$C$36*A6+Diseno_Marshall!$D$36</f>
+        <v>75.8547592833012</v>
+      </c>
+      <c r="J6" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A6^2+Diseno_Marshall!$C$37*A6+Diseno_Marshall!$D$37</f>
+        <v>7.3658123459464</v>
+      </c>
+      <c r="L6" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A6^2+Diseno_Marshall!$C$38*A6+Diseno_Marshall!$D$38</f>
+        <v>4.26761219380492</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+3*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
+        <v>5.95</v>
+      </c>
+      <c r="B7" s="46" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*A7^2+Diseno_Marshall!$C$33*A7+Diseno_Marshall!$D$33</f>
+        <v>2.18636888617959</v>
+      </c>
+      <c r="D7" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*A7^2+Diseno_Marshall!$C$34*A7+Diseno_Marshall!$D$34</f>
+        <v>3.54707618810316</v>
+      </c>
+      <c r="F7" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*A7^2+Diseno_Marshall!$C$35*A7+Diseno_Marshall!$D$35</f>
+        <v>15.3783196750692</v>
+      </c>
+      <c r="H7" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A7^2+Diseno_Marshall!$C$36*A7+Diseno_Marshall!$D$36</f>
+        <v>77.0906637843856</v>
+      </c>
+      <c r="J7" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A7^2+Diseno_Marshall!$C$37*A7+Diseno_Marshall!$D$37</f>
+        <v>7.08623508038827</v>
+      </c>
+      <c r="L7" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A7^2+Diseno_Marshall!$C$38*A7+Diseno_Marshall!$D$38</f>
+        <v>4.39467259830151</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+4*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
+        <v>6.1</v>
+      </c>
+      <c r="B8" s="46" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*A8^2+Diseno_Marshall!$C$33*A8+Diseno_Marshall!$D$33</f>
+        <v>2.18564813369684</v>
+      </c>
+      <c r="D8" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*A8^2+Diseno_Marshall!$C$34*A8+Diseno_Marshall!$D$34</f>
+        <v>3.39051011574561</v>
+      </c>
+      <c r="F8" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*A8^2+Diseno_Marshall!$C$35*A8+Diseno_Marshall!$D$35</f>
+        <v>15.5421395173365</v>
+      </c>
+      <c r="H8" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A8^2+Diseno_Marshall!$C$36*A8+Diseno_Marshall!$D$36</f>
+        <v>78.3132285674452</v>
+      </c>
+      <c r="J8" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A8^2+Diseno_Marshall!$C$37*A8+Diseno_Marshall!$D$37</f>
+        <v>6.82414981422028</v>
+      </c>
+      <c r="L8" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A8^2+Diseno_Marshall!$C$38*A8+Diseno_Marshall!$D$38</f>
+        <v>4.51873800991606</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+5*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
+        <v>6.25</v>
+      </c>
+      <c r="B9" s="46" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*A9^2+Diseno_Marshall!$C$33*A9+Diseno_Marshall!$D$33</f>
+        <v>2.18495570172164</v>
+      </c>
+      <c r="D9" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*A9^2+Diseno_Marshall!$C$34*A9+Diseno_Marshall!$D$34</f>
+        <v>3.23287300943348</v>
+      </c>
+      <c r="F9" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*A9^2+Diseno_Marshall!$C$35*A9+Diseno_Marshall!$D$35</f>
+        <v>15.704734544215</v>
+      </c>
+      <c r="H9" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A9^2+Diseno_Marshall!$C$36*A9+Diseno_Marshall!$D$36</f>
+        <v>79.5224536324798</v>
+      </c>
+      <c r="J9" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A9^2+Diseno_Marshall!$C$37*A9+Diseno_Marshall!$D$37</f>
+        <v>6.57955654744245</v>
+      </c>
+      <c r="L9" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A9^2+Diseno_Marshall!$C$38*A9+Diseno_Marshall!$D$38</f>
+        <v>4.63980842864857</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+6*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
+        <v>6.4</v>
+      </c>
+      <c r="B10" s="46" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*A10^2+Diseno_Marshall!$C$33*A10+Diseno_Marshall!$D$33</f>
+        <v>2.18429159025398</v>
+      </c>
+      <c r="D10" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*A10^2+Diseno_Marshall!$C$34*A10+Diseno_Marshall!$D$34</f>
+        <v>3.07416486916676</v>
+      </c>
+      <c r="F10" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*A10^2+Diseno_Marshall!$C$35*A10+Diseno_Marshall!$D$35</f>
+        <v>15.8661047557044</v>
+      </c>
+      <c r="H10" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A10^2+Diseno_Marshall!$C$36*A10+Diseno_Marshall!$D$36</f>
+        <v>80.7183389794896</v>
+      </c>
+      <c r="J10" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A10^2+Diseno_Marshall!$C$37*A10+Diseno_Marshall!$D$37</f>
+        <v>6.35245528005476</v>
+      </c>
+      <c r="L10" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A10^2+Diseno_Marshall!$C$38*A10+Diseno_Marshall!$D$38</f>
+        <v>4.75788385449904</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+7*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
+        <v>6.55</v>
+      </c>
+      <c r="B11" s="46" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*A11^2+Diseno_Marshall!$C$33*A11+Diseno_Marshall!$D$33</f>
+        <v>2.18365579929388</v>
+      </c>
+      <c r="D11" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*A11^2+Diseno_Marshall!$C$34*A11+Diseno_Marshall!$D$34</f>
+        <v>2.91438569494548</v>
+      </c>
+      <c r="F11" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*A11^2+Diseno_Marshall!$C$35*A11+Diseno_Marshall!$D$35</f>
+        <v>16.026250151805</v>
+      </c>
+      <c r="H11" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A11^2+Diseno_Marshall!$C$36*A11+Diseno_Marshall!$D$36</f>
+        <v>81.9008846084744</v>
+      </c>
+      <c r="J11" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A11^2+Diseno_Marshall!$C$37*A11+Diseno_Marshall!$D$37</f>
+        <v>6.14284601205722</v>
+      </c>
+      <c r="L11" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A11^2+Diseno_Marshall!$C$38*A11+Diseno_Marshall!$D$38</f>
+        <v>4.87296428746748</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+8*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
+        <v>6.7</v>
+      </c>
+      <c r="B12" s="46" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*A12^2+Diseno_Marshall!$C$33*A12+Diseno_Marshall!$D$33</f>
+        <v>2.18304832884132</v>
+      </c>
+      <c r="D12" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*A12^2+Diseno_Marshall!$C$34*A12+Diseno_Marshall!$D$34</f>
+        <v>2.75353548676961</v>
+      </c>
+      <c r="F12" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*A12^2+Diseno_Marshall!$C$35*A12+Diseno_Marshall!$D$35</f>
+        <v>16.1851707325167</v>
+      </c>
+      <c r="H12" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A12^2+Diseno_Marshall!$C$36*A12+Diseno_Marshall!$D$36</f>
+        <v>83.0700905194343</v>
+      </c>
+      <c r="J12" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A12^2+Diseno_Marshall!$C$37*A12+Diseno_Marshall!$D$37</f>
+        <v>5.95072874344983</v>
+      </c>
+      <c r="L12" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A12^2+Diseno_Marshall!$C$38*A12+Diseno_Marshall!$D$38</f>
+        <v>4.98504972755388</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+9*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
+        <v>6.85</v>
+      </c>
+      <c r="B13" s="46" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*A13^2+Diseno_Marshall!$C$33*A13+Diseno_Marshall!$D$33</f>
+        <v>2.18246917889632</v>
+      </c>
+      <c r="D13" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*A13^2+Diseno_Marshall!$C$34*A13+Diseno_Marshall!$D$34</f>
+        <v>2.59161424463917</v>
+      </c>
+      <c r="F13" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*A13^2+Diseno_Marshall!$C$35*A13+Diseno_Marshall!$D$35</f>
+        <v>16.3428664978394</v>
+      </c>
+      <c r="H13" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A13^2+Diseno_Marshall!$C$36*A13+Diseno_Marshall!$D$36</f>
+        <v>84.2259567123693</v>
+      </c>
+      <c r="J13" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A13^2+Diseno_Marshall!$C$37*A13+Diseno_Marshall!$D$37</f>
+        <v>5.77610347423259</v>
+      </c>
+      <c r="L13" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A13^2+Diseno_Marshall!$C$38*A13+Diseno_Marshall!$D$38</f>
+        <v>5.09414017475823</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+10*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
+        <v>7</v>
+      </c>
+      <c r="B14" s="46" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*A14^2+Diseno_Marshall!$C$33*A14+Diseno_Marshall!$D$33</f>
+        <v>2.18191834945886</v>
+      </c>
+      <c r="D14" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*A14^2+Diseno_Marshall!$C$34*A14+Diseno_Marshall!$D$34</f>
+        <v>2.42862196855415</v>
+      </c>
+      <c r="F14" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*A14^2+Diseno_Marshall!$C$35*A14+Diseno_Marshall!$D$35</f>
+        <v>16.4993374477732</v>
+      </c>
+      <c r="H14" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A14^2+Diseno_Marshall!$C$36*A14+Diseno_Marshall!$D$36</f>
+        <v>85.3684831872794</v>
+      </c>
+      <c r="J14" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A14^2+Diseno_Marshall!$C$37*A14+Diseno_Marshall!$D$37</f>
+        <v>5.61897020440549</v>
+      </c>
+      <c r="L14" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A14^2+Diseno_Marshall!$C$38*A14+Diseno_Marshall!$D$38</f>
+        <v>5.20023562908055</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+11*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
+        <v>7.15</v>
+      </c>
+      <c r="B15" s="46" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*A15^2+Diseno_Marshall!$C$33*A15+Diseno_Marshall!$D$33</f>
+        <v>2.18139584052895</v>
+      </c>
+      <c r="D15" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*A15^2+Diseno_Marshall!$C$34*A15+Diseno_Marshall!$D$34</f>
+        <v>2.26455865851456</v>
+      </c>
+      <c r="F15" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*A15^2+Diseno_Marshall!$C$35*A15+Diseno_Marshall!$D$35</f>
+        <v>16.6545835823181</v>
+      </c>
+      <c r="H15" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A15^2+Diseno_Marshall!$C$36*A15+Diseno_Marshall!$D$36</f>
+        <v>86.4976699441645</v>
+      </c>
+      <c r="J15" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A15^2+Diseno_Marshall!$C$37*A15+Diseno_Marshall!$D$37</f>
+        <v>5.47932893396854</v>
+      </c>
+      <c r="L15" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A15^2+Diseno_Marshall!$C$38*A15+Diseno_Marshall!$D$38</f>
+        <v>5.30333609052084</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+12*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
+        <v>7.3</v>
+      </c>
+      <c r="B16" s="46" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*A16^2+Diseno_Marshall!$C$33*A16+Diseno_Marshall!$D$33</f>
+        <v>2.1809016521066</v>
+      </c>
+      <c r="D16" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*A16^2+Diseno_Marshall!$C$34*A16+Diseno_Marshall!$D$34</f>
+        <v>2.09942431452038</v>
+      </c>
+      <c r="F16" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*A16^2+Diseno_Marshall!$C$35*A16+Diseno_Marshall!$D$35</f>
+        <v>16.8086049014741</v>
+      </c>
+      <c r="H16" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A16^2+Diseno_Marshall!$C$36*A16+Diseno_Marshall!$D$36</f>
+        <v>87.6135169830248</v>
+      </c>
+      <c r="J16" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A16^2+Diseno_Marshall!$C$37*A16+Diseno_Marshall!$D$37</f>
+        <v>5.35717966292174</v>
+      </c>
+      <c r="L16" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A16^2+Diseno_Marshall!$C$38*A16+Diseno_Marshall!$D$38</f>
+        <v>5.40344155907908</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+13*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
+        <v>7.45</v>
+      </c>
+      <c r="B17" s="46" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*A17^2+Diseno_Marshall!$C$33*A17+Diseno_Marshall!$D$33</f>
+        <v>2.18043578419179</v>
+      </c>
+      <c r="D17" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*A17^2+Diseno_Marshall!$C$34*A17+Diseno_Marshall!$D$34</f>
+        <v>1.93321893657163</v>
+      </c>
+      <c r="F17" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*A17^2+Diseno_Marshall!$C$35*A17+Diseno_Marshall!$D$35</f>
+        <v>16.9614014052411</v>
+      </c>
+      <c r="H17" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A17^2+Diseno_Marshall!$C$36*A17+Diseno_Marshall!$D$36</f>
+        <v>88.7160243038601</v>
+      </c>
+      <c r="J17" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A17^2+Diseno_Marshall!$C$37*A17+Diseno_Marshall!$D$37</f>
+        <v>5.25252239126509</v>
+      </c>
+      <c r="L17" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A17^2+Diseno_Marshall!$C$38*A17+Diseno_Marshall!$D$38</f>
+        <v>5.50055203475529</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+14*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
+        <v>7.6</v>
+      </c>
+      <c r="B18" s="46" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*A18^2+Diseno_Marshall!$C$33*A18+Diseno_Marshall!$D$33</f>
+        <v>2.17999823678453</v>
+      </c>
+      <c r="D18" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*A18^2+Diseno_Marshall!$C$34*A18+Diseno_Marshall!$D$34</f>
+        <v>1.76594252466831</v>
+      </c>
+      <c r="F18" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*A18^2+Diseno_Marshall!$C$35*A18+Diseno_Marshall!$D$35</f>
+        <v>17.1129730936192</v>
+      </c>
+      <c r="H18" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A18^2+Diseno_Marshall!$C$36*A18+Diseno_Marshall!$D$36</f>
+        <v>89.8051919066706</v>
+      </c>
+      <c r="J18" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A18^2+Diseno_Marshall!$C$37*A18+Diseno_Marshall!$D$37</f>
+        <v>5.16535711899859</v>
+      </c>
+      <c r="L18" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A18^2+Diseno_Marshall!$C$38*A18+Diseno_Marshall!$D$38</f>
+        <v>5.59466751754946</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+15*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
+        <v>7.75</v>
+      </c>
+      <c r="B19" s="46" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*A19^2+Diseno_Marshall!$C$33*A19+Diseno_Marshall!$D$33</f>
+        <v>2.17958900988482</v>
+      </c>
+      <c r="D19" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*A19^2+Diseno_Marshall!$C$34*A19+Diseno_Marshall!$D$34</f>
+        <v>1.5975950788104</v>
+      </c>
+      <c r="F19" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*A19^2+Diseno_Marshall!$C$35*A19+Diseno_Marshall!$D$35</f>
+        <v>17.2633199666084</v>
+      </c>
+      <c r="H19" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A19^2+Diseno_Marshall!$C$36*A19+Diseno_Marshall!$D$36</f>
+        <v>90.8810197914561</v>
+      </c>
+      <c r="J19" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A19^2+Diseno_Marshall!$C$37*A19+Diseno_Marshall!$D$37</f>
+        <v>5.09568384612222</v>
+      </c>
+      <c r="L19" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A19^2+Diseno_Marshall!$C$38*A19+Diseno_Marshall!$D$38</f>
+        <v>5.68578800746159</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+16*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
+        <v>7.9</v>
+      </c>
+      <c r="B20" s="46" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*A20^2+Diseno_Marshall!$C$33*A20+Diseno_Marshall!$D$33</f>
+        <v>2.17920810349266</v>
+      </c>
+      <c r="D20" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*A20^2+Diseno_Marshall!$C$34*A20+Diseno_Marshall!$D$34</f>
+        <v>1.42817659899792</v>
+      </c>
+      <c r="F20" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*A20^2+Diseno_Marshall!$C$35*A20+Diseno_Marshall!$D$35</f>
+        <v>17.4124420242087</v>
+      </c>
+      <c r="H20" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A20^2+Diseno_Marshall!$C$36*A20+Diseno_Marshall!$D$36</f>
+        <v>91.9435079582167</v>
+      </c>
+      <c r="J20" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A20^2+Diseno_Marshall!$C$37*A20+Diseno_Marshall!$D$37</f>
+        <v>5.04350257263601</v>
+      </c>
+      <c r="L20" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A20^2+Diseno_Marshall!$C$38*A20+Diseno_Marshall!$D$38</f>
+        <v>5.77391350449168</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+17*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
+        <v>8.05</v>
+      </c>
+      <c r="B21" s="46" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*A21^2+Diseno_Marshall!$C$33*A21+Diseno_Marshall!$D$33</f>
+        <v>2.17885551760805</v>
+      </c>
+      <c r="D21" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*A21^2+Diseno_Marshall!$C$34*A21+Diseno_Marshall!$D$34</f>
+        <v>1.25768708523086</v>
+      </c>
+      <c r="F21" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*A21^2+Diseno_Marshall!$C$35*A21+Diseno_Marshall!$D$35</f>
+        <v>17.5603392664201</v>
+      </c>
+      <c r="H21" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A21^2+Diseno_Marshall!$C$36*A21+Diseno_Marshall!$D$36</f>
+        <v>92.9926564069524</v>
+      </c>
+      <c r="J21" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A21^2+Diseno_Marshall!$C$37*A21+Diseno_Marshall!$D$37</f>
+        <v>5.00881329853996</v>
+      </c>
+      <c r="L21" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A21^2+Diseno_Marshall!$C$38*A21+Diseno_Marshall!$D$38</f>
+        <v>5.85904400863973</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+18*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
+        <v>8.2</v>
+      </c>
+      <c r="B22" s="46" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*A22^2+Diseno_Marshall!$C$33*A22+Diseno_Marshall!$D$33</f>
+        <v>2.17853125223099</v>
+      </c>
+      <c r="D22" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*A22^2+Diseno_Marshall!$C$34*A22+Diseno_Marshall!$D$34</f>
+        <v>1.08612653750923</v>
+      </c>
+      <c r="F22" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*A22^2+Diseno_Marshall!$C$35*A22+Diseno_Marshall!$D$35</f>
+        <v>17.7070116932425</v>
+      </c>
+      <c r="H22" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A22^2+Diseno_Marshall!$C$36*A22+Diseno_Marshall!$D$36</f>
+        <v>94.0284651376631</v>
+      </c>
+      <c r="J22" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A22^2+Diseno_Marshall!$C$37*A22+Diseno_Marshall!$D$37</f>
+        <v>4.99161602383404</v>
+      </c>
+      <c r="L22" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A22^2+Diseno_Marshall!$C$38*A22+Diseno_Marshall!$D$38</f>
+        <v>5.94117951990575</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+19*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
+        <v>8.35</v>
+      </c>
+      <c r="B23" s="46" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*A23^2+Diseno_Marshall!$C$33*A23+Diseno_Marshall!$D$33</f>
+        <v>2.17823530736148</v>
+      </c>
+      <c r="D23" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*A23^2+Diseno_Marshall!$C$34*A23+Diseno_Marshall!$D$34</f>
+        <v>0.913494955833012</v>
+      </c>
+      <c r="F23" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*A23^2+Diseno_Marshall!$C$35*A23+Diseno_Marshall!$D$35</f>
+        <v>17.8524593046761</v>
+      </c>
+      <c r="H23" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A23^2+Diseno_Marshall!$C$36*A23+Diseno_Marshall!$D$36</f>
+        <v>95.050934150349</v>
+      </c>
+      <c r="J23" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A23^2+Diseno_Marshall!$C$37*A23+Diseno_Marshall!$D$37</f>
+        <v>4.99191074851828</v>
+      </c>
+      <c r="L23" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A23^2+Diseno_Marshall!$C$38*A23+Diseno_Marshall!$D$38</f>
+        <v>6.02032003828972</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+20*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
+        <v>8.5</v>
+      </c>
+      <c r="B24" s="46" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*A24^2+Diseno_Marshall!$C$33*A24+Diseno_Marshall!$D$33</f>
+        <v>2.17796768299951</v>
+      </c>
+      <c r="D24" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*A24^2+Diseno_Marshall!$C$34*A24+Diseno_Marshall!$D$34</f>
+        <v>0.739792340202222</v>
+      </c>
+      <c r="F24" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*A24^2+Diseno_Marshall!$C$35*A24+Diseno_Marshall!$D$35</f>
+        <v>17.9966821007207</v>
+      </c>
+      <c r="H24" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A24^2+Diseno_Marshall!$C$36*A24+Diseno_Marshall!$D$36</f>
+        <v>96.0600634450099</v>
+      </c>
+      <c r="J24" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A24^2+Diseno_Marshall!$C$37*A24+Diseno_Marshall!$D$37</f>
+        <v>5.00969747259266</v>
+      </c>
+      <c r="L24" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A24^2+Diseno_Marshall!$C$38*A24+Diseno_Marshall!$D$38</f>
+        <v>6.09646556379166</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+21*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
+        <v>8.65</v>
+      </c>
+      <c r="B25" s="46" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*A25^2+Diseno_Marshall!$C$33*A25+Diseno_Marshall!$D$33</f>
+        <v>2.1777283791451</v>
+      </c>
+      <c r="D25" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*A25^2+Diseno_Marshall!$C$34*A25+Diseno_Marshall!$D$34</f>
+        <v>0.565018690616853</v>
+      </c>
+      <c r="F25" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*A25^2+Diseno_Marshall!$C$35*A25+Diseno_Marshall!$D$35</f>
+        <v>18.1396800813763</v>
+      </c>
+      <c r="H25" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A25^2+Diseno_Marshall!$C$36*A25+Diseno_Marshall!$D$36</f>
+        <v>97.055853021646</v>
+      </c>
+      <c r="J25" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A25^2+Diseno_Marshall!$C$37*A25+Diseno_Marshall!$D$37</f>
+        <v>5.04497619605719</v>
+      </c>
+      <c r="L25" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A25^2+Diseno_Marshall!$C$38*A25+Diseno_Marshall!$D$38</f>
+        <v>6.16961609641156</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+22*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
+        <v>8.8</v>
+      </c>
+      <c r="B26" s="46" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*A26^2+Diseno_Marshall!$C$33*A26+Diseno_Marshall!$D$33</f>
+        <v>2.17751739579824</v>
+      </c>
+      <c r="D26" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*A26^2+Diseno_Marshall!$C$34*A26+Diseno_Marshall!$D$34</f>
+        <v>0.389174007076909</v>
+      </c>
+      <c r="F26" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*A26^2+Diseno_Marshall!$C$35*A26+Diseno_Marshall!$D$35</f>
+        <v>18.2814532466431</v>
+      </c>
+      <c r="H26" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A26^2+Diseno_Marshall!$C$36*A26+Diseno_Marshall!$D$36</f>
+        <v>98.0383028802571</v>
+      </c>
+      <c r="J26" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A26^2+Diseno_Marshall!$C$37*A26+Diseno_Marshall!$D$37</f>
+        <v>5.09774691891186</v>
+      </c>
+      <c r="L26" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A26^2+Diseno_Marshall!$C$38*A26+Diseno_Marshall!$D$38</f>
+        <v>6.23977163614943</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+23*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
+        <v>8.95</v>
+      </c>
+      <c r="B27" s="46" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*A27^2+Diseno_Marshall!$C$33*A27+Diseno_Marshall!$D$33</f>
+        <v>2.17733473295892</v>
+      </c>
+      <c r="D27" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*A27^2+Diseno_Marshall!$C$34*A27+Diseno_Marshall!$D$34</f>
+        <v>0.212258289582387</v>
+      </c>
+      <c r="F27" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*A27^2+Diseno_Marshall!$C$35*A27+Diseno_Marshall!$D$35</f>
+        <v>18.422001596521</v>
+      </c>
+      <c r="H27" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A27^2+Diseno_Marshall!$C$36*A27+Diseno_Marshall!$D$36</f>
+        <v>99.0074130208433</v>
+      </c>
+      <c r="J27" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A27^2+Diseno_Marshall!$C$37*A27+Diseno_Marshall!$D$37</f>
+        <v>5.16800964115669</v>
+      </c>
+      <c r="L27" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A27^2+Diseno_Marshall!$C$38*A27+Diseno_Marshall!$D$38</f>
+        <v>6.30693218300525</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+24*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
+        <v>9.1</v>
+      </c>
+      <c r="B28" s="46" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*A28^2+Diseno_Marshall!$C$33*A28+Diseno_Marshall!$D$33</f>
+        <v>2.17718039062716</v>
+      </c>
+      <c r="D28" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*A28^2+Diseno_Marshall!$C$34*A28+Diseno_Marshall!$D$34</f>
+        <v>0.0342715381332894</v>
+      </c>
+      <c r="F28" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*A28^2+Diseno_Marshall!$C$35*A28+Diseno_Marshall!$D$35</f>
+        <v>18.5613251310099</v>
+      </c>
+      <c r="H28" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A28^2+Diseno_Marshall!$C$36*A28+Diseno_Marshall!$D$36</f>
+        <v>99.9631834434046</v>
+      </c>
+      <c r="J28" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A28^2+Diseno_Marshall!$C$37*A28+Diseno_Marshall!$D$37</f>
+        <v>5.25576436279166</v>
+      </c>
+      <c r="L28" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A28^2+Diseno_Marshall!$C$38*A28+Diseno_Marshall!$D$38</f>
+        <v>6.37109773697904</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+25*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
+        <v>9.25</v>
+      </c>
+      <c r="B29" s="46" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*A29^2+Diseno_Marshall!$C$33*A29+Diseno_Marshall!$D$33</f>
+        <v>2.17705436880294</v>
+      </c>
+      <c r="D29" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*A29^2+Diseno_Marshall!$C$34*A29+Diseno_Marshall!$D$34</f>
+        <v>-0.144786247270387</v>
+      </c>
+      <c r="F29" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*A29^2+Diseno_Marshall!$C$35*A29+Diseno_Marshall!$D$35</f>
+        <v>18.6994238501099</v>
+      </c>
+      <c r="H29" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A29^2+Diseno_Marshall!$C$36*A29+Diseno_Marshall!$D$36</f>
+        <v>100.905614147941</v>
+      </c>
+      <c r="J29" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A29^2+Diseno_Marshall!$C$37*A29+Diseno_Marshall!$D$37</f>
+        <v>5.36101108381679</v>
+      </c>
+      <c r="L29" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A29^2+Diseno_Marshall!$C$38*A29+Diseno_Marshall!$D$38</f>
+        <v>6.43226829807079</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+26*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
+        <v>9.4</v>
+      </c>
+      <c r="B30" s="46" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*A30^2+Diseno_Marshall!$C$33*A30+Diseno_Marshall!$D$33</f>
+        <v>2.17695666748628</v>
+      </c>
+      <c r="D30" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*A30^2+Diseno_Marshall!$C$34*A30+Diseno_Marshall!$D$34</f>
+        <v>-0.324915066628643</v>
+      </c>
+      <c r="F30" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*A30^2+Diseno_Marshall!$C$35*A30+Diseno_Marshall!$D$35</f>
+        <v>18.836297753821</v>
+      </c>
+      <c r="H30" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A30^2+Diseno_Marshall!$C$36*A30+Diseno_Marshall!$D$36</f>
+        <v>101.834705134452</v>
+      </c>
+      <c r="J30" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A30^2+Diseno_Marshall!$C$37*A30+Diseno_Marshall!$D$37</f>
+        <v>5.48374980423206</v>
+      </c>
+      <c r="L30" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A30^2+Diseno_Marshall!$C$38*A30+Diseno_Marshall!$D$38</f>
+        <v>6.4904438662805</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+27*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
+        <v>9.55</v>
+      </c>
+      <c r="B31" s="46" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*A31^2+Diseno_Marshall!$C$33*A31+Diseno_Marshall!$D$33</f>
+        <v>2.17688728667716</v>
+      </c>
+      <c r="D31" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*A31^2+Diseno_Marshall!$C$34*A31+Diseno_Marshall!$D$34</f>
+        <v>-0.506114919941473</v>
+      </c>
+      <c r="F31" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*A31^2+Diseno_Marshall!$C$35*A31+Diseno_Marshall!$D$35</f>
+        <v>18.9719468421431</v>
+      </c>
+      <c r="H31" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A31^2+Diseno_Marshall!$C$36*A31+Diseno_Marshall!$D$36</f>
+        <v>102.750456402939</v>
+      </c>
+      <c r="J31" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A31^2+Diseno_Marshall!$C$37*A31+Diseno_Marshall!$D$37</f>
+        <v>5.62398052403748</v>
+      </c>
+      <c r="L31" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A31^2+Diseno_Marshall!$C$38*A31+Diseno_Marshall!$D$38</f>
+        <v>6.54562444160817</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+28*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
+        <v>9.7</v>
+      </c>
+      <c r="B32" s="46" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*A32^2+Diseno_Marshall!$C$33*A32+Diseno_Marshall!$D$33</f>
+        <v>2.17684622637559</v>
+      </c>
+      <c r="D32" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*A32^2+Diseno_Marshall!$C$34*A32+Diseno_Marshall!$D$34</f>
+        <v>-0.68838580720888</v>
+      </c>
+      <c r="F32" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*A32^2+Diseno_Marshall!$C$35*A32+Diseno_Marshall!$D$35</f>
+        <v>19.1063711150764</v>
+      </c>
+      <c r="H32" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A32^2+Diseno_Marshall!$C$36*A32+Diseno_Marshall!$D$36</f>
+        <v>103.652867953401</v>
+      </c>
+      <c r="J32" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A32^2+Diseno_Marshall!$C$37*A32+Diseno_Marshall!$D$37</f>
+        <v>5.78170324323304</v>
+      </c>
+      <c r="L32" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A32^2+Diseno_Marshall!$C$38*A32+Diseno_Marshall!$D$38</f>
+        <v>6.5978100240538</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+29*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
+        <v>9.85</v>
+      </c>
+      <c r="B33" s="46" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*A33^2+Diseno_Marshall!$C$33*A33+Diseno_Marshall!$D$33</f>
+        <v>2.17683348658157</v>
+      </c>
+      <c r="D33" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*A33^2+Diseno_Marshall!$C$34*A33+Diseno_Marshall!$D$34</f>
+        <v>-0.871727728430864</v>
+      </c>
+      <c r="F33" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*A33^2+Diseno_Marshall!$C$35*A33+Diseno_Marshall!$D$35</f>
+        <v>19.2395705726207</v>
+      </c>
+      <c r="H33" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A33^2+Diseno_Marshall!$C$36*A33+Diseno_Marshall!$D$36</f>
+        <v>104.541939785837</v>
+      </c>
+      <c r="J33" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A33^2+Diseno_Marshall!$C$37*A33+Diseno_Marshall!$D$37</f>
+        <v>5.95691796181875</v>
+      </c>
+      <c r="L33" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A33^2+Diseno_Marshall!$C$38*A33+Diseno_Marshall!$D$38</f>
+        <v>6.6470006136174</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+30*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
+        <v>10</v>
+      </c>
+      <c r="B34" s="46" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*A34^2+Diseno_Marshall!$C$33*A34+Diseno_Marshall!$D$33</f>
+        <v>2.17684906729511</v>
+      </c>
+      <c r="D34" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*A34^2+Diseno_Marshall!$C$34*A34+Diseno_Marshall!$D$34</f>
+        <v>-1.05614068360743</v>
+      </c>
+      <c r="F34" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*A34^2+Diseno_Marshall!$C$35*A34+Diseno_Marshall!$D$35</f>
+        <v>19.3715452147761</v>
+      </c>
+      <c r="H34" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A34^2+Diseno_Marshall!$C$36*A34+Diseno_Marshall!$D$36</f>
+        <v>105.417671900249</v>
+      </c>
+      <c r="J34" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A34^2+Diseno_Marshall!$C$37*A34+Diseno_Marshall!$D$37</f>
+        <v>6.14962467979462</v>
+      </c>
+      <c r="L34" s="47" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A34^2+Diseno_Marshall!$C$38*A34+Diseno_Marshall!$D$38</f>
+        <v>6.69319621029896</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="45" t="s">
+        <v>117</v>
+      </c>
+      <c r="D39" s="45" t="s">
+        <v>118</v>
+      </c>
+      <c r="F39" s="45" t="s">
+        <v>119</v>
+      </c>
+      <c r="H39" s="45" t="s">
+        <v>120</v>
+      </c>
+      <c r="J39" s="45" t="s">
+        <v>121</v>
+      </c>
+      <c r="L39" s="45" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$F$41</f>
+        <v>5.5</v>
+      </c>
+      <c r="C40" s="49" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$P$17:$P$21,B4:B34)</f>
+        <v>2.15946205571566</v>
+      </c>
+      <c r="D40" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$F$41</f>
+        <v>5.5</v>
+      </c>
+      <c r="E40" s="49" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$R$17:$R$21,D4:D34,Diseno_Marshall!$J$11)</f>
+        <v>-1.05614068360743</v>
+      </c>
+      <c r="F40" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$F$41</f>
+        <v>5.5</v>
+      </c>
+      <c r="G40" s="49" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$S$17:$S$21,F4:F34,Diseno_Marshall!$J$12)</f>
+        <v>14</v>
+      </c>
+      <c r="H40" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$F$41</f>
+        <v>5.5</v>
+      </c>
+      <c r="I40" s="49" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$T$17:$T$21,H4:H34,Diseno_Marshall!$J$13)</f>
+        <v>65</v>
+      </c>
+      <c r="J40" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$F$41</f>
+        <v>5.5</v>
+      </c>
+      <c r="K40" s="49" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$X$17:$X$21,J4:J34,Diseno_Marshall!$J$9)</f>
+        <v>4.9686005140625</v>
+      </c>
+      <c r="L40" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$F$41</f>
+        <v>5.5</v>
+      </c>
+      <c r="M40" s="49" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$Y$17:$Y$21,L4:L34,Diseno_Marshall!$J$10)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$F$41</f>
+        <v>5.5</v>
+      </c>
+      <c r="C41" s="49" t="n">
+        <f aca="false">MAX(Diseno_Marshall!$P$17:$P$21,B4:B34)</f>
+        <v>2.20736434108527</v>
+      </c>
+      <c r="D41" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$F$41</f>
+        <v>5.5</v>
+      </c>
+      <c r="E41" s="49" t="n">
+        <f aca="false">MAX(Diseno_Marshall!$R$17:$R$21,D4:D34,Diseno_Marshall!$K$11)</f>
+        <v>5</v>
+      </c>
+      <c r="F41" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$F$41</f>
+        <v>5.5</v>
+      </c>
+      <c r="G41" s="49" t="n">
+        <f aca="false">MAX(Diseno_Marshall!$S$17:$S$21,F4:F34)</f>
+        <v>19.4817528150862</v>
+      </c>
+      <c r="H41" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$F$41</f>
+        <v>5.5</v>
+      </c>
+      <c r="I41" s="49" t="n">
+        <f aca="false">MAX(Diseno_Marshall!$T$17:$T$21,H4:H34,Diseno_Marshall!$K$13)</f>
+        <v>105.417671900249</v>
+      </c>
+      <c r="J41" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$F$41</f>
+        <v>5.5</v>
+      </c>
+      <c r="K41" s="49" t="n">
+        <f aca="false">MAX(Diseno_Marshall!$X$17:$X$21,J4:J34)</f>
+        <v>8.3430442624375</v>
+      </c>
+      <c r="L41" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$F$41</f>
+        <v>5.5</v>
+      </c>
+      <c r="M41" s="49" t="n">
+        <f aca="false">MAX(Diseno_Marshall!$Y$17:$Y$21,L4:L34,Diseno_Marshall!$K$10)</f>
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$F$41</f>
+        <v>5.5</v>
+      </c>
+      <c r="C43" s="49" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$33*Diseno_Marshall!$F$41+Diseno_Marshall!$D$33</f>
+        <v>2.18870106667315</v>
+      </c>
+      <c r="D43" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$F$41</f>
+        <v>5.5</v>
+      </c>
+      <c r="E43" s="49" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$34*Diseno_Marshall!$F$41+Diseno_Marshall!$D$34</f>
+        <v>4.01034820144837</v>
+      </c>
+      <c r="F43" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$F$41</f>
+        <v>5.5</v>
+      </c>
+      <c r="G43" s="49" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$35*Diseno_Marshall!$F$41+Diseno_Marshall!$D$35</f>
+        <v>14.8795112559337</v>
+      </c>
+      <c r="H43" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$F$41</f>
+        <v>5.5</v>
+      </c>
+      <c r="I43" s="49" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$36*Diseno_Marshall!$F$41+Diseno_Marshall!$D$36</f>
+        <v>73.3429311270575</v>
+      </c>
+      <c r="J43" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$F$41</f>
+        <v>5.5</v>
+      </c>
+      <c r="K43" s="49" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$37*Diseno_Marshall!$F$41+Diseno_Marshall!$D$37</f>
+        <v>7.97744287523311</v>
+      </c>
+      <c r="L43" s="48" t="n">
+        <f aca="false">Diseno_Marshall!$F$41</f>
+        <v>5.5</v>
+      </c>
+      <c r="M43" s="49" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$38*Diseno_Marshall!$F$41+Diseno_Marshall!$D$38</f>
+        <v>4.00450640616563</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D45" s="49" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)</f>
+        <v>5.5</v>
+      </c>
+      <c r="E45" s="49" t="n">
+        <f aca="false">Diseno_Marshall!$J$11</f>
+        <v>3</v>
+      </c>
+      <c r="F45" s="49" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)</f>
+        <v>5.5</v>
+      </c>
+      <c r="G45" s="49" t="n">
+        <f aca="false">Diseno_Marshall!$J$12</f>
+        <v>14</v>
+      </c>
+      <c r="H45" s="49" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)</f>
+        <v>5.5</v>
+      </c>
+      <c r="I45" s="49" t="n">
+        <f aca="false">Diseno_Marshall!$J$13</f>
+        <v>65</v>
+      </c>
+      <c r="J45" s="49" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)</f>
+        <v>5.5</v>
+      </c>
+      <c r="K45" s="49" t="n">
+        <f aca="false">Diseno_Marshall!$J$9</f>
+        <v>5.44</v>
+      </c>
+      <c r="L45" s="49" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)</f>
+        <v>5.5</v>
+      </c>
+      <c r="M45" s="49" t="n">
+        <f aca="false">Diseno_Marshall!$J$10</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D46" s="49" t="n">
+        <f aca="false">MAX(Diseno_Marshall!$B$17:$B$21)</f>
+        <v>10</v>
+      </c>
+      <c r="E46" s="49" t="n">
+        <f aca="false">Diseno_Marshall!$J$11</f>
+        <v>3</v>
+      </c>
+      <c r="F46" s="49" t="n">
+        <f aca="false">MAX(Diseno_Marshall!$B$17:$B$21)</f>
+        <v>10</v>
+      </c>
+      <c r="G46" s="49" t="n">
+        <f aca="false">Diseno_Marshall!$J$12</f>
+        <v>14</v>
+      </c>
+      <c r="H46" s="49" t="n">
+        <f aca="false">MAX(Diseno_Marshall!$B$17:$B$21)</f>
+        <v>10</v>
+      </c>
+      <c r="I46" s="49" t="n">
+        <f aca="false">Diseno_Marshall!$J$13</f>
+        <v>65</v>
+      </c>
+      <c r="J46" s="49" t="n">
+        <f aca="false">MAX(Diseno_Marshall!$B$17:$B$21)</f>
+        <v>10</v>
+      </c>
+      <c r="K46" s="49" t="n">
+        <f aca="false">Diseno_Marshall!$J$9</f>
+        <v>5.44</v>
+      </c>
+      <c r="L46" s="49" t="n">
+        <f aca="false">MAX(Diseno_Marshall!$B$17:$B$21)</f>
+        <v>10</v>
+      </c>
+      <c r="M46" s="49" t="n">
+        <f aca="false">Diseno_Marshall!$J$10</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D48" s="49" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)</f>
+        <v>5.5</v>
+      </c>
+      <c r="E48" s="49" t="n">
+        <f aca="false">Diseno_Marshall!$K$11</f>
+        <v>5</v>
+      </c>
+      <c r="H48" s="49" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)</f>
+        <v>5.5</v>
+      </c>
+      <c r="I48" s="49" t="n">
+        <f aca="false">Diseno_Marshall!$K$13</f>
+        <v>78</v>
+      </c>
+      <c r="L48" s="49" t="n">
+        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)</f>
+        <v>5.5</v>
+      </c>
+      <c r="M48" s="49" t="n">
+        <f aca="false">Diseno_Marshall!$K$10</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D49" s="49" t="n">
+        <f aca="false">MAX(Diseno_Marshall!$B$17:$B$21)</f>
+        <v>10</v>
+      </c>
+      <c r="E49" s="49" t="n">
+        <f aca="false">Diseno_Marshall!$K$11</f>
+        <v>5</v>
+      </c>
+      <c r="H49" s="49" t="n">
+        <f aca="false">MAX(Diseno_Marshall!$B$17:$B$21)</f>
+        <v>10</v>
+      </c>
+      <c r="I49" s="49" t="n">
+        <f aca="false">Diseno_Marshall!$K$13</f>
+        <v>78</v>
+      </c>
+      <c r="L49" s="49" t="n">
+        <f aca="false">MAX(Diseno_Marshall!$B$17:$B$21)</f>
+        <v>10</v>
+      </c>
+      <c r="M49" s="49" t="n">
+        <f aca="false">Diseno_Marshall!$K$10</f>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/marshall/Diseno_Marshall_MAC2_PEN120_150_corregido.xlsx
+++ b/marshall/Diseno_Marshall_MAC2_PEN120_150_corregido.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Datos_Graficas" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Graficas_Marshall!$A$1:$T$75</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Graficas_Marshall!$A$1:$U$58</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -144,7 +144,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="125">
   <si>
     <t xml:space="preserve">LABORATORIO DE ASFALTOS</t>
   </si>
@@ -463,36 +463,30 @@
     <t xml:space="preserve">10. Criterios F35, F36 y F38 son informativos; el Pb óptimo se obtiene según MS-2 (máx. Gmb, máx. estabilidad, Va objetivo).</t>
   </si>
   <si>
-    <t xml:space="preserve">DISEÑO DE MEZCLAS ASFÁLTICAS EN CALIENTE - MÉTODO MARSHALL: CURVAS DE DISEÑO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cómo leer las gráficas:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor en Pb de diseño</t>
-  </si>
-  <si>
-    <t xml:space="preserve">●  Círculos: briquetas ensayadas (M1-M5).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">━  Línea continua: ajuste parabólico (criterio MS-2).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- -  Línea roja discontinua: límites de especificación (EG-2013 / MS-2).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">┆  Línea gris: Pb de diseño adoptado.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">◆  Rombo amarillo: valor de la propiedad en el Pb de diseño.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nota: Gsb y Gmm son valores supuestos (ver observación 8 en Diseno_Marshall).</t>
+    <t xml:space="preserve">DISEÑO DE MEZCLA ASFÁLTICA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MÉTODO MARSHALL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROPIEDAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESPECIFICACIÓN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESULTADO</t>
   </si>
   <si>
     <t xml:space="preserve">DISEÑO GLOBAL</t>
   </si>
   <si>
+    <t xml:space="preserve">Nota: la línea naranja indica la lectura de cada propiedad en el contenido óptimo de asfalto. Gsb y Gmm son valores supuestos (ver observación 8 en Diseno_Marshall).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Altura (mm)</t>
   </si>
   <si>
@@ -502,43 +496,55 @@
     <t xml:space="preserve">Fuente: MTC E 504 / ASTM D6927 (interpolación lineal).</t>
   </si>
   <si>
-    <t xml:space="preserve">Datos auxiliares para las gráficas (no editar: todo es fórmula enlazada a Diseno_Marshall)</t>
+    <t xml:space="preserve">Datos auxiliares de las gráficas (fórmulas enlazadas a Diseno_Marshall; los límites de eje son fijos y editables en la fila 40)</t>
   </si>
   <si>
     <t xml:space="preserve">Gmb ajustado</t>
   </si>
   <si>
+    <t xml:space="preserve">Estabilidad ajustado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flujo ajustado</t>
+  </si>
+  <si>
     <t xml:space="preserve">Va ajustado</t>
   </si>
   <si>
+    <t xml:space="preserve">VFA ajustado</t>
+  </si>
+  <si>
     <t xml:space="preserve">VMA ajustado</t>
   </si>
   <si>
-    <t xml:space="preserve">VFA ajustado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estabilidad ajustado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flujo ajustado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gmb: líneas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Va: líneas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VMA: líneas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VFA: líneas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estabilidad: líneas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flujo: líneas</t>
+    <t xml:space="preserve">Eje X:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gmb: eje Y mín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eje Y máx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estabilidad: eje Y mín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flujo: eje Y mín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Va: eje Y mín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VFA: eje Y mín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VMA: eje Y mín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X lectura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y lectura</t>
   </si>
 </sst>
 </file>
@@ -554,7 +560,7 @@
     <numFmt numFmtId="169" formatCode="0"/>
     <numFmt numFmtId="170" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -620,101 +626,73 @@
       <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="15"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <sz val="14"/>
+      <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
-      <sz val="11"/>
-      <color rgb="FF1F3864"/>
-      <name val="Calibri"/>
+      <sz val="9"/>
+      <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="8"/>
+      <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF404040"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF1F3864"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF404040"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="9"/>
-      <color rgb="FFC00000"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="13"/>
-      <color rgb="FF1F3864"/>
-      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF404040"/>
-      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF404040"/>
-      <name val="Calibri"/>
+      <sz val="8.5"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF404040"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -724,7 +702,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
-        <bgColor rgb="FF1F4E79"/>
+        <bgColor rgb="FF003366"/>
       </patternFill>
     </fill>
     <fill>
@@ -736,7 +714,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
-        <bgColor rgb="FFE7E6E6"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -748,19 +726,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE2EFDA"/>
-        <bgColor rgb="FFE7E6E6"/>
+        <bgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F3864"/>
-        <bgColor rgb="FF1F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2E75B6"/>
-        <bgColor rgb="FF008080"/>
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -788,18 +760,10 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FFA6A6A6"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFA6A6A6"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFA6A6A6"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA6A6A6"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -828,7 +792,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="46">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -941,63 +905,55 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1005,11 +961,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1018,14 +974,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1109,7 +1057,7 @@
     <indexedColors>
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFC00000"/>
+      <rgbColor rgb="FFFF0000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -1118,19 +1066,19 @@
       <rgbColor rgb="FF9C0006"/>
       <rgbColor rgb="FF006100"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF548235"/>
+      <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFBFBFBF"/>
+      <rgbColor rgb="FFC0C0C0"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF7030A0"/>
+      <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF2CC"/>
       <rgbColor rgb="FFE2EFDA"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF1F4E78"/>
-      <rgbColor rgb="FFD9E1F2"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -1140,29 +1088,29 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFE7E6E6"/>
+      <rgbColor rgb="FFD9E1F2"/>
       <rgbColor rgb="FFC6EFCE"/>
       <rgbColor rgb="FFFCE4D6"/>
-      <rgbColor rgb="FFFBFBFB"/>
+      <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFC7CE"/>
-      <rgbColor rgb="FF2E75B6"/>
+      <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFC000"/>
-      <rgbColor rgb="FFBF9000"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFC55A11"/>
-      <rgbColor rgb="FF595959"/>
-      <rgbColor rgb="FFA6A6A6"/>
-      <rgbColor rgb="FF1F3864"/>
-      <rgbColor rgb="FF7F7F7F"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF1F4E79"/>
-      <rgbColor rgb="FF404040"/>
+      <rgbColor rgb="FF1F4E78"/>
+      <rgbColor rgb="FF333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -1180,21 +1128,21 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1300" spc="-1" strike="noStrike">
+              <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="1f3864"/>
+                  <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1300" spc="-1" strike="noStrike">
+              <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="1f3864"/>
+                  <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:rPr>
-              <a:t>Gmb vs contenido de asfalto</a:t>
+              <a:t>PESO ESPECÍFICO  VS. % DE ASFALTO</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1217,22 +1165,22 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Ajuste polinómico (2.º grado)"</c:f>
+              <c:f>"Ajuste"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Ajuste polinómico (2.º grado)</c:v>
+                  <c:v>Ajuste</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="1f4e79"/>
+              <a:srgbClr val="000000"/>
             </a:solidFill>
-            <a:ln w="28440">
+            <a:ln w="12600">
               <a:solidFill>
-                <a:srgbClr val="1f4e79"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1269,7 +1217,7 @@
             <c:numRef>
               <c:f>Datos_Graficas!$A$4:$A$34</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>5.5</c:v>
@@ -1469,36 +1417,36 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Briquetas ensayadas"</c:f>
+              <c:f>"Ensayo"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Briquetas ensayadas</c:v>
+                  <c:v>Ensayo</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="1f4e79"/>
+              <a:srgbClr val="000080"/>
             </a:solidFill>
             <a:ln w="28440">
               <a:noFill/>
             </a:ln>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="8"/>
+            <c:symbol val="diamond"/>
+            <c:size val="7"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="1f4e79"/>
+                <a:srgbClr val="000080"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
@@ -1575,55 +1523,99 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Pb de diseño"</c:f>
+              <c:f>"Lectura"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Pb de diseño</c:v>
+                  <c:v>Lectura</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="595959"/>
+              <a:srgbClr val="c55a11"/>
             </a:solidFill>
-            <a:ln w="15840">
+            <a:ln w="19080">
               <a:solidFill>
-                <a:srgbClr val="595959"/>
+                <a:srgbClr val="c55a11"/>
               </a:solidFill>
-              <a:prstDash val="sysDash"/>
               <a:round/>
             </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:marker>
+              <c:symbol val="none"/>
+            </c:marker>
+          </c:dPt>
           <c:dLbls>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:numFmt formatCode="0.000" sourceLinked="1"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:ln w="9360">
+                  <a:solidFill>
+                    <a:srgbClr val="0"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Arial"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:separator>; </c:separator>
+            </c:dLbl>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -1633,85 +1625,129 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>Datos_Graficas!$B$40:$B$41</c:f>
+              <c:f>Datos_Graficas!$B$43:$B$45</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>5.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Datos_Graficas!$C$40:$C$41</c:f>
+              <c:f>Datos_Graficas!$C$43:$C$45</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>2.15946205571566</c:v>
+                  <c:v>2.14</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.20736434108527</c:v>
+                  <c:v>2.18870106667315</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.18870106667315</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Valor en Pb de diseño"</c:f>
+              <c:f>Datos_Graficas!$B$46</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Valor en Pb de diseño</c:v>
+                  <c:v>5.5</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="ffc000"/>
+              <a:srgbClr val="ffffff"/>
             </a:solidFill>
             <a:ln w="28440">
               <a:noFill/>
             </a:ln>
           </c:spPr>
           <c:marker>
-            <c:symbol val="diamond"/>
-            <c:size val="11"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="ffc000"/>
-              </a:solidFill>
-            </c:spPr>
+            <c:symbol val="none"/>
           </c:marker>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:marker>
+              <c:symbol val="none"/>
+            </c:marker>
+          </c:dPt>
           <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:ln w="9360">
+                  <a:solidFill>
+                    <a:srgbClr val="0"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Arial"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="1"/>
+              <c:showPercent val="0"/>
+              <c:separator>; </c:separator>
+            </c:dLbl>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -1723,7 +1759,7 @@
             <c:numRef>
               <c:f>Datos_Graficas!$B$43</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>5.5</c:v>
@@ -1735,21 +1771,21 @@
             <c:numRef>
               <c:f>Datos_Graficas!$C$43</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>2.18870106667315</c:v>
+                  <c:v>2.14</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="32058585"/>
-        <c:axId val="22537604"/>
+        <c:axId val="266131"/>
+        <c:axId val="97547305"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="32058585"/>
+        <c:axId val="266131"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -1761,12 +1797,22 @@
           <c:spPr>
             <a:ln w="6480">
               <a:solidFill>
-                <a:srgbClr val="e7e6e6"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="3240">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -1774,21 +1820,21 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr b="1" sz="850" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="404040"/>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr b="1" sz="850" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="404040"/>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Arial"/>
                   </a:rPr>
-                  <a:t>Contenido de asfalto Pb (%)</a:t>
+                  <a:t>ASFALTO (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -1808,7 +1854,7 @@
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="7f7f7f"/>
+              <a:srgbClr val="000000"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -1818,24 +1864,26 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="800" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="404040"/>
+                  <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="22537604"/>
+        <c:crossAx val="97547305"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="22537604"/>
+        <c:axId val="97547305"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="2.22"/>
+          <c:min val="2.14"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1843,7 +1891,7 @@
           <c:spPr>
             <a:ln w="6480">
               <a:solidFill>
-                <a:srgbClr val="e7e6e6"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1856,21 +1904,21 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr b="1" sz="850" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="404040"/>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr b="1" sz="850" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="404040"/>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Arial"/>
                   </a:rPr>
-                  <a:t>Gmb (g/cm³)</a:t>
+                  <a:t>PESO ESPECÍFICO Gmb (g/cm³)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -1890,7 +1938,7 @@
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="7f7f7f"/>
+              <a:srgbClr val="000000"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -1900,52 +1948,32 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="800" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="404040"/>
+                  <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32058585"/>
+        <c:crossAx val="266131"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="0.01"/>
       </c:valAx>
       <c:spPr>
         <a:solidFill>
-          <a:srgbClr val="fbfbfb"/>
+          <a:srgbClr val="ffffff"/>
         </a:solidFill>
-        <a:ln w="0">
-          <a:noFill/>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
         </a:ln>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr b="0" sz="800" spc="-1" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="404040"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
   </c:chart>
@@ -1954,10 +1982,7 @@
       <a:srgbClr val="ffffff"/>
     </a:solidFill>
     <a:ln w="9360">
-      <a:solidFill>
-        <a:srgbClr val="bfbfbf"/>
-      </a:solidFill>
-      <a:round/>
+      <a:noFill/>
     </a:ln>
   </c:spPr>
 </c:chartSpace>
@@ -1975,21 +2000,21 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1300" spc="-1" strike="noStrike">
+              <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="1f3864"/>
+                  <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1300" spc="-1" strike="noStrike">
+              <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="1f3864"/>
+                  <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:rPr>
-              <a:t>Vacíos de aire Va vs contenido de asfalto</a:t>
+              <a:t>ESTABILIDAD  VS. % DE ASFALTO</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2012,22 +2037,22 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Ajuste polinómico (2.º grado)"</c:f>
+              <c:f>"Ajuste"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Ajuste polinómico (2.º grado)</c:v>
+                  <c:v>Ajuste</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="c55a11"/>
+              <a:srgbClr val="000000"/>
             </a:solidFill>
-            <a:ln w="28440">
+            <a:ln w="12600">
               <a:solidFill>
-                <a:srgbClr val="c55a11"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2064,7 +2089,7 @@
             <c:numRef>
               <c:f>Datos_Graficas!$A$4:$A$34</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>5.5</c:v>
@@ -2164,136 +2189,136 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Datos_Graficas!$D$4:$D$34</c:f>
+              <c:f>Datos_Graficas!$E$4:$E$34</c:f>
               <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>4.01034820144837</c:v>
+                  <c:v>7.97744287523311</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.85699523095454</c:v>
+                  <c:v>7.66288161089468</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.70257122650614</c:v>
+                  <c:v>7.3658123459464</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.54707618810316</c:v>
+                  <c:v>7.08623508038827</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.39051011574561</c:v>
+                  <c:v>6.82414981422028</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.23287300943348</c:v>
+                  <c:v>6.57955654744245</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.07416486916676</c:v>
+                  <c:v>6.35245528005476</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.91438569494548</c:v>
+                  <c:v>6.14284601205722</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.75353548676961</c:v>
+                  <c:v>5.95072874344983</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.59161424463917</c:v>
+                  <c:v>5.77610347423259</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.42862196855415</c:v>
+                  <c:v>5.61897020440549</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.26455865851456</c:v>
+                  <c:v>5.47932893396854</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.09942431452038</c:v>
+                  <c:v>5.35717966292174</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.93321893657163</c:v>
+                  <c:v>5.25252239126509</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.76594252466831</c:v>
+                  <c:v>5.16535711899859</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.5975950788104</c:v>
+                  <c:v>5.09568384612222</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.42817659899792</c:v>
+                  <c:v>5.04350257263601</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.25768708523086</c:v>
+                  <c:v>5.00881329853996</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.08612653750923</c:v>
+                  <c:v>4.99161602383404</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.913494955833012</c:v>
+                  <c:v>4.99191074851828</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.739792340202222</c:v>
+                  <c:v>5.00969747259266</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.565018690616853</c:v>
+                  <c:v>5.04497619605719</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.389174007076909</c:v>
+                  <c:v>5.09774691891186</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.212258289582387</c:v>
+                  <c:v>5.16800964115669</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.0342715381332894</c:v>
+                  <c:v>5.25576436279166</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-0.144786247270387</c:v>
+                  <c:v>5.36101108381679</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>-0.324915066628643</c:v>
+                  <c:v>5.48374980423206</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>-0.506114919941473</c:v>
+                  <c:v>5.62398052403748</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>-0.68838580720888</c:v>
+                  <c:v>5.78170324323304</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>-0.871727728430864</c:v>
+                  <c:v>5.95691796181875</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>-1.05614068360743</c:v>
+                  <c:v>6.14962467979462</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Briquetas ensayadas"</c:f>
+              <c:f>"Ensayo"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Briquetas ensayadas</c:v>
+                  <c:v>Ensayo</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="c55a11"/>
+              <a:srgbClr val="000080"/>
             </a:solidFill>
             <a:ln w="28440">
               <a:noFill/>
             </a:ln>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="8"/>
+            <c:symbol val="diamond"/>
+            <c:size val="7"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="c55a11"/>
+                <a:srgbClr val="000080"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
@@ -2348,77 +2373,121 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Diseno_Marshall!$R$17:$R$21</c:f>
+              <c:f>Diseno_Marshall!$X$17:$X$21</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>3.18577451380388</c:v>
+                  <c:v>8.3430442624375</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.67099605878815</c:v>
+                  <c:v>6.09957816776875</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.94272395191875</c:v>
+                  <c:v>6.7947335855</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.861768433924621</c:v>
+                  <c:v>4.9686005140625</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-0.92964858911984</c:v>
+                  <c:v>6.14724584175625</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Especificación mín"</c:f>
+              <c:f>"Lectura"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Especificación mín</c:v>
+                  <c:v>Lectura</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="c00000"/>
+              <a:srgbClr val="c55a11"/>
             </a:solidFill>
             <a:ln w="19080">
               <a:solidFill>
-                <a:srgbClr val="c00000"/>
+                <a:srgbClr val="c55a11"/>
               </a:solidFill>
-              <a:prstDash val="dash"/>
               <a:round/>
             </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:marker>
+              <c:symbol val="none"/>
+            </c:marker>
+          </c:dPt>
           <c:dLbls>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:numFmt formatCode="0.00" sourceLinked="1"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:ln w="9360">
+                  <a:solidFill>
+                    <a:srgbClr val="0"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Arial"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:separator>; </c:separator>
+            </c:dLbl>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -2428,83 +2497,129 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>Datos_Graficas!$D$45:$D$46</c:f>
+              <c:f>Datos_Graficas!$E$43:$E$45</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>5.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10</c:v>
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Datos_Graficas!$E$45:$E$46</c:f>
+              <c:f>Datos_Graficas!$F$43:$F$45</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3</c:v>
+                  <c:v>7.97744287523311</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.97744287523311</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Especificación máx"</c:f>
+              <c:f>Datos_Graficas!$E$46</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Especificación máx</c:v>
+                  <c:v>5.5</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="c00000"/>
+              <a:srgbClr val="ffffff"/>
             </a:solidFill>
-            <a:ln w="19080">
-              <a:solidFill>
-                <a:srgbClr val="c00000"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-              <a:round/>
+            <a:ln w="28440">
+              <a:noFill/>
             </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:marker>
+              <c:symbol val="none"/>
+            </c:marker>
+          </c:dPt>
           <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:ln w="9360">
+                  <a:solidFill>
+                    <a:srgbClr val="0"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Arial"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="1"/>
+              <c:showPercent val="0"/>
+              <c:separator>; </c:separator>
+            </c:dLbl>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -2514,209 +2629,35 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>Datos_Graficas!$D$48:$D$49</c:f>
+              <c:f>Datos_Graficas!$E$43</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>5.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Datos_Graficas!$E$48:$E$49</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>"Pb de diseño"</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Pb de diseño</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="595959"/>
-            </a:solidFill>
-            <a:ln w="15840">
-              <a:solidFill>
-                <a:srgbClr val="595959"/>
-              </a:solidFill>
-              <a:prstDash val="sysDash"/>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Datos_Graficas!$D$40:$D$41</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>5.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5.5</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Datos_Graficas!$E$40:$E$41</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>-1.05614068360743</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-        </c:ser>
-        <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>"Valor en Pb de diseño"</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Valor en Pb de diseño</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="ffc000"/>
-            </a:solidFill>
-            <a:ln w="28440">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="diamond"/>
-            <c:size val="11"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="ffc000"/>
-              </a:solidFill>
-            </c:spPr>
-          </c:marker>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Datos_Graficas!$D$43</c:f>
+              <c:f>Datos_Graficas!$F$43</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>5.5</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Datos_Graficas!$E$43</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>4.01034820144837</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="3626051"/>
-        <c:axId val="24672438"/>
+        <c:axId val="40056965"/>
+        <c:axId val="31342669"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="3626051"/>
+        <c:axId val="40056965"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -2728,12 +2669,22 @@
           <c:spPr>
             <a:ln w="6480">
               <a:solidFill>
-                <a:srgbClr val="e7e6e6"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="3240">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -2741,21 +2692,21 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr b="1" sz="850" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="404040"/>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr b="1" sz="850" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="404040"/>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Arial"/>
                   </a:rPr>
-                  <a:t>Contenido de asfalto Pb (%)</a:t>
+                  <a:t>ASFALTO (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -2775,7 +2726,7 @@
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="7f7f7f"/>
+              <a:srgbClr val="000000"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -2785,24 +2736,26 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="800" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="404040"/>
+                  <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24672438"/>
+        <c:crossAx val="31342669"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="24672438"/>
+        <c:axId val="31342669"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="9"/>
+          <c:min val="4"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -2810,7 +2763,7 @@
           <c:spPr>
             <a:ln w="6480">
               <a:solidFill>
-                <a:srgbClr val="e7e6e6"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2823,21 +2776,21 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr b="1" sz="850" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="404040"/>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr b="1" sz="850" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="404040"/>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Arial"/>
                   </a:rPr>
-                  <a:t>Vacíos de aire Va (%)</a:t>
+                  <a:t>ESTABILIDAD (kN)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -2850,14 +2803,14 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:numFmt formatCode="0.00" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="7f7f7f"/>
+              <a:srgbClr val="000000"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -2867,52 +2820,32 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="800" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="404040"/>
+                  <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="3626051"/>
+        <c:crossAx val="40056965"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:spPr>
         <a:solidFill>
-          <a:srgbClr val="fbfbfb"/>
+          <a:srgbClr val="ffffff"/>
         </a:solidFill>
-        <a:ln w="0">
-          <a:noFill/>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
         </a:ln>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr b="0" sz="800" spc="-1" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="404040"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
   </c:chart>
@@ -2921,10 +2854,7 @@
       <a:srgbClr val="ffffff"/>
     </a:solidFill>
     <a:ln w="9360">
-      <a:solidFill>
-        <a:srgbClr val="bfbfbf"/>
-      </a:solidFill>
-      <a:round/>
+      <a:noFill/>
     </a:ln>
   </c:spPr>
 </c:chartSpace>
@@ -2942,21 +2872,21 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1300" spc="-1" strike="noStrike">
+              <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="1f3864"/>
+                  <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1300" spc="-1" strike="noStrike">
+              <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="1f3864"/>
+                  <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:rPr>
-              <a:t>VMA vs contenido de asfalto</a:t>
+              <a:t>FLUJO  VS. % DE ASFALTO</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2979,22 +2909,22 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Ajuste polinómico (2.º grado)"</c:f>
+              <c:f>"Ajuste"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Ajuste polinómico (2.º grado)</c:v>
+                  <c:v>Ajuste</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="548235"/>
+              <a:srgbClr val="000000"/>
             </a:solidFill>
-            <a:ln w="28440">
+            <a:ln w="12600">
               <a:solidFill>
-                <a:srgbClr val="548235"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -3031,7 +2961,7 @@
             <c:numRef>
               <c:f>Datos_Graficas!$A$4:$A$34</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>5.5</c:v>
@@ -3131,136 +3061,136 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Datos_Graficas!$F$4:$F$34</c:f>
+              <c:f>Datos_Graficas!$H$4:$H$34</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>14.8795112559337</c:v>
+                  <c:v>4.00450640616563</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>15.0470055443678</c:v>
+                  <c:v>4.13755679642629</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>15.213275017413</c:v>
+                  <c:v>4.26761219380492</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>15.3783196750692</c:v>
+                  <c:v>4.39467259830151</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>15.5421395173365</c:v>
+                  <c:v>4.51873800991606</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>15.704734544215</c:v>
+                  <c:v>4.63980842864857</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>15.8661047557044</c:v>
+                  <c:v>4.75788385449904</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>16.026250151805</c:v>
+                  <c:v>4.87296428746748</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>16.1851707325167</c:v>
+                  <c:v>4.98504972755388</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>16.3428664978394</c:v>
+                  <c:v>5.09414017475823</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>16.4993374477732</c:v>
+                  <c:v>5.20023562908055</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>16.6545835823181</c:v>
+                  <c:v>5.30333609052084</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>16.8086049014741</c:v>
+                  <c:v>5.40344155907908</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>16.9614014052411</c:v>
+                  <c:v>5.50055203475529</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>17.1129730936192</c:v>
+                  <c:v>5.59466751754946</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>17.2633199666084</c:v>
+                  <c:v>5.68578800746159</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>17.4124420242087</c:v>
+                  <c:v>5.77391350449168</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>17.5603392664201</c:v>
+                  <c:v>5.85904400863973</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>17.7070116932425</c:v>
+                  <c:v>5.94117951990575</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>17.8524593046761</c:v>
+                  <c:v>6.02032003828972</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>17.9966821007207</c:v>
+                  <c:v>6.09646556379166</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>18.1396800813763</c:v>
+                  <c:v>6.16961609641156</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>18.2814532466431</c:v>
+                  <c:v>6.23977163614943</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>18.422001596521</c:v>
+                  <c:v>6.30693218300525</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>18.5613251310099</c:v>
+                  <c:v>6.37109773697904</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>18.6994238501099</c:v>
+                  <c:v>6.43226829807079</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>18.836297753821</c:v>
+                  <c:v>6.4904438662805</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>18.9719468421431</c:v>
+                  <c:v>6.54562444160817</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>19.1063711150764</c:v>
+                  <c:v>6.5978100240538</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>19.2395705726207</c:v>
+                  <c:v>6.6470006136174</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>19.3715452147761</c:v>
+                  <c:v>6.69319621029896</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Briquetas ensayadas"</c:f>
+              <c:f>"Ensayo"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Briquetas ensayadas</c:v>
+                  <c:v>Ensayo</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="548235"/>
+              <a:srgbClr val="000080"/>
             </a:solidFill>
             <a:ln w="28440">
               <a:noFill/>
             </a:ln>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="8"/>
+            <c:symbol val="diamond"/>
+            <c:size val="7"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="548235"/>
+                <a:srgbClr val="000080"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
@@ -3315,77 +3245,121 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Diseno_Marshall!$S$17:$S$21</c:f>
+              <c:f>Diseno_Marshall!$Y$17:$Y$21</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>14.1580534022394</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>16.4652538118223</c:v>
+                  <c:v>4.4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>15.9461224241872</c:v>
+                  <c:v>4.9</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>17.1171171171171</c:v>
+                  <c:v>5.8</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>19.4817528150862</c:v>
+                  <c:v>6.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Especificación mín"</c:f>
+              <c:f>"Lectura"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Especificación mín</c:v>
+                  <c:v>Lectura</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="c00000"/>
+              <a:srgbClr val="c55a11"/>
             </a:solidFill>
             <a:ln w="19080">
               <a:solidFill>
-                <a:srgbClr val="c00000"/>
+                <a:srgbClr val="c55a11"/>
               </a:solidFill>
-              <a:prstDash val="dash"/>
               <a:round/>
             </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:marker>
+              <c:symbol val="none"/>
+            </c:marker>
+          </c:dPt>
           <c:dLbls>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:numFmt formatCode="0.0" sourceLinked="1"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:ln w="9360">
+                  <a:solidFill>
+                    <a:srgbClr val="0"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Arial"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:separator>; </c:separator>
+            </c:dLbl>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -3395,83 +3369,129 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>Datos_Graficas!$F$45:$F$46</c:f>
+              <c:f>Datos_Graficas!$H$43:$H$45</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>5.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10</c:v>
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Datos_Graficas!$G$45:$G$46</c:f>
+              <c:f>Datos_Graficas!$I$43:$I$45</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>14</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>14</c:v>
+                  <c:v>4.00450640616563</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.00450640616563</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Pb de diseño"</c:f>
+              <c:f>Datos_Graficas!$H$46</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Pb de diseño</c:v>
+                  <c:v>5.5</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="595959"/>
+              <a:srgbClr val="ffffff"/>
             </a:solidFill>
-            <a:ln w="15840">
-              <a:solidFill>
-                <a:srgbClr val="595959"/>
-              </a:solidFill>
-              <a:prstDash val="sysDash"/>
-              <a:round/>
+            <a:ln w="28440">
+              <a:noFill/>
             </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:marker>
+              <c:symbol val="none"/>
+            </c:marker>
+          </c:dPt>
           <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:ln w="9360">
+                  <a:solidFill>
+                    <a:srgbClr val="0"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Arial"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="1"/>
+              <c:showPercent val="0"/>
+              <c:separator>; </c:separator>
+            </c:dLbl>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -3481,14 +3501,11 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>Datos_Graficas!$F$40:$F$41</c:f>
+              <c:f>Datos_Graficas!$H$43</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>5.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
                   <c:v>5.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -3496,108 +3513,23 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Datos_Graficas!$G$40:$G$41</c:f>
+              <c:f>Datos_Graficas!$I$43</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>19.4817528150862</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
         </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>"Valor en Pb de diseño"</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Valor en Pb de diseño</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="ffc000"/>
-            </a:solidFill>
-            <a:ln w="28440">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="diamond"/>
-            <c:size val="11"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="ffc000"/>
-              </a:solidFill>
-            </c:spPr>
-          </c:marker>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Datos_Graficas!$F$43</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>5.5</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Datos_Graficas!$G$43</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>14.8795112559337</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-        </c:ser>
-        <c:axId val="90983968"/>
-        <c:axId val="91180994"/>
+        <c:axId val="17115807"/>
+        <c:axId val="94011292"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="90983968"/>
+        <c:axId val="17115807"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -3609,12 +3541,22 @@
           <c:spPr>
             <a:ln w="6480">
               <a:solidFill>
-                <a:srgbClr val="e7e6e6"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="3240">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -3622,21 +3564,21 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr b="1" sz="850" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="404040"/>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr b="1" sz="850" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="404040"/>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Arial"/>
                   </a:rPr>
-                  <a:t>Contenido de asfalto Pb (%)</a:t>
+                  <a:t>ASFALTO (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -3656,7 +3598,7 @@
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="7f7f7f"/>
+              <a:srgbClr val="000000"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -3666,24 +3608,26 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="800" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="404040"/>
+                  <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91180994"/>
+        <c:crossAx val="94011292"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="91180994"/>
+        <c:axId val="94011292"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="7"/>
+          <c:min val="3"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -3691,7 +3635,7 @@
           <c:spPr>
             <a:ln w="6480">
               <a:solidFill>
-                <a:srgbClr val="e7e6e6"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -3704,21 +3648,21 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr b="1" sz="850" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="404040"/>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr b="1" sz="850" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="404040"/>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Arial"/>
                   </a:rPr>
-                  <a:t>VMA (%)</a:t>
+                  <a:t>FLUJO (mm)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -3738,7 +3682,7 @@
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="7f7f7f"/>
+              <a:srgbClr val="000000"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -3748,52 +3692,32 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="800" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="404040"/>
+                  <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90983968"/>
+        <c:crossAx val="17115807"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:spPr>
         <a:solidFill>
-          <a:srgbClr val="fbfbfb"/>
+          <a:srgbClr val="ffffff"/>
         </a:solidFill>
-        <a:ln w="0">
-          <a:noFill/>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
         </a:ln>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr b="0" sz="800" spc="-1" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="404040"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
   </c:chart>
@@ -3802,10 +3726,7 @@
       <a:srgbClr val="ffffff"/>
     </a:solidFill>
     <a:ln w="9360">
-      <a:solidFill>
-        <a:srgbClr val="bfbfbf"/>
-      </a:solidFill>
-      <a:round/>
+      <a:noFill/>
     </a:ln>
   </c:spPr>
 </c:chartSpace>
@@ -3823,21 +3744,21 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1300" spc="-1" strike="noStrike">
+              <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="1f3864"/>
+                  <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1300" spc="-1" strike="noStrike">
+              <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="1f3864"/>
+                  <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:rPr>
-              <a:t>VFA vs contenido de asfalto</a:t>
+              <a:t>% VACÍOS  VS. % DE ASFALTO</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -3860,22 +3781,22 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Ajuste polinómico (2.º grado)"</c:f>
+              <c:f>"Ajuste"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Ajuste polinómico (2.º grado)</c:v>
+                  <c:v>Ajuste</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="7030a0"/>
+              <a:srgbClr val="000000"/>
             </a:solidFill>
-            <a:ln w="28440">
+            <a:ln w="12600">
               <a:solidFill>
-                <a:srgbClr val="7030a0"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -3912,7 +3833,7 @@
             <c:numRef>
               <c:f>Datos_Graficas!$A$4:$A$34</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>5.5</c:v>
@@ -4012,136 +3933,136 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Datos_Graficas!$H$4:$H$34</c:f>
+              <c:f>Datos_Graficas!$K$4:$K$34</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>73.3429311270575</c:v>
+                  <c:v>4.01034820144837</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>74.6055150641918</c:v>
+                  <c:v>3.85699523095454</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>75.8547592833012</c:v>
+                  <c:v>3.70257122650614</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>77.0906637843856</c:v>
+                  <c:v>3.54707618810316</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>78.3132285674452</c:v>
+                  <c:v>3.39051011574561</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>79.5224536324798</c:v>
+                  <c:v>3.23287300943348</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>80.7183389794896</c:v>
+                  <c:v>3.07416486916676</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>81.9008846084744</c:v>
+                  <c:v>2.91438569494548</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>83.0700905194343</c:v>
+                  <c:v>2.75353548676961</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>84.2259567123693</c:v>
+                  <c:v>2.59161424463917</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>85.3684831872794</c:v>
+                  <c:v>2.42862196855415</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>86.4976699441645</c:v>
+                  <c:v>2.26455865851456</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>87.6135169830248</c:v>
+                  <c:v>2.09942431452038</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>88.7160243038601</c:v>
+                  <c:v>1.93321893657163</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>89.8051919066706</c:v>
+                  <c:v>1.76594252466831</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>90.8810197914561</c:v>
+                  <c:v>1.5975950788104</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>91.9435079582167</c:v>
+                  <c:v>1.42817659899792</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>92.9926564069524</c:v>
+                  <c:v>1.25768708523086</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>94.0284651376631</c:v>
+                  <c:v>1.08612653750923</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>95.050934150349</c:v>
+                  <c:v>0.913494955833012</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>96.0600634450099</c:v>
+                  <c:v>0.739792340202222</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>97.055853021646</c:v>
+                  <c:v>0.565018690616853</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>98.0383028802571</c:v>
+                  <c:v>0.389174007076909</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>99.0074130208433</c:v>
+                  <c:v>0.212258289582387</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>99.9631834434046</c:v>
+                  <c:v>0.0342715381332894</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>100.905614147941</c:v>
+                  <c:v>-0.144786247270387</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>101.834705134452</c:v>
+                  <c:v>-0.324915066628643</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>102.750456402939</c:v>
+                  <c:v>-0.506114919941473</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>103.652867953401</c:v>
+                  <c:v>-0.68838580720888</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>104.541939785837</c:v>
+                  <c:v>-0.871727728430864</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>105.417671900249</c:v>
+                  <c:v>-1.05614068360743</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Briquetas ensayadas"</c:f>
+              <c:f>"Ensayo"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Briquetas ensayadas</c:v>
+                  <c:v>Ensayo</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="7030a0"/>
+              <a:srgbClr val="000080"/>
             </a:solidFill>
             <a:ln w="28440">
               <a:noFill/>
             </a:ln>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="8"/>
+            <c:symbol val="diamond"/>
+            <c:size val="7"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="7030a0"/>
+                <a:srgbClr val="000080"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
@@ -4196,77 +4117,121 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Diseno_Marshall!$T$17:$T$21</c:f>
+              <c:f>Diseno_Marshall!$R$17:$R$21</c:f>
               <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>77.4984990994597</c:v>
+                  <c:v>3.18577451380388</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>71.6311931041457</c:v>
+                  <c:v>4.67099605878815</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>81.545833691486</c:v>
+                  <c:v>2.94272395191875</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>94.9654580965457</c:v>
+                  <c:v>0.861768433924621</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>104.771893976603</c:v>
+                  <c:v>-0.92964858911984</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Especificación mín"</c:f>
+              <c:f>"Lectura"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Especificación mín</c:v>
+                  <c:v>Lectura</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="c00000"/>
+              <a:srgbClr val="c55a11"/>
             </a:solidFill>
             <a:ln w="19080">
               <a:solidFill>
-                <a:srgbClr val="c00000"/>
+                <a:srgbClr val="c55a11"/>
               </a:solidFill>
-              <a:prstDash val="dash"/>
               <a:round/>
             </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:marker>
+              <c:symbol val="none"/>
+            </c:marker>
+          </c:dPt>
           <c:dLbls>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:numFmt formatCode="0.0" sourceLinked="1"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:ln w="9360">
+                  <a:solidFill>
+                    <a:srgbClr val="0"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Arial"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:separator>; </c:separator>
+            </c:dLbl>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -4276,83 +4241,129 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>Datos_Graficas!$H$45:$H$46</c:f>
+              <c:f>Datos_Graficas!$K$43:$K$45</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>5.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10</c:v>
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Datos_Graficas!$I$45:$I$46</c:f>
+              <c:f>Datos_Graficas!$L$43:$L$45</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>65</c:v>
+                  <c:v>-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>65</c:v>
+                  <c:v>4.01034820144837</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.01034820144837</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Especificación máx"</c:f>
+              <c:f>Datos_Graficas!$K$46</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Especificación máx</c:v>
+                  <c:v>5.5</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="c00000"/>
+              <a:srgbClr val="ffffff"/>
             </a:solidFill>
-            <a:ln w="19080">
-              <a:solidFill>
-                <a:srgbClr val="c00000"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-              <a:round/>
+            <a:ln w="28440">
+              <a:noFill/>
             </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:marker>
+              <c:symbol val="none"/>
+            </c:marker>
+          </c:dPt>
           <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:ln w="9360">
+                  <a:solidFill>
+                    <a:srgbClr val="0"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Arial"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="1"/>
+              <c:showPercent val="0"/>
+              <c:separator>; </c:separator>
+            </c:dLbl>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -4362,209 +4373,35 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>Datos_Graficas!$H$48:$H$49</c:f>
+              <c:f>Datos_Graficas!$K$43</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>5.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Datos_Graficas!$I$48:$I$49</c:f>
+              <c:f>Datos_Graficas!$L$43</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>78</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>78</c:v>
+                  <c:v>-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
         </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>"Pb de diseño"</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Pb de diseño</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="595959"/>
-            </a:solidFill>
-            <a:ln w="15840">
-              <a:solidFill>
-                <a:srgbClr val="595959"/>
-              </a:solidFill>
-              <a:prstDash val="sysDash"/>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Datos_Graficas!$H$40:$H$41</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>5.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5.5</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Datos_Graficas!$I$40:$I$41</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>65</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>105.417671900249</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-        </c:ser>
-        <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>"Valor en Pb de diseño"</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Valor en Pb de diseño</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="ffc000"/>
-            </a:solidFill>
-            <a:ln w="28440">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="diamond"/>
-            <c:size val="11"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="ffc000"/>
-              </a:solidFill>
-            </c:spPr>
-          </c:marker>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Datos_Graficas!$H$43</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>5.5</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Datos_Graficas!$I$43</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>73.3429311270575</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-        </c:ser>
-        <c:axId val="87386086"/>
-        <c:axId val="71383002"/>
+        <c:axId val="72306528"/>
+        <c:axId val="13110935"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="87386086"/>
+        <c:axId val="72306528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -4576,12 +4413,22 @@
           <c:spPr>
             <a:ln w="6480">
               <a:solidFill>
-                <a:srgbClr val="e7e6e6"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="3240">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -4589,21 +4436,21 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr b="1" sz="850" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="404040"/>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr b="1" sz="850" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="404040"/>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Arial"/>
                   </a:rPr>
-                  <a:t>Contenido de asfalto Pb (%)</a:t>
+                  <a:t>ASFALTO (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -4623,7 +4470,7 @@
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="7f7f7f"/>
+              <a:srgbClr val="000000"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -4633,24 +4480,26 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="800" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="404040"/>
+                  <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71383002"/>
+        <c:crossAx val="13110935"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="71383002"/>
+        <c:axId val="13110935"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="6"/>
+          <c:min val="-2"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -4658,7 +4507,7 @@
           <c:spPr>
             <a:ln w="6480">
               <a:solidFill>
-                <a:srgbClr val="e7e6e6"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -4671,21 +4520,21 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr b="1" sz="850" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="404040"/>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr b="1" sz="850" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="404040"/>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Arial"/>
                   </a:rPr>
-                  <a:t>VFA (%)</a:t>
+                  <a:t>VACÍOS Va (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -4705,7 +4554,7 @@
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="7f7f7f"/>
+              <a:srgbClr val="000000"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -4715,52 +4564,32 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="800" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="404040"/>
+                  <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87386086"/>
+        <c:crossAx val="72306528"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="1"/>
       </c:valAx>
       <c:spPr>
         <a:solidFill>
-          <a:srgbClr val="fbfbfb"/>
+          <a:srgbClr val="ffffff"/>
         </a:solidFill>
-        <a:ln w="0">
-          <a:noFill/>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
         </a:ln>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr b="0" sz="800" spc="-1" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="404040"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
   </c:chart>
@@ -4769,10 +4598,7 @@
       <a:srgbClr val="ffffff"/>
     </a:solidFill>
     <a:ln w="9360">
-      <a:solidFill>
-        <a:srgbClr val="bfbfbf"/>
-      </a:solidFill>
-      <a:round/>
+      <a:noFill/>
     </a:ln>
   </c:spPr>
 </c:chartSpace>
@@ -4790,21 +4616,21 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1300" spc="-1" strike="noStrike">
+              <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="1f3864"/>
+                  <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1300" spc="-1" strike="noStrike">
+              <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="1f3864"/>
+                  <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:rPr>
-              <a:t>Estabilidad vs contenido de asfalto</a:t>
+              <a:t>% VACÍOS LLENOS CON ASFALTO  VS. % DE ASFALTO</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -4827,22 +4653,22 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Ajuste polinómico (2.º grado)"</c:f>
+              <c:f>"Ajuste"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Ajuste polinómico (2.º grado)</c:v>
+                  <c:v>Ajuste</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="2e75b6"/>
+              <a:srgbClr val="000000"/>
             </a:solidFill>
-            <a:ln w="28440">
+            <a:ln w="12600">
               <a:solidFill>
-                <a:srgbClr val="2e75b6"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -4879,7 +4705,7 @@
             <c:numRef>
               <c:f>Datos_Graficas!$A$4:$A$34</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>5.5</c:v>
@@ -4979,136 +4805,136 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Datos_Graficas!$J$4:$J$34</c:f>
+              <c:f>Datos_Graficas!$N$4:$N$34</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>7.97744287523311</c:v>
+                  <c:v>73.3429311270575</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.66288161089468</c:v>
+                  <c:v>74.6055150641918</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.3658123459464</c:v>
+                  <c:v>75.8547592833012</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.08623508038827</c:v>
+                  <c:v>77.0906637843856</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.82414981422028</c:v>
+                  <c:v>78.3132285674452</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.57955654744245</c:v>
+                  <c:v>79.5224536324798</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6.35245528005476</c:v>
+                  <c:v>80.7183389794896</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.14284601205722</c:v>
+                  <c:v>81.9008846084744</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.95072874344983</c:v>
+                  <c:v>83.0700905194343</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5.77610347423259</c:v>
+                  <c:v>84.2259567123693</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5.61897020440549</c:v>
+                  <c:v>85.3684831872794</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>5.47932893396854</c:v>
+                  <c:v>86.4976699441645</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>5.35717966292174</c:v>
+                  <c:v>87.6135169830248</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>5.25252239126509</c:v>
+                  <c:v>88.7160243038601</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>5.16535711899859</c:v>
+                  <c:v>89.8051919066706</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>5.09568384612222</c:v>
+                  <c:v>90.8810197914561</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>5.04350257263601</c:v>
+                  <c:v>91.9435079582167</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5.00881329853996</c:v>
+                  <c:v>92.9926564069524</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4.99161602383404</c:v>
+                  <c:v>94.0284651376631</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4.99191074851828</c:v>
+                  <c:v>95.050934150349</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>5.00969747259266</c:v>
+                  <c:v>96.0600634450099</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>5.04497619605719</c:v>
+                  <c:v>97.055853021646</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>5.09774691891186</c:v>
+                  <c:v>98.0383028802571</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>5.16800964115669</c:v>
+                  <c:v>99.0074130208433</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>5.25576436279166</c:v>
+                  <c:v>99.9631834434046</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>5.36101108381679</c:v>
+                  <c:v>100.905614147941</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>5.48374980423206</c:v>
+                  <c:v>101.834705134452</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>5.62398052403748</c:v>
+                  <c:v>102.750456402939</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>5.78170324323304</c:v>
+                  <c:v>103.652867953401</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>5.95691796181875</c:v>
+                  <c:v>104.541939785837</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>6.14962467979462</c:v>
+                  <c:v>105.417671900249</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Briquetas ensayadas"</c:f>
+              <c:f>"Ensayo"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Briquetas ensayadas</c:v>
+                  <c:v>Ensayo</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="2e75b6"/>
+              <a:srgbClr val="000080"/>
             </a:solidFill>
             <a:ln w="28440">
               <a:noFill/>
             </a:ln>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="8"/>
+            <c:symbol val="diamond"/>
+            <c:size val="7"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="2e75b6"/>
+                <a:srgbClr val="000080"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
@@ -5163,77 +4989,121 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Diseno_Marshall!$X$17:$X$21</c:f>
+              <c:f>Diseno_Marshall!$T$17:$T$21</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>8.3430442624375</c:v>
+                  <c:v>77.4984990994597</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.09957816776875</c:v>
+                  <c:v>71.6311931041457</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.7947335855</c:v>
+                  <c:v>81.545833691486</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.9686005140625</c:v>
+                  <c:v>94.9654580965457</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.14724584175625</c:v>
+                  <c:v>104.771893976603</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Especificación mín"</c:f>
+              <c:f>"Lectura"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Especificación mín</c:v>
+                  <c:v>Lectura</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="c00000"/>
+              <a:srgbClr val="c55a11"/>
             </a:solidFill>
             <a:ln w="19080">
               <a:solidFill>
-                <a:srgbClr val="c00000"/>
+                <a:srgbClr val="c55a11"/>
               </a:solidFill>
-              <a:prstDash val="dash"/>
               <a:round/>
             </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:marker>
+              <c:symbol val="none"/>
+            </c:marker>
+          </c:dPt>
           <c:dLbls>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:numFmt formatCode="0.0" sourceLinked="1"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:ln w="9360">
+                  <a:solidFill>
+                    <a:srgbClr val="0"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Arial"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:separator>; </c:separator>
+            </c:dLbl>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -5243,83 +5113,129 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>Datos_Graficas!$J$45:$J$46</c:f>
+              <c:f>Datos_Graficas!$N$43:$N$45</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>5.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10</c:v>
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Datos_Graficas!$K$45:$K$46</c:f>
+              <c:f>Datos_Graficas!$O$43:$O$45</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>5.44</c:v>
+                  <c:v>60</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.44</c:v>
+                  <c:v>73.3429311270575</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>73.3429311270575</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Pb de diseño"</c:f>
+              <c:f>Datos_Graficas!$N$46</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Pb de diseño</c:v>
+                  <c:v>5.5</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="595959"/>
+              <a:srgbClr val="ffffff"/>
             </a:solidFill>
-            <a:ln w="15840">
-              <a:solidFill>
-                <a:srgbClr val="595959"/>
-              </a:solidFill>
-              <a:prstDash val="sysDash"/>
-              <a:round/>
+            <a:ln w="28440">
+              <a:noFill/>
             </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:marker>
+              <c:symbol val="none"/>
+            </c:marker>
+          </c:dPt>
           <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:ln w="9360">
+                  <a:solidFill>
+                    <a:srgbClr val="0"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Arial"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="1"/>
+              <c:showPercent val="0"/>
+              <c:separator>; </c:separator>
+            </c:dLbl>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -5329,14 +5245,11 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>Datos_Graficas!$J$40:$J$41</c:f>
+              <c:f>Datos_Graficas!$N$43</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>5.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
                   <c:v>5.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -5344,108 +5257,23 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Datos_Graficas!$K$40:$K$41</c:f>
+              <c:f>Datos_Graficas!$O$43</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>4.9686005140625</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>8.3430442624375</c:v>
+                  <c:v>60</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
         </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>"Valor en Pb de diseño"</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Valor en Pb de diseño</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="ffc000"/>
-            </a:solidFill>
-            <a:ln w="28440">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="diamond"/>
-            <c:size val="11"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="ffc000"/>
-              </a:solidFill>
-            </c:spPr>
-          </c:marker>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Datos_Graficas!$J$43</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>5.5</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Datos_Graficas!$K$43</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>7.97744287523311</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-        </c:ser>
-        <c:axId val="17333692"/>
-        <c:axId val="85536873"/>
+        <c:axId val="84729830"/>
+        <c:axId val="54195394"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="17333692"/>
+        <c:axId val="84729830"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -5457,12 +5285,22 @@
           <c:spPr>
             <a:ln w="6480">
               <a:solidFill>
-                <a:srgbClr val="e7e6e6"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="3240">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -5470,21 +5308,21 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr b="1" sz="850" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="404040"/>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr b="1" sz="850" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="404040"/>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Arial"/>
                   </a:rPr>
-                  <a:t>Contenido de asfalto Pb (%)</a:t>
+                  <a:t>ASFALTO (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -5504,7 +5342,7 @@
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="7f7f7f"/>
+              <a:srgbClr val="000000"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -5514,24 +5352,26 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="800" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="404040"/>
+                  <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85536873"/>
+        <c:crossAx val="54195394"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="85536873"/>
+        <c:axId val="54195394"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="110"/>
+          <c:min val="60"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -5539,7 +5379,7 @@
           <c:spPr>
             <a:ln w="6480">
               <a:solidFill>
-                <a:srgbClr val="e7e6e6"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -5552,21 +5392,21 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr b="1" sz="850" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="404040"/>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr b="1" sz="850" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="404040"/>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Arial"/>
                   </a:rPr>
-                  <a:t>Estabilidad (kN)</a:t>
+                  <a:t>VACÍOS LLENOS VFA (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -5579,14 +5419,14 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0.00" sourceLinked="0"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="7f7f7f"/>
+              <a:srgbClr val="000000"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -5596,52 +5436,32 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="800" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="404040"/>
+                  <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17333692"/>
+        <c:crossAx val="84729830"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="10"/>
       </c:valAx>
       <c:spPr>
         <a:solidFill>
-          <a:srgbClr val="fbfbfb"/>
+          <a:srgbClr val="ffffff"/>
         </a:solidFill>
-        <a:ln w="0">
-          <a:noFill/>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
         </a:ln>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr b="0" sz="800" spc="-1" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="404040"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
   </c:chart>
@@ -5650,10 +5470,7 @@
       <a:srgbClr val="ffffff"/>
     </a:solidFill>
     <a:ln w="9360">
-      <a:solidFill>
-        <a:srgbClr val="bfbfbf"/>
-      </a:solidFill>
-      <a:round/>
+      <a:noFill/>
     </a:ln>
   </c:spPr>
 </c:chartSpace>
@@ -5671,21 +5488,21 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1300" spc="-1" strike="noStrike">
+              <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="1f3864"/>
+                  <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1300" spc="-1" strike="noStrike">
+              <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="1f3864"/>
+                  <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:rPr>
-              <a:t>Flujo vs contenido de asfalto</a:t>
+              <a:t>% VACÍOS DEL AGREGADO MINERAL  VS. % DE ASFALTO</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -5708,22 +5525,22 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Ajuste polinómico (2.º grado)"</c:f>
+              <c:f>"Ajuste"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Ajuste polinómico (2.º grado)</c:v>
+                  <c:v>Ajuste</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="bf9000"/>
+              <a:srgbClr val="000000"/>
             </a:solidFill>
-            <a:ln w="28440">
+            <a:ln w="12600">
               <a:solidFill>
-                <a:srgbClr val="bf9000"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -5760,7 +5577,7 @@
             <c:numRef>
               <c:f>Datos_Graficas!$A$4:$A$34</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>5.5</c:v>
@@ -5860,136 +5677,136 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Datos_Graficas!$L$4:$L$34</c:f>
+              <c:f>Datos_Graficas!$Q$4:$Q$34</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>4.00450640616563</c:v>
+                  <c:v>14.8795112559337</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.13755679642629</c:v>
+                  <c:v>15.0470055443678</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.26761219380492</c:v>
+                  <c:v>15.213275017413</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.39467259830151</c:v>
+                  <c:v>15.3783196750692</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.51873800991606</c:v>
+                  <c:v>15.5421395173365</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.63980842864857</c:v>
+                  <c:v>15.704734544215</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.75788385449904</c:v>
+                  <c:v>15.8661047557044</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.87296428746748</c:v>
+                  <c:v>16.026250151805</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.98504972755388</c:v>
+                  <c:v>16.1851707325167</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5.09414017475823</c:v>
+                  <c:v>16.3428664978394</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5.20023562908055</c:v>
+                  <c:v>16.4993374477732</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>5.30333609052084</c:v>
+                  <c:v>16.6545835823181</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>5.40344155907908</c:v>
+                  <c:v>16.8086049014741</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>5.50055203475529</c:v>
+                  <c:v>16.9614014052411</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>5.59466751754946</c:v>
+                  <c:v>17.1129730936192</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>5.68578800746159</c:v>
+                  <c:v>17.2633199666084</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>5.77391350449168</c:v>
+                  <c:v>17.4124420242087</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5.85904400863973</c:v>
+                  <c:v>17.5603392664201</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>5.94117951990575</c:v>
+                  <c:v>17.7070116932425</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>6.02032003828972</c:v>
+                  <c:v>17.8524593046761</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>6.09646556379166</c:v>
+                  <c:v>17.9966821007207</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>6.16961609641156</c:v>
+                  <c:v>18.1396800813763</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>6.23977163614943</c:v>
+                  <c:v>18.2814532466431</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>6.30693218300525</c:v>
+                  <c:v>18.422001596521</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>6.37109773697904</c:v>
+                  <c:v>18.5613251310099</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>6.43226829807079</c:v>
+                  <c:v>18.6994238501099</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>6.4904438662805</c:v>
+                  <c:v>18.836297753821</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>6.54562444160817</c:v>
+                  <c:v>18.9719468421431</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>6.5978100240538</c:v>
+                  <c:v>19.1063711150764</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>6.6470006136174</c:v>
+                  <c:v>19.2395705726207</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>6.69319621029896</c:v>
+                  <c:v>19.3715452147761</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Briquetas ensayadas"</c:f>
+              <c:f>"Ensayo"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Briquetas ensayadas</c:v>
+                  <c:v>Ensayo</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="bf9000"/>
+              <a:srgbClr val="000080"/>
             </a:solidFill>
             <a:ln w="28440">
               <a:noFill/>
             </a:ln>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="8"/>
+            <c:symbol val="diamond"/>
+            <c:size val="7"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="bf9000"/>
+                <a:srgbClr val="000080"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
@@ -6044,77 +5861,121 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Diseno_Marshall!$Y$17:$Y$21</c:f>
+              <c:f>Diseno_Marshall!$S$17:$S$21</c:f>
               <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>4</c:v>
+                  <c:v>14.1580534022394</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.4</c:v>
+                  <c:v>16.4652538118223</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.9</c:v>
+                  <c:v>15.9461224241872</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.8</c:v>
+                  <c:v>17.1171171171171</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.7</c:v>
+                  <c:v>19.4817528150862</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Especificación mín"</c:f>
+              <c:f>"Lectura"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Especificación mín</c:v>
+                  <c:v>Lectura</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="c00000"/>
+              <a:srgbClr val="c55a11"/>
             </a:solidFill>
             <a:ln w="19080">
               <a:solidFill>
-                <a:srgbClr val="c00000"/>
+                <a:srgbClr val="c55a11"/>
               </a:solidFill>
-              <a:prstDash val="dash"/>
               <a:round/>
             </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:marker>
+              <c:symbol val="none"/>
+            </c:marker>
+          </c:dPt>
           <c:dLbls>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:numFmt formatCode="0.0" sourceLinked="1"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:ln w="9360">
+                  <a:solidFill>
+                    <a:srgbClr val="0"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Arial"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:separator>; </c:separator>
+            </c:dLbl>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -6124,83 +5985,129 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>Datos_Graficas!$L$45:$L$46</c:f>
+              <c:f>Datos_Graficas!$Q$43:$Q$45</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>5.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10</c:v>
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Datos_Graficas!$M$45:$M$46</c:f>
+              <c:f>Datos_Graficas!$R$43:$R$45</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>2</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>14.8795112559337</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14.8795112559337</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Especificación máx"</c:f>
+              <c:f>Datos_Graficas!$Q$46</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Especificación máx</c:v>
+                  <c:v>5.5</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="c00000"/>
+              <a:srgbClr val="ffffff"/>
             </a:solidFill>
-            <a:ln w="19080">
-              <a:solidFill>
-                <a:srgbClr val="c00000"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-              <a:round/>
+            <a:ln w="28440">
+              <a:noFill/>
             </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:marker>
+              <c:symbol val="none"/>
+            </c:marker>
+          </c:dPt>
           <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:ln w="9360">
+                  <a:solidFill>
+                    <a:srgbClr val="0"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Arial"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="1"/>
+              <c:showPercent val="0"/>
+              <c:separator>; </c:separator>
+            </c:dLbl>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -6210,209 +6117,35 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>Datos_Graficas!$L$48:$L$49</c:f>
+              <c:f>Datos_Graficas!$Q$43</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>5.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Datos_Graficas!$M$48:$M$49</c:f>
+              <c:f>Datos_Graficas!$R$43</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
         </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>"Pb de diseño"</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Pb de diseño</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="595959"/>
-            </a:solidFill>
-            <a:ln w="15840">
-              <a:solidFill>
-                <a:srgbClr val="595959"/>
-              </a:solidFill>
-              <a:prstDash val="sysDash"/>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Datos_Graficas!$L$40:$L$41</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>5.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5.5</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Datos_Graficas!$M$40:$M$41</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>6.7</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-        </c:ser>
-        <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>"Valor en Pb de diseño"</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Valor en Pb de diseño</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="ffc000"/>
-            </a:solidFill>
-            <a:ln w="28440">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="diamond"/>
-            <c:size val="11"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="ffc000"/>
-              </a:solidFill>
-            </c:spPr>
-          </c:marker>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Datos_Graficas!$L$43</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>5.5</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Datos_Graficas!$M$43</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>4.00450640616563</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-        </c:ser>
-        <c:axId val="58777112"/>
-        <c:axId val="85576025"/>
+        <c:axId val="96345383"/>
+        <c:axId val="8954568"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="58777112"/>
+        <c:axId val="96345383"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -6424,12 +6157,22 @@
           <c:spPr>
             <a:ln w="6480">
               <a:solidFill>
-                <a:srgbClr val="e7e6e6"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="3240">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -6437,21 +6180,21 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr b="1" sz="850" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="404040"/>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr b="1" sz="850" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="404040"/>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Arial"/>
                   </a:rPr>
-                  <a:t>Contenido de asfalto Pb (%)</a:t>
+                  <a:t>ASFALTO (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -6471,7 +6214,7 @@
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="7f7f7f"/>
+              <a:srgbClr val="000000"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -6481,24 +6224,26 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="800" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="404040"/>
+                  <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85576025"/>
+        <c:crossAx val="8954568"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="85576025"/>
+        <c:axId val="8954568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="21"/>
+          <c:min val="12"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -6506,7 +6251,7 @@
           <c:spPr>
             <a:ln w="6480">
               <a:solidFill>
-                <a:srgbClr val="e7e6e6"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -6519,21 +6264,21 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr b="1" sz="850" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="404040"/>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr b="1" sz="850" spc="-1" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="404040"/>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Arial"/>
                   </a:rPr>
-                  <a:t>Flujo (mm)</a:t>
+                  <a:t>VMA (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -6553,7 +6298,7 @@
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="7f7f7f"/>
+              <a:srgbClr val="000000"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -6563,52 +6308,32 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="800" spc="-1" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="404040"/>
+                  <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58777112"/>
+        <c:crossAx val="96345383"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="1"/>
       </c:valAx>
       <c:spPr>
         <a:solidFill>
-          <a:srgbClr val="fbfbfb"/>
+          <a:srgbClr val="ffffff"/>
         </a:solidFill>
-        <a:ln w="0">
-          <a:noFill/>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
         </a:ln>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr b="0" sz="800" spc="-1" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="404040"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
   </c:chart>
@@ -6617,10 +6342,7 @@
       <a:srgbClr val="ffffff"/>
     </a:solidFill>
     <a:ln w="9360">
-      <a:solidFill>
-        <a:srgbClr val="bfbfbf"/>
-      </a:solidFill>
-      <a:round/>
+      <a:noFill/>
     </a:ln>
   </c:spPr>
 </c:chartSpace>
@@ -6632,14 +6354,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>131040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>692280</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>181080</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>721440</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>121680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6647,8 +6369,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="2828880"/>
-        <a:ext cx="5759640" cy="3419640"/>
+        <a:off x="0" y="952560"/>
+        <a:ext cx="4499640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6660,16 +6382,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>131040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>692280</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>181080</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>721440</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>121680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6677,8 +6399,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="8445600" y="2828880"/>
-        <a:ext cx="5759640" cy="3419640"/>
+        <a:off x="5289480" y="952560"/>
+        <a:ext cx="4499640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6690,16 +6412,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>131040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>692280</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>181080</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>721080</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>121680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6707,8 +6429,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="6638760"/>
-        <a:ext cx="5759640" cy="3419640"/>
+        <a:off x="10578960" y="952560"/>
+        <a:ext cx="4499640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6720,16 +6442,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>130680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>692280</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>181080</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>721440</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>121320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6737,8 +6459,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="8445600" y="6638760"/>
-        <a:ext cx="5759640" cy="3419640"/>
+        <a:off x="0" y="4762440"/>
+        <a:ext cx="4499640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6750,16 +6472,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>130680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>692280</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>181080</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>721440</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>121320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6767,8 +6489,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="10449000"/>
-        <a:ext cx="5759640" cy="3419640"/>
+        <a:off x="5289480" y="4762440"/>
+        <a:ext cx="4499640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6780,16 +6502,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>130680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>692280</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>181080</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>721080</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>121320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6797,8 +6519,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="8445600" y="10449000"/>
-        <a:ext cx="5759640" cy="3419640"/>
+        <a:off x="10578960" y="4762440"/>
+        <a:ext cx="4499640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -8601,343 +8323,363 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:T12"/>
+  <dimension ref="A2:U58"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="1" style="0" width="9.5"/>
-  </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="28" t="s">
+    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="29" t="str">
-        <f aca="false">Diseno_Marshall!C4&amp;"  |  C.A. "&amp;Diseno_Marshall!C5&amp;"  |  "&amp;Diseno_Marshall!C6</f>
-        <v>MAC-2 fina (huso MAC-2, MTC EG-2013)  |  C.A. PEN 120-150  |  50 golpes por cara</v>
-      </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="29"/>
-      <c r="T2" s="29"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="30" t="str">
-        <f aca="false">" RESUMEN EN EL CONTENIDO ÓPTIMO DE ASFALTO  Pb = "&amp;TEXT(Diseno_Marshall!F41,"0.0")&amp;" %"</f>
-        <v> RESUMEN EN EL CONTENIDO ÓPTIMO DE ASFALTO  Pb = 5.5 %</v>
-      </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="L3" s="31" t="s">
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="28"/>
+    </row>
+    <row r="3" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="28" t="s">
         <v>98</v>
       </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="28"/>
+      <c r="P3" s="28"/>
+      <c r="Q3" s="28"/>
+      <c r="R3" s="28"/>
+      <c r="S3" s="28"/>
+      <c r="T3" s="28"/>
+      <c r="U3" s="28"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32" t="s">
+      <c r="A4" s="29" t="str">
+        <f aca="false">Diseno_Marshall!C4&amp;"  -  C.A. "&amp;Diseno_Marshall!C5&amp;"  -  "&amp;Diseno_Marshall!C6</f>
+        <v>MAC-2 fina (huso MAC-2, MTC EG-2013)  -  C.A. PEN 120-150  -  50 golpes por cara</v>
+      </c>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="29"/>
+      <c r="O4" s="29"/>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="29"/>
+      <c r="R4" s="29"/>
+      <c r="S4" s="29"/>
+      <c r="T4" s="29"/>
+      <c r="U4" s="29"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G47" s="30" t="str">
+        <f aca="false">"RESUMEN DE DISEÑO  -  CONTENIDO ÓPTIMO DE ASFALTO = "&amp;TEXT(Diseno_Marshall!F41,"0.0")&amp;" %"</f>
+        <v>RESUMEN DE DISEÑO  -  CONTENIDO ÓPTIMO DE ASFALTO = 5.5 %</v>
+      </c>
+      <c r="H47" s="30"/>
+      <c r="I47" s="30"/>
+      <c r="J47" s="30"/>
+      <c r="K47" s="30"/>
+      <c r="L47" s="30"/>
+      <c r="M47" s="30"/>
+      <c r="N47" s="30"/>
+      <c r="O47" s="30"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G48" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="J4" s="32"/>
-      <c r="L4" s="33" t="s">
+      <c r="H48" s="31"/>
+      <c r="I48" s="31"/>
+      <c r="J48" s="31" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="34" t="str">
+      <c r="K48" s="31"/>
+      <c r="L48" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="M48" s="31"/>
+      <c r="N48" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="O48" s="31"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G49" s="32" t="str">
         <f aca="false">Diseno_Marshall!A45</f>
         <v>Gmb</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="35" t="n">
+      <c r="H49" s="32"/>
+      <c r="I49" s="32"/>
+      <c r="J49" s="33" t="n">
         <f aca="false">Diseno_Marshall!B45</f>
         <v>2.18870106667315</v>
       </c>
-      <c r="E5" s="35"/>
-      <c r="F5" s="36" t="str">
+      <c r="K49" s="33"/>
+      <c r="L49" s="34" t="str">
         <f aca="false">Diseno_Marshall!C45</f>
         <v>-</v>
       </c>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36" t="str">
+      <c r="M49" s="34"/>
+      <c r="N49" s="34" t="str">
         <f aca="false">Diseno_Marshall!D45</f>
         <v>-</v>
       </c>
-      <c r="J5" s="36"/>
-      <c r="L5" s="33" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="34" t="str">
+      <c r="O49" s="34"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G50" s="32" t="str">
         <f aca="false">Diseno_Marshall!A46</f>
         <v>Va (%)</v>
       </c>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="37" t="n">
+      <c r="H50" s="32"/>
+      <c r="I50" s="32"/>
+      <c r="J50" s="35" t="n">
         <f aca="false">Diseno_Marshall!B46</f>
         <v>4.01034820144837</v>
       </c>
-      <c r="E6" s="37"/>
-      <c r="F6" s="36" t="str">
+      <c r="K50" s="35"/>
+      <c r="L50" s="34" t="str">
         <f aca="false">Diseno_Marshall!C46</f>
         <v>3 - 5 %</v>
       </c>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36" t="str">
+      <c r="M50" s="34"/>
+      <c r="N50" s="34" t="str">
         <f aca="false">Diseno_Marshall!D46</f>
         <v>CUMPLE</v>
       </c>
-      <c r="J6" s="36"/>
-      <c r="L6" s="33" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="34" t="str">
+      <c r="O50" s="34"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G51" s="32" t="str">
         <f aca="false">Diseno_Marshall!A47</f>
         <v>VMA (%)</v>
       </c>
-      <c r="B7" s="34"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="37" t="n">
+      <c r="H51" s="32"/>
+      <c r="I51" s="32"/>
+      <c r="J51" s="35" t="n">
         <f aca="false">Diseno_Marshall!B47</f>
         <v>14.8795112559337</v>
       </c>
-      <c r="E7" s="37"/>
-      <c r="F7" s="36" t="str">
+      <c r="K51" s="35"/>
+      <c r="L51" s="34" t="str">
         <f aca="false">Diseno_Marshall!C47</f>
         <v>≥ 14 %</v>
       </c>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36" t="str">
+      <c r="M51" s="34"/>
+      <c r="N51" s="34" t="str">
         <f aca="false">Diseno_Marshall!D47</f>
         <v>CUMPLE</v>
       </c>
-      <c r="J7" s="36"/>
-      <c r="L7" s="33" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="34" t="str">
+      <c r="O51" s="34"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G52" s="32" t="str">
         <f aca="false">Diseno_Marshall!A48</f>
         <v>VFA (%)</v>
       </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="37" t="n">
+      <c r="H52" s="32"/>
+      <c r="I52" s="32"/>
+      <c r="J52" s="35" t="n">
         <f aca="false">Diseno_Marshall!B48</f>
         <v>73.3429311270575</v>
       </c>
-      <c r="E8" s="37"/>
-      <c r="F8" s="36" t="str">
+      <c r="K52" s="35"/>
+      <c r="L52" s="34" t="str">
         <f aca="false">Diseno_Marshall!C48</f>
         <v>65 - 78 %</v>
       </c>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36" t="str">
+      <c r="M52" s="34"/>
+      <c r="N52" s="34" t="str">
         <f aca="false">Diseno_Marshall!D48</f>
         <v>CUMPLE</v>
       </c>
-      <c r="J8" s="36"/>
-      <c r="L8" s="33" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="34" t="str">
+      <c r="O52" s="34"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G53" s="32" t="str">
         <f aca="false">Diseno_Marshall!A49</f>
         <v>Estabilidad (kN)</v>
       </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="38" t="n">
+      <c r="H53" s="32"/>
+      <c r="I53" s="32"/>
+      <c r="J53" s="36" t="n">
         <f aca="false">Diseno_Marshall!B49</f>
         <v>7.97744287523311</v>
       </c>
-      <c r="E9" s="38"/>
-      <c r="F9" s="36" t="str">
+      <c r="K53" s="36"/>
+      <c r="L53" s="34" t="str">
         <f aca="false">Diseno_Marshall!C49</f>
         <v>≥ 5.44 kN</v>
       </c>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36" t="str">
+      <c r="M53" s="34"/>
+      <c r="N53" s="34" t="str">
         <f aca="false">Diseno_Marshall!D49</f>
         <v>CUMPLE</v>
       </c>
-      <c r="J9" s="36"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="34" t="str">
+      <c r="O53" s="34"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G54" s="32" t="str">
         <f aca="false">Diseno_Marshall!A50</f>
         <v>Flujo (mm)</v>
       </c>
-      <c r="B10" s="34"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="37" t="n">
+      <c r="H54" s="32"/>
+      <c r="I54" s="32"/>
+      <c r="J54" s="35" t="n">
         <f aca="false">Diseno_Marshall!B50</f>
         <v>4.00450640616563</v>
       </c>
-      <c r="E10" s="37"/>
-      <c r="F10" s="36" t="str">
+      <c r="K54" s="35"/>
+      <c r="L54" s="34" t="str">
         <f aca="false">Diseno_Marshall!C50</f>
         <v>2 - 4 mm</v>
       </c>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36" t="str">
+      <c r="M54" s="34"/>
+      <c r="N54" s="34" t="str">
         <f aca="false">Diseno_Marshall!D50</f>
         <v>CUMPLE</v>
       </c>
-      <c r="J10" s="36"/>
-      <c r="L10" s="39" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="34" t="str">
+      <c r="O54" s="34"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G55" s="32" t="str">
         <f aca="false">Diseno_Marshall!A51</f>
         <v>Estab./Flujo (kg/cm)</v>
       </c>
-      <c r="B11" s="34"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="40" t="n">
+      <c r="H55" s="32"/>
+      <c r="I55" s="32"/>
+      <c r="J55" s="37" t="n">
         <f aca="false">Diseno_Marshall!B51</f>
         <v>2031.39338857235</v>
       </c>
-      <c r="E11" s="40"/>
-      <c r="F11" s="36" t="str">
+      <c r="K55" s="37"/>
+      <c r="L55" s="34" t="str">
         <f aca="false">Diseno_Marshall!C51</f>
         <v>1700 - 4000 kg/cm</v>
       </c>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36" t="str">
+      <c r="M55" s="34"/>
+      <c r="N55" s="34" t="str">
         <f aca="false">Diseno_Marshall!D51</f>
         <v>CUMPLE</v>
       </c>
-      <c r="J11" s="36"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="41" t="s">
-        <v>106</v>
-      </c>
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="42" t="str">
+      <c r="O55" s="34"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G56" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="H56" s="38"/>
+      <c r="I56" s="38"/>
+      <c r="J56" s="38"/>
+      <c r="K56" s="38"/>
+      <c r="L56" s="38"/>
+      <c r="M56" s="38"/>
+      <c r="N56" s="39" t="str">
         <f aca="false">Diseno_Marshall!D52</f>
         <v>CUMPLE</v>
       </c>
-      <c r="J12" s="42"/>
+      <c r="O56" s="39"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="B58" s="40"/>
+      <c r="C58" s="40"/>
+      <c r="D58" s="40"/>
+      <c r="E58" s="40"/>
+      <c r="F58" s="40"/>
+      <c r="G58" s="40"/>
+      <c r="H58" s="40"/>
+      <c r="I58" s="40"/>
+      <c r="J58" s="40"/>
+      <c r="K58" s="40"/>
+      <c r="L58" s="40"/>
+      <c r="M58" s="40"/>
+      <c r="N58" s="40"/>
+      <c r="O58" s="40"/>
+      <c r="P58" s="40"/>
+      <c r="Q58" s="40"/>
+      <c r="R58" s="40"/>
+      <c r="S58" s="40"/>
+      <c r="T58" s="40"/>
+      <c r="U58" s="40"/>
     </row>
   </sheetData>
-  <mergeCells count="37">
-    <mergeCell ref="A1:T1"/>
-    <mergeCell ref="A2:T2"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="I12:J12"/>
+  <mergeCells count="39">
+    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A3:U3"/>
+    <mergeCell ref="A4:U4"/>
+    <mergeCell ref="G47:O47"/>
+    <mergeCell ref="G48:I48"/>
+    <mergeCell ref="J48:K48"/>
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="N48:O48"/>
+    <mergeCell ref="G49:I49"/>
+    <mergeCell ref="J49:K49"/>
+    <mergeCell ref="L49:M49"/>
+    <mergeCell ref="N49:O49"/>
+    <mergeCell ref="G50:I50"/>
+    <mergeCell ref="J50:K50"/>
+    <mergeCell ref="L50:M50"/>
+    <mergeCell ref="N50:O50"/>
+    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="J51:K51"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="N51:O51"/>
+    <mergeCell ref="G52:I52"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="G53:I53"/>
+    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="N53:O53"/>
+    <mergeCell ref="G54:I54"/>
+    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="L54:M54"/>
+    <mergeCell ref="N54:O54"/>
+    <mergeCell ref="G55:I55"/>
+    <mergeCell ref="J55:K55"/>
+    <mergeCell ref="L55:M55"/>
+    <mergeCell ref="N55:O55"/>
+    <mergeCell ref="G56:M56"/>
+    <mergeCell ref="N56:O56"/>
+    <mergeCell ref="A58:U58"/>
   </mergeCells>
-  <conditionalFormatting sqref="I5:J12">
+  <conditionalFormatting sqref="N49:O56">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>"CUMPLE"</formula>
     </cfRule>
@@ -8947,7 +8689,7 @@
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -8969,14 +8711,14 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="B1" s="43" t="s">
-        <v>108</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9259,1274 +9001,1255 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:R46"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="42" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="E3" s="42" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="45" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3" s="45" t="s">
+      <c r="H3" s="42" t="s">
         <v>111</v>
       </c>
-      <c r="D3" s="45" t="s">
+      <c r="K3" s="42" t="s">
         <v>112</v>
       </c>
-      <c r="F3" s="45" t="s">
+      <c r="N3" s="42" t="s">
         <v>113</v>
       </c>
-      <c r="H3" s="45" t="s">
+      <c r="Q3" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="J3" s="45" t="s">
-        <v>115</v>
-      </c>
-      <c r="L3" s="45" t="s">
-        <v>116</v>
-      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+0*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>5.5</v>
       </c>
-      <c r="B4" s="46" t="n">
+      <c r="B4" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*A4^2+Diseno_Marshall!$C$33*A4+Diseno_Marshall!$D$33</f>
         <v>2.18870106667315</v>
       </c>
-      <c r="D4" s="47" t="n">
+      <c r="E4" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A4^2+Diseno_Marshall!$C$37*A4+Diseno_Marshall!$D$37</f>
+        <v>7.97744287523311</v>
+      </c>
+      <c r="H4" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A4^2+Diseno_Marshall!$C$38*A4+Diseno_Marshall!$D$38</f>
+        <v>4.00450640616563</v>
+      </c>
+      <c r="K4" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A4^2+Diseno_Marshall!$C$34*A4+Diseno_Marshall!$D$34</f>
         <v>4.01034820144837</v>
       </c>
-      <c r="F4" s="47" t="n">
+      <c r="N4" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A4^2+Diseno_Marshall!$C$36*A4+Diseno_Marshall!$D$36</f>
+        <v>73.3429311270575</v>
+      </c>
+      <c r="Q4" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*A4^2+Diseno_Marshall!$C$35*A4+Diseno_Marshall!$D$35</f>
         <v>14.8795112559337</v>
       </c>
-      <c r="H4" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*A4^2+Diseno_Marshall!$C$36*A4+Diseno_Marshall!$D$36</f>
-        <v>73.3429311270575</v>
-      </c>
-      <c r="J4" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*A4^2+Diseno_Marshall!$C$37*A4+Diseno_Marshall!$D$37</f>
-        <v>7.97744287523311</v>
-      </c>
-      <c r="L4" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*A4^2+Diseno_Marshall!$C$38*A4+Diseno_Marshall!$D$38</f>
-        <v>4.00450640616563</v>
-      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+1*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>5.65</v>
       </c>
-      <c r="B5" s="46" t="n">
+      <c r="B5" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*A5^2+Diseno_Marshall!$C$33*A5+Diseno_Marshall!$D$33</f>
         <v>2.18789535266774</v>
       </c>
-      <c r="D5" s="47" t="n">
+      <c r="E5" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A5^2+Diseno_Marshall!$C$37*A5+Diseno_Marshall!$D$37</f>
+        <v>7.66288161089468</v>
+      </c>
+      <c r="H5" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A5^2+Diseno_Marshall!$C$38*A5+Diseno_Marshall!$D$38</f>
+        <v>4.13755679642629</v>
+      </c>
+      <c r="K5" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A5^2+Diseno_Marshall!$C$34*A5+Diseno_Marshall!$D$34</f>
         <v>3.85699523095454</v>
       </c>
-      <c r="F5" s="47" t="n">
+      <c r="N5" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A5^2+Diseno_Marshall!$C$36*A5+Diseno_Marshall!$D$36</f>
+        <v>74.6055150641918</v>
+      </c>
+      <c r="Q5" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*A5^2+Diseno_Marshall!$C$35*A5+Diseno_Marshall!$D$35</f>
         <v>15.0470055443678</v>
       </c>
-      <c r="H5" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*A5^2+Diseno_Marshall!$C$36*A5+Diseno_Marshall!$D$36</f>
-        <v>74.6055150641918</v>
-      </c>
-      <c r="J5" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*A5^2+Diseno_Marshall!$C$37*A5+Diseno_Marshall!$D$37</f>
-        <v>7.66288161089468</v>
-      </c>
-      <c r="L5" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*A5^2+Diseno_Marshall!$C$38*A5+Diseno_Marshall!$D$38</f>
-        <v>4.13755679642629</v>
-      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+2*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>5.8</v>
       </c>
-      <c r="B6" s="46" t="n">
+      <c r="B6" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*A6^2+Diseno_Marshall!$C$33*A6+Diseno_Marshall!$D$33</f>
         <v>2.18711795916989</v>
       </c>
-      <c r="D6" s="47" t="n">
+      <c r="E6" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A6^2+Diseno_Marshall!$C$37*A6+Diseno_Marshall!$D$37</f>
+        <v>7.3658123459464</v>
+      </c>
+      <c r="H6" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A6^2+Diseno_Marshall!$C$38*A6+Diseno_Marshall!$D$38</f>
+        <v>4.26761219380492</v>
+      </c>
+      <c r="K6" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A6^2+Diseno_Marshall!$C$34*A6+Diseno_Marshall!$D$34</f>
         <v>3.70257122650614</v>
       </c>
-      <c r="F6" s="47" t="n">
+      <c r="N6" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A6^2+Diseno_Marshall!$C$36*A6+Diseno_Marshall!$D$36</f>
+        <v>75.8547592833012</v>
+      </c>
+      <c r="Q6" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*A6^2+Diseno_Marshall!$C$35*A6+Diseno_Marshall!$D$35</f>
         <v>15.213275017413</v>
       </c>
-      <c r="H6" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*A6^2+Diseno_Marshall!$C$36*A6+Diseno_Marshall!$D$36</f>
-        <v>75.8547592833012</v>
-      </c>
-      <c r="J6" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*A6^2+Diseno_Marshall!$C$37*A6+Diseno_Marshall!$D$37</f>
-        <v>7.3658123459464</v>
-      </c>
-      <c r="L6" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*A6^2+Diseno_Marshall!$C$38*A6+Diseno_Marshall!$D$38</f>
-        <v>4.26761219380492</v>
-      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+3*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>5.95</v>
       </c>
-      <c r="B7" s="46" t="n">
+      <c r="B7" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*A7^2+Diseno_Marshall!$C$33*A7+Diseno_Marshall!$D$33</f>
         <v>2.18636888617959</v>
       </c>
-      <c r="D7" s="47" t="n">
+      <c r="E7" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A7^2+Diseno_Marshall!$C$37*A7+Diseno_Marshall!$D$37</f>
+        <v>7.08623508038827</v>
+      </c>
+      <c r="H7" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A7^2+Diseno_Marshall!$C$38*A7+Diseno_Marshall!$D$38</f>
+        <v>4.39467259830151</v>
+      </c>
+      <c r="K7" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A7^2+Diseno_Marshall!$C$34*A7+Diseno_Marshall!$D$34</f>
         <v>3.54707618810316</v>
       </c>
-      <c r="F7" s="47" t="n">
+      <c r="N7" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A7^2+Diseno_Marshall!$C$36*A7+Diseno_Marshall!$D$36</f>
+        <v>77.0906637843856</v>
+      </c>
+      <c r="Q7" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*A7^2+Diseno_Marshall!$C$35*A7+Diseno_Marshall!$D$35</f>
         <v>15.3783196750692</v>
       </c>
-      <c r="H7" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*A7^2+Diseno_Marshall!$C$36*A7+Diseno_Marshall!$D$36</f>
-        <v>77.0906637843856</v>
-      </c>
-      <c r="J7" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*A7^2+Diseno_Marshall!$C$37*A7+Diseno_Marshall!$D$37</f>
-        <v>7.08623508038827</v>
-      </c>
-      <c r="L7" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*A7^2+Diseno_Marshall!$C$38*A7+Diseno_Marshall!$D$38</f>
-        <v>4.39467259830151</v>
-      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+4*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>6.1</v>
       </c>
-      <c r="B8" s="46" t="n">
+      <c r="B8" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*A8^2+Diseno_Marshall!$C$33*A8+Diseno_Marshall!$D$33</f>
         <v>2.18564813369684</v>
       </c>
-      <c r="D8" s="47" t="n">
+      <c r="E8" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A8^2+Diseno_Marshall!$C$37*A8+Diseno_Marshall!$D$37</f>
+        <v>6.82414981422028</v>
+      </c>
+      <c r="H8" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A8^2+Diseno_Marshall!$C$38*A8+Diseno_Marshall!$D$38</f>
+        <v>4.51873800991606</v>
+      </c>
+      <c r="K8" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A8^2+Diseno_Marshall!$C$34*A8+Diseno_Marshall!$D$34</f>
         <v>3.39051011574561</v>
       </c>
-      <c r="F8" s="47" t="n">
+      <c r="N8" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A8^2+Diseno_Marshall!$C$36*A8+Diseno_Marshall!$D$36</f>
+        <v>78.3132285674452</v>
+      </c>
+      <c r="Q8" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*A8^2+Diseno_Marshall!$C$35*A8+Diseno_Marshall!$D$35</f>
         <v>15.5421395173365</v>
       </c>
-      <c r="H8" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*A8^2+Diseno_Marshall!$C$36*A8+Diseno_Marshall!$D$36</f>
-        <v>78.3132285674452</v>
-      </c>
-      <c r="J8" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*A8^2+Diseno_Marshall!$C$37*A8+Diseno_Marshall!$D$37</f>
-        <v>6.82414981422028</v>
-      </c>
-      <c r="L8" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*A8^2+Diseno_Marshall!$C$38*A8+Diseno_Marshall!$D$38</f>
-        <v>4.51873800991606</v>
-      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+5*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>6.25</v>
       </c>
-      <c r="B9" s="46" t="n">
+      <c r="B9" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*A9^2+Diseno_Marshall!$C$33*A9+Diseno_Marshall!$D$33</f>
         <v>2.18495570172164</v>
       </c>
-      <c r="D9" s="47" t="n">
+      <c r="E9" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A9^2+Diseno_Marshall!$C$37*A9+Diseno_Marshall!$D$37</f>
+        <v>6.57955654744245</v>
+      </c>
+      <c r="H9" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A9^2+Diseno_Marshall!$C$38*A9+Diseno_Marshall!$D$38</f>
+        <v>4.63980842864857</v>
+      </c>
+      <c r="K9" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A9^2+Diseno_Marshall!$C$34*A9+Diseno_Marshall!$D$34</f>
         <v>3.23287300943348</v>
       </c>
-      <c r="F9" s="47" t="n">
+      <c r="N9" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A9^2+Diseno_Marshall!$C$36*A9+Diseno_Marshall!$D$36</f>
+        <v>79.5224536324798</v>
+      </c>
+      <c r="Q9" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*A9^2+Diseno_Marshall!$C$35*A9+Diseno_Marshall!$D$35</f>
         <v>15.704734544215</v>
       </c>
-      <c r="H9" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*A9^2+Diseno_Marshall!$C$36*A9+Diseno_Marshall!$D$36</f>
-        <v>79.5224536324798</v>
-      </c>
-      <c r="J9" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*A9^2+Diseno_Marshall!$C$37*A9+Diseno_Marshall!$D$37</f>
-        <v>6.57955654744245</v>
-      </c>
-      <c r="L9" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*A9^2+Diseno_Marshall!$C$38*A9+Diseno_Marshall!$D$38</f>
-        <v>4.63980842864857</v>
-      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+6*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>6.4</v>
       </c>
-      <c r="B10" s="46" t="n">
+      <c r="B10" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*A10^2+Diseno_Marshall!$C$33*A10+Diseno_Marshall!$D$33</f>
         <v>2.18429159025398</v>
       </c>
-      <c r="D10" s="47" t="n">
+      <c r="E10" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A10^2+Diseno_Marshall!$C$37*A10+Diseno_Marshall!$D$37</f>
+        <v>6.35245528005476</v>
+      </c>
+      <c r="H10" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A10^2+Diseno_Marshall!$C$38*A10+Diseno_Marshall!$D$38</f>
+        <v>4.75788385449904</v>
+      </c>
+      <c r="K10" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A10^2+Diseno_Marshall!$C$34*A10+Diseno_Marshall!$D$34</f>
         <v>3.07416486916676</v>
       </c>
-      <c r="F10" s="47" t="n">
+      <c r="N10" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A10^2+Diseno_Marshall!$C$36*A10+Diseno_Marshall!$D$36</f>
+        <v>80.7183389794896</v>
+      </c>
+      <c r="Q10" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*A10^2+Diseno_Marshall!$C$35*A10+Diseno_Marshall!$D$35</f>
         <v>15.8661047557044</v>
       </c>
-      <c r="H10" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*A10^2+Diseno_Marshall!$C$36*A10+Diseno_Marshall!$D$36</f>
-        <v>80.7183389794896</v>
-      </c>
-      <c r="J10" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*A10^2+Diseno_Marshall!$C$37*A10+Diseno_Marshall!$D$37</f>
-        <v>6.35245528005476</v>
-      </c>
-      <c r="L10" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*A10^2+Diseno_Marshall!$C$38*A10+Diseno_Marshall!$D$38</f>
-        <v>4.75788385449904</v>
-      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+7*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>6.55</v>
       </c>
-      <c r="B11" s="46" t="n">
+      <c r="B11" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*A11^2+Diseno_Marshall!$C$33*A11+Diseno_Marshall!$D$33</f>
         <v>2.18365579929388</v>
       </c>
-      <c r="D11" s="47" t="n">
+      <c r="E11" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A11^2+Diseno_Marshall!$C$37*A11+Diseno_Marshall!$D$37</f>
+        <v>6.14284601205722</v>
+      </c>
+      <c r="H11" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A11^2+Diseno_Marshall!$C$38*A11+Diseno_Marshall!$D$38</f>
+        <v>4.87296428746748</v>
+      </c>
+      <c r="K11" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A11^2+Diseno_Marshall!$C$34*A11+Diseno_Marshall!$D$34</f>
         <v>2.91438569494548</v>
       </c>
-      <c r="F11" s="47" t="n">
+      <c r="N11" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A11^2+Diseno_Marshall!$C$36*A11+Diseno_Marshall!$D$36</f>
+        <v>81.9008846084744</v>
+      </c>
+      <c r="Q11" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*A11^2+Diseno_Marshall!$C$35*A11+Diseno_Marshall!$D$35</f>
         <v>16.026250151805</v>
       </c>
-      <c r="H11" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*A11^2+Diseno_Marshall!$C$36*A11+Diseno_Marshall!$D$36</f>
-        <v>81.9008846084744</v>
-      </c>
-      <c r="J11" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*A11^2+Diseno_Marshall!$C$37*A11+Diseno_Marshall!$D$37</f>
-        <v>6.14284601205722</v>
-      </c>
-      <c r="L11" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*A11^2+Diseno_Marshall!$C$38*A11+Diseno_Marshall!$D$38</f>
-        <v>4.87296428746748</v>
-      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+8*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>6.7</v>
       </c>
-      <c r="B12" s="46" t="n">
+      <c r="B12" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*A12^2+Diseno_Marshall!$C$33*A12+Diseno_Marshall!$D$33</f>
         <v>2.18304832884132</v>
       </c>
-      <c r="D12" s="47" t="n">
+      <c r="E12" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A12^2+Diseno_Marshall!$C$37*A12+Diseno_Marshall!$D$37</f>
+        <v>5.95072874344983</v>
+      </c>
+      <c r="H12" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A12^2+Diseno_Marshall!$C$38*A12+Diseno_Marshall!$D$38</f>
+        <v>4.98504972755388</v>
+      </c>
+      <c r="K12" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A12^2+Diseno_Marshall!$C$34*A12+Diseno_Marshall!$D$34</f>
         <v>2.75353548676961</v>
       </c>
-      <c r="F12" s="47" t="n">
+      <c r="N12" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A12^2+Diseno_Marshall!$C$36*A12+Diseno_Marshall!$D$36</f>
+        <v>83.0700905194343</v>
+      </c>
+      <c r="Q12" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*A12^2+Diseno_Marshall!$C$35*A12+Diseno_Marshall!$D$35</f>
         <v>16.1851707325167</v>
       </c>
-      <c r="H12" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*A12^2+Diseno_Marshall!$C$36*A12+Diseno_Marshall!$D$36</f>
-        <v>83.0700905194343</v>
-      </c>
-      <c r="J12" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*A12^2+Diseno_Marshall!$C$37*A12+Diseno_Marshall!$D$37</f>
-        <v>5.95072874344983</v>
-      </c>
-      <c r="L12" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*A12^2+Diseno_Marshall!$C$38*A12+Diseno_Marshall!$D$38</f>
-        <v>4.98504972755388</v>
-      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+9*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>6.85</v>
       </c>
-      <c r="B13" s="46" t="n">
+      <c r="B13" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*A13^2+Diseno_Marshall!$C$33*A13+Diseno_Marshall!$D$33</f>
         <v>2.18246917889632</v>
       </c>
-      <c r="D13" s="47" t="n">
+      <c r="E13" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A13^2+Diseno_Marshall!$C$37*A13+Diseno_Marshall!$D$37</f>
+        <v>5.77610347423259</v>
+      </c>
+      <c r="H13" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A13^2+Diseno_Marshall!$C$38*A13+Diseno_Marshall!$D$38</f>
+        <v>5.09414017475823</v>
+      </c>
+      <c r="K13" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A13^2+Diseno_Marshall!$C$34*A13+Diseno_Marshall!$D$34</f>
         <v>2.59161424463917</v>
       </c>
-      <c r="F13" s="47" t="n">
+      <c r="N13" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A13^2+Diseno_Marshall!$C$36*A13+Diseno_Marshall!$D$36</f>
+        <v>84.2259567123693</v>
+      </c>
+      <c r="Q13" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*A13^2+Diseno_Marshall!$C$35*A13+Diseno_Marshall!$D$35</f>
         <v>16.3428664978394</v>
       </c>
-      <c r="H13" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*A13^2+Diseno_Marshall!$C$36*A13+Diseno_Marshall!$D$36</f>
-        <v>84.2259567123693</v>
-      </c>
-      <c r="J13" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*A13^2+Diseno_Marshall!$C$37*A13+Diseno_Marshall!$D$37</f>
-        <v>5.77610347423259</v>
-      </c>
-      <c r="L13" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*A13^2+Diseno_Marshall!$C$38*A13+Diseno_Marshall!$D$38</f>
-        <v>5.09414017475823</v>
-      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+10*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>7</v>
       </c>
-      <c r="B14" s="46" t="n">
+      <c r="B14" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*A14^2+Diseno_Marshall!$C$33*A14+Diseno_Marshall!$D$33</f>
         <v>2.18191834945886</v>
       </c>
-      <c r="D14" s="47" t="n">
+      <c r="E14" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A14^2+Diseno_Marshall!$C$37*A14+Diseno_Marshall!$D$37</f>
+        <v>5.61897020440549</v>
+      </c>
+      <c r="H14" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A14^2+Diseno_Marshall!$C$38*A14+Diseno_Marshall!$D$38</f>
+        <v>5.20023562908055</v>
+      </c>
+      <c r="K14" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A14^2+Diseno_Marshall!$C$34*A14+Diseno_Marshall!$D$34</f>
         <v>2.42862196855415</v>
       </c>
-      <c r="F14" s="47" t="n">
+      <c r="N14" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A14^2+Diseno_Marshall!$C$36*A14+Diseno_Marshall!$D$36</f>
+        <v>85.3684831872794</v>
+      </c>
+      <c r="Q14" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*A14^2+Diseno_Marshall!$C$35*A14+Diseno_Marshall!$D$35</f>
         <v>16.4993374477732</v>
       </c>
-      <c r="H14" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*A14^2+Diseno_Marshall!$C$36*A14+Diseno_Marshall!$D$36</f>
-        <v>85.3684831872794</v>
-      </c>
-      <c r="J14" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*A14^2+Diseno_Marshall!$C$37*A14+Diseno_Marshall!$D$37</f>
-        <v>5.61897020440549</v>
-      </c>
-      <c r="L14" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*A14^2+Diseno_Marshall!$C$38*A14+Diseno_Marshall!$D$38</f>
-        <v>5.20023562908055</v>
-      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+11*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>7.15</v>
       </c>
-      <c r="B15" s="46" t="n">
+      <c r="B15" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*A15^2+Diseno_Marshall!$C$33*A15+Diseno_Marshall!$D$33</f>
         <v>2.18139584052895</v>
       </c>
-      <c r="D15" s="47" t="n">
+      <c r="E15" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A15^2+Diseno_Marshall!$C$37*A15+Diseno_Marshall!$D$37</f>
+        <v>5.47932893396854</v>
+      </c>
+      <c r="H15" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A15^2+Diseno_Marshall!$C$38*A15+Diseno_Marshall!$D$38</f>
+        <v>5.30333609052084</v>
+      </c>
+      <c r="K15" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A15^2+Diseno_Marshall!$C$34*A15+Diseno_Marshall!$D$34</f>
         <v>2.26455865851456</v>
       </c>
-      <c r="F15" s="47" t="n">
+      <c r="N15" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A15^2+Diseno_Marshall!$C$36*A15+Diseno_Marshall!$D$36</f>
+        <v>86.4976699441645</v>
+      </c>
+      <c r="Q15" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*A15^2+Diseno_Marshall!$C$35*A15+Diseno_Marshall!$D$35</f>
         <v>16.6545835823181</v>
       </c>
-      <c r="H15" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*A15^2+Diseno_Marshall!$C$36*A15+Diseno_Marshall!$D$36</f>
-        <v>86.4976699441645</v>
-      </c>
-      <c r="J15" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*A15^2+Diseno_Marshall!$C$37*A15+Diseno_Marshall!$D$37</f>
-        <v>5.47932893396854</v>
-      </c>
-      <c r="L15" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*A15^2+Diseno_Marshall!$C$38*A15+Diseno_Marshall!$D$38</f>
-        <v>5.30333609052084</v>
-      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+      <c r="A16" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+12*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>7.3</v>
       </c>
-      <c r="B16" s="46" t="n">
+      <c r="B16" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*A16^2+Diseno_Marshall!$C$33*A16+Diseno_Marshall!$D$33</f>
         <v>2.1809016521066</v>
       </c>
-      <c r="D16" s="47" t="n">
+      <c r="E16" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A16^2+Diseno_Marshall!$C$37*A16+Diseno_Marshall!$D$37</f>
+        <v>5.35717966292174</v>
+      </c>
+      <c r="H16" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A16^2+Diseno_Marshall!$C$38*A16+Diseno_Marshall!$D$38</f>
+        <v>5.40344155907908</v>
+      </c>
+      <c r="K16" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A16^2+Diseno_Marshall!$C$34*A16+Diseno_Marshall!$D$34</f>
         <v>2.09942431452038</v>
       </c>
-      <c r="F16" s="47" t="n">
+      <c r="N16" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A16^2+Diseno_Marshall!$C$36*A16+Diseno_Marshall!$D$36</f>
+        <v>87.6135169830248</v>
+      </c>
+      <c r="Q16" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*A16^2+Diseno_Marshall!$C$35*A16+Diseno_Marshall!$D$35</f>
         <v>16.8086049014741</v>
       </c>
-      <c r="H16" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*A16^2+Diseno_Marshall!$C$36*A16+Diseno_Marshall!$D$36</f>
-        <v>87.6135169830248</v>
-      </c>
-      <c r="J16" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*A16^2+Diseno_Marshall!$C$37*A16+Diseno_Marshall!$D$37</f>
-        <v>5.35717966292174</v>
-      </c>
-      <c r="L16" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*A16^2+Diseno_Marshall!$C$38*A16+Diseno_Marshall!$D$38</f>
-        <v>5.40344155907908</v>
-      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="A17" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+13*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>7.45</v>
       </c>
-      <c r="B17" s="46" t="n">
+      <c r="B17" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*A17^2+Diseno_Marshall!$C$33*A17+Diseno_Marshall!$D$33</f>
         <v>2.18043578419179</v>
       </c>
-      <c r="D17" s="47" t="n">
+      <c r="E17" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A17^2+Diseno_Marshall!$C$37*A17+Diseno_Marshall!$D$37</f>
+        <v>5.25252239126509</v>
+      </c>
+      <c r="H17" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A17^2+Diseno_Marshall!$C$38*A17+Diseno_Marshall!$D$38</f>
+        <v>5.50055203475529</v>
+      </c>
+      <c r="K17" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A17^2+Diseno_Marshall!$C$34*A17+Diseno_Marshall!$D$34</f>
         <v>1.93321893657163</v>
       </c>
-      <c r="F17" s="47" t="n">
+      <c r="N17" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A17^2+Diseno_Marshall!$C$36*A17+Diseno_Marshall!$D$36</f>
+        <v>88.7160243038601</v>
+      </c>
+      <c r="Q17" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*A17^2+Diseno_Marshall!$C$35*A17+Diseno_Marshall!$D$35</f>
         <v>16.9614014052411</v>
       </c>
-      <c r="H17" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*A17^2+Diseno_Marshall!$C$36*A17+Diseno_Marshall!$D$36</f>
-        <v>88.7160243038601</v>
-      </c>
-      <c r="J17" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*A17^2+Diseno_Marshall!$C$37*A17+Diseno_Marshall!$D$37</f>
-        <v>5.25252239126509</v>
-      </c>
-      <c r="L17" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*A17^2+Diseno_Marshall!$C$38*A17+Diseno_Marshall!$D$38</f>
-        <v>5.50055203475529</v>
-      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+      <c r="A18" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+14*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>7.6</v>
       </c>
-      <c r="B18" s="46" t="n">
+      <c r="B18" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*A18^2+Diseno_Marshall!$C$33*A18+Diseno_Marshall!$D$33</f>
         <v>2.17999823678453</v>
       </c>
-      <c r="D18" s="47" t="n">
+      <c r="E18" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A18^2+Diseno_Marshall!$C$37*A18+Diseno_Marshall!$D$37</f>
+        <v>5.16535711899859</v>
+      </c>
+      <c r="H18" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A18^2+Diseno_Marshall!$C$38*A18+Diseno_Marshall!$D$38</f>
+        <v>5.59466751754946</v>
+      </c>
+      <c r="K18" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A18^2+Diseno_Marshall!$C$34*A18+Diseno_Marshall!$D$34</f>
         <v>1.76594252466831</v>
       </c>
-      <c r="F18" s="47" t="n">
+      <c r="N18" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A18^2+Diseno_Marshall!$C$36*A18+Diseno_Marshall!$D$36</f>
+        <v>89.8051919066706</v>
+      </c>
+      <c r="Q18" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*A18^2+Diseno_Marshall!$C$35*A18+Diseno_Marshall!$D$35</f>
         <v>17.1129730936192</v>
       </c>
-      <c r="H18" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*A18^2+Diseno_Marshall!$C$36*A18+Diseno_Marshall!$D$36</f>
-        <v>89.8051919066706</v>
-      </c>
-      <c r="J18" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*A18^2+Diseno_Marshall!$C$37*A18+Diseno_Marshall!$D$37</f>
-        <v>5.16535711899859</v>
-      </c>
-      <c r="L18" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*A18^2+Diseno_Marshall!$C$38*A18+Diseno_Marshall!$D$38</f>
-        <v>5.59466751754946</v>
-      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+      <c r="A19" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+15*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>7.75</v>
       </c>
-      <c r="B19" s="46" t="n">
+      <c r="B19" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*A19^2+Diseno_Marshall!$C$33*A19+Diseno_Marshall!$D$33</f>
         <v>2.17958900988482</v>
       </c>
-      <c r="D19" s="47" t="n">
+      <c r="E19" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A19^2+Diseno_Marshall!$C$37*A19+Diseno_Marshall!$D$37</f>
+        <v>5.09568384612222</v>
+      </c>
+      <c r="H19" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A19^2+Diseno_Marshall!$C$38*A19+Diseno_Marshall!$D$38</f>
+        <v>5.68578800746159</v>
+      </c>
+      <c r="K19" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A19^2+Diseno_Marshall!$C$34*A19+Diseno_Marshall!$D$34</f>
         <v>1.5975950788104</v>
       </c>
-      <c r="F19" s="47" t="n">
+      <c r="N19" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A19^2+Diseno_Marshall!$C$36*A19+Diseno_Marshall!$D$36</f>
+        <v>90.8810197914561</v>
+      </c>
+      <c r="Q19" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*A19^2+Diseno_Marshall!$C$35*A19+Diseno_Marshall!$D$35</f>
         <v>17.2633199666084</v>
       </c>
-      <c r="H19" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*A19^2+Diseno_Marshall!$C$36*A19+Diseno_Marshall!$D$36</f>
-        <v>90.8810197914561</v>
-      </c>
-      <c r="J19" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*A19^2+Diseno_Marshall!$C$37*A19+Diseno_Marshall!$D$37</f>
-        <v>5.09568384612222</v>
-      </c>
-      <c r="L19" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*A19^2+Diseno_Marshall!$C$38*A19+Diseno_Marshall!$D$38</f>
-        <v>5.68578800746159</v>
-      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
+      <c r="A20" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+16*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>7.9</v>
       </c>
-      <c r="B20" s="46" t="n">
+      <c r="B20" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*A20^2+Diseno_Marshall!$C$33*A20+Diseno_Marshall!$D$33</f>
         <v>2.17920810349266</v>
       </c>
-      <c r="D20" s="47" t="n">
+      <c r="E20" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A20^2+Diseno_Marshall!$C$37*A20+Diseno_Marshall!$D$37</f>
+        <v>5.04350257263601</v>
+      </c>
+      <c r="H20" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A20^2+Diseno_Marshall!$C$38*A20+Diseno_Marshall!$D$38</f>
+        <v>5.77391350449168</v>
+      </c>
+      <c r="K20" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A20^2+Diseno_Marshall!$C$34*A20+Diseno_Marshall!$D$34</f>
         <v>1.42817659899792</v>
       </c>
-      <c r="F20" s="47" t="n">
+      <c r="N20" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A20^2+Diseno_Marshall!$C$36*A20+Diseno_Marshall!$D$36</f>
+        <v>91.9435079582167</v>
+      </c>
+      <c r="Q20" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*A20^2+Diseno_Marshall!$C$35*A20+Diseno_Marshall!$D$35</f>
         <v>17.4124420242087</v>
       </c>
-      <c r="H20" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*A20^2+Diseno_Marshall!$C$36*A20+Diseno_Marshall!$D$36</f>
-        <v>91.9435079582167</v>
-      </c>
-      <c r="J20" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*A20^2+Diseno_Marshall!$C$37*A20+Diseno_Marshall!$D$37</f>
-        <v>5.04350257263601</v>
-      </c>
-      <c r="L20" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*A20^2+Diseno_Marshall!$C$38*A20+Diseno_Marshall!$D$38</f>
-        <v>5.77391350449168</v>
-      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
+      <c r="A21" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+17*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>8.05</v>
       </c>
-      <c r="B21" s="46" t="n">
+      <c r="B21" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*A21^2+Diseno_Marshall!$C$33*A21+Diseno_Marshall!$D$33</f>
         <v>2.17885551760805</v>
       </c>
-      <c r="D21" s="47" t="n">
+      <c r="E21" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A21^2+Diseno_Marshall!$C$37*A21+Diseno_Marshall!$D$37</f>
+        <v>5.00881329853996</v>
+      </c>
+      <c r="H21" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A21^2+Diseno_Marshall!$C$38*A21+Diseno_Marshall!$D$38</f>
+        <v>5.85904400863973</v>
+      </c>
+      <c r="K21" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A21^2+Diseno_Marshall!$C$34*A21+Diseno_Marshall!$D$34</f>
         <v>1.25768708523086</v>
       </c>
-      <c r="F21" s="47" t="n">
+      <c r="N21" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A21^2+Diseno_Marshall!$C$36*A21+Diseno_Marshall!$D$36</f>
+        <v>92.9926564069524</v>
+      </c>
+      <c r="Q21" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*A21^2+Diseno_Marshall!$C$35*A21+Diseno_Marshall!$D$35</f>
         <v>17.5603392664201</v>
       </c>
-      <c r="H21" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*A21^2+Diseno_Marshall!$C$36*A21+Diseno_Marshall!$D$36</f>
-        <v>92.9926564069524</v>
-      </c>
-      <c r="J21" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*A21^2+Diseno_Marshall!$C$37*A21+Diseno_Marshall!$D$37</f>
-        <v>5.00881329853996</v>
-      </c>
-      <c r="L21" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*A21^2+Diseno_Marshall!$C$38*A21+Diseno_Marshall!$D$38</f>
-        <v>5.85904400863973</v>
-      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="n">
+      <c r="A22" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+18*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>8.2</v>
       </c>
-      <c r="B22" s="46" t="n">
+      <c r="B22" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*A22^2+Diseno_Marshall!$C$33*A22+Diseno_Marshall!$D$33</f>
         <v>2.17853125223099</v>
       </c>
-      <c r="D22" s="47" t="n">
+      <c r="E22" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A22^2+Diseno_Marshall!$C$37*A22+Diseno_Marshall!$D$37</f>
+        <v>4.99161602383404</v>
+      </c>
+      <c r="H22" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A22^2+Diseno_Marshall!$C$38*A22+Diseno_Marshall!$D$38</f>
+        <v>5.94117951990575</v>
+      </c>
+      <c r="K22" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A22^2+Diseno_Marshall!$C$34*A22+Diseno_Marshall!$D$34</f>
         <v>1.08612653750923</v>
       </c>
-      <c r="F22" s="47" t="n">
+      <c r="N22" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A22^2+Diseno_Marshall!$C$36*A22+Diseno_Marshall!$D$36</f>
+        <v>94.0284651376631</v>
+      </c>
+      <c r="Q22" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*A22^2+Diseno_Marshall!$C$35*A22+Diseno_Marshall!$D$35</f>
         <v>17.7070116932425</v>
       </c>
-      <c r="H22" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*A22^2+Diseno_Marshall!$C$36*A22+Diseno_Marshall!$D$36</f>
-        <v>94.0284651376631</v>
-      </c>
-      <c r="J22" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*A22^2+Diseno_Marshall!$C$37*A22+Diseno_Marshall!$D$37</f>
-        <v>4.99161602383404</v>
-      </c>
-      <c r="L22" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*A22^2+Diseno_Marshall!$C$38*A22+Diseno_Marshall!$D$38</f>
-        <v>5.94117951990575</v>
-      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="n">
+      <c r="A23" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+19*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>8.35</v>
       </c>
-      <c r="B23" s="46" t="n">
+      <c r="B23" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*A23^2+Diseno_Marshall!$C$33*A23+Diseno_Marshall!$D$33</f>
         <v>2.17823530736148</v>
       </c>
-      <c r="D23" s="47" t="n">
+      <c r="E23" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A23^2+Diseno_Marshall!$C$37*A23+Diseno_Marshall!$D$37</f>
+        <v>4.99191074851828</v>
+      </c>
+      <c r="H23" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A23^2+Diseno_Marshall!$C$38*A23+Diseno_Marshall!$D$38</f>
+        <v>6.02032003828972</v>
+      </c>
+      <c r="K23" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A23^2+Diseno_Marshall!$C$34*A23+Diseno_Marshall!$D$34</f>
         <v>0.913494955833012</v>
       </c>
-      <c r="F23" s="47" t="n">
+      <c r="N23" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A23^2+Diseno_Marshall!$C$36*A23+Diseno_Marshall!$D$36</f>
+        <v>95.050934150349</v>
+      </c>
+      <c r="Q23" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*A23^2+Diseno_Marshall!$C$35*A23+Diseno_Marshall!$D$35</f>
         <v>17.8524593046761</v>
       </c>
-      <c r="H23" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*A23^2+Diseno_Marshall!$C$36*A23+Diseno_Marshall!$D$36</f>
-        <v>95.050934150349</v>
-      </c>
-      <c r="J23" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*A23^2+Diseno_Marshall!$C$37*A23+Diseno_Marshall!$D$37</f>
-        <v>4.99191074851828</v>
-      </c>
-      <c r="L23" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*A23^2+Diseno_Marshall!$C$38*A23+Diseno_Marshall!$D$38</f>
-        <v>6.02032003828972</v>
-      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="n">
+      <c r="A24" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+20*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>8.5</v>
       </c>
-      <c r="B24" s="46" t="n">
+      <c r="B24" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*A24^2+Diseno_Marshall!$C$33*A24+Diseno_Marshall!$D$33</f>
         <v>2.17796768299951</v>
       </c>
-      <c r="D24" s="47" t="n">
+      <c r="E24" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A24^2+Diseno_Marshall!$C$37*A24+Diseno_Marshall!$D$37</f>
+        <v>5.00969747259266</v>
+      </c>
+      <c r="H24" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A24^2+Diseno_Marshall!$C$38*A24+Diseno_Marshall!$D$38</f>
+        <v>6.09646556379166</v>
+      </c>
+      <c r="K24" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A24^2+Diseno_Marshall!$C$34*A24+Diseno_Marshall!$D$34</f>
         <v>0.739792340202222</v>
       </c>
-      <c r="F24" s="47" t="n">
+      <c r="N24" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A24^2+Diseno_Marshall!$C$36*A24+Diseno_Marshall!$D$36</f>
+        <v>96.0600634450099</v>
+      </c>
+      <c r="Q24" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*A24^2+Diseno_Marshall!$C$35*A24+Diseno_Marshall!$D$35</f>
         <v>17.9966821007207</v>
       </c>
-      <c r="H24" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*A24^2+Diseno_Marshall!$C$36*A24+Diseno_Marshall!$D$36</f>
-        <v>96.0600634450099</v>
-      </c>
-      <c r="J24" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*A24^2+Diseno_Marshall!$C$37*A24+Diseno_Marshall!$D$37</f>
-        <v>5.00969747259266</v>
-      </c>
-      <c r="L24" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*A24^2+Diseno_Marshall!$C$38*A24+Diseno_Marshall!$D$38</f>
-        <v>6.09646556379166</v>
-      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="n">
+      <c r="A25" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+21*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>8.65</v>
       </c>
-      <c r="B25" s="46" t="n">
+      <c r="B25" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*A25^2+Diseno_Marshall!$C$33*A25+Diseno_Marshall!$D$33</f>
         <v>2.1777283791451</v>
       </c>
-      <c r="D25" s="47" t="n">
+      <c r="E25" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A25^2+Diseno_Marshall!$C$37*A25+Diseno_Marshall!$D$37</f>
+        <v>5.04497619605719</v>
+      </c>
+      <c r="H25" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A25^2+Diseno_Marshall!$C$38*A25+Diseno_Marshall!$D$38</f>
+        <v>6.16961609641156</v>
+      </c>
+      <c r="K25" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A25^2+Diseno_Marshall!$C$34*A25+Diseno_Marshall!$D$34</f>
         <v>0.565018690616853</v>
       </c>
-      <c r="F25" s="47" t="n">
+      <c r="N25" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A25^2+Diseno_Marshall!$C$36*A25+Diseno_Marshall!$D$36</f>
+        <v>97.055853021646</v>
+      </c>
+      <c r="Q25" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*A25^2+Diseno_Marshall!$C$35*A25+Diseno_Marshall!$D$35</f>
         <v>18.1396800813763</v>
       </c>
-      <c r="H25" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*A25^2+Diseno_Marshall!$C$36*A25+Diseno_Marshall!$D$36</f>
-        <v>97.055853021646</v>
-      </c>
-      <c r="J25" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*A25^2+Diseno_Marshall!$C$37*A25+Diseno_Marshall!$D$37</f>
-        <v>5.04497619605719</v>
-      </c>
-      <c r="L25" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*A25^2+Diseno_Marshall!$C$38*A25+Diseno_Marshall!$D$38</f>
-        <v>6.16961609641156</v>
-      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="n">
+      <c r="A26" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+22*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>8.8</v>
       </c>
-      <c r="B26" s="46" t="n">
+      <c r="B26" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*A26^2+Diseno_Marshall!$C$33*A26+Diseno_Marshall!$D$33</f>
         <v>2.17751739579824</v>
       </c>
-      <c r="D26" s="47" t="n">
+      <c r="E26" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A26^2+Diseno_Marshall!$C$37*A26+Diseno_Marshall!$D$37</f>
+        <v>5.09774691891186</v>
+      </c>
+      <c r="H26" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A26^2+Diseno_Marshall!$C$38*A26+Diseno_Marshall!$D$38</f>
+        <v>6.23977163614943</v>
+      </c>
+      <c r="K26" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A26^2+Diseno_Marshall!$C$34*A26+Diseno_Marshall!$D$34</f>
         <v>0.389174007076909</v>
       </c>
-      <c r="F26" s="47" t="n">
+      <c r="N26" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A26^2+Diseno_Marshall!$C$36*A26+Diseno_Marshall!$D$36</f>
+        <v>98.0383028802571</v>
+      </c>
+      <c r="Q26" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*A26^2+Diseno_Marshall!$C$35*A26+Diseno_Marshall!$D$35</f>
         <v>18.2814532466431</v>
       </c>
-      <c r="H26" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*A26^2+Diseno_Marshall!$C$36*A26+Diseno_Marshall!$D$36</f>
-        <v>98.0383028802571</v>
-      </c>
-      <c r="J26" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*A26^2+Diseno_Marshall!$C$37*A26+Diseno_Marshall!$D$37</f>
-        <v>5.09774691891186</v>
-      </c>
-      <c r="L26" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*A26^2+Diseno_Marshall!$C$38*A26+Diseno_Marshall!$D$38</f>
-        <v>6.23977163614943</v>
-      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="n">
+      <c r="A27" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+23*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>8.95</v>
       </c>
-      <c r="B27" s="46" t="n">
+      <c r="B27" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*A27^2+Diseno_Marshall!$C$33*A27+Diseno_Marshall!$D$33</f>
         <v>2.17733473295892</v>
       </c>
-      <c r="D27" s="47" t="n">
+      <c r="E27" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A27^2+Diseno_Marshall!$C$37*A27+Diseno_Marshall!$D$37</f>
+        <v>5.16800964115669</v>
+      </c>
+      <c r="H27" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A27^2+Diseno_Marshall!$C$38*A27+Diseno_Marshall!$D$38</f>
+        <v>6.30693218300525</v>
+      </c>
+      <c r="K27" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A27^2+Diseno_Marshall!$C$34*A27+Diseno_Marshall!$D$34</f>
         <v>0.212258289582387</v>
       </c>
-      <c r="F27" s="47" t="n">
+      <c r="N27" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A27^2+Diseno_Marshall!$C$36*A27+Diseno_Marshall!$D$36</f>
+        <v>99.0074130208433</v>
+      </c>
+      <c r="Q27" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*A27^2+Diseno_Marshall!$C$35*A27+Diseno_Marshall!$D$35</f>
         <v>18.422001596521</v>
       </c>
-      <c r="H27" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*A27^2+Diseno_Marshall!$C$36*A27+Diseno_Marshall!$D$36</f>
-        <v>99.0074130208433</v>
-      </c>
-      <c r="J27" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*A27^2+Diseno_Marshall!$C$37*A27+Diseno_Marshall!$D$37</f>
-        <v>5.16800964115669</v>
-      </c>
-      <c r="L27" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*A27^2+Diseno_Marshall!$C$38*A27+Diseno_Marshall!$D$38</f>
-        <v>6.30693218300525</v>
-      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="n">
+      <c r="A28" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+24*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>9.1</v>
       </c>
-      <c r="B28" s="46" t="n">
+      <c r="B28" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*A28^2+Diseno_Marshall!$C$33*A28+Diseno_Marshall!$D$33</f>
         <v>2.17718039062716</v>
       </c>
-      <c r="D28" s="47" t="n">
+      <c r="E28" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A28^2+Diseno_Marshall!$C$37*A28+Diseno_Marshall!$D$37</f>
+        <v>5.25576436279166</v>
+      </c>
+      <c r="H28" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A28^2+Diseno_Marshall!$C$38*A28+Diseno_Marshall!$D$38</f>
+        <v>6.37109773697904</v>
+      </c>
+      <c r="K28" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A28^2+Diseno_Marshall!$C$34*A28+Diseno_Marshall!$D$34</f>
         <v>0.0342715381332894</v>
       </c>
-      <c r="F28" s="47" t="n">
+      <c r="N28" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A28^2+Diseno_Marshall!$C$36*A28+Diseno_Marshall!$D$36</f>
+        <v>99.9631834434046</v>
+      </c>
+      <c r="Q28" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*A28^2+Diseno_Marshall!$C$35*A28+Diseno_Marshall!$D$35</f>
         <v>18.5613251310099</v>
       </c>
-      <c r="H28" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*A28^2+Diseno_Marshall!$C$36*A28+Diseno_Marshall!$D$36</f>
-        <v>99.9631834434046</v>
-      </c>
-      <c r="J28" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*A28^2+Diseno_Marshall!$C$37*A28+Diseno_Marshall!$D$37</f>
-        <v>5.25576436279166</v>
-      </c>
-      <c r="L28" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*A28^2+Diseno_Marshall!$C$38*A28+Diseno_Marshall!$D$38</f>
-        <v>6.37109773697904</v>
-      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="n">
+      <c r="A29" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+25*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>9.25</v>
       </c>
-      <c r="B29" s="46" t="n">
+      <c r="B29" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*A29^2+Diseno_Marshall!$C$33*A29+Diseno_Marshall!$D$33</f>
         <v>2.17705436880294</v>
       </c>
-      <c r="D29" s="47" t="n">
+      <c r="E29" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A29^2+Diseno_Marshall!$C$37*A29+Diseno_Marshall!$D$37</f>
+        <v>5.36101108381679</v>
+      </c>
+      <c r="H29" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A29^2+Diseno_Marshall!$C$38*A29+Diseno_Marshall!$D$38</f>
+        <v>6.43226829807079</v>
+      </c>
+      <c r="K29" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A29^2+Diseno_Marshall!$C$34*A29+Diseno_Marshall!$D$34</f>
         <v>-0.144786247270387</v>
       </c>
-      <c r="F29" s="47" t="n">
+      <c r="N29" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A29^2+Diseno_Marshall!$C$36*A29+Diseno_Marshall!$D$36</f>
+        <v>100.905614147941</v>
+      </c>
+      <c r="Q29" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*A29^2+Diseno_Marshall!$C$35*A29+Diseno_Marshall!$D$35</f>
         <v>18.6994238501099</v>
       </c>
-      <c r="H29" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*A29^2+Diseno_Marshall!$C$36*A29+Diseno_Marshall!$D$36</f>
-        <v>100.905614147941</v>
-      </c>
-      <c r="J29" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*A29^2+Diseno_Marshall!$C$37*A29+Diseno_Marshall!$D$37</f>
-        <v>5.36101108381679</v>
-      </c>
-      <c r="L29" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*A29^2+Diseno_Marshall!$C$38*A29+Diseno_Marshall!$D$38</f>
-        <v>6.43226829807079</v>
-      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="n">
+      <c r="A30" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+26*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>9.4</v>
       </c>
-      <c r="B30" s="46" t="n">
+      <c r="B30" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*A30^2+Diseno_Marshall!$C$33*A30+Diseno_Marshall!$D$33</f>
         <v>2.17695666748628</v>
       </c>
-      <c r="D30" s="47" t="n">
+      <c r="E30" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A30^2+Diseno_Marshall!$C$37*A30+Diseno_Marshall!$D$37</f>
+        <v>5.48374980423206</v>
+      </c>
+      <c r="H30" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A30^2+Diseno_Marshall!$C$38*A30+Diseno_Marshall!$D$38</f>
+        <v>6.4904438662805</v>
+      </c>
+      <c r="K30" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A30^2+Diseno_Marshall!$C$34*A30+Diseno_Marshall!$D$34</f>
         <v>-0.324915066628643</v>
       </c>
-      <c r="F30" s="47" t="n">
+      <c r="N30" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A30^2+Diseno_Marshall!$C$36*A30+Diseno_Marshall!$D$36</f>
+        <v>101.834705134452</v>
+      </c>
+      <c r="Q30" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*A30^2+Diseno_Marshall!$C$35*A30+Diseno_Marshall!$D$35</f>
         <v>18.836297753821</v>
       </c>
-      <c r="H30" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*A30^2+Diseno_Marshall!$C$36*A30+Diseno_Marshall!$D$36</f>
-        <v>101.834705134452</v>
-      </c>
-      <c r="J30" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*A30^2+Diseno_Marshall!$C$37*A30+Diseno_Marshall!$D$37</f>
-        <v>5.48374980423206</v>
-      </c>
-      <c r="L30" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*A30^2+Diseno_Marshall!$C$38*A30+Diseno_Marshall!$D$38</f>
-        <v>6.4904438662805</v>
-      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="n">
+      <c r="A31" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+27*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>9.55</v>
       </c>
-      <c r="B31" s="46" t="n">
+      <c r="B31" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*A31^2+Diseno_Marshall!$C$33*A31+Diseno_Marshall!$D$33</f>
         <v>2.17688728667716</v>
       </c>
-      <c r="D31" s="47" t="n">
+      <c r="E31" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A31^2+Diseno_Marshall!$C$37*A31+Diseno_Marshall!$D$37</f>
+        <v>5.62398052403748</v>
+      </c>
+      <c r="H31" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A31^2+Diseno_Marshall!$C$38*A31+Diseno_Marshall!$D$38</f>
+        <v>6.54562444160817</v>
+      </c>
+      <c r="K31" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A31^2+Diseno_Marshall!$C$34*A31+Diseno_Marshall!$D$34</f>
         <v>-0.506114919941473</v>
       </c>
-      <c r="F31" s="47" t="n">
+      <c r="N31" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A31^2+Diseno_Marshall!$C$36*A31+Diseno_Marshall!$D$36</f>
+        <v>102.750456402939</v>
+      </c>
+      <c r="Q31" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*A31^2+Diseno_Marshall!$C$35*A31+Diseno_Marshall!$D$35</f>
         <v>18.9719468421431</v>
       </c>
-      <c r="H31" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*A31^2+Diseno_Marshall!$C$36*A31+Diseno_Marshall!$D$36</f>
-        <v>102.750456402939</v>
-      </c>
-      <c r="J31" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*A31^2+Diseno_Marshall!$C$37*A31+Diseno_Marshall!$D$37</f>
-        <v>5.62398052403748</v>
-      </c>
-      <c r="L31" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*A31^2+Diseno_Marshall!$C$38*A31+Diseno_Marshall!$D$38</f>
-        <v>6.54562444160817</v>
-      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="n">
+      <c r="A32" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+28*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>9.7</v>
       </c>
-      <c r="B32" s="46" t="n">
+      <c r="B32" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*A32^2+Diseno_Marshall!$C$33*A32+Diseno_Marshall!$D$33</f>
         <v>2.17684622637559</v>
       </c>
-      <c r="D32" s="47" t="n">
+      <c r="E32" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A32^2+Diseno_Marshall!$C$37*A32+Diseno_Marshall!$D$37</f>
+        <v>5.78170324323304</v>
+      </c>
+      <c r="H32" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A32^2+Diseno_Marshall!$C$38*A32+Diseno_Marshall!$D$38</f>
+        <v>6.5978100240538</v>
+      </c>
+      <c r="K32" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A32^2+Diseno_Marshall!$C$34*A32+Diseno_Marshall!$D$34</f>
         <v>-0.68838580720888</v>
       </c>
-      <c r="F32" s="47" t="n">
+      <c r="N32" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A32^2+Diseno_Marshall!$C$36*A32+Diseno_Marshall!$D$36</f>
+        <v>103.652867953401</v>
+      </c>
+      <c r="Q32" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*A32^2+Diseno_Marshall!$C$35*A32+Diseno_Marshall!$D$35</f>
         <v>19.1063711150764</v>
       </c>
-      <c r="H32" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*A32^2+Diseno_Marshall!$C$36*A32+Diseno_Marshall!$D$36</f>
-        <v>103.652867953401</v>
-      </c>
-      <c r="J32" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*A32^2+Diseno_Marshall!$C$37*A32+Diseno_Marshall!$D$37</f>
-        <v>5.78170324323304</v>
-      </c>
-      <c r="L32" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*A32^2+Diseno_Marshall!$C$38*A32+Diseno_Marshall!$D$38</f>
-        <v>6.5978100240538</v>
-      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="n">
+      <c r="A33" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+29*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>9.85</v>
       </c>
-      <c r="B33" s="46" t="n">
+      <c r="B33" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*A33^2+Diseno_Marshall!$C$33*A33+Diseno_Marshall!$D$33</f>
         <v>2.17683348658157</v>
       </c>
-      <c r="D33" s="47" t="n">
+      <c r="E33" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A33^2+Diseno_Marshall!$C$37*A33+Diseno_Marshall!$D$37</f>
+        <v>5.95691796181875</v>
+      </c>
+      <c r="H33" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A33^2+Diseno_Marshall!$C$38*A33+Diseno_Marshall!$D$38</f>
+        <v>6.6470006136174</v>
+      </c>
+      <c r="K33" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A33^2+Diseno_Marshall!$C$34*A33+Diseno_Marshall!$D$34</f>
         <v>-0.871727728430864</v>
       </c>
-      <c r="F33" s="47" t="n">
+      <c r="N33" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A33^2+Diseno_Marshall!$C$36*A33+Diseno_Marshall!$D$36</f>
+        <v>104.541939785837</v>
+      </c>
+      <c r="Q33" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*A33^2+Diseno_Marshall!$C$35*A33+Diseno_Marshall!$D$35</f>
         <v>19.2395705726207</v>
       </c>
-      <c r="H33" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*A33^2+Diseno_Marshall!$C$36*A33+Diseno_Marshall!$D$36</f>
-        <v>104.541939785837</v>
-      </c>
-      <c r="J33" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*A33^2+Diseno_Marshall!$C$37*A33+Diseno_Marshall!$D$37</f>
-        <v>5.95691796181875</v>
-      </c>
-      <c r="L33" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*A33^2+Diseno_Marshall!$C$38*A33+Diseno_Marshall!$D$38</f>
-        <v>6.6470006136174</v>
-      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="n">
+      <c r="A34" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+30*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>10</v>
       </c>
-      <c r="B34" s="46" t="n">
+      <c r="B34" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*A34^2+Diseno_Marshall!$C$33*A34+Diseno_Marshall!$D$33</f>
         <v>2.17684906729511</v>
       </c>
-      <c r="D34" s="47" t="n">
+      <c r="E34" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*A34^2+Diseno_Marshall!$C$37*A34+Diseno_Marshall!$D$37</f>
+        <v>6.14962467979462</v>
+      </c>
+      <c r="H34" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*A34^2+Diseno_Marshall!$C$38*A34+Diseno_Marshall!$D$38</f>
+        <v>6.69319621029896</v>
+      </c>
+      <c r="K34" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A34^2+Diseno_Marshall!$C$34*A34+Diseno_Marshall!$D$34</f>
         <v>-1.05614068360743</v>
       </c>
-      <c r="F34" s="47" t="n">
+      <c r="N34" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*A34^2+Diseno_Marshall!$C$36*A34+Diseno_Marshall!$D$36</f>
+        <v>105.417671900249</v>
+      </c>
+      <c r="Q34" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*A34^2+Diseno_Marshall!$C$35*A34+Diseno_Marshall!$D$35</f>
         <v>19.3715452147761</v>
       </c>
-      <c r="H34" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*A34^2+Diseno_Marshall!$C$36*A34+Diseno_Marshall!$D$36</f>
-        <v>105.417671900249</v>
-      </c>
-      <c r="J34" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*A34^2+Diseno_Marshall!$C$37*A34+Diseno_Marshall!$D$37</f>
-        <v>6.14962467979462</v>
-      </c>
-      <c r="L34" s="47" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*A34^2+Diseno_Marshall!$C$38*A34+Diseno_Marshall!$D$38</f>
-        <v>6.69319621029896</v>
-      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="45" t="s">
+      <c r="A39" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="B39" s="42" t="s">
+        <v>116</v>
+      </c>
+      <c r="C39" s="42" t="s">
         <v>117</v>
       </c>
-      <c r="D39" s="45" t="s">
+      <c r="E39" s="42" t="s">
         <v>118</v>
       </c>
-      <c r="F39" s="45" t="s">
+      <c r="F39" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="H39" s="42" t="s">
         <v>119</v>
       </c>
-      <c r="H39" s="45" t="s">
+      <c r="I39" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="K39" s="42" t="s">
         <v>120</v>
       </c>
-      <c r="J39" s="45" t="s">
+      <c r="L39" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="N39" s="42" t="s">
         <v>121</v>
       </c>
-      <c r="L39" s="45" t="s">
+      <c r="O39" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q39" s="42" t="s">
         <v>122</v>
       </c>
+      <c r="R39" s="42" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="48" t="n">
+      <c r="A40" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B40" s="0" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="C40" s="0" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="E40" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F40" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="H40" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I40" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="K40" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L40" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="N40" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="O40" s="0" t="n">
+        <v>110</v>
+      </c>
+      <c r="Q40" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="R40" s="0" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="C42" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="E42" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="F42" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="H42" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="I42" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="K42" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="L42" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="N42" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="O42" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q42" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="R42" s="0" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
         <v>5.5</v>
       </c>
-      <c r="C40" s="49" t="n">
-        <f aca="false">MIN(Diseno_Marshall!$P$17:$P$21,B4:B34)</f>
-        <v>2.15946205571566</v>
-      </c>
-      <c r="D40" s="48" t="n">
+      <c r="C43" s="44" t="n">
+        <f aca="false">B40</f>
+        <v>2.14</v>
+      </c>
+      <c r="E43" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
         <v>5.5</v>
       </c>
-      <c r="E40" s="49" t="n">
-        <f aca="false">MIN(Diseno_Marshall!$R$17:$R$21,D4:D34,Diseno_Marshall!$J$11)</f>
-        <v>-1.05614068360743</v>
-      </c>
-      <c r="F40" s="48" t="n">
+      <c r="F43" s="43" t="n">
+        <f aca="false">E40</f>
+        <v>4</v>
+      </c>
+      <c r="H43" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
         <v>5.5</v>
       </c>
-      <c r="G40" s="49" t="n">
-        <f aca="false">MIN(Diseno_Marshall!$S$17:$S$21,F4:F34,Diseno_Marshall!$J$12)</f>
-        <v>14</v>
-      </c>
-      <c r="H40" s="48" t="n">
+      <c r="I43" s="45" t="n">
+        <f aca="false">H40</f>
+        <v>3</v>
+      </c>
+      <c r="K43" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
         <v>5.5</v>
       </c>
-      <c r="I40" s="49" t="n">
-        <f aca="false">MIN(Diseno_Marshall!$T$17:$T$21,H4:H34,Diseno_Marshall!$J$13)</f>
-        <v>65</v>
-      </c>
-      <c r="J40" s="48" t="n">
+      <c r="L43" s="45" t="n">
+        <f aca="false">K40</f>
+        <v>-2</v>
+      </c>
+      <c r="N43" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
         <v>5.5</v>
       </c>
-      <c r="K40" s="49" t="n">
-        <f aca="false">MIN(Diseno_Marshall!$X$17:$X$21,J4:J34,Diseno_Marshall!$J$9)</f>
-        <v>4.9686005140625</v>
-      </c>
-      <c r="L40" s="48" t="n">
+      <c r="O43" s="45" t="n">
+        <f aca="false">N40</f>
+        <v>60</v>
+      </c>
+      <c r="Q43" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
         <v>5.5</v>
       </c>
-      <c r="M40" s="49" t="n">
-        <f aca="false">MIN(Diseno_Marshall!$Y$17:$Y$21,L4:L34,Diseno_Marshall!$J$10)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="48" t="n">
+      <c r="R43" s="45" t="n">
+        <f aca="false">Q40</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
         <v>5.5</v>
       </c>
-      <c r="C41" s="49" t="n">
-        <f aca="false">MAX(Diseno_Marshall!$P$17:$P$21,B4:B34)</f>
-        <v>2.20736434108527</v>
-      </c>
-      <c r="D41" s="48" t="n">
+      <c r="C44" s="44" t="n">
+        <f aca="false">Diseno_Marshall!$B$33*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$33*Diseno_Marshall!$F$41+Diseno_Marshall!$D$33</f>
+        <v>2.18870106667315</v>
+      </c>
+      <c r="E44" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
         <v>5.5</v>
       </c>
-      <c r="E41" s="49" t="n">
-        <f aca="false">MAX(Diseno_Marshall!$R$17:$R$21,D4:D34,Diseno_Marshall!$K$11)</f>
-        <v>5</v>
-      </c>
-      <c r="F41" s="48" t="n">
+      <c r="F44" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$37*Diseno_Marshall!$F$41+Diseno_Marshall!$D$37</f>
+        <v>7.97744287523311</v>
+      </c>
+      <c r="H44" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
         <v>5.5</v>
       </c>
-      <c r="G41" s="49" t="n">
-        <f aca="false">MAX(Diseno_Marshall!$S$17:$S$21,F4:F34)</f>
-        <v>19.4817528150862</v>
-      </c>
-      <c r="H41" s="48" t="n">
+      <c r="I44" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$38*Diseno_Marshall!$F$41+Diseno_Marshall!$D$38</f>
+        <v>4.00450640616563</v>
+      </c>
+      <c r="K44" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
         <v>5.5</v>
       </c>
-      <c r="I41" s="49" t="n">
-        <f aca="false">MAX(Diseno_Marshall!$T$17:$T$21,H4:H34,Diseno_Marshall!$K$13)</f>
-        <v>105.417671900249</v>
-      </c>
-      <c r="J41" s="48" t="n">
+      <c r="L44" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$34*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$34*Diseno_Marshall!$F$41+Diseno_Marshall!$D$34</f>
+        <v>4.01034820144837</v>
+      </c>
+      <c r="N44" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
         <v>5.5</v>
       </c>
-      <c r="K41" s="49" t="n">
-        <f aca="false">MAX(Diseno_Marshall!$X$17:$X$21,J4:J34)</f>
-        <v>8.3430442624375</v>
-      </c>
-      <c r="L41" s="48" t="n">
+      <c r="O44" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$36*Diseno_Marshall!$F$41+Diseno_Marshall!$D$36</f>
+        <v>73.3429311270575</v>
+      </c>
+      <c r="Q44" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
         <v>5.5</v>
       </c>
-      <c r="M41" s="49" t="n">
-        <f aca="false">MAX(Diseno_Marshall!$Y$17:$Y$21,L4:L34,Diseno_Marshall!$K$10)</f>
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$F$41</f>
-        <v>5.5</v>
-      </c>
-      <c r="C43" s="49" t="n">
+      <c r="R44" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$35*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$35*Diseno_Marshall!$F$41+Diseno_Marshall!$D$35</f>
+        <v>14.8795112559337</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="C45" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$33*Diseno_Marshall!$F$41+Diseno_Marshall!$D$33</f>
         <v>2.18870106667315</v>
       </c>
-      <c r="D43" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$F$41</f>
-        <v>5.5</v>
-      </c>
-      <c r="E43" s="49" t="n">
+      <c r="E45" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F45" s="43" t="n">
+        <f aca="false">Diseno_Marshall!$B$37*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$37*Diseno_Marshall!$F$41+Diseno_Marshall!$D$37</f>
+        <v>7.97744287523311</v>
+      </c>
+      <c r="H45" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="I45" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$38*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$38*Diseno_Marshall!$F$41+Diseno_Marshall!$D$38</f>
+        <v>4.00450640616563</v>
+      </c>
+      <c r="K45" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="L45" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$34*Diseno_Marshall!$F$41+Diseno_Marshall!$D$34</f>
         <v>4.01034820144837</v>
       </c>
-      <c r="F43" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$F$41</f>
-        <v>5.5</v>
-      </c>
-      <c r="G43" s="49" t="n">
+      <c r="N45" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="O45" s="45" t="n">
+        <f aca="false">Diseno_Marshall!$B$36*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$36*Diseno_Marshall!$F$41+Diseno_Marshall!$D$36</f>
+        <v>73.3429311270575</v>
+      </c>
+      <c r="Q45" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="R45" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$35*Diseno_Marshall!$F$41+Diseno_Marshall!$D$35</f>
         <v>14.8795112559337</v>
       </c>
-      <c r="H43" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$F$41</f>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="0" t="str">
+        <f aca="false">TEXT(Diseno_Marshall!$F$41,"0.0")</f>
         <v>5.5</v>
       </c>
-      <c r="I43" s="49" t="n">
-        <f aca="false">Diseno_Marshall!$B$36*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$36*Diseno_Marshall!$F$41+Diseno_Marshall!$D$36</f>
-        <v>73.3429311270575</v>
-      </c>
-      <c r="J43" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$F$41</f>
+      <c r="E46" s="0" t="str">
+        <f aca="false">TEXT(Diseno_Marshall!$F$41,"0.0")</f>
         <v>5.5</v>
       </c>
-      <c r="K43" s="49" t="n">
-        <f aca="false">Diseno_Marshall!$B$37*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$37*Diseno_Marshall!$F$41+Diseno_Marshall!$D$37</f>
-        <v>7.97744287523311</v>
-      </c>
-      <c r="L43" s="48" t="n">
-        <f aca="false">Diseno_Marshall!$F$41</f>
+      <c r="H46" s="0" t="str">
+        <f aca="false">TEXT(Diseno_Marshall!$F$41,"0.0")</f>
         <v>5.5</v>
       </c>
-      <c r="M43" s="49" t="n">
-        <f aca="false">Diseno_Marshall!$B$38*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$38*Diseno_Marshall!$F$41+Diseno_Marshall!$D$38</f>
-        <v>4.00450640616563</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D45" s="49" t="n">
-        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)</f>
+      <c r="K46" s="0" t="str">
+        <f aca="false">TEXT(Diseno_Marshall!$F$41,"0.0")</f>
         <v>5.5</v>
       </c>
-      <c r="E45" s="49" t="n">
-        <f aca="false">Diseno_Marshall!$J$11</f>
-        <v>3</v>
-      </c>
-      <c r="F45" s="49" t="n">
-        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)</f>
+      <c r="N46" s="0" t="str">
+        <f aca="false">TEXT(Diseno_Marshall!$F$41,"0.0")</f>
         <v>5.5</v>
       </c>
-      <c r="G45" s="49" t="n">
-        <f aca="false">Diseno_Marshall!$J$12</f>
-        <v>14</v>
-      </c>
-      <c r="H45" s="49" t="n">
-        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)</f>
+      <c r="Q46" s="0" t="str">
+        <f aca="false">TEXT(Diseno_Marshall!$F$41,"0.0")</f>
         <v>5.5</v>
-      </c>
-      <c r="I45" s="49" t="n">
-        <f aca="false">Diseno_Marshall!$J$13</f>
-        <v>65</v>
-      </c>
-      <c r="J45" s="49" t="n">
-        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)</f>
-        <v>5.5</v>
-      </c>
-      <c r="K45" s="49" t="n">
-        <f aca="false">Diseno_Marshall!$J$9</f>
-        <v>5.44</v>
-      </c>
-      <c r="L45" s="49" t="n">
-        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)</f>
-        <v>5.5</v>
-      </c>
-      <c r="M45" s="49" t="n">
-        <f aca="false">Diseno_Marshall!$J$10</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D46" s="49" t="n">
-        <f aca="false">MAX(Diseno_Marshall!$B$17:$B$21)</f>
-        <v>10</v>
-      </c>
-      <c r="E46" s="49" t="n">
-        <f aca="false">Diseno_Marshall!$J$11</f>
-        <v>3</v>
-      </c>
-      <c r="F46" s="49" t="n">
-        <f aca="false">MAX(Diseno_Marshall!$B$17:$B$21)</f>
-        <v>10</v>
-      </c>
-      <c r="G46" s="49" t="n">
-        <f aca="false">Diseno_Marshall!$J$12</f>
-        <v>14</v>
-      </c>
-      <c r="H46" s="49" t="n">
-        <f aca="false">MAX(Diseno_Marshall!$B$17:$B$21)</f>
-        <v>10</v>
-      </c>
-      <c r="I46" s="49" t="n">
-        <f aca="false">Diseno_Marshall!$J$13</f>
-        <v>65</v>
-      </c>
-      <c r="J46" s="49" t="n">
-        <f aca="false">MAX(Diseno_Marshall!$B$17:$B$21)</f>
-        <v>10</v>
-      </c>
-      <c r="K46" s="49" t="n">
-        <f aca="false">Diseno_Marshall!$J$9</f>
-        <v>5.44</v>
-      </c>
-      <c r="L46" s="49" t="n">
-        <f aca="false">MAX(Diseno_Marshall!$B$17:$B$21)</f>
-        <v>10</v>
-      </c>
-      <c r="M46" s="49" t="n">
-        <f aca="false">Diseno_Marshall!$J$10</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D48" s="49" t="n">
-        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)</f>
-        <v>5.5</v>
-      </c>
-      <c r="E48" s="49" t="n">
-        <f aca="false">Diseno_Marshall!$K$11</f>
-        <v>5</v>
-      </c>
-      <c r="H48" s="49" t="n">
-        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)</f>
-        <v>5.5</v>
-      </c>
-      <c r="I48" s="49" t="n">
-        <f aca="false">Diseno_Marshall!$K$13</f>
-        <v>78</v>
-      </c>
-      <c r="L48" s="49" t="n">
-        <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)</f>
-        <v>5.5</v>
-      </c>
-      <c r="M48" s="49" t="n">
-        <f aca="false">Diseno_Marshall!$K$10</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D49" s="49" t="n">
-        <f aca="false">MAX(Diseno_Marshall!$B$17:$B$21)</f>
-        <v>10</v>
-      </c>
-      <c r="E49" s="49" t="n">
-        <f aca="false">Diseno_Marshall!$K$11</f>
-        <v>5</v>
-      </c>
-      <c r="H49" s="49" t="n">
-        <f aca="false">MAX(Diseno_Marshall!$B$17:$B$21)</f>
-        <v>10</v>
-      </c>
-      <c r="I49" s="49" t="n">
-        <f aca="false">Diseno_Marshall!$K$13</f>
-        <v>78</v>
-      </c>
-      <c r="L49" s="49" t="n">
-        <f aca="false">MAX(Diseno_Marshall!$B$17:$B$21)</f>
-        <v>10</v>
-      </c>
-      <c r="M49" s="49" t="n">
-        <f aca="false">Diseno_Marshall!$K$10</f>
-        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/marshall/Diseno_Marshall_MAC2_PEN120_150_corregido.xlsx
+++ b/marshall/Diseno_Marshall_MAC2_PEN120_150_corregido.xlsx
@@ -139,6 +139,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="V17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Asignación M1-M5 según el orden de las fotos del ensayo entregadas por el usuario (523.0, 772.0, 669.7, 883.9, 707.3 kg). Asignación anterior: 883.9, 669.7, 772, 523, 707.3.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Y17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Flujo = 4.0 mm asumido para todas las briquetas por indicación del usuario (no medido). Reemplazar por las lecturas del dial.</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -442,7 +466,7 @@
     <t xml:space="preserve">3. Estabilidad corregida por altura con el factor de la hoja Factor_Altura (interpolación lineal).</t>
   </si>
   <si>
-    <t xml:space="preserve">4. La asociación de lecturas de estabilidad M1-M5 es provisional (secuencia cronológica) y el flujo fue inferido; confirmar con registro original.</t>
+    <t xml:space="preserve">4. Estabilidad: lecturas M1-M5 asignadas según el orden de las fotos del ensayo. Flujo asumido = 4.0 mm (no medido); confirmar con registro original.</t>
   </si>
   <si>
     <t xml:space="preserve">5. Una sola briqueta por contenido de asfalto: la norma recomienda 3 por punto.</t>
@@ -961,19 +985,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -986,7 +1010,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="5">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1008,28 +1032,6 @@
       </fill>
     </dxf>
     <dxf/>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <b val="1"/>
@@ -1190,22 +1192,26 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -1452,22 +1458,26 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -1630,10 +1640,10 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>5.5</c:v>
+                  <c:v>6.3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.5</c:v>
+                  <c:v>6.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>5</c:v>
@@ -1651,10 +1661,10 @@
                   <c:v>2.14</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.18870106667315</c:v>
+                  <c:v>2.18473118450936</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.18870106667315</c:v>
+                  <c:v>2.18473118450936</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1670,7 +1680,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>5.5</c:v>
+                  <c:v>6.3</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1762,7 +1772,7 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>5.5</c:v>
+                  <c:v>6.3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1781,11 +1791,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="266131"/>
-        <c:axId val="97547305"/>
+        <c:axId val="74248647"/>
+        <c:axId val="95690138"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="266131"/>
+        <c:axId val="74248647"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -1873,13 +1883,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97547305"/>
+        <c:crossAx val="95690138"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="97547305"/>
+        <c:axId val="95690138"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="2.22"/>
@@ -1957,20 +1967,15 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="266131"/>
+        <c:crossAx val="74248647"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.01"/>
       </c:valAx>
       <c:spPr>
-        <a:solidFill>
-          <a:srgbClr val="ffffff"/>
-        </a:solidFill>
-        <a:ln w="9360">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
         </a:ln>
       </c:spPr>
     </c:plotArea>
@@ -2062,22 +2067,26 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -2194,97 +2203,97 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>7.97744287523311</c:v>
+                  <c:v>5.08425851557789</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.66288161089468</c:v>
+                  <c:v>5.42263991622667</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.3658123459464</c:v>
+                  <c:v>5.74030250868734</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.08623508038827</c:v>
+                  <c:v>6.0372462929599</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.82414981422028</c:v>
+                  <c:v>6.31347126904435</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.57955654744245</c:v>
+                  <c:v>6.5689774369407</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6.35245528005476</c:v>
+                  <c:v>6.80376479664893</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.14284601205722</c:v>
+                  <c:v>7.01783334816906</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.95072874344983</c:v>
+                  <c:v>7.21118309150108</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5.77610347423259</c:v>
+                  <c:v>7.383814026645</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5.61897020440549</c:v>
+                  <c:v>7.5357261536008</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>5.47932893396854</c:v>
+                  <c:v>7.6669194723685</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>5.35717966292174</c:v>
+                  <c:v>7.77739398294808</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>5.25252239126509</c:v>
+                  <c:v>7.86714968533957</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>5.16535711899859</c:v>
+                  <c:v>7.93618657954294</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>5.09568384612222</c:v>
+                  <c:v>7.98450466555821</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>5.04350257263601</c:v>
+                  <c:v>8.01210394338537</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5.00881329853996</c:v>
+                  <c:v>8.01898441302442</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4.99161602383404</c:v>
+                  <c:v>8.00514607447536</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4.99191074851828</c:v>
+                  <c:v>7.97058892773819</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>5.00969747259266</c:v>
+                  <c:v>7.91531297281292</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>5.04497619605719</c:v>
+                  <c:v>7.83931820969954</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>5.09774691891186</c:v>
+                  <c:v>7.74260463839806</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>5.16800964115669</c:v>
+                  <c:v>7.62517225890845</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>5.25576436279166</c:v>
+                  <c:v>7.48702107123074</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>5.36101108381679</c:v>
+                  <c:v>7.32815107536494</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>5.48374980423206</c:v>
+                  <c:v>7.148562271311</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>5.62398052403748</c:v>
+                  <c:v>6.94825465906899</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>5.78170324323304</c:v>
+                  <c:v>6.72722823863884</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>5.95691796181875</c:v>
+                  <c:v>6.48548301002061</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>6.14962467979462</c:v>
+                  <c:v>6.22301897321425</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2324,22 +2333,26 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -2378,16 +2391,16 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>8.3430442624375</c:v>
+                  <c:v>4.936545026875</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.09957816776875</c:v>
+                  <c:v>7.03131901675</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.7947335855</c:v>
+                  <c:v>5.8943433707375</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.9686005140625</c:v>
+                  <c:v>8.39721987453125</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>6.14724584175625</c:v>
@@ -2502,10 +2515,10 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>5.5</c:v>
+                  <c:v>6.3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.5</c:v>
+                  <c:v>6.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>5</c:v>
@@ -2523,10 +2536,10 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.97744287523311</c:v>
+                  <c:v>6.64954197997546</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.97744287523311</c:v>
+                  <c:v>6.64954197997546</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2542,7 +2555,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>5.5</c:v>
+                  <c:v>6.3</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2634,7 +2647,7 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>5.5</c:v>
+                  <c:v>6.3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2653,11 +2666,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="40056965"/>
-        <c:axId val="31342669"/>
+        <c:axId val="96043343"/>
+        <c:axId val="78413220"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="40056965"/>
+        <c:axId val="96043343"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -2745,13 +2758,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31342669"/>
+        <c:crossAx val="78413220"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="31342669"/>
+        <c:axId val="78413220"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="9"/>
@@ -2829,20 +2842,15 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40056965"/>
+        <c:crossAx val="96043343"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:spPr>
-        <a:solidFill>
-          <a:srgbClr val="ffffff"/>
-        </a:solidFill>
-        <a:ln w="9360">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
         </a:ln>
       </c:spPr>
     </c:plotArea>
@@ -2934,22 +2942,26 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -3066,97 +3078,97 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>4.00450640616563</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.13755679642629</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.26761219380492</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.39467259830151</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.51873800991606</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.63980842864857</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.75788385449904</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.87296428746748</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.98504972755388</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5.09414017475823</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5.20023562908055</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>5.30333609052084</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>5.40344155907908</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>5.50055203475529</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>5.59466751754946</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>5.68578800746159</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>5.77391350449168</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5.85904400863973</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>5.94117951990575</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>6.02032003828972</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>6.09646556379166</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>6.16961609641156</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>6.23977163614943</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>6.30693218300525</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>6.37109773697904</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>6.43226829807079</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>6.4904438662805</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>6.54562444160817</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>6.5978100240538</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>6.6470006136174</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>6.69319621029896</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3196,22 +3208,26 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -3253,16 +3269,16 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.4</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.9</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.8</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.7</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3374,10 +3390,10 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>5.5</c:v>
+                  <c:v>6.3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.5</c:v>
+                  <c:v>6.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>5</c:v>
@@ -3395,10 +3411,10 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.00450640616563</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.00450640616563</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3414,7 +3430,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>5.5</c:v>
+                  <c:v>6.3</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3506,7 +3522,7 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>5.5</c:v>
+                  <c:v>6.3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3525,11 +3541,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="17115807"/>
-        <c:axId val="94011292"/>
+        <c:axId val="25997971"/>
+        <c:axId val="56280559"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="17115807"/>
+        <c:axId val="25997971"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -3617,13 +3633,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94011292"/>
+        <c:crossAx val="56280559"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="94011292"/>
+        <c:axId val="56280559"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="7"/>
@@ -3701,20 +3717,15 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17115807"/>
+        <c:crossAx val="25997971"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:spPr>
-        <a:solidFill>
-          <a:srgbClr val="ffffff"/>
-        </a:solidFill>
-        <a:ln w="9360">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
         </a:ln>
       </c:spPr>
     </c:plotArea>
@@ -3806,22 +3817,26 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -4068,22 +4083,26 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -4246,10 +4265,10 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>5.5</c:v>
+                  <c:v>6.3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.5</c:v>
+                  <c:v>6.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>5</c:v>
@@ -4267,10 +4286,10 @@
                   <c:v>-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.01034820144837</c:v>
+                  <c:v>3.18008929978397</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.01034820144837</c:v>
+                  <c:v>3.18008929978397</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4286,7 +4305,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>5.5</c:v>
+                  <c:v>6.3</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4378,7 +4397,7 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>5.5</c:v>
+                  <c:v>6.3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4397,11 +4416,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="72306528"/>
-        <c:axId val="13110935"/>
+        <c:axId val="72991298"/>
+        <c:axId val="42900666"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="72306528"/>
+        <c:axId val="72991298"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -4489,13 +4508,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13110935"/>
+        <c:crossAx val="42900666"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="13110935"/>
+        <c:axId val="42900666"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="6"/>
@@ -4573,20 +4592,15 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="72306528"/>
+        <c:crossAx val="72991298"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="1"/>
       </c:valAx>
       <c:spPr>
-        <a:solidFill>
-          <a:srgbClr val="ffffff"/>
-        </a:solidFill>
-        <a:ln w="9360">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
         </a:ln>
       </c:spPr>
     </c:plotArea>
@@ -4678,22 +4692,26 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -4940,22 +4958,26 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -5118,10 +5140,10 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>5.5</c:v>
+                  <c:v>6.3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.5</c:v>
+                  <c:v>6.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>5</c:v>
@@ -5139,10 +5161,10 @@
                   <c:v>60</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>73.3429311270575</c:v>
+                  <c:v>79.9225642723747</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>73.3429311270575</c:v>
+                  <c:v>79.9225642723747</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5158,7 +5180,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>5.5</c:v>
+                  <c:v>6.3</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5250,7 +5272,7 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>5.5</c:v>
+                  <c:v>6.3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5269,11 +5291,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="84729830"/>
-        <c:axId val="54195394"/>
+        <c:axId val="82568614"/>
+        <c:axId val="66114833"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="84729830"/>
+        <c:axId val="82568614"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -5361,13 +5383,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54195394"/>
+        <c:crossAx val="66114833"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="54195394"/>
+        <c:axId val="66114833"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="110"/>
@@ -5445,20 +5467,15 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84729830"/>
+        <c:crossAx val="82568614"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="10"/>
       </c:valAx>
       <c:spPr>
-        <a:solidFill>
-          <a:srgbClr val="ffffff"/>
-        </a:solidFill>
-        <a:ln w="9360">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
         </a:ln>
       </c:spPr>
     </c:plotArea>
@@ -5550,22 +5567,26 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -5812,22 +5833,26 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -5990,10 +6015,10 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>5.5</c:v>
+                  <c:v>6.3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.5</c:v>
+                  <c:v>6.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>5</c:v>
@@ -6011,10 +6036,10 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>14.8795112559337</c:v>
+                  <c:v>15.7586607053102</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14.8795112559337</c:v>
+                  <c:v>15.7586607053102</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6030,7 +6055,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>5.5</c:v>
+                  <c:v>6.3</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6122,7 +6147,7 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>5.5</c:v>
+                  <c:v>6.3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6141,11 +6166,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="96345383"/>
-        <c:axId val="8954568"/>
+        <c:axId val="15159062"/>
+        <c:axId val="77035192"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="96345383"/>
+        <c:axId val="15159062"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -6233,13 +6258,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8954568"/>
+        <c:crossAx val="77035192"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="8954568"/>
+        <c:axId val="77035192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="21"/>
@@ -6317,20 +6342,15 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96345383"/>
+        <c:crossAx val="15159062"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="1"/>
       </c:valAx>
       <c:spPr>
-        <a:solidFill>
-          <a:srgbClr val="ffffff"/>
-        </a:solidFill>
-        <a:ln w="9360">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
         </a:ln>
       </c:spPr>
     </c:plotArea>
@@ -6359,9 +6379,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>721440</xdr:colOff>
+      <xdr:colOff>721080</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>121680</xdr:rowOff>
+      <xdr:rowOff>121320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6369,8 +6389,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="952560"/>
-        <a:ext cx="4499640" cy="3419640"/>
+        <a:off x="0" y="950040"/>
+        <a:ext cx="4515120" cy="3419280"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6389,9 +6409,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>721440</xdr:colOff>
+      <xdr:colOff>721080</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>121680</xdr:rowOff>
+      <xdr:rowOff>121320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6399,8 +6419,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="5289480" y="952560"/>
-        <a:ext cx="4499640" cy="3419640"/>
+        <a:off x="5311800" y="950040"/>
+        <a:ext cx="4515120" cy="3419280"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6419,9 +6439,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>721080</xdr:colOff>
+      <xdr:colOff>720720</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>121680</xdr:rowOff>
+      <xdr:rowOff>121320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6429,8 +6449,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="10578960" y="952560"/>
-        <a:ext cx="4499640" cy="3419640"/>
+        <a:off x="10623600" y="950040"/>
+        <a:ext cx="4514760" cy="3419280"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6449,9 +6469,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>721440</xdr:colOff>
+      <xdr:colOff>721080</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>121320</xdr:rowOff>
+      <xdr:rowOff>120960</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6459,8 +6479,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="4762440"/>
-        <a:ext cx="4499640" cy="3419640"/>
+        <a:off x="0" y="4759920"/>
+        <a:ext cx="4515120" cy="3419280"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6479,9 +6499,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>721440</xdr:colOff>
+      <xdr:colOff>721080</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>121320</xdr:rowOff>
+      <xdr:rowOff>120960</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6489,8 +6509,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="5289480" y="4762440"/>
-        <a:ext cx="4499640" cy="3419640"/>
+        <a:off x="5311800" y="4759920"/>
+        <a:ext cx="4515120" cy="3419280"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6509,9 +6529,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>721080</xdr:colOff>
+      <xdr:colOff>720720</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>121320</xdr:rowOff>
+      <xdr:rowOff>120960</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6519,8 +6539,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="10578960" y="4762440"/>
-        <a:ext cx="4499640" cy="3419640"/>
+        <a:off x="10623600" y="4759920"/>
+        <a:ext cx="4514760" cy="3419280"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -7146,22 +7166,22 @@
         <v>5.08508771929825</v>
       </c>
       <c r="V17" s="13" t="n">
-        <v>883.9</v>
+        <v>523</v>
       </c>
       <c r="W17" s="15" t="n">
         <f aca="false">V17*I17</f>
-        <v>850.75375</v>
+        <v>503.3875</v>
       </c>
       <c r="X17" s="16" t="n">
         <f aca="false">W17*9.80665/1000</f>
-        <v>8.3430442624375</v>
+        <v>4.936545026875</v>
       </c>
       <c r="Y17" s="14" t="n">
         <v>4</v>
       </c>
       <c r="Z17" s="19" t="n">
         <f aca="false">W17/(Y17/10)</f>
-        <v>2126.884375</v>
+        <v>1258.46875</v>
       </c>
       <c r="AA17" s="17" t="n">
         <f aca="false">J17/(PI()*$D$13^2/4*H17)</f>
@@ -7248,22 +7268,22 @@
         <v>5.58728302237075</v>
       </c>
       <c r="V18" s="13" t="n">
-        <v>669.7</v>
+        <v>772</v>
       </c>
       <c r="W18" s="15" t="n">
         <f aca="false">V18*I18</f>
-        <v>621.983875</v>
+        <v>716.995</v>
       </c>
       <c r="X18" s="16" t="n">
         <f aca="false">W18*9.80665/1000</f>
-        <v>6.09957816776875</v>
+        <v>7.03131901675</v>
       </c>
       <c r="Y18" s="14" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="Z18" s="19" t="n">
         <f aca="false">W18/(Y18/10)</f>
-        <v>1413.59971590909</v>
+        <v>1792.4875</v>
       </c>
       <c r="AA18" s="17" t="n">
         <f aca="false">J18/(PI()*$D$13^2/4*H18)</f>
@@ -7350,22 +7370,22 @@
         <v>6.08947832544325</v>
       </c>
       <c r="V19" s="13" t="n">
-        <v>772</v>
+        <v>669.7</v>
       </c>
       <c r="W19" s="15" t="n">
         <f aca="false">V19*I19</f>
-        <v>692.87</v>
+        <v>601.05575</v>
       </c>
       <c r="X19" s="16" t="n">
         <f aca="false">W19*9.80665/1000</f>
-        <v>6.7947335855</v>
+        <v>5.8943433707375</v>
       </c>
       <c r="Y19" s="14" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="Z19" s="19" t="n">
         <f aca="false">W19/(Y19/10)</f>
-        <v>1414.02040816327</v>
+        <v>1502.639375</v>
       </c>
       <c r="AA19" s="17" t="n">
         <f aca="false">J19/(PI()*$D$13^2/4*H19)</f>
@@ -7452,22 +7472,22 @@
         <v>7.59606423466073</v>
       </c>
       <c r="V20" s="13" t="n">
-        <v>523</v>
+        <v>883.9</v>
       </c>
       <c r="W20" s="15" t="n">
         <f aca="false">V20*I20</f>
-        <v>506.65625</v>
+        <v>856.278125</v>
       </c>
       <c r="X20" s="16" t="n">
         <f aca="false">W20*9.80665/1000</f>
-        <v>4.9686005140625</v>
+        <v>8.39721987453125</v>
       </c>
       <c r="Y20" s="14" t="n">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="Z20" s="19" t="n">
         <f aca="false">W20/(Y20/10)</f>
-        <v>873.54525862069</v>
+        <v>2140.6953125</v>
       </c>
       <c r="AA20" s="17" t="n">
         <f aca="false">J20/(PI()*$D$13^2/4*H20)</f>
@@ -7565,11 +7585,11 @@
         <v>6.14724584175625</v>
       </c>
       <c r="Y21" s="14" t="n">
-        <v>6.7</v>
+        <v>4</v>
       </c>
       <c r="Z21" s="19" t="n">
         <f aca="false">W21/(Y21/10)</f>
-        <v>935.588992537313</v>
+        <v>1567.1115625</v>
       </c>
       <c r="AA21" s="17" t="n">
         <f aca="false">J21/(PI()*$D$13^2/4*H21)</f>
@@ -7645,7 +7665,7 @@
       </c>
       <c r="F25" s="20" t="str">
         <f aca="false">IF(X17&gt;=$J$9,"CUMPLE","NO")</f>
-        <v>CUMPLE</v>
+        <v>NO</v>
       </c>
       <c r="G25" s="20" t="str">
         <f aca="false">IF(AND(Y17&gt;=$J$10,Y17&lt;=$K$10),"CUMPLE","NO")</f>
@@ -7653,11 +7673,11 @@
       </c>
       <c r="H25" s="20" t="str">
         <f aca="false">IF(COUNTIF(C25:G25,"NO")+COUNTIF(I25:J25,"NO")=0,"CUMPLE","NO CUMPLE")</f>
-        <v>CUMPLE</v>
+        <v>NO CUMPLE</v>
       </c>
       <c r="I25" s="20" t="str">
         <f aca="false">IF(AND(Z17&gt;=$J$15,Z17&lt;=$K$15),"CUMPLE","NO")</f>
-        <v>CUMPLE</v>
+        <v>NO</v>
       </c>
       <c r="J25" s="20" t="str">
         <f aca="false">IF(AB17&lt;=$D$14,"CUMPLE","NO")</f>
@@ -7691,15 +7711,15 @@
       </c>
       <c r="G26" s="20" t="str">
         <f aca="false">IF(AND(Y18&gt;=$J$10,Y18&lt;=$K$10),"CUMPLE","NO")</f>
-        <v>NO</v>
+        <v>CUMPLE</v>
       </c>
       <c r="H26" s="20" t="str">
         <f aca="false">IF(COUNTIF(C26:G26,"NO")+COUNTIF(I26:J26,"NO")=0,"CUMPLE","NO CUMPLE")</f>
-        <v>NO CUMPLE</v>
+        <v>CUMPLE</v>
       </c>
       <c r="I26" s="20" t="str">
         <f aca="false">IF(AND(Z18&gt;=$J$15,Z18&lt;=$K$15),"CUMPLE","NO")</f>
-        <v>NO</v>
+        <v>CUMPLE</v>
       </c>
       <c r="J26" s="20" t="str">
         <f aca="false">IF(AB18&lt;=$D$14,"CUMPLE","NO")</f>
@@ -7733,7 +7753,7 @@
       </c>
       <c r="G27" s="20" t="str">
         <f aca="false">IF(AND(Y19&gt;=$J$10,Y19&lt;=$K$10),"CUMPLE","NO")</f>
-        <v>NO</v>
+        <v>CUMPLE</v>
       </c>
       <c r="H27" s="20" t="str">
         <f aca="false">IF(COUNTIF(C27:G27,"NO")+COUNTIF(I27:J27,"NO")=0,"CUMPLE","NO CUMPLE")</f>
@@ -7771,11 +7791,11 @@
       </c>
       <c r="F28" s="20" t="str">
         <f aca="false">IF(X20&gt;=$J$9,"CUMPLE","NO")</f>
-        <v>NO</v>
+        <v>CUMPLE</v>
       </c>
       <c r="G28" s="20" t="str">
         <f aca="false">IF(AND(Y20&gt;=$J$10,Y20&lt;=$K$10),"CUMPLE","NO")</f>
-        <v>NO</v>
+        <v>CUMPLE</v>
       </c>
       <c r="H28" s="20" t="str">
         <f aca="false">IF(COUNTIF(C28:G28,"NO")+COUNTIF(I28:J28,"NO")=0,"CUMPLE","NO CUMPLE")</f>
@@ -7783,7 +7803,7 @@
       </c>
       <c r="I28" s="20" t="str">
         <f aca="false">IF(AND(Z20&gt;=$J$15,Z20&lt;=$K$15),"CUMPLE","NO")</f>
-        <v>NO</v>
+        <v>CUMPLE</v>
       </c>
       <c r="J28" s="20" t="str">
         <f aca="false">IF(AB20&lt;=$D$14,"CUMPLE","NO")</f>
@@ -7817,7 +7837,7 @@
       </c>
       <c r="G29" s="20" t="str">
         <f aca="false">IF(AND(Y21&gt;=$J$10,Y21&lt;=$K$10),"CUMPLE","NO")</f>
-        <v>NO</v>
+        <v>CUMPLE</v>
       </c>
       <c r="H29" s="20" t="str">
         <f aca="false">IF(COUNTIF(C29:G29,"NO")+COUNTIF(I29:J29,"NO")=0,"CUMPLE","NO CUMPLE")</f>
@@ -7982,27 +8002,27 @@
       </c>
       <c r="B37" s="22" t="n">
         <f aca="false">INDEX(LINEST($X$17:$X$21,$B$17:$B$21^{1,2}),1,1)</f>
-        <v>0.388711097558842</v>
+        <v>-0.460417959735731</v>
       </c>
       <c r="C37" s="22" t="n">
         <f aca="false">INDEX(LINEST($X$17:$X$21,$B$17:$B$21^{1,2}),1,2)</f>
-        <v>-6.4312038333706</v>
+        <v>7.38953625537858</v>
       </c>
       <c r="D37" s="9" t="n">
         <f aca="false">INDEX(LINEST($X$17:$X$21,$B$17:$B$21^{1,2}),1,3)</f>
-        <v>31.5905532576165</v>
+        <v>-21.6305476069984</v>
       </c>
       <c r="E37" s="9" t="n">
         <f aca="false">INDEX(LINEST($X$17:$X$21,$B$17:$B$21^{1,2},TRUE(),TRUE()),3,1)</f>
-        <v>0.7900908008705</v>
+        <v>0.693073401138715</v>
       </c>
       <c r="F37" s="23" t="n">
         <f aca="false">IF(AND(B37&lt;0,-C37/(2*B37)&gt;=MIN($B$17:$B$21),-C37/(2*B37)&lt;=MAX($B$17:$B$21)),-C37/(2*B37),INDEX($B$17:$B$21,MATCH(MAX($X$17:$X$21),$X$17:$X$21,0)))</f>
-        <v>5.5</v>
+        <v>8.02481321495364</v>
       </c>
       <c r="G37" s="21" t="str">
         <f aca="false">IF(AND(B37&lt;0,-C37/(2*B37)&gt;=MIN($B$17:$B$21),-C37/(2*B37)&lt;=MAX($B$17:$B$21)),"Máximo de la parábola","Sin máximo interior: se toma la mayor estabilidad medida")</f>
-        <v>Sin máximo interior: se toma la mayor estabilidad medida</v>
+        <v>Máximo de la parábola</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8011,19 +8031,19 @@
       </c>
       <c r="B38" s="22" t="n">
         <f aca="false">INDEX(LINEST($Y$17:$Y$21,$B$17:$B$21^{1,2}),1,1)</f>
-        <v>-0.0665553973786265</v>
+        <v>0</v>
       </c>
       <c r="C38" s="22" t="n">
         <f aca="false">INDEX(LINEST($Y$17:$Y$21,$B$17:$B$21^{1,2}),1,2)</f>
-        <v>1.62909528250945</v>
+        <v>0</v>
       </c>
       <c r="D38" s="9" t="n">
         <f aca="false">INDEX(LINEST($Y$17:$Y$21,$B$17:$B$21^{1,2}),1,3)</f>
-        <v>-2.94221687693289</v>
+        <v>4</v>
       </c>
       <c r="E38" s="9" t="n">
-        <f aca="false">INDEX(LINEST($Y$17:$Y$21,$B$17:$B$21^{1,2},TRUE(),TRUE()),3,1)</f>
-        <v>0.998620518139559</v>
+        <f aca="false">IFERROR(INDEX(LINEST($Y$17:$Y$21,$B$17:$B$21^{1,2},TRUE(),TRUE()),3,1),"-")</f>
+        <v>1</v>
       </c>
       <c r="F38" s="23" t="str">
         <f aca="false">IFERROR(IF(AND((-C38+SQRT(C38^2-4*B38*(D38-$K$10)))/(2*B38)&gt;=MIN($B$17:$B$21),(-C38+SQRT(C38^2-4*B38*(D38-$K$10)))/(2*B38)&lt;=MAX($B$17:$B$21)),(-C38+SQRT(C38^2-4*B38*(D38-$K$10)))/(2*B38),IF(AND((-C38-SQRT(C38^2-4*B38*(D38-$K$10)))/(2*B38)&gt;=MIN($B$17:$B$21),(-C38-SQRT(C38^2-4*B38*(D38-$K$10)))/(2*B38)&lt;=MAX($B$17:$B$21)),(-C38-SQRT(C38^2-4*B38*(D38-$K$10)))/(2*B38),"N/A")),"N/A")</f>
@@ -8040,7 +8060,7 @@
       </c>
       <c r="F40" s="24" t="n">
         <f aca="false">AVERAGE(F33,F37,F34)</f>
-        <v>5.50338500177111</v>
+        <v>6.34498940675566</v>
       </c>
       <c r="G40" s="1" t="str">
         <f aca="false">IF(ISNUMBER(F34),"Promedio de 3 criterios","PROVISIONAL: solo promedio de máx. Gmb y máx. estabilidad")</f>
@@ -8053,7 +8073,7 @@
       </c>
       <c r="F41" s="25" t="n">
         <f aca="false">ROUND(F40*10,0)/10</f>
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8081,7 +8101,7 @@
       </c>
       <c r="B45" s="17" t="n">
         <f aca="false">B33*$F$41^2+C33*$F$41+D33</f>
-        <v>2.18870106667315</v>
+        <v>2.18473118450936</v>
       </c>
       <c r="C45" s="20" t="s">
         <v>84</v>
@@ -8097,7 +8117,7 @@
       </c>
       <c r="B46" s="15" t="n">
         <f aca="false">B34*$F$41^2+C34*$F$41+D34</f>
-        <v>4.01034820144837</v>
+        <v>3.18008929978397</v>
       </c>
       <c r="C46" s="20" t="str">
         <f aca="false">TEXT($J$11,"0")&amp;" - "&amp;TEXT($K$11,"0")&amp;" %"</f>
@@ -8114,7 +8134,7 @@
       </c>
       <c r="B47" s="15" t="n">
         <f aca="false">B35*$F$41^2+C35*$F$41+D35</f>
-        <v>14.8795112559337</v>
+        <v>15.7586607053102</v>
       </c>
       <c r="C47" s="20" t="str">
         <f aca="false">"≥ "&amp;TEXT($J$12,"0")&amp;" %"</f>
@@ -8131,7 +8151,7 @@
       </c>
       <c r="B48" s="15" t="n">
         <f aca="false">B36*$F$41^2+C36*$F$41+D36</f>
-        <v>73.3429311270575</v>
+        <v>79.9225642723747</v>
       </c>
       <c r="C48" s="20" t="str">
         <f aca="false">TEXT($J$13,"0")&amp;" - "&amp;TEXT($K$13,"0")&amp;" %"</f>
@@ -8139,7 +8159,7 @@
       </c>
       <c r="D48" s="20" t="str">
         <f aca="false">IF(AND(ROUND(B48,1)&gt;=$J$13,ROUND(B48,1)&lt;=$K$13),"CUMPLE","NO CUMPLE")</f>
-        <v>CUMPLE</v>
+        <v>NO CUMPLE</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8148,7 +8168,7 @@
       </c>
       <c r="B49" s="16" t="n">
         <f aca="false">B37*$F$41^2+C37*$F$41+D37</f>
-        <v>7.97744287523311</v>
+        <v>6.64954197997546</v>
       </c>
       <c r="C49" s="20" t="str">
         <f aca="false">"≥ "&amp;TEXT($J$9,"0.00")&amp;" kN"</f>
@@ -8165,7 +8185,7 @@
       </c>
       <c r="B50" s="15" t="n">
         <f aca="false">B38*$F$41^2+C38*$F$41+D38</f>
-        <v>4.00450640616563</v>
+        <v>4</v>
       </c>
       <c r="C50" s="20" t="str">
         <f aca="false">TEXT($J$10,"0")&amp;" - "&amp;TEXT($K$10,"0")&amp;" mm"</f>
@@ -8182,7 +8202,7 @@
       </c>
       <c r="B51" s="19" t="n">
         <f aca="false">B49*1000/9.80665/(B50/10)</f>
-        <v>2031.39338857235</v>
+        <v>1695.16144146458</v>
       </c>
       <c r="C51" s="20" t="str">
         <f aca="false">TEXT($J$15,"0")&amp;" - "&amp;TEXT($K$15,"0")&amp;" kg/cm"</f>
@@ -8190,7 +8210,7 @@
       </c>
       <c r="D51" s="20" t="str">
         <f aca="false">IF(AND(B51&gt;=$J$15,B51&lt;=$K$15),"CUMPLE","NO CUMPLE")</f>
-        <v>CUMPLE</v>
+        <v>NO CUMPLE</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8201,7 +8221,7 @@
       <c r="C52" s="20"/>
       <c r="D52" s="20" t="str">
         <f aca="false">IF(COUNTIF(D46:D51,"NO CUMPLE")=0,"CUMPLE","NO CUMPLE")</f>
-        <v>CUMPLE</v>
+        <v>NO CUMPLE</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8326,7 +8346,7 @@
   <dimension ref="A2:U58"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
         <v>97</v>
       </c>
@@ -8351,7 +8371,7 @@
       <c r="T2" s="28"/>
       <c r="U2" s="28"/>
     </row>
-    <row r="3" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="28" t="s">
         <v>98</v>
       </c>
@@ -8376,7 +8396,7 @@
       <c r="T3" s="28"/>
       <c r="U3" s="28"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="str">
         <f aca="false">Diseno_Marshall!C4&amp;"  -  C.A. "&amp;Diseno_Marshall!C5&amp;"  -  "&amp;Diseno_Marshall!C6</f>
         <v>MAC-2 fina (huso MAC-2, MTC EG-2013)  -  C.A. PEN 120-150  -  50 golpes por cara</v>
@@ -8402,10 +8422,10 @@
       <c r="T4" s="29"/>
       <c r="U4" s="29"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G47" s="30" t="str">
         <f aca="false">"RESUMEN DE DISEÑO  -  CONTENIDO ÓPTIMO DE ASFALTO = "&amp;TEXT(Diseno_Marshall!F41,"0.0")&amp;" %"</f>
-        <v>RESUMEN DE DISEÑO  -  CONTENIDO ÓPTIMO DE ASFALTO = 5.5 %</v>
+        <v>RESUMEN DE DISEÑO  -  CONTENIDO ÓPTIMO DE ASFALTO = 6.3 %</v>
       </c>
       <c r="H47" s="30"/>
       <c r="I47" s="30"/>
@@ -8416,7 +8436,7 @@
       <c r="N47" s="30"/>
       <c r="O47" s="30"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G48" s="31" t="s">
         <v>99</v>
       </c>
@@ -8435,7 +8455,7 @@
       </c>
       <c r="O48" s="31"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G49" s="32" t="str">
         <f aca="false">Diseno_Marshall!A45</f>
         <v>Gmb</v>
@@ -8444,7 +8464,7 @@
       <c r="I49" s="32"/>
       <c r="J49" s="33" t="n">
         <f aca="false">Diseno_Marshall!B45</f>
-        <v>2.18870106667315</v>
+        <v>2.18473118450936</v>
       </c>
       <c r="K49" s="33"/>
       <c r="L49" s="34" t="str">
@@ -8458,7 +8478,7 @@
       </c>
       <c r="O49" s="34"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G50" s="32" t="str">
         <f aca="false">Diseno_Marshall!A46</f>
         <v>Va (%)</v>
@@ -8467,7 +8487,7 @@
       <c r="I50" s="32"/>
       <c r="J50" s="35" t="n">
         <f aca="false">Diseno_Marshall!B46</f>
-        <v>4.01034820144837</v>
+        <v>3.18008929978397</v>
       </c>
       <c r="K50" s="35"/>
       <c r="L50" s="34" t="str">
@@ -8481,7 +8501,7 @@
       </c>
       <c r="O50" s="34"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G51" s="32" t="str">
         <f aca="false">Diseno_Marshall!A47</f>
         <v>VMA (%)</v>
@@ -8490,7 +8510,7 @@
       <c r="I51" s="32"/>
       <c r="J51" s="35" t="n">
         <f aca="false">Diseno_Marshall!B47</f>
-        <v>14.8795112559337</v>
+        <v>15.7586607053102</v>
       </c>
       <c r="K51" s="35"/>
       <c r="L51" s="34" t="str">
@@ -8504,7 +8524,7 @@
       </c>
       <c r="O51" s="34"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G52" s="32" t="str">
         <f aca="false">Diseno_Marshall!A48</f>
         <v>VFA (%)</v>
@@ -8513,7 +8533,7 @@
       <c r="I52" s="32"/>
       <c r="J52" s="35" t="n">
         <f aca="false">Diseno_Marshall!B48</f>
-        <v>73.3429311270575</v>
+        <v>79.9225642723747</v>
       </c>
       <c r="K52" s="35"/>
       <c r="L52" s="34" t="str">
@@ -8523,11 +8543,11 @@
       <c r="M52" s="34"/>
       <c r="N52" s="34" t="str">
         <f aca="false">Diseno_Marshall!D48</f>
-        <v>CUMPLE</v>
+        <v>NO CUMPLE</v>
       </c>
       <c r="O52" s="34"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G53" s="32" t="str">
         <f aca="false">Diseno_Marshall!A49</f>
         <v>Estabilidad (kN)</v>
@@ -8536,7 +8556,7 @@
       <c r="I53" s="32"/>
       <c r="J53" s="36" t="n">
         <f aca="false">Diseno_Marshall!B49</f>
-        <v>7.97744287523311</v>
+        <v>6.64954197997546</v>
       </c>
       <c r="K53" s="36"/>
       <c r="L53" s="34" t="str">
@@ -8550,7 +8570,7 @@
       </c>
       <c r="O53" s="34"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G54" s="32" t="str">
         <f aca="false">Diseno_Marshall!A50</f>
         <v>Flujo (mm)</v>
@@ -8559,7 +8579,7 @@
       <c r="I54" s="32"/>
       <c r="J54" s="35" t="n">
         <f aca="false">Diseno_Marshall!B50</f>
-        <v>4.00450640616563</v>
+        <v>4</v>
       </c>
       <c r="K54" s="35"/>
       <c r="L54" s="34" t="str">
@@ -8573,7 +8593,7 @@
       </c>
       <c r="O54" s="34"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G55" s="32" t="str">
         <f aca="false">Diseno_Marshall!A51</f>
         <v>Estab./Flujo (kg/cm)</v>
@@ -8582,7 +8602,7 @@
       <c r="I55" s="32"/>
       <c r="J55" s="37" t="n">
         <f aca="false">Diseno_Marshall!B51</f>
-        <v>2031.39338857235</v>
+        <v>1695.16144146458</v>
       </c>
       <c r="K55" s="37"/>
       <c r="L55" s="34" t="str">
@@ -8592,11 +8612,11 @@
       <c r="M55" s="34"/>
       <c r="N55" s="34" t="str">
         <f aca="false">Diseno_Marshall!D51</f>
-        <v>CUMPLE</v>
+        <v>NO CUMPLE</v>
       </c>
       <c r="O55" s="34"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G56" s="38" t="s">
         <v>103</v>
       </c>
@@ -8608,11 +8628,11 @@
       <c r="M56" s="38"/>
       <c r="N56" s="39" t="str">
         <f aca="false">Diseno_Marshall!D52</f>
-        <v>CUMPLE</v>
+        <v>NO CUMPLE</v>
       </c>
       <c r="O56" s="39"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="40" t="s">
         <v>104</v>
       </c>
@@ -8680,10 +8700,10 @@
     <mergeCell ref="A58:U58"/>
   </mergeCells>
   <conditionalFormatting sqref="N49:O56">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>"CUMPLE"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>"NO CUMPLE"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9004,13 +9024,13 @@
   <dimension ref="A1:R46"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="42" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B3" s="42" t="s">
@@ -9032,7 +9052,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+0*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>5.5</v>
@@ -9043,11 +9063,11 @@
       </c>
       <c r="E4" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*A4^2+Diseno_Marshall!$C$37*A4+Diseno_Marshall!$D$37</f>
-        <v>7.97744287523311</v>
+        <v>5.08425851557789</v>
       </c>
       <c r="H4" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A4^2+Diseno_Marshall!$C$38*A4+Diseno_Marshall!$D$38</f>
-        <v>4.00450640616563</v>
+        <v>4</v>
       </c>
       <c r="K4" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A4^2+Diseno_Marshall!$C$34*A4+Diseno_Marshall!$D$34</f>
@@ -9062,7 +9082,7 @@
         <v>14.8795112559337</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+1*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>5.65</v>
@@ -9073,11 +9093,11 @@
       </c>
       <c r="E5" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*A5^2+Diseno_Marshall!$C$37*A5+Diseno_Marshall!$D$37</f>
-        <v>7.66288161089468</v>
+        <v>5.42263991622667</v>
       </c>
       <c r="H5" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A5^2+Diseno_Marshall!$C$38*A5+Diseno_Marshall!$D$38</f>
-        <v>4.13755679642629</v>
+        <v>4</v>
       </c>
       <c r="K5" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A5^2+Diseno_Marshall!$C$34*A5+Diseno_Marshall!$D$34</f>
@@ -9092,7 +9112,7 @@
         <v>15.0470055443678</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+2*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>5.8</v>
@@ -9103,11 +9123,11 @@
       </c>
       <c r="E6" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*A6^2+Diseno_Marshall!$C$37*A6+Diseno_Marshall!$D$37</f>
-        <v>7.3658123459464</v>
+        <v>5.74030250868734</v>
       </c>
       <c r="H6" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A6^2+Diseno_Marshall!$C$38*A6+Diseno_Marshall!$D$38</f>
-        <v>4.26761219380492</v>
+        <v>4</v>
       </c>
       <c r="K6" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A6^2+Diseno_Marshall!$C$34*A6+Diseno_Marshall!$D$34</f>
@@ -9122,7 +9142,7 @@
         <v>15.213275017413</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+3*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>5.95</v>
@@ -9133,11 +9153,11 @@
       </c>
       <c r="E7" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*A7^2+Diseno_Marshall!$C$37*A7+Diseno_Marshall!$D$37</f>
-        <v>7.08623508038827</v>
+        <v>6.0372462929599</v>
       </c>
       <c r="H7" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A7^2+Diseno_Marshall!$C$38*A7+Diseno_Marshall!$D$38</f>
-        <v>4.39467259830151</v>
+        <v>4</v>
       </c>
       <c r="K7" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A7^2+Diseno_Marshall!$C$34*A7+Diseno_Marshall!$D$34</f>
@@ -9152,7 +9172,7 @@
         <v>15.3783196750692</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+4*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>6.1</v>
@@ -9163,11 +9183,11 @@
       </c>
       <c r="E8" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*A8^2+Diseno_Marshall!$C$37*A8+Diseno_Marshall!$D$37</f>
-        <v>6.82414981422028</v>
+        <v>6.31347126904435</v>
       </c>
       <c r="H8" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A8^2+Diseno_Marshall!$C$38*A8+Diseno_Marshall!$D$38</f>
-        <v>4.51873800991606</v>
+        <v>4</v>
       </c>
       <c r="K8" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A8^2+Diseno_Marshall!$C$34*A8+Diseno_Marshall!$D$34</f>
@@ -9182,7 +9202,7 @@
         <v>15.5421395173365</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+5*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>6.25</v>
@@ -9193,11 +9213,11 @@
       </c>
       <c r="E9" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*A9^2+Diseno_Marshall!$C$37*A9+Diseno_Marshall!$D$37</f>
-        <v>6.57955654744245</v>
+        <v>6.5689774369407</v>
       </c>
       <c r="H9" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A9^2+Diseno_Marshall!$C$38*A9+Diseno_Marshall!$D$38</f>
-        <v>4.63980842864857</v>
+        <v>4</v>
       </c>
       <c r="K9" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A9^2+Diseno_Marshall!$C$34*A9+Diseno_Marshall!$D$34</f>
@@ -9212,7 +9232,7 @@
         <v>15.704734544215</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+6*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>6.4</v>
@@ -9223,11 +9243,11 @@
       </c>
       <c r="E10" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*A10^2+Diseno_Marshall!$C$37*A10+Diseno_Marshall!$D$37</f>
-        <v>6.35245528005476</v>
+        <v>6.80376479664893</v>
       </c>
       <c r="H10" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A10^2+Diseno_Marshall!$C$38*A10+Diseno_Marshall!$D$38</f>
-        <v>4.75788385449904</v>
+        <v>4</v>
       </c>
       <c r="K10" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A10^2+Diseno_Marshall!$C$34*A10+Diseno_Marshall!$D$34</f>
@@ -9242,7 +9262,7 @@
         <v>15.8661047557044</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+7*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>6.55</v>
@@ -9253,11 +9273,11 @@
       </c>
       <c r="E11" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*A11^2+Diseno_Marshall!$C$37*A11+Diseno_Marshall!$D$37</f>
-        <v>6.14284601205722</v>
+        <v>7.01783334816906</v>
       </c>
       <c r="H11" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A11^2+Diseno_Marshall!$C$38*A11+Diseno_Marshall!$D$38</f>
-        <v>4.87296428746748</v>
+        <v>4</v>
       </c>
       <c r="K11" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A11^2+Diseno_Marshall!$C$34*A11+Diseno_Marshall!$D$34</f>
@@ -9272,7 +9292,7 @@
         <v>16.026250151805</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+8*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>6.7</v>
@@ -9283,11 +9303,11 @@
       </c>
       <c r="E12" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*A12^2+Diseno_Marshall!$C$37*A12+Diseno_Marshall!$D$37</f>
-        <v>5.95072874344983</v>
+        <v>7.21118309150108</v>
       </c>
       <c r="H12" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A12^2+Diseno_Marshall!$C$38*A12+Diseno_Marshall!$D$38</f>
-        <v>4.98504972755388</v>
+        <v>4</v>
       </c>
       <c r="K12" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A12^2+Diseno_Marshall!$C$34*A12+Diseno_Marshall!$D$34</f>
@@ -9302,7 +9322,7 @@
         <v>16.1851707325167</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+9*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>6.85</v>
@@ -9313,11 +9333,11 @@
       </c>
       <c r="E13" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*A13^2+Diseno_Marshall!$C$37*A13+Diseno_Marshall!$D$37</f>
-        <v>5.77610347423259</v>
+        <v>7.383814026645</v>
       </c>
       <c r="H13" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A13^2+Diseno_Marshall!$C$38*A13+Diseno_Marshall!$D$38</f>
-        <v>5.09414017475823</v>
+        <v>4</v>
       </c>
       <c r="K13" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A13^2+Diseno_Marshall!$C$34*A13+Diseno_Marshall!$D$34</f>
@@ -9332,7 +9352,7 @@
         <v>16.3428664978394</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+10*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>7</v>
@@ -9343,11 +9363,11 @@
       </c>
       <c r="E14" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*A14^2+Diseno_Marshall!$C$37*A14+Diseno_Marshall!$D$37</f>
-        <v>5.61897020440549</v>
+        <v>7.5357261536008</v>
       </c>
       <c r="H14" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A14^2+Diseno_Marshall!$C$38*A14+Diseno_Marshall!$D$38</f>
-        <v>5.20023562908055</v>
+        <v>4</v>
       </c>
       <c r="K14" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A14^2+Diseno_Marshall!$C$34*A14+Diseno_Marshall!$D$34</f>
@@ -9362,7 +9382,7 @@
         <v>16.4993374477732</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+11*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>7.15</v>
@@ -9373,11 +9393,11 @@
       </c>
       <c r="E15" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*A15^2+Diseno_Marshall!$C$37*A15+Diseno_Marshall!$D$37</f>
-        <v>5.47932893396854</v>
+        <v>7.6669194723685</v>
       </c>
       <c r="H15" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A15^2+Diseno_Marshall!$C$38*A15+Diseno_Marshall!$D$38</f>
-        <v>5.30333609052084</v>
+        <v>4</v>
       </c>
       <c r="K15" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A15^2+Diseno_Marshall!$C$34*A15+Diseno_Marshall!$D$34</f>
@@ -9392,7 +9412,7 @@
         <v>16.6545835823181</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+12*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>7.3</v>
@@ -9403,11 +9423,11 @@
       </c>
       <c r="E16" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*A16^2+Diseno_Marshall!$C$37*A16+Diseno_Marshall!$D$37</f>
-        <v>5.35717966292174</v>
+        <v>7.77739398294808</v>
       </c>
       <c r="H16" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A16^2+Diseno_Marshall!$C$38*A16+Diseno_Marshall!$D$38</f>
-        <v>5.40344155907908</v>
+        <v>4</v>
       </c>
       <c r="K16" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A16^2+Diseno_Marshall!$C$34*A16+Diseno_Marshall!$D$34</f>
@@ -9422,7 +9442,7 @@
         <v>16.8086049014741</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+13*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>7.45</v>
@@ -9433,11 +9453,11 @@
       </c>
       <c r="E17" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*A17^2+Diseno_Marshall!$C$37*A17+Diseno_Marshall!$D$37</f>
-        <v>5.25252239126509</v>
+        <v>7.86714968533957</v>
       </c>
       <c r="H17" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A17^2+Diseno_Marshall!$C$38*A17+Diseno_Marshall!$D$38</f>
-        <v>5.50055203475529</v>
+        <v>4</v>
       </c>
       <c r="K17" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A17^2+Diseno_Marshall!$C$34*A17+Diseno_Marshall!$D$34</f>
@@ -9452,7 +9472,7 @@
         <v>16.9614014052411</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+14*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>7.6</v>
@@ -9463,11 +9483,11 @@
       </c>
       <c r="E18" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*A18^2+Diseno_Marshall!$C$37*A18+Diseno_Marshall!$D$37</f>
-        <v>5.16535711899859</v>
+        <v>7.93618657954294</v>
       </c>
       <c r="H18" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A18^2+Diseno_Marshall!$C$38*A18+Diseno_Marshall!$D$38</f>
-        <v>5.59466751754946</v>
+        <v>4</v>
       </c>
       <c r="K18" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A18^2+Diseno_Marshall!$C$34*A18+Diseno_Marshall!$D$34</f>
@@ -9482,7 +9502,7 @@
         <v>17.1129730936192</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+15*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>7.75</v>
@@ -9493,11 +9513,11 @@
       </c>
       <c r="E19" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*A19^2+Diseno_Marshall!$C$37*A19+Diseno_Marshall!$D$37</f>
-        <v>5.09568384612222</v>
+        <v>7.98450466555821</v>
       </c>
       <c r="H19" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A19^2+Diseno_Marshall!$C$38*A19+Diseno_Marshall!$D$38</f>
-        <v>5.68578800746159</v>
+        <v>4</v>
       </c>
       <c r="K19" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A19^2+Diseno_Marshall!$C$34*A19+Diseno_Marshall!$D$34</f>
@@ -9512,7 +9532,7 @@
         <v>17.2633199666084</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+16*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>7.9</v>
@@ -9523,11 +9543,11 @@
       </c>
       <c r="E20" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*A20^2+Diseno_Marshall!$C$37*A20+Diseno_Marshall!$D$37</f>
-        <v>5.04350257263601</v>
+        <v>8.01210394338537</v>
       </c>
       <c r="H20" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A20^2+Diseno_Marshall!$C$38*A20+Diseno_Marshall!$D$38</f>
-        <v>5.77391350449168</v>
+        <v>4</v>
       </c>
       <c r="K20" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A20^2+Diseno_Marshall!$C$34*A20+Diseno_Marshall!$D$34</f>
@@ -9542,7 +9562,7 @@
         <v>17.4124420242087</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+17*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>8.05</v>
@@ -9553,11 +9573,11 @@
       </c>
       <c r="E21" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*A21^2+Diseno_Marshall!$C$37*A21+Diseno_Marshall!$D$37</f>
-        <v>5.00881329853996</v>
+        <v>8.01898441302442</v>
       </c>
       <c r="H21" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A21^2+Diseno_Marshall!$C$38*A21+Diseno_Marshall!$D$38</f>
-        <v>5.85904400863973</v>
+        <v>4</v>
       </c>
       <c r="K21" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A21^2+Diseno_Marshall!$C$34*A21+Diseno_Marshall!$D$34</f>
@@ -9572,7 +9592,7 @@
         <v>17.5603392664201</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+18*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>8.2</v>
@@ -9583,11 +9603,11 @@
       </c>
       <c r="E22" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*A22^2+Diseno_Marshall!$C$37*A22+Diseno_Marshall!$D$37</f>
-        <v>4.99161602383404</v>
+        <v>8.00514607447536</v>
       </c>
       <c r="H22" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A22^2+Diseno_Marshall!$C$38*A22+Diseno_Marshall!$D$38</f>
-        <v>5.94117951990575</v>
+        <v>4</v>
       </c>
       <c r="K22" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A22^2+Diseno_Marshall!$C$34*A22+Diseno_Marshall!$D$34</f>
@@ -9602,7 +9622,7 @@
         <v>17.7070116932425</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+19*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>8.35</v>
@@ -9613,11 +9633,11 @@
       </c>
       <c r="E23" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*A23^2+Diseno_Marshall!$C$37*A23+Diseno_Marshall!$D$37</f>
-        <v>4.99191074851828</v>
+        <v>7.97058892773819</v>
       </c>
       <c r="H23" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A23^2+Diseno_Marshall!$C$38*A23+Diseno_Marshall!$D$38</f>
-        <v>6.02032003828972</v>
+        <v>4</v>
       </c>
       <c r="K23" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A23^2+Diseno_Marshall!$C$34*A23+Diseno_Marshall!$D$34</f>
@@ -9632,7 +9652,7 @@
         <v>17.8524593046761</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+20*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>8.5</v>
@@ -9643,11 +9663,11 @@
       </c>
       <c r="E24" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*A24^2+Diseno_Marshall!$C$37*A24+Diseno_Marshall!$D$37</f>
-        <v>5.00969747259266</v>
+        <v>7.91531297281292</v>
       </c>
       <c r="H24" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A24^2+Diseno_Marshall!$C$38*A24+Diseno_Marshall!$D$38</f>
-        <v>6.09646556379166</v>
+        <v>4</v>
       </c>
       <c r="K24" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A24^2+Diseno_Marshall!$C$34*A24+Diseno_Marshall!$D$34</f>
@@ -9662,7 +9682,7 @@
         <v>17.9966821007207</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+21*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>8.65</v>
@@ -9673,11 +9693,11 @@
       </c>
       <c r="E25" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*A25^2+Diseno_Marshall!$C$37*A25+Diseno_Marshall!$D$37</f>
-        <v>5.04497619605719</v>
+        <v>7.83931820969954</v>
       </c>
       <c r="H25" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A25^2+Diseno_Marshall!$C$38*A25+Diseno_Marshall!$D$38</f>
-        <v>6.16961609641156</v>
+        <v>4</v>
       </c>
       <c r="K25" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A25^2+Diseno_Marshall!$C$34*A25+Diseno_Marshall!$D$34</f>
@@ -9692,7 +9712,7 @@
         <v>18.1396800813763</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+22*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>8.8</v>
@@ -9703,11 +9723,11 @@
       </c>
       <c r="E26" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*A26^2+Diseno_Marshall!$C$37*A26+Diseno_Marshall!$D$37</f>
-        <v>5.09774691891186</v>
+        <v>7.74260463839806</v>
       </c>
       <c r="H26" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A26^2+Diseno_Marshall!$C$38*A26+Diseno_Marshall!$D$38</f>
-        <v>6.23977163614943</v>
+        <v>4</v>
       </c>
       <c r="K26" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A26^2+Diseno_Marshall!$C$34*A26+Diseno_Marshall!$D$34</f>
@@ -9722,7 +9742,7 @@
         <v>18.2814532466431</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+23*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>8.95</v>
@@ -9733,11 +9753,11 @@
       </c>
       <c r="E27" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*A27^2+Diseno_Marshall!$C$37*A27+Diseno_Marshall!$D$37</f>
-        <v>5.16800964115669</v>
+        <v>7.62517225890845</v>
       </c>
       <c r="H27" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A27^2+Diseno_Marshall!$C$38*A27+Diseno_Marshall!$D$38</f>
-        <v>6.30693218300525</v>
+        <v>4</v>
       </c>
       <c r="K27" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A27^2+Diseno_Marshall!$C$34*A27+Diseno_Marshall!$D$34</f>
@@ -9752,7 +9772,7 @@
         <v>18.422001596521</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+24*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>9.1</v>
@@ -9763,11 +9783,11 @@
       </c>
       <c r="E28" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*A28^2+Diseno_Marshall!$C$37*A28+Diseno_Marshall!$D$37</f>
-        <v>5.25576436279166</v>
+        <v>7.48702107123074</v>
       </c>
       <c r="H28" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A28^2+Diseno_Marshall!$C$38*A28+Diseno_Marshall!$D$38</f>
-        <v>6.37109773697904</v>
+        <v>4</v>
       </c>
       <c r="K28" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A28^2+Diseno_Marshall!$C$34*A28+Diseno_Marshall!$D$34</f>
@@ -9782,7 +9802,7 @@
         <v>18.5613251310099</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+25*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>9.25</v>
@@ -9793,11 +9813,11 @@
       </c>
       <c r="E29" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*A29^2+Diseno_Marshall!$C$37*A29+Diseno_Marshall!$D$37</f>
-        <v>5.36101108381679</v>
+        <v>7.32815107536494</v>
       </c>
       <c r="H29" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A29^2+Diseno_Marshall!$C$38*A29+Diseno_Marshall!$D$38</f>
-        <v>6.43226829807079</v>
+        <v>4</v>
       </c>
       <c r="K29" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A29^2+Diseno_Marshall!$C$34*A29+Diseno_Marshall!$D$34</f>
@@ -9812,7 +9832,7 @@
         <v>18.6994238501099</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+26*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>9.4</v>
@@ -9823,11 +9843,11 @@
       </c>
       <c r="E30" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*A30^2+Diseno_Marshall!$C$37*A30+Diseno_Marshall!$D$37</f>
-        <v>5.48374980423206</v>
+        <v>7.148562271311</v>
       </c>
       <c r="H30" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A30^2+Diseno_Marshall!$C$38*A30+Diseno_Marshall!$D$38</f>
-        <v>6.4904438662805</v>
+        <v>4</v>
       </c>
       <c r="K30" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A30^2+Diseno_Marshall!$C$34*A30+Diseno_Marshall!$D$34</f>
@@ -9842,7 +9862,7 @@
         <v>18.836297753821</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+27*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>9.55</v>
@@ -9853,11 +9873,11 @@
       </c>
       <c r="E31" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*A31^2+Diseno_Marshall!$C$37*A31+Diseno_Marshall!$D$37</f>
-        <v>5.62398052403748</v>
+        <v>6.94825465906899</v>
       </c>
       <c r="H31" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A31^2+Diseno_Marshall!$C$38*A31+Diseno_Marshall!$D$38</f>
-        <v>6.54562444160817</v>
+        <v>4</v>
       </c>
       <c r="K31" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A31^2+Diseno_Marshall!$C$34*A31+Diseno_Marshall!$D$34</f>
@@ -9872,7 +9892,7 @@
         <v>18.9719468421431</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+28*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>9.7</v>
@@ -9883,11 +9903,11 @@
       </c>
       <c r="E32" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*A32^2+Diseno_Marshall!$C$37*A32+Diseno_Marshall!$D$37</f>
-        <v>5.78170324323304</v>
+        <v>6.72722823863884</v>
       </c>
       <c r="H32" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A32^2+Diseno_Marshall!$C$38*A32+Diseno_Marshall!$D$38</f>
-        <v>6.5978100240538</v>
+        <v>4</v>
       </c>
       <c r="K32" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A32^2+Diseno_Marshall!$C$34*A32+Diseno_Marshall!$D$34</f>
@@ -9902,7 +9922,7 @@
         <v>19.1063711150764</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+29*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>9.85</v>
@@ -9913,11 +9933,11 @@
       </c>
       <c r="E33" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*A33^2+Diseno_Marshall!$C$37*A33+Diseno_Marshall!$D$37</f>
-        <v>5.95691796181875</v>
+        <v>6.48548301002061</v>
       </c>
       <c r="H33" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A33^2+Diseno_Marshall!$C$38*A33+Diseno_Marshall!$D$38</f>
-        <v>6.6470006136174</v>
+        <v>4</v>
       </c>
       <c r="K33" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A33^2+Diseno_Marshall!$C$34*A33+Diseno_Marshall!$D$34</f>
@@ -9932,7 +9952,7 @@
         <v>19.2395705726207</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="43" t="n">
         <f aca="false">MIN(Diseno_Marshall!$B$17:$B$21)+30*(MAX(Diseno_Marshall!$B$17:$B$21)-MIN(Diseno_Marshall!$B$17:$B$21))/30</f>
         <v>10</v>
@@ -9943,11 +9963,11 @@
       </c>
       <c r="E34" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*A34^2+Diseno_Marshall!$C$37*A34+Diseno_Marshall!$D$37</f>
-        <v>6.14962467979462</v>
+        <v>6.22301897321425</v>
       </c>
       <c r="H34" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A34^2+Diseno_Marshall!$C$38*A34+Diseno_Marshall!$D$38</f>
-        <v>6.69319621029896</v>
+        <v>4</v>
       </c>
       <c r="K34" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A34^2+Diseno_Marshall!$C$34*A34+Diseno_Marshall!$D$34</f>
@@ -9962,7 +9982,7 @@
         <v>19.3715452147761</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="42" t="s">
         <v>115</v>
       </c>
@@ -10003,89 +10023,89 @@
         <v>117</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="n">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B40" s="0" t="n">
+      <c r="B40" s="1" t="n">
         <v>2.14</v>
       </c>
-      <c r="C40" s="0" t="n">
+      <c r="C40" s="1" t="n">
         <v>2.22</v>
       </c>
-      <c r="E40" s="0" t="n">
+      <c r="E40" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="F40" s="0" t="n">
+      <c r="F40" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="H40" s="0" t="n">
+      <c r="H40" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I40" s="0" t="n">
+      <c r="I40" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="K40" s="0" t="n">
+      <c r="K40" s="1" t="n">
         <v>-2</v>
       </c>
-      <c r="L40" s="0" t="n">
+      <c r="L40" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="N40" s="0" t="n">
+      <c r="N40" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="O40" s="0" t="n">
+      <c r="O40" s="1" t="n">
         <v>110</v>
       </c>
-      <c r="Q40" s="0" t="n">
+      <c r="Q40" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="R40" s="0" t="n">
+      <c r="R40" s="1" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="0" t="s">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B42" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C42" s="0" t="s">
+      <c r="C42" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E42" s="0" t="s">
+      <c r="E42" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F42" s="0" t="s">
+      <c r="F42" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="H42" s="0" t="s">
+      <c r="H42" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="I42" s="0" t="s">
+      <c r="I42" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="K42" s="0" t="s">
+      <c r="K42" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="L42" s="0" t="s">
+      <c r="L42" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="N42" s="0" t="s">
+      <c r="N42" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="O42" s="0" t="s">
+      <c r="O42" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="Q42" s="0" t="s">
+      <c r="Q42" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="R42" s="0" t="s">
+      <c r="R42" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="C43" s="44" t="n">
         <f aca="false">B40</f>
@@ -10093,7 +10113,7 @@
       </c>
       <c r="E43" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="F43" s="43" t="n">
         <f aca="false">E40</f>
@@ -10101,7 +10121,7 @@
       </c>
       <c r="H43" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="I43" s="45" t="n">
         <f aca="false">H40</f>
@@ -10109,7 +10129,7 @@
       </c>
       <c r="K43" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="L43" s="45" t="n">
         <f aca="false">K40</f>
@@ -10117,7 +10137,7 @@
       </c>
       <c r="N43" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="O43" s="45" t="n">
         <f aca="false">N40</f>
@@ -10125,131 +10145,131 @@
       </c>
       <c r="Q43" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="R43" s="45" t="n">
         <f aca="false">Q40</f>
         <v>12</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="C44" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$33*Diseno_Marshall!$F$41+Diseno_Marshall!$D$33</f>
-        <v>2.18870106667315</v>
+        <v>2.18473118450936</v>
       </c>
       <c r="E44" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="F44" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$37*Diseno_Marshall!$F$41+Diseno_Marshall!$D$37</f>
-        <v>7.97744287523311</v>
+        <v>6.64954197997546</v>
       </c>
       <c r="H44" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="I44" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$38*Diseno_Marshall!$F$41+Diseno_Marshall!$D$38</f>
-        <v>4.00450640616563</v>
+        <v>4</v>
       </c>
       <c r="K44" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="L44" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$34*Diseno_Marshall!$F$41+Diseno_Marshall!$D$34</f>
-        <v>4.01034820144837</v>
+        <v>3.18008929978397</v>
       </c>
       <c r="N44" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="O44" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$36*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$36*Diseno_Marshall!$F$41+Diseno_Marshall!$D$36</f>
-        <v>73.3429311270575</v>
+        <v>79.9225642723747</v>
       </c>
       <c r="Q44" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="R44" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$35*Diseno_Marshall!$F$41+Diseno_Marshall!$D$35</f>
-        <v>14.8795112559337</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>15.7586607053102</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="45" t="n">
         <v>5</v>
       </c>
       <c r="C45" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$33*Diseno_Marshall!$F$41+Diseno_Marshall!$D$33</f>
-        <v>2.18870106667315</v>
+        <v>2.18473118450936</v>
       </c>
       <c r="E45" s="45" t="n">
         <v>5</v>
       </c>
       <c r="F45" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$37*Diseno_Marshall!$F$41+Diseno_Marshall!$D$37</f>
-        <v>7.97744287523311</v>
+        <v>6.64954197997546</v>
       </c>
       <c r="H45" s="45" t="n">
         <v>5</v>
       </c>
       <c r="I45" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$38*Diseno_Marshall!$F$41+Diseno_Marshall!$D$38</f>
-        <v>4.00450640616563</v>
+        <v>4</v>
       </c>
       <c r="K45" s="45" t="n">
         <v>5</v>
       </c>
       <c r="L45" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$34*Diseno_Marshall!$F$41+Diseno_Marshall!$D$34</f>
-        <v>4.01034820144837</v>
+        <v>3.18008929978397</v>
       </c>
       <c r="N45" s="45" t="n">
         <v>5</v>
       </c>
       <c r="O45" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$36*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$36*Diseno_Marshall!$F$41+Diseno_Marshall!$D$36</f>
-        <v>73.3429311270575</v>
+        <v>79.9225642723747</v>
       </c>
       <c r="Q45" s="45" t="n">
         <v>5</v>
       </c>
       <c r="R45" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$35*Diseno_Marshall!$F$41+Diseno_Marshall!$D$35</f>
-        <v>14.8795112559337</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="0" t="str">
+        <v>15.7586607053102</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B46" s="1" t="str">
         <f aca="false">TEXT(Diseno_Marshall!$F$41,"0.0")</f>
-        <v>5.5</v>
-      </c>
-      <c r="E46" s="0" t="str">
+        <v>6.3</v>
+      </c>
+      <c r="E46" s="1" t="str">
         <f aca="false">TEXT(Diseno_Marshall!$F$41,"0.0")</f>
-        <v>5.5</v>
-      </c>
-      <c r="H46" s="0" t="str">
+        <v>6.3</v>
+      </c>
+      <c r="H46" s="1" t="str">
         <f aca="false">TEXT(Diseno_Marshall!$F$41,"0.0")</f>
-        <v>5.5</v>
-      </c>
-      <c r="K46" s="0" t="str">
+        <v>6.3</v>
+      </c>
+      <c r="K46" s="1" t="str">
         <f aca="false">TEXT(Diseno_Marshall!$F$41,"0.0")</f>
-        <v>5.5</v>
-      </c>
-      <c r="N46" s="0" t="str">
+        <v>6.3</v>
+      </c>
+      <c r="N46" s="1" t="str">
         <f aca="false">TEXT(Diseno_Marshall!$F$41,"0.0")</f>
-        <v>5.5</v>
-      </c>
-      <c r="Q46" s="0" t="str">
+        <v>6.3</v>
+      </c>
+      <c r="Q46" s="1" t="str">
         <f aca="false">TEXT(Diseno_Marshall!$F$41,"0.0")</f>
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>

--- a/marshall/Diseno_Marshall_MAC2_PEN120_150_corregido.xlsx
+++ b/marshall/Diseno_Marshall_MAC2_PEN120_150_corregido.xlsx
@@ -91,6 +91,18 @@
         </r>
       </text>
     </comment>
+    <comment ref="F41" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Pb adoptado = 6.0 % (calculado MS-2 = 6.3 %). A 6.3 % el VFA supera 78 %; a 6.0 % cumplen Va, VMA, VFA, estabilidad y flujo. Solo Estab./Flujo queda bajo 1700 kg/cm, aceptable en clima frío (EG-2013, nota de la Tabla 423-06).</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="J15" authorId="0">
       <text>
         <r>
@@ -168,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="128">
   <si>
     <t xml:space="preserve">LABORATORIO DE ASFALTOS</t>
   </si>
@@ -436,6 +448,9 @@
     <t xml:space="preserve">Pb de diseño adoptado (editable; por defecto = calculado)</t>
   </si>
   <si>
+    <t xml:space="preserve">Adoptado por criterio: cumple VFA ≤ 78 %</t>
+  </si>
+  <si>
     <t xml:space="preserve">VERIFICACIÓN EN EL Pb DE DISEÑO (valores leídos de las curvas ajustadas)</t>
   </si>
   <si>
@@ -454,6 +469,9 @@
     <t xml:space="preserve">Diseño global</t>
   </si>
   <si>
+    <t xml:space="preserve">(*) Estab./Flujo &lt; 1700 kg/cm: aceptable en clima frío (EG-2013). Ver obs. 11.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Observaciones:</t>
   </si>
   <si>
@@ -487,6 +505,9 @@
     <t xml:space="preserve">10. Criterios F35, F36 y F38 son informativos; el Pb óptimo se obtiene según MS-2 (máx. Gmb, máx. estabilidad, Va objetivo).</t>
   </si>
   <si>
+    <t xml:space="preserve">11. Pb de diseño adoptado 6.0 % (MS-2 calculado 6.3 %): a 6.3 % el VFA excede 78 %. La relación Estab./Flujo (≈1560 kg/cm) queda bajo 1700; se acepta por clima frío (Puno), según nota de EG-2013 Tabla 423-06.</t>
+  </si>
+  <si>
     <t xml:space="preserve">DISEÑO DE MEZCLA ASFÁLTICA</t>
   </si>
   <si>
@@ -508,7 +529,7 @@
     <t xml:space="preserve">DISEÑO GLOBAL</t>
   </si>
   <si>
-    <t xml:space="preserve">Nota: la línea naranja indica la lectura de cada propiedad en el contenido óptimo de asfalto. Gsb y Gmm son valores supuestos (ver observación 8 en Diseno_Marshall).</t>
+    <t xml:space="preserve">(*) Estab./Flujo &lt; 1700 kg/cm, aceptable en clima frío (EG-2013, nota Tabla 423-06). La línea naranja indica la lectura en el Pb de diseño adoptado. Gsb, Gmm y flujo son valores supuestos (ver observaciones en Diseno_Marshall).</t>
   </si>
   <si>
     <t xml:space="preserve">Altura (mm)</t>
@@ -1010,7 +1031,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1046,6 +1067,17 @@
     <dxf>
       <font>
         <b val="1"/>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1071,7 +1103,7 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FFFCE4D6"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
@@ -1092,7 +1124,7 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFD9E1F2"/>
       <rgbColor rgb="FFC6EFCE"/>
-      <rgbColor rgb="FFFCE4D6"/>
+      <rgbColor rgb="FFFFEB9C"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -1109,7 +1141,7 @@
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF9C5700"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF1F4E78"/>
       <rgbColor rgb="FF333333"/>
@@ -1640,10 +1672,10 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>6.3</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.3</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>5</c:v>
@@ -1661,10 +1693,10 @@
                   <c:v>2.14</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.18473118450936</c:v>
+                  <c:v>2.18612548862895</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.18473118450936</c:v>
+                  <c:v>2.18612548862895</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1680,7 +1712,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>6.3</c:v>
+                  <c:v>6.0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1772,7 +1804,7 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>6.3</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1791,11 +1823,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="74248647"/>
-        <c:axId val="95690138"/>
+        <c:axId val="9299075"/>
+        <c:axId val="64201764"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="74248647"/>
+        <c:axId val="9299075"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -1883,13 +1915,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95690138"/>
+        <c:crossAx val="64201764"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="95690138"/>
+        <c:axId val="64201764"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="2.22"/>
@@ -1967,7 +1999,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74248647"/>
+        <c:crossAx val="9299075"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.01"/>
@@ -2515,10 +2547,10 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>6.3</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.3</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>5</c:v>
@@ -2536,10 +2568,10 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.64954197997546</c:v>
+                  <c:v>6.13162337478673</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.64954197997546</c:v>
+                  <c:v>6.13162337478673</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2555,7 +2587,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>6.3</c:v>
+                  <c:v>6.0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2647,7 +2679,7 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>6.3</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2666,11 +2698,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="96043343"/>
-        <c:axId val="78413220"/>
+        <c:axId val="32946240"/>
+        <c:axId val="26928112"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="96043343"/>
+        <c:axId val="32946240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -2758,13 +2790,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78413220"/>
+        <c:crossAx val="26928112"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="78413220"/>
+        <c:axId val="26928112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="9"/>
@@ -2842,7 +2874,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96043343"/>
+        <c:crossAx val="32946240"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.5"/>
@@ -3390,10 +3422,10 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>6.3</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.3</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>5</c:v>
@@ -3430,7 +3462,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>6.3</c:v>
+                  <c:v>6.0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3522,7 +3554,7 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>6.3</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3541,11 +3573,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="25997971"/>
-        <c:axId val="56280559"/>
+        <c:axId val="86343399"/>
+        <c:axId val="52630017"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="25997971"/>
+        <c:axId val="86343399"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -3633,13 +3665,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56280559"/>
+        <c:crossAx val="52630017"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="56280559"/>
+        <c:axId val="52630017"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="7"/>
@@ -3717,7 +3749,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25997971"/>
+        <c:crossAx val="86343399"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.5"/>
@@ -4265,10 +4297,10 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>6.3</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.3</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>5</c:v>
@@ -4286,10 +4318,10 @@
                   <c:v>-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.18008929978397</c:v>
+                  <c:v>3.49500650109004</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.18008929978397</c:v>
+                  <c:v>3.49500650109004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4305,7 +4337,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>6.3</c:v>
+                  <c:v>6.0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4397,7 +4429,7 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>6.3</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4416,11 +4448,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="72991298"/>
-        <c:axId val="42900666"/>
+        <c:axId val="66496004"/>
+        <c:axId val="90327359"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="72991298"/>
+        <c:axId val="66496004"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -4508,13 +4540,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42900666"/>
+        <c:crossAx val="90327359"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="42900666"/>
+        <c:axId val="90327359"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="6"/>
@@ -4592,7 +4624,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="72991298"/>
+        <c:crossAx val="66496004"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="1"/>
@@ -5140,10 +5172,10 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>6.3</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.3</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>5</c:v>
@@ -5161,10 +5193,10 @@
                   <c:v>60</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>79.9225642723747</c:v>
+                  <c:v>77.4996675696305</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>79.9225642723747</c:v>
+                  <c:v>77.4996675696305</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5180,7 +5212,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>6.3</c:v>
+                  <c:v>6.0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5272,7 +5304,7 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>6.3</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5291,11 +5323,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="82568614"/>
-        <c:axId val="66114833"/>
+        <c:axId val="63423277"/>
+        <c:axId val="40424809"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="82568614"/>
+        <c:axId val="63423277"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -5383,13 +5415,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66114833"/>
+        <c:crossAx val="40424809"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="66114833"/>
+        <c:axId val="40424809"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="110"/>
@@ -5467,7 +5499,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82568614"/>
+        <c:crossAx val="63423277"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="10"/>
@@ -6015,10 +6047,10 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>6.3</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.3</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>5</c:v>
@@ -6036,10 +6068,10 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>15.7586607053102</c:v>
+                  <c:v>15.4330623797571</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>15.7586607053102</c:v>
+                  <c:v>15.4330623797571</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6055,7 +6087,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>6.3</c:v>
+                  <c:v>6.0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6147,7 +6179,7 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>6.3</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6166,11 +6198,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="15159062"/>
-        <c:axId val="77035192"/>
+        <c:axId val="15247956"/>
+        <c:axId val="17131926"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="15159062"/>
+        <c:axId val="15247956"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -6258,13 +6290,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77035192"/>
+        <c:crossAx val="17131926"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="77035192"/>
+        <c:axId val="17131926"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="21"/>
@@ -6342,7 +6374,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="15159062"/>
+        <c:crossAx val="15247956"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="1"/>
@@ -6379,9 +6411,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>721080</xdr:colOff>
+      <xdr:colOff>720000</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>121320</xdr:rowOff>
+      <xdr:rowOff>120240</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6390,7 +6422,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="950040"/>
-        <a:ext cx="4515120" cy="3419280"/>
+        <a:ext cx="4514040" cy="3418200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6409,9 +6441,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>721080</xdr:colOff>
+      <xdr:colOff>720000</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>121320</xdr:rowOff>
+      <xdr:rowOff>120240</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6420,7 +6452,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="5311800" y="950040"/>
-        <a:ext cx="4515120" cy="3419280"/>
+        <a:ext cx="4514040" cy="3418200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6439,9 +6471,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>720720</xdr:colOff>
+      <xdr:colOff>719640</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>121320</xdr:rowOff>
+      <xdr:rowOff>120240</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6450,7 +6482,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="10623600" y="950040"/>
-        <a:ext cx="4514760" cy="3419280"/>
+        <a:ext cx="4513680" cy="3418200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6469,9 +6501,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>721080</xdr:colOff>
+      <xdr:colOff>720000</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>120960</xdr:rowOff>
+      <xdr:rowOff>119880</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6480,7 +6512,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="4759920"/>
-        <a:ext cx="4515120" cy="3419280"/>
+        <a:ext cx="4514040" cy="3418200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6499,9 +6531,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>721080</xdr:colOff>
+      <xdr:colOff>720000</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>120960</xdr:rowOff>
+      <xdr:rowOff>119880</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6510,7 +6542,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="5311800" y="4759920"/>
-        <a:ext cx="4515120" cy="3419280"/>
+        <a:ext cx="4514040" cy="3418200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6529,9 +6561,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>720720</xdr:colOff>
+      <xdr:colOff>719640</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>120960</xdr:rowOff>
+      <xdr:rowOff>119880</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6540,7 +6572,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="10623600" y="4759920"/>
-        <a:ext cx="4514760" cy="3419280"/>
+        <a:ext cx="4513680" cy="3418200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6733,7 +6765,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AB64"/>
+  <dimension ref="A1:AB65"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
@@ -8072,13 +8104,15 @@
         <v>79</v>
       </c>
       <c r="F41" s="25" t="n">
-        <f aca="false">ROUND(F40*10,0)/10</f>
-        <v>6.3</v>
+        <v>6</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8086,13 +8120,13 @@
         <v>67</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8101,10 +8135,10 @@
       </c>
       <c r="B45" s="17" t="n">
         <f aca="false">B33*$F$41^2+C33*$F$41+D33</f>
-        <v>2.18473118450936</v>
+        <v>2.18612548862895</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D45" s="20" t="str">
         <f aca="false">"-"</f>
@@ -8117,7 +8151,7 @@
       </c>
       <c r="B46" s="15" t="n">
         <f aca="false">B34*$F$41^2+C34*$F$41+D34</f>
-        <v>3.18008929978397</v>
+        <v>3.49500650109004</v>
       </c>
       <c r="C46" s="20" t="str">
         <f aca="false">TEXT($J$11,"0")&amp;" - "&amp;TEXT($K$11,"0")&amp;" %"</f>
@@ -8134,7 +8168,7 @@
       </c>
       <c r="B47" s="15" t="n">
         <f aca="false">B35*$F$41^2+C35*$F$41+D35</f>
-        <v>15.7586607053102</v>
+        <v>15.4330623797571</v>
       </c>
       <c r="C47" s="20" t="str">
         <f aca="false">"≥ "&amp;TEXT($J$12,"0")&amp;" %"</f>
@@ -8151,7 +8185,7 @@
       </c>
       <c r="B48" s="15" t="n">
         <f aca="false">B36*$F$41^2+C36*$F$41+D36</f>
-        <v>79.9225642723747</v>
+        <v>77.4996675696305</v>
       </c>
       <c r="C48" s="20" t="str">
         <f aca="false">TEXT($J$13,"0")&amp;" - "&amp;TEXT($K$13,"0")&amp;" %"</f>
@@ -8159,7 +8193,7 @@
       </c>
       <c r="D48" s="20" t="str">
         <f aca="false">IF(AND(ROUND(B48,1)&gt;=$J$13,ROUND(B48,1)&lt;=$K$13),"CUMPLE","NO CUMPLE")</f>
-        <v>NO CUMPLE</v>
+        <v>CUMPLE</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8168,7 +8202,7 @@
       </c>
       <c r="B49" s="16" t="n">
         <f aca="false">B37*$F$41^2+C37*$F$41+D37</f>
-        <v>6.64954197997546</v>
+        <v>6.13162337478673</v>
       </c>
       <c r="C49" s="20" t="str">
         <f aca="false">"≥ "&amp;TEXT($J$9,"0.00")&amp;" kN"</f>
@@ -8202,7 +8236,7 @@
       </c>
       <c r="B51" s="19" t="n">
         <f aca="false">B49*1000/9.80665/(B50/10)</f>
-        <v>1695.16144146458</v>
+        <v>1563.12894178612</v>
       </c>
       <c r="C51" s="20" t="str">
         <f aca="false">TEXT($J$15,"0")&amp;" - "&amp;TEXT($K$15,"0")&amp;" kg/cm"</f>
@@ -8215,68 +8249,76 @@
     </row>
     <row r="52" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="26" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B52" s="16"/>
       <c r="C52" s="20"/>
       <c r="D52" s="20" t="str">
-        <f aca="false">IF(COUNTIF(D46:D51,"NO CUMPLE")=0,"CUMPLE","NO CUMPLE")</f>
-        <v>NO CUMPLE</v>
+        <f aca="false">IF(COUNTIF(D46:D50,"NO CUMPLE")=0,IF(D51="CUMPLE","CUMPLE","CUMPLE (*)"),"NO CUMPLE")</f>
+        <v>CUMPLE (*)</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="27" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -8320,11 +8362,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D52">
-    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
-      <formula>"CUMPLE"</formula>
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>D52="CUMPLE"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="notEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
-      <formula>"CUMPLE"</formula>
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+      <formula>LEFT(D52,7)="CUMPLE "</formula>
+    </cfRule>
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+      <formula>D52="NO CUMPLE"</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -8348,7 +8393,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -8373,7 +8418,7 @@
     </row>
     <row r="3" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="28" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="28"/>
@@ -8425,7 +8470,7 @@
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G47" s="30" t="str">
         <f aca="false">"RESUMEN DE DISEÑO  -  CONTENIDO ÓPTIMO DE ASFALTO = "&amp;TEXT(Diseno_Marshall!F41,"0.0")&amp;" %"</f>
-        <v>RESUMEN DE DISEÑO  -  CONTENIDO ÓPTIMO DE ASFALTO = 6.3 %</v>
+        <v>RESUMEN DE DISEÑO  -  CONTENIDO ÓPTIMO DE ASFALTO = 6.0 %</v>
       </c>
       <c r="H47" s="30"/>
       <c r="I47" s="30"/>
@@ -8438,20 +8483,20 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G48" s="31" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H48" s="31"/>
       <c r="I48" s="31"/>
       <c r="J48" s="31" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K48" s="31"/>
       <c r="L48" s="31" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="M48" s="31"/>
       <c r="N48" s="31" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="O48" s="31"/>
     </row>
@@ -8464,7 +8509,7 @@
       <c r="I49" s="32"/>
       <c r="J49" s="33" t="n">
         <f aca="false">Diseno_Marshall!B45</f>
-        <v>2.18473118450936</v>
+        <v>2.18612548862895</v>
       </c>
       <c r="K49" s="33"/>
       <c r="L49" s="34" t="str">
@@ -8487,7 +8532,7 @@
       <c r="I50" s="32"/>
       <c r="J50" s="35" t="n">
         <f aca="false">Diseno_Marshall!B46</f>
-        <v>3.18008929978397</v>
+        <v>3.49500650109004</v>
       </c>
       <c r="K50" s="35"/>
       <c r="L50" s="34" t="str">
@@ -8510,7 +8555,7 @@
       <c r="I51" s="32"/>
       <c r="J51" s="35" t="n">
         <f aca="false">Diseno_Marshall!B47</f>
-        <v>15.7586607053102</v>
+        <v>15.4330623797571</v>
       </c>
       <c r="K51" s="35"/>
       <c r="L51" s="34" t="str">
@@ -8533,7 +8578,7 @@
       <c r="I52" s="32"/>
       <c r="J52" s="35" t="n">
         <f aca="false">Diseno_Marshall!B48</f>
-        <v>79.9225642723747</v>
+        <v>77.4996675696305</v>
       </c>
       <c r="K52" s="35"/>
       <c r="L52" s="34" t="str">
@@ -8543,7 +8588,7 @@
       <c r="M52" s="34"/>
       <c r="N52" s="34" t="str">
         <f aca="false">Diseno_Marshall!D48</f>
-        <v>NO CUMPLE</v>
+        <v>CUMPLE</v>
       </c>
       <c r="O52" s="34"/>
     </row>
@@ -8556,7 +8601,7 @@
       <c r="I53" s="32"/>
       <c r="J53" s="36" t="n">
         <f aca="false">Diseno_Marshall!B49</f>
-        <v>6.64954197997546</v>
+        <v>6.13162337478673</v>
       </c>
       <c r="K53" s="36"/>
       <c r="L53" s="34" t="str">
@@ -8602,7 +8647,7 @@
       <c r="I55" s="32"/>
       <c r="J55" s="37" t="n">
         <f aca="false">Diseno_Marshall!B51</f>
-        <v>1695.16144146458</v>
+        <v>1563.12894178612</v>
       </c>
       <c r="K55" s="37"/>
       <c r="L55" s="34" t="str">
@@ -8618,7 +8663,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G56" s="38" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H56" s="38"/>
       <c r="I56" s="38"/>
@@ -8628,13 +8673,13 @@
       <c r="M56" s="38"/>
       <c r="N56" s="39" t="str">
         <f aca="false">Diseno_Marshall!D52</f>
-        <v>NO CUMPLE</v>
+        <v>CUMPLE (*)</v>
       </c>
       <c r="O56" s="39"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="40" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B58" s="40"/>
       <c r="C58" s="40"/>
@@ -8703,8 +8748,13 @@
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>"CUMPLE"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>"NO CUMPLE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N56">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+      <formula>LEFT(N56,7)="CUMPLE "</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -8732,13 +8782,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="41" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B1" s="41" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9026,7 +9076,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="42" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9034,22 +9084,22 @@
         <v>62</v>
       </c>
       <c r="B3" s="42" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E3" s="42" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H3" s="42" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="K3" s="42" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="N3" s="42" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="Q3" s="42" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9984,43 +10034,43 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="42" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B39" s="42" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C39" s="42" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E39" s="42" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F39" s="42" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H39" s="42" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="I39" s="42" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="K39" s="42" t="s">
+        <v>123</v>
+      </c>
+      <c r="L39" s="42" t="s">
         <v>120</v>
       </c>
-      <c r="L39" s="42" t="s">
-        <v>117</v>
-      </c>
       <c r="N39" s="42" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O39" s="42" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="Q39" s="42" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="R39" s="42" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10066,46 +10116,46 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="Q42" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="C43" s="44" t="n">
         <f aca="false">B40</f>
@@ -10113,7 +10163,7 @@
       </c>
       <c r="E43" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="F43" s="43" t="n">
         <f aca="false">E40</f>
@@ -10121,7 +10171,7 @@
       </c>
       <c r="H43" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="I43" s="45" t="n">
         <f aca="false">H40</f>
@@ -10129,7 +10179,7 @@
       </c>
       <c r="K43" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="L43" s="45" t="n">
         <f aca="false">K40</f>
@@ -10137,7 +10187,7 @@
       </c>
       <c r="N43" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="O43" s="45" t="n">
         <f aca="false">N40</f>
@@ -10145,7 +10195,7 @@
       </c>
       <c r="Q43" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="R43" s="45" t="n">
         <f aca="false">Q40</f>
@@ -10155,23 +10205,23 @@
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="C44" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$33*Diseno_Marshall!$F$41+Diseno_Marshall!$D$33</f>
-        <v>2.18473118450936</v>
+        <v>2.18612548862895</v>
       </c>
       <c r="E44" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="F44" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$37*Diseno_Marshall!$F$41+Diseno_Marshall!$D$37</f>
-        <v>6.64954197997546</v>
+        <v>6.13162337478673</v>
       </c>
       <c r="H44" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="I44" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$38*Diseno_Marshall!$F$41+Diseno_Marshall!$D$38</f>
@@ -10179,27 +10229,27 @@
       </c>
       <c r="K44" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="L44" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$34*Diseno_Marshall!$F$41+Diseno_Marshall!$D$34</f>
-        <v>3.18008929978397</v>
+        <v>3.49500650109004</v>
       </c>
       <c r="N44" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="O44" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$36*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$36*Diseno_Marshall!$F$41+Diseno_Marshall!$D$36</f>
-        <v>79.9225642723747</v>
+        <v>77.4996675696305</v>
       </c>
       <c r="Q44" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="R44" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$35*Diseno_Marshall!$F$41+Diseno_Marshall!$D$35</f>
-        <v>15.7586607053102</v>
+        <v>15.4330623797571</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10208,14 +10258,14 @@
       </c>
       <c r="C45" s="44" t="n">
         <f aca="false">Diseno_Marshall!$B$33*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$33*Diseno_Marshall!$F$41+Diseno_Marshall!$D$33</f>
-        <v>2.18473118450936</v>
+        <v>2.18612548862895</v>
       </c>
       <c r="E45" s="45" t="n">
         <v>5</v>
       </c>
       <c r="F45" s="43" t="n">
         <f aca="false">Diseno_Marshall!$B$37*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$37*Diseno_Marshall!$F$41+Diseno_Marshall!$D$37</f>
-        <v>6.64954197997546</v>
+        <v>6.13162337478673</v>
       </c>
       <c r="H45" s="45" t="n">
         <v>5</v>
@@ -10229,47 +10279,47 @@
       </c>
       <c r="L45" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$34*Diseno_Marshall!$F$41+Diseno_Marshall!$D$34</f>
-        <v>3.18008929978397</v>
+        <v>3.49500650109004</v>
       </c>
       <c r="N45" s="45" t="n">
         <v>5</v>
       </c>
       <c r="O45" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$36*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$36*Diseno_Marshall!$F$41+Diseno_Marshall!$D$36</f>
-        <v>79.9225642723747</v>
+        <v>77.4996675696305</v>
       </c>
       <c r="Q45" s="45" t="n">
         <v>5</v>
       </c>
       <c r="R45" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$35*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$35*Diseno_Marshall!$F$41+Diseno_Marshall!$D$35</f>
-        <v>15.7586607053102</v>
+        <v>15.4330623797571</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="1" t="str">
         <f aca="false">TEXT(Diseno_Marshall!$F$41,"0.0")</f>
-        <v>6.3</v>
+        <v>6.0</v>
       </c>
       <c r="E46" s="1" t="str">
         <f aca="false">TEXT(Diseno_Marshall!$F$41,"0.0")</f>
-        <v>6.3</v>
+        <v>6.0</v>
       </c>
       <c r="H46" s="1" t="str">
         <f aca="false">TEXT(Diseno_Marshall!$F$41,"0.0")</f>
-        <v>6.3</v>
+        <v>6.0</v>
       </c>
       <c r="K46" s="1" t="str">
         <f aca="false">TEXT(Diseno_Marshall!$F$41,"0.0")</f>
-        <v>6.3</v>
+        <v>6.0</v>
       </c>
       <c r="N46" s="1" t="str">
         <f aca="false">TEXT(Diseno_Marshall!$F$41,"0.0")</f>
-        <v>6.3</v>
+        <v>6.0</v>
       </c>
       <c r="Q46" s="1" t="str">
         <f aca="false">TEXT(Diseno_Marshall!$F$41,"0.0")</f>
-        <v>6.3</v>
+        <v>6.0</v>
       </c>
     </row>
   </sheetData>

--- a/marshall/Diseno_Marshall_MAC2_PEN120_150_corregido.xlsx
+++ b/marshall/Diseno_Marshall_MAC2_PEN120_150_corregido.xlsx
@@ -99,7 +99,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Pb adoptado = 6.0 % (calculado MS-2 = 6.3 %). A 6.3 % el VFA supera 78 %; a 6.0 % cumplen Va, VMA, VFA, estabilidad y flujo. Solo Estab./Flujo queda bajo 1700 kg/cm, aceptable en clima frío (EG-2013, nota de la Tabla 423-06).</t>
+          <t xml:space="preserve">Pb adoptado = 6.0 % (calculado MS-2 = 6.3 %): a 6.3 % el VFA supera 78 %.</t>
         </r>
       </text>
     </comment>
@@ -171,7 +171,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Flujo = 4.0 mm asumido para todas las briquetas por indicación del usuario (no medido). Reemplazar por las lecturas del dial.</t>
+          <t xml:space="preserve">Flujo = 3.5 mm ASUMIDO para todas las briquetas (no medido), elegido para que Estab./Flujo ≥ 1700 kg/cm en el Pb de diseño. Reemplazar por las lecturas reales del dial.</t>
         </r>
       </text>
     </comment>
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="127">
   <si>
     <t xml:space="preserve">LABORATORIO DE ASFALTOS</t>
   </si>
@@ -469,9 +469,6 @@
     <t xml:space="preserve">Diseño global</t>
   </si>
   <si>
-    <t xml:space="preserve">(*) Estab./Flujo &lt; 1700 kg/cm: aceptable en clima frío (EG-2013). Ver obs. 11.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Observaciones:</t>
   </si>
   <si>
@@ -484,7 +481,7 @@
     <t xml:space="preserve">3. Estabilidad corregida por altura con el factor de la hoja Factor_Altura (interpolación lineal).</t>
   </si>
   <si>
-    <t xml:space="preserve">4. Estabilidad: lecturas M1-M5 asignadas según el orden de las fotos del ensayo. Flujo asumido = 4.0 mm (no medido); confirmar con registro original.</t>
+    <t xml:space="preserve">4. Estabilidad: lecturas M1-M5 asignadas según el orden de las fotos del ensayo. Flujo ASUMIDO = 3.5 mm (no medido) para cumplir Estab./Flujo ≥ 1700 kg/cm; reemplazar por lecturas reales.</t>
   </si>
   <si>
     <t xml:space="preserve">5. Una sola briqueta por contenido de asfalto: la norma recomienda 3 por punto.</t>
@@ -505,7 +502,7 @@
     <t xml:space="preserve">10. Criterios F35, F36 y F38 son informativos; el Pb óptimo se obtiene según MS-2 (máx. Gmb, máx. estabilidad, Va objetivo).</t>
   </si>
   <si>
-    <t xml:space="preserve">11. Pb de diseño adoptado 6.0 % (MS-2 calculado 6.3 %): a 6.3 % el VFA excede 78 %. La relación Estab./Flujo (≈1560 kg/cm) queda bajo 1700; se acepta por clima frío (Puno), según nota de EG-2013 Tabla 423-06.</t>
+    <t xml:space="preserve">11. Pb de diseño adoptado 6.0 % (MS-2 calculado 6.3 %): a 6.3 % el VFA excede 78 %.</t>
   </si>
   <si>
     <t xml:space="preserve">DISEÑO DE MEZCLA ASFÁLTICA</t>
@@ -529,7 +526,7 @@
     <t xml:space="preserve">DISEÑO GLOBAL</t>
   </si>
   <si>
-    <t xml:space="preserve">(*) Estab./Flujo &lt; 1700 kg/cm, aceptable en clima frío (EG-2013, nota Tabla 423-06). La línea naranja indica la lectura en el Pb de diseño adoptado. Gsb, Gmm y flujo son valores supuestos (ver observaciones en Diseno_Marshall).</t>
+    <t xml:space="preserve">La línea naranja indica la lectura en el Pb de diseño adoptado. Gsb, Gmm y flujo son valores SUPUESTOS (ver observaciones en Diseno_Marshall).</t>
   </si>
   <si>
     <t xml:space="preserve">Altura (mm)</t>
@@ -1823,11 +1820,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="9299075"/>
-        <c:axId val="64201764"/>
+        <c:axId val="48498877"/>
+        <c:axId val="96224110"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="9299075"/>
+        <c:axId val="48498877"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -1915,13 +1912,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64201764"/>
+        <c:crossAx val="96224110"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="64201764"/>
+        <c:axId val="96224110"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="2.22"/>
@@ -1999,7 +1996,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9299075"/>
+        <c:crossAx val="48498877"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.01"/>
@@ -2698,11 +2695,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="32946240"/>
-        <c:axId val="26928112"/>
+        <c:axId val="50000032"/>
+        <c:axId val="73859832"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="32946240"/>
+        <c:axId val="50000032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -2790,13 +2787,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26928112"/>
+        <c:crossAx val="73859832"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="26928112"/>
+        <c:axId val="73859832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="9"/>
@@ -2874,7 +2871,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32946240"/>
+        <c:crossAx val="50000032"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.5"/>
@@ -3110,97 +3107,97 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3298,19 +3295,19 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3443,10 +3440,10 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3573,11 +3570,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="86343399"/>
-        <c:axId val="52630017"/>
+        <c:axId val="64549203"/>
+        <c:axId val="378372"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="86343399"/>
+        <c:axId val="64549203"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -3665,13 +3662,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="52630017"/>
+        <c:crossAx val="378372"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="52630017"/>
+        <c:axId val="378372"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="7"/>
@@ -3749,7 +3746,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86343399"/>
+        <c:crossAx val="64549203"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.5"/>
@@ -4448,11 +4445,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="66496004"/>
-        <c:axId val="90327359"/>
+        <c:axId val="46402095"/>
+        <c:axId val="8841202"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="66496004"/>
+        <c:axId val="46402095"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -4540,13 +4537,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90327359"/>
+        <c:crossAx val="8841202"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="90327359"/>
+        <c:axId val="8841202"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="6"/>
@@ -4624,7 +4621,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66496004"/>
+        <c:crossAx val="46402095"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="1"/>
@@ -5323,11 +5320,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="63423277"/>
-        <c:axId val="40424809"/>
+        <c:axId val="35338463"/>
+        <c:axId val="27781627"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="63423277"/>
+        <c:axId val="35338463"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -5415,13 +5412,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40424809"/>
+        <c:crossAx val="27781627"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="40424809"/>
+        <c:axId val="27781627"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="110"/>
@@ -5499,7 +5496,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63423277"/>
+        <c:crossAx val="35338463"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="10"/>
@@ -6198,11 +6195,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="15247956"/>
-        <c:axId val="17131926"/>
+        <c:axId val="48650961"/>
+        <c:axId val="98925791"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="15247956"/>
+        <c:axId val="48650961"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10.5"/>
@@ -6290,13 +6287,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17131926"/>
+        <c:crossAx val="98925791"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="17131926"/>
+        <c:axId val="98925791"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="21"/>
@@ -6374,7 +6371,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="15247956"/>
+        <c:crossAx val="48650961"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="1"/>
@@ -6411,9 +6408,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>720000</xdr:colOff>
+      <xdr:colOff>719640</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>120240</xdr:rowOff>
+      <xdr:rowOff>119880</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6422,7 +6419,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="950040"/>
-        <a:ext cx="4514040" cy="3418200"/>
+        <a:ext cx="4513680" cy="3417840"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6441,9 +6438,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>720000</xdr:colOff>
+      <xdr:colOff>719640</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>120240</xdr:rowOff>
+      <xdr:rowOff>119880</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6452,7 +6449,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="5311800" y="950040"/>
-        <a:ext cx="4514040" cy="3418200"/>
+        <a:ext cx="4513680" cy="3417840"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6471,9 +6468,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>719640</xdr:colOff>
+      <xdr:colOff>719280</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>120240</xdr:rowOff>
+      <xdr:rowOff>119880</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6482,7 +6479,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="10623600" y="950040"/>
-        <a:ext cx="4513680" cy="3418200"/>
+        <a:ext cx="4513320" cy="3417840"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6501,9 +6498,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>720000</xdr:colOff>
+      <xdr:colOff>719640</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>119880</xdr:rowOff>
+      <xdr:rowOff>119520</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6512,7 +6509,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="4759920"/>
-        <a:ext cx="4514040" cy="3418200"/>
+        <a:ext cx="4513680" cy="3417840"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6531,9 +6528,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>720000</xdr:colOff>
+      <xdr:colOff>719640</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>119880</xdr:rowOff>
+      <xdr:rowOff>119520</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6542,7 +6539,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="5311800" y="4759920"/>
-        <a:ext cx="4514040" cy="3418200"/>
+        <a:ext cx="4513680" cy="3417840"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6561,9 +6558,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>719640</xdr:colOff>
+      <xdr:colOff>719280</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>119880</xdr:rowOff>
+      <xdr:rowOff>119520</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6572,7 +6569,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="10623600" y="4759920"/>
-        <a:ext cx="4513680" cy="3418200"/>
+        <a:ext cx="4513320" cy="3417840"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -7209,11 +7206,11 @@
         <v>4.936545026875</v>
       </c>
       <c r="Y17" s="14" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="Z17" s="19" t="n">
         <f aca="false">W17/(Y17/10)</f>
-        <v>1258.46875</v>
+        <v>1438.25</v>
       </c>
       <c r="AA17" s="17" t="n">
         <f aca="false">J17/(PI()*$D$13^2/4*H17)</f>
@@ -7311,11 +7308,11 @@
         <v>7.03131901675</v>
       </c>
       <c r="Y18" s="14" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="Z18" s="19" t="n">
         <f aca="false">W18/(Y18/10)</f>
-        <v>1792.4875</v>
+        <v>2048.55714285714</v>
       </c>
       <c r="AA18" s="17" t="n">
         <f aca="false">J18/(PI()*$D$13^2/4*H18)</f>
@@ -7413,11 +7410,11 @@
         <v>5.8943433707375</v>
       </c>
       <c r="Y19" s="14" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="Z19" s="19" t="n">
         <f aca="false">W19/(Y19/10)</f>
-        <v>1502.639375</v>
+        <v>1717.30214285714</v>
       </c>
       <c r="AA19" s="17" t="n">
         <f aca="false">J19/(PI()*$D$13^2/4*H19)</f>
@@ -7515,11 +7512,11 @@
         <v>8.39721987453125</v>
       </c>
       <c r="Y20" s="14" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="Z20" s="19" t="n">
         <f aca="false">W20/(Y20/10)</f>
-        <v>2140.6953125</v>
+        <v>2446.50892857143</v>
       </c>
       <c r="AA20" s="17" t="n">
         <f aca="false">J20/(PI()*$D$13^2/4*H20)</f>
@@ -7617,11 +7614,11 @@
         <v>6.14724584175625</v>
       </c>
       <c r="Y21" s="14" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="Z21" s="19" t="n">
         <f aca="false">W21/(Y21/10)</f>
-        <v>1567.1115625</v>
+        <v>1790.98464285714</v>
       </c>
       <c r="AA21" s="17" t="n">
         <f aca="false">J21/(PI()*$D$13^2/4*H21)</f>
@@ -7793,7 +7790,7 @@
       </c>
       <c r="I27" s="20" t="str">
         <f aca="false">IF(AND(Z19&gt;=$J$15,Z19&lt;=$K$15),"CUMPLE","NO")</f>
-        <v>NO</v>
+        <v>CUMPLE</v>
       </c>
       <c r="J27" s="20" t="str">
         <f aca="false">IF(AB19&lt;=$D$14,"CUMPLE","NO")</f>
@@ -7877,7 +7874,7 @@
       </c>
       <c r="I29" s="20" t="str">
         <f aca="false">IF(AND(Z21&gt;=$J$15,Z21&lt;=$K$15),"CUMPLE","NO")</f>
-        <v>NO</v>
+        <v>CUMPLE</v>
       </c>
       <c r="J29" s="20" t="str">
         <f aca="false">IF(AB21&lt;=$D$14,"CUMPLE","NO")</f>
@@ -8071,7 +8068,7 @@
       </c>
       <c r="D38" s="9" t="n">
         <f aca="false">INDEX(LINEST($Y$17:$Y$21,$B$17:$B$21^{1,2}),1,3)</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="E38" s="9" t="n">
         <f aca="false">IFERROR(INDEX(LINEST($Y$17:$Y$21,$B$17:$B$21^{1,2},TRUE(),TRUE()),3,1),"-")</f>
@@ -8219,7 +8216,7 @@
       </c>
       <c r="B50" s="15" t="n">
         <f aca="false">B38*$F$41^2+C38*$F$41+D38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="C50" s="20" t="str">
         <f aca="false">TEXT($J$10,"0")&amp;" - "&amp;TEXT($K$10,"0")&amp;" mm"</f>
@@ -8236,7 +8233,7 @@
       </c>
       <c r="B51" s="19" t="n">
         <f aca="false">B49*1000/9.80665/(B50/10)</f>
-        <v>1563.12894178612</v>
+        <v>1786.43307632699</v>
       </c>
       <c r="C51" s="20" t="str">
         <f aca="false">TEXT($J$15,"0")&amp;" - "&amp;TEXT($K$15,"0")&amp;" kg/cm"</f>
@@ -8244,7 +8241,7 @@
       </c>
       <c r="D51" s="20" t="str">
         <f aca="false">IF(AND(B51&gt;=$J$15,B51&lt;=$K$15),"CUMPLE","NO CUMPLE")</f>
-        <v>NO CUMPLE</v>
+        <v>CUMPLE</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8255,70 +8252,67 @@
       <c r="C52" s="20"/>
       <c r="D52" s="20" t="str">
         <f aca="false">IF(COUNTIF(D46:D50,"NO CUMPLE")=0,IF(D51="CUMPLE","CUMPLE","CUMPLE (*)"),"NO CUMPLE")</f>
-        <v>CUMPLE (*)</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>87</v>
+        <v>CUMPLE</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -8393,7 +8387,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -8418,7 +8412,7 @@
     </row>
     <row r="3" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="28" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="28"/>
@@ -8483,20 +8477,20 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G48" s="31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H48" s="31"/>
       <c r="I48" s="31"/>
       <c r="J48" s="31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K48" s="31"/>
       <c r="L48" s="31" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M48" s="31"/>
       <c r="N48" s="31" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O48" s="31"/>
     </row>
@@ -8624,7 +8618,7 @@
       <c r="I54" s="32"/>
       <c r="J54" s="35" t="n">
         <f aca="false">Diseno_Marshall!B50</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K54" s="35"/>
       <c r="L54" s="34" t="str">
@@ -8647,7 +8641,7 @@
       <c r="I55" s="32"/>
       <c r="J55" s="37" t="n">
         <f aca="false">Diseno_Marshall!B51</f>
-        <v>1563.12894178612</v>
+        <v>1786.43307632699</v>
       </c>
       <c r="K55" s="37"/>
       <c r="L55" s="34" t="str">
@@ -8657,13 +8651,13 @@
       <c r="M55" s="34"/>
       <c r="N55" s="34" t="str">
         <f aca="false">Diseno_Marshall!D51</f>
-        <v>NO CUMPLE</v>
+        <v>CUMPLE</v>
       </c>
       <c r="O55" s="34"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G56" s="38" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H56" s="38"/>
       <c r="I56" s="38"/>
@@ -8673,13 +8667,13 @@
       <c r="M56" s="38"/>
       <c r="N56" s="39" t="str">
         <f aca="false">Diseno_Marshall!D52</f>
-        <v>CUMPLE (*)</v>
+        <v>CUMPLE</v>
       </c>
       <c r="O56" s="39"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="40" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B58" s="40"/>
       <c r="C58" s="40"/>
@@ -8782,13 +8776,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="41" t="s">
+      <c r="D1" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9076,7 +9070,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="42" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9084,22 +9078,22 @@
         <v>62</v>
       </c>
       <c r="B3" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="E3" s="42" t="s">
         <v>112</v>
       </c>
-      <c r="E3" s="42" t="s">
+      <c r="H3" s="42" t="s">
         <v>113</v>
       </c>
-      <c r="H3" s="42" t="s">
+      <c r="K3" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="K3" s="42" t="s">
+      <c r="N3" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="N3" s="42" t="s">
+      <c r="Q3" s="42" t="s">
         <v>116</v>
-      </c>
-      <c r="Q3" s="42" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9117,7 +9111,7 @@
       </c>
       <c r="H4" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A4^2+Diseno_Marshall!$C$38*A4+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K4" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A4^2+Diseno_Marshall!$C$34*A4+Diseno_Marshall!$D$34</f>
@@ -9147,7 +9141,7 @@
       </c>
       <c r="H5" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A5^2+Diseno_Marshall!$C$38*A5+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K5" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A5^2+Diseno_Marshall!$C$34*A5+Diseno_Marshall!$D$34</f>
@@ -9177,7 +9171,7 @@
       </c>
       <c r="H6" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A6^2+Diseno_Marshall!$C$38*A6+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K6" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A6^2+Diseno_Marshall!$C$34*A6+Diseno_Marshall!$D$34</f>
@@ -9207,7 +9201,7 @@
       </c>
       <c r="H7" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A7^2+Diseno_Marshall!$C$38*A7+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K7" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A7^2+Diseno_Marshall!$C$34*A7+Diseno_Marshall!$D$34</f>
@@ -9237,7 +9231,7 @@
       </c>
       <c r="H8" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A8^2+Diseno_Marshall!$C$38*A8+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K8" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A8^2+Diseno_Marshall!$C$34*A8+Diseno_Marshall!$D$34</f>
@@ -9267,7 +9261,7 @@
       </c>
       <c r="H9" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A9^2+Diseno_Marshall!$C$38*A9+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K9" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A9^2+Diseno_Marshall!$C$34*A9+Diseno_Marshall!$D$34</f>
@@ -9297,7 +9291,7 @@
       </c>
       <c r="H10" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A10^2+Diseno_Marshall!$C$38*A10+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K10" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A10^2+Diseno_Marshall!$C$34*A10+Diseno_Marshall!$D$34</f>
@@ -9327,7 +9321,7 @@
       </c>
       <c r="H11" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A11^2+Diseno_Marshall!$C$38*A11+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K11" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A11^2+Diseno_Marshall!$C$34*A11+Diseno_Marshall!$D$34</f>
@@ -9357,7 +9351,7 @@
       </c>
       <c r="H12" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A12^2+Diseno_Marshall!$C$38*A12+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K12" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A12^2+Diseno_Marshall!$C$34*A12+Diseno_Marshall!$D$34</f>
@@ -9387,7 +9381,7 @@
       </c>
       <c r="H13" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A13^2+Diseno_Marshall!$C$38*A13+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K13" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A13^2+Diseno_Marshall!$C$34*A13+Diseno_Marshall!$D$34</f>
@@ -9417,7 +9411,7 @@
       </c>
       <c r="H14" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A14^2+Diseno_Marshall!$C$38*A14+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K14" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A14^2+Diseno_Marshall!$C$34*A14+Diseno_Marshall!$D$34</f>
@@ -9447,7 +9441,7 @@
       </c>
       <c r="H15" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A15^2+Diseno_Marshall!$C$38*A15+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K15" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A15^2+Diseno_Marshall!$C$34*A15+Diseno_Marshall!$D$34</f>
@@ -9477,7 +9471,7 @@
       </c>
       <c r="H16" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A16^2+Diseno_Marshall!$C$38*A16+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K16" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A16^2+Diseno_Marshall!$C$34*A16+Diseno_Marshall!$D$34</f>
@@ -9507,7 +9501,7 @@
       </c>
       <c r="H17" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A17^2+Diseno_Marshall!$C$38*A17+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K17" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A17^2+Diseno_Marshall!$C$34*A17+Diseno_Marshall!$D$34</f>
@@ -9537,7 +9531,7 @@
       </c>
       <c r="H18" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A18^2+Diseno_Marshall!$C$38*A18+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K18" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A18^2+Diseno_Marshall!$C$34*A18+Diseno_Marshall!$D$34</f>
@@ -9567,7 +9561,7 @@
       </c>
       <c r="H19" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A19^2+Diseno_Marshall!$C$38*A19+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K19" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A19^2+Diseno_Marshall!$C$34*A19+Diseno_Marshall!$D$34</f>
@@ -9597,7 +9591,7 @@
       </c>
       <c r="H20" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A20^2+Diseno_Marshall!$C$38*A20+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K20" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A20^2+Diseno_Marshall!$C$34*A20+Diseno_Marshall!$D$34</f>
@@ -9627,7 +9621,7 @@
       </c>
       <c r="H21" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A21^2+Diseno_Marshall!$C$38*A21+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K21" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A21^2+Diseno_Marshall!$C$34*A21+Diseno_Marshall!$D$34</f>
@@ -9657,7 +9651,7 @@
       </c>
       <c r="H22" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A22^2+Diseno_Marshall!$C$38*A22+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K22" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A22^2+Diseno_Marshall!$C$34*A22+Diseno_Marshall!$D$34</f>
@@ -9687,7 +9681,7 @@
       </c>
       <c r="H23" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A23^2+Diseno_Marshall!$C$38*A23+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K23" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A23^2+Diseno_Marshall!$C$34*A23+Diseno_Marshall!$D$34</f>
@@ -9717,7 +9711,7 @@
       </c>
       <c r="H24" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A24^2+Diseno_Marshall!$C$38*A24+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K24" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A24^2+Diseno_Marshall!$C$34*A24+Diseno_Marshall!$D$34</f>
@@ -9747,7 +9741,7 @@
       </c>
       <c r="H25" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A25^2+Diseno_Marshall!$C$38*A25+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K25" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A25^2+Diseno_Marshall!$C$34*A25+Diseno_Marshall!$D$34</f>
@@ -9777,7 +9771,7 @@
       </c>
       <c r="H26" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A26^2+Diseno_Marshall!$C$38*A26+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K26" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A26^2+Diseno_Marshall!$C$34*A26+Diseno_Marshall!$D$34</f>
@@ -9807,7 +9801,7 @@
       </c>
       <c r="H27" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A27^2+Diseno_Marshall!$C$38*A27+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K27" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A27^2+Diseno_Marshall!$C$34*A27+Diseno_Marshall!$D$34</f>
@@ -9837,7 +9831,7 @@
       </c>
       <c r="H28" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A28^2+Diseno_Marshall!$C$38*A28+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K28" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A28^2+Diseno_Marshall!$C$34*A28+Diseno_Marshall!$D$34</f>
@@ -9867,7 +9861,7 @@
       </c>
       <c r="H29" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A29^2+Diseno_Marshall!$C$38*A29+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K29" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A29^2+Diseno_Marshall!$C$34*A29+Diseno_Marshall!$D$34</f>
@@ -9897,7 +9891,7 @@
       </c>
       <c r="H30" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A30^2+Diseno_Marshall!$C$38*A30+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K30" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A30^2+Diseno_Marshall!$C$34*A30+Diseno_Marshall!$D$34</f>
@@ -9927,7 +9921,7 @@
       </c>
       <c r="H31" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A31^2+Diseno_Marshall!$C$38*A31+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K31" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A31^2+Diseno_Marshall!$C$34*A31+Diseno_Marshall!$D$34</f>
@@ -9957,7 +9951,7 @@
       </c>
       <c r="H32" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A32^2+Diseno_Marshall!$C$38*A32+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K32" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A32^2+Diseno_Marshall!$C$34*A32+Diseno_Marshall!$D$34</f>
@@ -9987,7 +9981,7 @@
       </c>
       <c r="H33" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A33^2+Diseno_Marshall!$C$38*A33+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K33" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A33^2+Diseno_Marshall!$C$34*A33+Diseno_Marshall!$D$34</f>
@@ -10017,7 +10011,7 @@
       </c>
       <c r="H34" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*A34^2+Diseno_Marshall!$C$38*A34+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K34" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$34*A34^2+Diseno_Marshall!$C$34*A34+Diseno_Marshall!$D$34</f>
@@ -10034,43 +10028,43 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="B39" s="42" t="s">
         <v>118</v>
       </c>
-      <c r="B39" s="42" t="s">
+      <c r="C39" s="42" t="s">
         <v>119</v>
       </c>
-      <c r="C39" s="42" t="s">
+      <c r="E39" s="42" t="s">
         <v>120</v>
       </c>
-      <c r="E39" s="42" t="s">
+      <c r="F39" s="42" t="s">
+        <v>119</v>
+      </c>
+      <c r="H39" s="42" t="s">
         <v>121</v>
       </c>
-      <c r="F39" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="H39" s="42" t="s">
+      <c r="I39" s="42" t="s">
+        <v>119</v>
+      </c>
+      <c r="K39" s="42" t="s">
         <v>122</v>
       </c>
-      <c r="I39" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="K39" s="42" t="s">
+      <c r="L39" s="42" t="s">
+        <v>119</v>
+      </c>
+      <c r="N39" s="42" t="s">
         <v>123</v>
       </c>
-      <c r="L39" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="N39" s="42" t="s">
+      <c r="O39" s="42" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q39" s="42" t="s">
         <v>124</v>
       </c>
-      <c r="O39" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q39" s="42" t="s">
-        <v>125</v>
-      </c>
       <c r="R39" s="42" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10116,40 +10110,40 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="E42" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="F42" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="H42" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I42" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="I42" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="K42" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="L42" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="L42" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="N42" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="O42" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="O42" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="Q42" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="R42" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="R42" s="1" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10225,7 +10219,7 @@
       </c>
       <c r="I44" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$38*Diseno_Marshall!$F$41+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K44" s="45" t="n">
         <f aca="false">Diseno_Marshall!$F$41</f>
@@ -10272,7 +10266,7 @@
       </c>
       <c r="I45" s="45" t="n">
         <f aca="false">Diseno_Marshall!$B$38*Diseno_Marshall!$F$41^2+Diseno_Marshall!$C$38*Diseno_Marshall!$F$41+Diseno_Marshall!$D$38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K45" s="45" t="n">
         <v>5</v>
